--- a/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
+++ b/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
@@ -17,8 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التقنية الرقمية" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الموارد البشرية" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التسويق" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل المشاريع" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قاعدة المؤشرات" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الجودة" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل المشاريع" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قاعدة المؤشرات" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'الإدارة التنفيذية'!$A$3:$O$13</definedName>
@@ -29,6 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'التقنية الرقمية'!$A$3:$O$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'الموارد البشرية'!$A$3:$O$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'التسويق'!$A$3:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'الجودة'!$A$3:$O$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1076,11 +1078,11 @@
         </is>
       </c>
       <c r="D19" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"التوسع في المواقع")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"التوسع في المواقع")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"التوسع في المواقع"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"التوسع في المواقع"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1096,11 +1098,11 @@
         </is>
       </c>
       <c r="D20" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"الامتياز التجاري")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1116,11 +1118,11 @@
         </is>
       </c>
       <c r="D21" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"زيادة وصول العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"زيادة وصول العملاء")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"زيادة وصول العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"زيادة وصول العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1136,11 +1138,11 @@
         </is>
       </c>
       <c r="D22" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"إطلاق مشاريع جديدة")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"إطلاق مشاريع جديدة")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"إطلاق مشاريع جديدة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"إطلاق مشاريع جديدة"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1156,11 +1158,11 @@
         </is>
       </c>
       <c r="D23" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"تطوير التصاميم والهوية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"تطوير التصاميم والهوية")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"تطوير التصاميم والهوية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"تطوير التصاميم والهوية"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1176,11 +1178,11 @@
         </is>
       </c>
       <c r="D24" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"التحول التقني")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"التحول التقني")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"التحول التقني"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"التحول التقني"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1196,11 +1198,11 @@
         </is>
       </c>
       <c r="D25" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"ساحات درب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"ساحات درب")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"ساحات درب"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"ساحات درب"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1216,11 +1218,11 @@
         </is>
       </c>
       <c r="D26" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"تطبيق «تانكي»")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"تطبيق «تانكي»")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"تطبيق «تانكي»"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"تطبيق «تانكي»"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1236,11 +1238,11 @@
         </is>
       </c>
       <c r="D27" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"تعزيز تجربة العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"تعزيز تجربة العملاء")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"تعزيز تجربة العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"تعزيز تجربة العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1256,11 +1258,11 @@
         </is>
       </c>
       <c r="D28" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"جودة التشغيل")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"جودة التشغيل")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"جودة التشغيل"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"جودة التشغيل"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1276,11 +1278,11 @@
         </is>
       </c>
       <c r="D29" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"منظومة التأجير")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"منظومة التأجير")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"منظومة التأجير"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"منظومة التأجير"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1296,11 +1298,11 @@
         </is>
       </c>
       <c r="D30" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$144,"الاستثمار في الموظفين")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"الاستثمار في الموظفين")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$E$2:$E$144,"الاستثمار في الموظفين"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"الاستثمار في الموظفين"),"—")</f>
         <v/>
       </c>
     </row>
@@ -2453,7 +2455,1114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>إدارة الجودة · مؤشرات الأداء 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>المحور</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>المؤشر</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>الوحدة</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>القطبية</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>الأولوية</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>الوزن %</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>المستهدف</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>نص المستهدف</t>
+        </is>
+      </c>
+      <c r="J3" s="24" t="inlineStr">
+        <is>
+          <t>الركيزة</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>المشروع</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>منظور BSC</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
+        <is>
+          <t>المُحقَّق</t>
+        </is>
+      </c>
+      <c r="N3" s="24" t="inlineStr">
+        <is>
+          <t>نسبة التحقيق</t>
+        </is>
+      </c>
+      <c r="O3" s="24" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>جودة المحطات والتشغيل</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>نسبة الالتزام العام بمعايير الجودة في المحطات</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>🔴 رئيسي</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>≥ 90%</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M4" s="34" t="n"/>
+      <c r="N4" s="16">
+        <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
+        <v/>
+      </c>
+      <c r="O4" s="15">
+        <f>IF($N4="","—",IF($N4&gt;=1,"✅ محقق",IF($N4&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>مخاطر الجودة</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>نسبة المحطات الحرجة</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>🔴 رئيسي</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>&lt; 5%</t>
+        </is>
+      </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M5" s="34" t="n"/>
+      <c r="N5" s="16">
+        <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
+        <v/>
+      </c>
+      <c r="O5" s="15">
+        <f>IF($N5="","—",IF($N5&gt;=1,"✅ محقق",IF($N5&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>جودة الوقود</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>نسبة مطابقة جودة الوقود</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="I6" s="29" t="inlineStr">
+        <is>
+          <t>99.5%</t>
+        </is>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="16">
+        <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
+        <v/>
+      </c>
+      <c r="O6" s="15">
+        <f>IF($N6="","—",IF($N6&gt;=1,"✅ محقق",IF($N6&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>معالجة وتصحيح</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>نسبة إغلاق الملاحظات في الوقت المحدد</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" s="29" t="inlineStr">
+        <is>
+          <t>≥ 90%</t>
+        </is>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="16">
+        <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="15">
+        <f>IF($N7="","—",IF($N7&gt;=1,"✅ محقق",IF($N7&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>تحسين ووقاية</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>نسبة فعالية الإجراءات التصحيحية</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I8" s="29" t="inlineStr">
+        <is>
+          <t>≥ 85%</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K8" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M8" s="34" t="n"/>
+      <c r="N8" s="16">
+        <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="15">
+        <f>IF($N8="","—",IF($N8&gt;=1,"✅ محقق",IF($N8&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>منع التكرار</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>نسبة تكرار الملاحظات</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>&lt; 10%</t>
+        </is>
+      </c>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="16">
+        <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
+        <v/>
+      </c>
+      <c r="O9" s="15">
+        <f>IF($N9="","—",IF($N9&gt;=1,"✅ محقق",IF($N9&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>تفتيش وتدقيق</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>نسبة تنفيذ خطة التفتيش والتدقيق</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>≥ 95%</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K10" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="16">
+        <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="15">
+        <f>IF($N10="","—",IF($N10&gt;=1,"✅ محقق",IF($N10&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>حوكمة الجودة</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>نسبة جاهزية نظام إدارة الجودة QMS</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>🔴 رئيسي</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>80% ← 90%</t>
+        </is>
+      </c>
+      <c r="J11" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="16">
+        <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="15">
+        <f>IF($N11="","—",IF($N11&gt;=1,"✅ محقق",IF($N11&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>مخاطر الجودة</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>عدد مخاطر الجودة الحرجة المفتوحة</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>خطر</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="29" t="inlineStr">
+        <is>
+          <t>صفر</t>
+        </is>
+      </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K12" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M12" s="32" t="n"/>
+      <c r="N12" s="16">
+        <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
+        <v/>
+      </c>
+      <c r="O12" s="15">
+        <f>IF($N12="","—",IF($N12&gt;=1,"✅ محقق",IF($N12&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>مخاطر الجودة</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>نسبة إغلاق مخاطر الجودة في الوقت المحدد</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>≥ 90%</t>
+        </is>
+      </c>
+      <c r="J13" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M13" s="34" t="n"/>
+      <c r="N13" s="16">
+        <f>IF($H13="","",IF($M13="","",IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0)))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="15">
+        <f>IF($N13="","—",IF($N13&gt;=1,"✅ محقق",IF($N13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>تجربة العميل</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>نسبة انخفاض الشكاوى المتكررة ذات العلاقة بالجودة</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>انخفاض 15% ربعياً</t>
+        </is>
+      </c>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K14" s="31" t="inlineStr">
+        <is>
+          <t>تعزيز تجربة العملاء</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="M14" s="34" t="n"/>
+      <c r="N14" s="16">
+        <f>IF($H14="","",IF($M14="","",IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0)))))</f>
+        <v/>
+      </c>
+      <c r="O14" s="15">
+        <f>IF($N14="","—",IF($N14&gt;=1,"✅ محقق",IF($N14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>الجودة الإدارية</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>نسبة اكتمال وتحديث الإجراءات المعتمدة</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>🟡 متابعة</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>≥ 95%</t>
+        </is>
+      </c>
+      <c r="J15" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M15" s="34" t="n"/>
+      <c r="N15" s="16">
+        <f>IF($H15="","",IF($M15="","",IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0)))))</f>
+        <v/>
+      </c>
+      <c r="O15" s="15">
+        <f>IF($N15="","—",IF($N15&gt;=1,"✅ محقق",IF($N15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>توثيق وحوكمة</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>نسبة اكتمال سجلات الجودة</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I16" s="29" t="inlineStr">
+        <is>
+          <t>≥ 95%</t>
+        </is>
+      </c>
+      <c r="J16" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K16" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="16">
+        <f>IF($H16="","",IF($M16="","",IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0)))))</f>
+        <v/>
+      </c>
+      <c r="O16" s="15">
+        <f>IF($N16="","—",IF($N16&gt;=1,"✅ محقق",IF($N16&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>الابتكار والرقمنة</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>نسبة رقمنة عمليات الجودة</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>≥ 80%</t>
+        </is>
+      </c>
+      <c r="J17" s="30" t="inlineStr">
+        <is>
+          <t>الابتكار</t>
+        </is>
+      </c>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t>التحول التقني</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M17" s="34" t="n"/>
+      <c r="N17" s="16">
+        <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
+        <v/>
+      </c>
+      <c r="O17" s="15">
+        <f>IF($N17="","—",IF($N17&gt;=1,"✅ محقق",IF($N17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>التحسين المستمر</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>عدد مبادرات التحسين المؤثرة</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>مبادرة</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="29" t="inlineStr">
+        <is>
+          <t>≥ 8 سنوياً (2 ربعياً)</t>
+        </is>
+      </c>
+      <c r="J18" s="30" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K18" s="31" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M18" s="32" t="n"/>
+      <c r="N18" s="16">
+        <f>IF($H18="","",IF($M18="","",IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0)))))</f>
+        <v/>
+      </c>
+      <c r="O18" s="15">
+        <f>IF($N18="","—",IF($N18&gt;=1,"✅ محقق",IF($N18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O18"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3278,13 +4387,72 @@
       </c>
       <c r="H41" s="7" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>▾ مشاريع الجودة</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="n"/>
+      <c r="D43" s="42" t="n"/>
+      <c r="E43" s="42" t="n"/>
+      <c r="F43" s="42" t="n"/>
+      <c r="G43" s="16">
+        <f>IFERROR(F43/D43,0)</f>
+        <v/>
+      </c>
+      <c r="H43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="n"/>
+      <c r="D44" s="42" t="n"/>
+      <c r="E44" s="42" t="n"/>
+      <c r="F44" s="42" t="n"/>
+      <c r="G44" s="16">
+        <f>IFERROR(F44/D44,0)</f>
+        <v/>
+      </c>
+      <c r="H44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="n"/>
+      <c r="D45" s="42" t="n"/>
+      <c r="E45" s="42" t="n"/>
+      <c r="F45" s="42" t="n"/>
+      <c r="G45" s="16">
+        <f>IFERROR(F45/D45,0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A22:H22"/>
@@ -3294,13 +4462,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8792,6 +9960,576 @@
       </c>
       <c r="I144" s="45">
         <f>'التسويق'!G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C145" s="43">
+        <f>'الجودة'!C4</f>
+        <v/>
+      </c>
+      <c r="D145" s="26">
+        <f>'الجودة'!J4</f>
+        <v/>
+      </c>
+      <c r="E145" s="43">
+        <f>'الجودة'!K4</f>
+        <v/>
+      </c>
+      <c r="F145" s="26">
+        <f>'الجودة'!L4</f>
+        <v/>
+      </c>
+      <c r="G145" s="44">
+        <f>'الجودة'!N4</f>
+        <v/>
+      </c>
+      <c r="H145" s="26">
+        <f>'الجودة'!O4</f>
+        <v/>
+      </c>
+      <c r="I145" s="45">
+        <f>'الجودة'!G4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="26" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C146" s="43">
+        <f>'الجودة'!C5</f>
+        <v/>
+      </c>
+      <c r="D146" s="26">
+        <f>'الجودة'!J5</f>
+        <v/>
+      </c>
+      <c r="E146" s="43">
+        <f>'الجودة'!K5</f>
+        <v/>
+      </c>
+      <c r="F146" s="26">
+        <f>'الجودة'!L5</f>
+        <v/>
+      </c>
+      <c r="G146" s="44">
+        <f>'الجودة'!N5</f>
+        <v/>
+      </c>
+      <c r="H146" s="26">
+        <f>'الجودة'!O5</f>
+        <v/>
+      </c>
+      <c r="I146" s="45">
+        <f>'الجودة'!G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="26" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C147" s="43">
+        <f>'الجودة'!C6</f>
+        <v/>
+      </c>
+      <c r="D147" s="26">
+        <f>'الجودة'!J6</f>
+        <v/>
+      </c>
+      <c r="E147" s="43">
+        <f>'الجودة'!K6</f>
+        <v/>
+      </c>
+      <c r="F147" s="26">
+        <f>'الجودة'!L6</f>
+        <v/>
+      </c>
+      <c r="G147" s="44">
+        <f>'الجودة'!N6</f>
+        <v/>
+      </c>
+      <c r="H147" s="26">
+        <f>'الجودة'!O6</f>
+        <v/>
+      </c>
+      <c r="I147" s="45">
+        <f>'الجودة'!G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="26" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C148" s="43">
+        <f>'الجودة'!C7</f>
+        <v/>
+      </c>
+      <c r="D148" s="26">
+        <f>'الجودة'!J7</f>
+        <v/>
+      </c>
+      <c r="E148" s="43">
+        <f>'الجودة'!K7</f>
+        <v/>
+      </c>
+      <c r="F148" s="26">
+        <f>'الجودة'!L7</f>
+        <v/>
+      </c>
+      <c r="G148" s="44">
+        <f>'الجودة'!N7</f>
+        <v/>
+      </c>
+      <c r="H148" s="26">
+        <f>'الجودة'!O7</f>
+        <v/>
+      </c>
+      <c r="I148" s="45">
+        <f>'الجودة'!G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="26" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C149" s="43">
+        <f>'الجودة'!C8</f>
+        <v/>
+      </c>
+      <c r="D149" s="26">
+        <f>'الجودة'!J8</f>
+        <v/>
+      </c>
+      <c r="E149" s="43">
+        <f>'الجودة'!K8</f>
+        <v/>
+      </c>
+      <c r="F149" s="26">
+        <f>'الجودة'!L8</f>
+        <v/>
+      </c>
+      <c r="G149" s="44">
+        <f>'الجودة'!N8</f>
+        <v/>
+      </c>
+      <c r="H149" s="26">
+        <f>'الجودة'!O8</f>
+        <v/>
+      </c>
+      <c r="I149" s="45">
+        <f>'الجودة'!G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="26" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C150" s="43">
+        <f>'الجودة'!C9</f>
+        <v/>
+      </c>
+      <c r="D150" s="26">
+        <f>'الجودة'!J9</f>
+        <v/>
+      </c>
+      <c r="E150" s="43">
+        <f>'الجودة'!K9</f>
+        <v/>
+      </c>
+      <c r="F150" s="26">
+        <f>'الجودة'!L9</f>
+        <v/>
+      </c>
+      <c r="G150" s="44">
+        <f>'الجودة'!N9</f>
+        <v/>
+      </c>
+      <c r="H150" s="26">
+        <f>'الجودة'!O9</f>
+        <v/>
+      </c>
+      <c r="I150" s="45">
+        <f>'الجودة'!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C151" s="43">
+        <f>'الجودة'!C10</f>
+        <v/>
+      </c>
+      <c r="D151" s="26">
+        <f>'الجودة'!J10</f>
+        <v/>
+      </c>
+      <c r="E151" s="43">
+        <f>'الجودة'!K10</f>
+        <v/>
+      </c>
+      <c r="F151" s="26">
+        <f>'الجودة'!L10</f>
+        <v/>
+      </c>
+      <c r="G151" s="44">
+        <f>'الجودة'!N10</f>
+        <v/>
+      </c>
+      <c r="H151" s="26">
+        <f>'الجودة'!O10</f>
+        <v/>
+      </c>
+      <c r="I151" s="45">
+        <f>'الجودة'!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="26" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C152" s="43">
+        <f>'الجودة'!C11</f>
+        <v/>
+      </c>
+      <c r="D152" s="26">
+        <f>'الجودة'!J11</f>
+        <v/>
+      </c>
+      <c r="E152" s="43">
+        <f>'الجودة'!K11</f>
+        <v/>
+      </c>
+      <c r="F152" s="26">
+        <f>'الجودة'!L11</f>
+        <v/>
+      </c>
+      <c r="G152" s="44">
+        <f>'الجودة'!N11</f>
+        <v/>
+      </c>
+      <c r="H152" s="26">
+        <f>'الجودة'!O11</f>
+        <v/>
+      </c>
+      <c r="I152" s="45">
+        <f>'الجودة'!G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="26" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C153" s="43">
+        <f>'الجودة'!C12</f>
+        <v/>
+      </c>
+      <c r="D153" s="26">
+        <f>'الجودة'!J12</f>
+        <v/>
+      </c>
+      <c r="E153" s="43">
+        <f>'الجودة'!K12</f>
+        <v/>
+      </c>
+      <c r="F153" s="26">
+        <f>'الجودة'!L12</f>
+        <v/>
+      </c>
+      <c r="G153" s="44">
+        <f>'الجودة'!N12</f>
+        <v/>
+      </c>
+      <c r="H153" s="26">
+        <f>'الجودة'!O12</f>
+        <v/>
+      </c>
+      <c r="I153" s="45">
+        <f>'الجودة'!G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="26" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C154" s="43">
+        <f>'الجودة'!C13</f>
+        <v/>
+      </c>
+      <c r="D154" s="26">
+        <f>'الجودة'!J13</f>
+        <v/>
+      </c>
+      <c r="E154" s="43">
+        <f>'الجودة'!K13</f>
+        <v/>
+      </c>
+      <c r="F154" s="26">
+        <f>'الجودة'!L13</f>
+        <v/>
+      </c>
+      <c r="G154" s="44">
+        <f>'الجودة'!N13</f>
+        <v/>
+      </c>
+      <c r="H154" s="26">
+        <f>'الجودة'!O13</f>
+        <v/>
+      </c>
+      <c r="I154" s="45">
+        <f>'الجودة'!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="26" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C155" s="43">
+        <f>'الجودة'!C14</f>
+        <v/>
+      </c>
+      <c r="D155" s="26">
+        <f>'الجودة'!J14</f>
+        <v/>
+      </c>
+      <c r="E155" s="43">
+        <f>'الجودة'!K14</f>
+        <v/>
+      </c>
+      <c r="F155" s="26">
+        <f>'الجودة'!L14</f>
+        <v/>
+      </c>
+      <c r="G155" s="44">
+        <f>'الجودة'!N14</f>
+        <v/>
+      </c>
+      <c r="H155" s="26">
+        <f>'الجودة'!O14</f>
+        <v/>
+      </c>
+      <c r="I155" s="45">
+        <f>'الجودة'!G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="26" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C156" s="43">
+        <f>'الجودة'!C15</f>
+        <v/>
+      </c>
+      <c r="D156" s="26">
+        <f>'الجودة'!J15</f>
+        <v/>
+      </c>
+      <c r="E156" s="43">
+        <f>'الجودة'!K15</f>
+        <v/>
+      </c>
+      <c r="F156" s="26">
+        <f>'الجودة'!L15</f>
+        <v/>
+      </c>
+      <c r="G156" s="44">
+        <f>'الجودة'!N15</f>
+        <v/>
+      </c>
+      <c r="H156" s="26">
+        <f>'الجودة'!O15</f>
+        <v/>
+      </c>
+      <c r="I156" s="45">
+        <f>'الجودة'!G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C157" s="43">
+        <f>'الجودة'!C16</f>
+        <v/>
+      </c>
+      <c r="D157" s="26">
+        <f>'الجودة'!J16</f>
+        <v/>
+      </c>
+      <c r="E157" s="43">
+        <f>'الجودة'!K16</f>
+        <v/>
+      </c>
+      <c r="F157" s="26">
+        <f>'الجودة'!L16</f>
+        <v/>
+      </c>
+      <c r="G157" s="44">
+        <f>'الجودة'!N16</f>
+        <v/>
+      </c>
+      <c r="H157" s="26">
+        <f>'الجودة'!O16</f>
+        <v/>
+      </c>
+      <c r="I157" s="45">
+        <f>'الجودة'!G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="26" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C158" s="43">
+        <f>'الجودة'!C17</f>
+        <v/>
+      </c>
+      <c r="D158" s="26">
+        <f>'الجودة'!J17</f>
+        <v/>
+      </c>
+      <c r="E158" s="43">
+        <f>'الجودة'!K17</f>
+        <v/>
+      </c>
+      <c r="F158" s="26">
+        <f>'الجودة'!L17</f>
+        <v/>
+      </c>
+      <c r="G158" s="44">
+        <f>'الجودة'!N17</f>
+        <v/>
+      </c>
+      <c r="H158" s="26">
+        <f>'الجودة'!O17</f>
+        <v/>
+      </c>
+      <c r="I158" s="45">
+        <f>'الجودة'!G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="26" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="43" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C159" s="43">
+        <f>'الجودة'!C18</f>
+        <v/>
+      </c>
+      <c r="D159" s="26">
+        <f>'الجودة'!J18</f>
+        <v/>
+      </c>
+      <c r="E159" s="43">
+        <f>'الجودة'!K18</f>
+        <v/>
+      </c>
+      <c r="F159" s="26">
+        <f>'الجودة'!L18</f>
+        <v/>
+      </c>
+      <c r="G159" s="44">
+        <f>'الجودة'!N18</f>
+        <v/>
+      </c>
+      <c r="H159" s="26">
+        <f>'الجودة'!O18</f>
+        <v/>
+      </c>
+      <c r="I159" s="45">
+        <f>'الجودة'!G18</f>
         <v/>
       </c>
     </row>
@@ -8847,19 +10585,19 @@
     </row>
     <row r="5">
       <c r="B5" s="19">
-        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$G$2:$G$144),0)</f>
+        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$G$2:$G$159),0)</f>
         <v/>
       </c>
       <c r="C5" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$144,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$159,"✅ محقق")</f>
         <v/>
       </c>
       <c r="D5" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$144,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$159,"🟡 قريب")</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$144,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$159,"🔴 تحت الهدف")</f>
         <v/>
       </c>
     </row>
@@ -8906,7 +10644,7 @@
         </is>
       </c>
       <c r="C9" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"الإدارة التنفيذية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الإدارة التنفيذية"),"—")</f>
         <v/>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -8915,7 +10653,7 @@
         </is>
       </c>
       <c r="E9" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$D$2:$D$144,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$D$2:$D$159,"النمو"),"—")</f>
         <v/>
       </c>
     </row>
@@ -8926,7 +10664,7 @@
         </is>
       </c>
       <c r="C10" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -8935,7 +10673,7 @@
         </is>
       </c>
       <c r="E10" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$D$2:$D$144,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$D$2:$D$159,"الابتكار"),"—")</f>
         <v/>
       </c>
     </row>
@@ -8946,7 +10684,7 @@
         </is>
       </c>
       <c r="C11" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"التشغيل والمحطات"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"التشغيل والمحطات"),"—")</f>
         <v/>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -8955,7 +10693,7 @@
         </is>
       </c>
       <c r="E11" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$D$2:$D$144,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$D$2:$D$159,"الاستدامة"),"—")</f>
         <v/>
       </c>
     </row>
@@ -8966,7 +10704,7 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"الاستثمار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الاستثمار"),"—")</f>
         <v/>
       </c>
     </row>
@@ -8977,7 +10715,7 @@
         </is>
       </c>
       <c r="C13" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"العقار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"العقار"),"—")</f>
         <v/>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -8994,7 +10732,7 @@
         </is>
       </c>
       <c r="C14" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"التقنية الرقمية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"التقنية الرقمية"),"—")</f>
         <v/>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -9003,7 +10741,7 @@
         </is>
       </c>
       <c r="E14" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$F$2:$F$144,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"مالي"),"—")</f>
         <v/>
       </c>
     </row>
@@ -9014,7 +10752,7 @@
         </is>
       </c>
       <c r="C15" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"الموارد البشرية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الموارد البشرية"),"—")</f>
         <v/>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -9023,7 +10761,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$F$2:$F$144,"العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -9034,7 +10772,7 @@
         </is>
       </c>
       <c r="C16" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$B$2:$B$144,"التسويق"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"التسويق"),"—")</f>
         <v/>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -9043,18 +10781,27 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$F$2:$F$144,"العمليات الداخلية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"العمليات الداخلية"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="17">
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>الجودة</t>
+        </is>
+      </c>
+      <c r="C17" s="16">
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الجودة"),"—")</f>
+        <v/>
+      </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t>التعلّم والنمو</t>
         </is>
       </c>
       <c r="E17" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$144,'قاعدة المؤشرات'!$F$2:$F$144,"التعلّم والنمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"التعلّم والنمو"),"—")</f>
         <v/>
       </c>
     </row>

--- a/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
+++ b/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
@@ -18,9 +18,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الموارد البشرية" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التسويق" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الجودة" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإدارة المالية" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل المشاريع" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قاعدة المؤشرات" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإدارة القانونية" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإدارة المالية" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل المشاريع" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قاعدة المؤشرات" sheetId="15" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'الإدارة التنفيذية'!$A$3:$O$13</definedName>
@@ -31,7 +32,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'التقنية الرقمية'!$A$3:$O$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'الموارد البشرية'!$A$3:$O$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'التسويق'!$A$3:$O$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'الجودة'!$A$3:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'الجودة'!$A$3:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'الإدارة القانونية'!$A$3:$O$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1127,11 +1129,11 @@
         </is>
       </c>
       <c r="D19" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"التوسع في المواقع")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"التوسع في المواقع")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"التوسع في المواقع"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"التوسع في المواقع"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1147,11 +1149,11 @@
         </is>
       </c>
       <c r="D20" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"الامتياز التجاري")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1167,11 +1169,11 @@
         </is>
       </c>
       <c r="D21" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"زيادة وصول العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"زيادة وصول العملاء")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"زيادة وصول العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"زيادة وصول العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1187,11 +1189,11 @@
         </is>
       </c>
       <c r="D22" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"إطلاق مشاريع جديدة")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"إطلاق مشاريع جديدة")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"إطلاق مشاريع جديدة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"إطلاق مشاريع جديدة"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1207,11 +1209,11 @@
         </is>
       </c>
       <c r="D23" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"تطوير التصاميم والهوية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"تطوير التصاميم والهوية")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"تطوير التصاميم والهوية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"تطوير التصاميم والهوية"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1227,11 +1229,11 @@
         </is>
       </c>
       <c r="D24" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"التحول التقني")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"التحول التقني")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"التحول التقني"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"التحول التقني"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1247,11 +1249,11 @@
         </is>
       </c>
       <c r="D25" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"ساحات درب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"ساحات درب")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"ساحات درب"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"ساحات درب"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1267,11 +1269,11 @@
         </is>
       </c>
       <c r="D26" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"تطبيق «تانكي»")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"تطبيق «تانكي»")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"تطبيق «تانكي»"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"تطبيق «تانكي»"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1287,11 +1289,11 @@
         </is>
       </c>
       <c r="D27" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"تعزيز تجربة العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"تعزيز تجربة العملاء")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"تعزيز تجربة العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"تعزيز تجربة العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1307,11 +1309,11 @@
         </is>
       </c>
       <c r="D28" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"جودة التشغيل")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"جودة التشغيل")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"جودة التشغيل"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"جودة التشغيل"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1327,11 +1329,11 @@
         </is>
       </c>
       <c r="D29" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"منظومة التأجير")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"منظومة التأجير")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"منظومة التأجير"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"منظومة التأجير"),"—")</f>
         <v/>
       </c>
     </row>
@@ -1347,11 +1349,11 @@
         </is>
       </c>
       <c r="D30" s="15">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$159,"الاستثمار في الموظفين")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$166,"الاستثمار في الموظفين")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$E$2:$E$159,"الاستثمار في الموظفين"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$E$2:$E$166,"الاستثمار في الموظفين"),"—")</f>
         <v/>
       </c>
     </row>
@@ -2504,7 +2506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2621,12 +2623,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>جودة المحطات والتشغيل</t>
+          <t>مخاطر الجودة</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>نسبة الالتزام العام بمعايير الجودة في المحطات</t>
+          <t>نسبة المحطات الحرجة</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
@@ -2636,7 +2638,7 @@
       </c>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="F4" s="28" t="inlineStr">
@@ -2645,14 +2647,14 @@
         </is>
       </c>
       <c r="G4" s="29" t="n">
-        <v>0.09375</v>
+        <v>0.10345</v>
       </c>
       <c r="H4" s="29" t="n">
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>&lt; 5%</t>
         </is>
       </c>
       <c r="J4" s="32" t="inlineStr">
@@ -2686,12 +2688,12 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>مخاطر الجودة</t>
+          <t>جودة الوقود</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>نسبة المحطات الحرجة</t>
+          <t>نسبة مطابقة جودة الوقود</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -2701,23 +2703,23 @@
       </c>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>0.09375</v>
+        <v>0.06897</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>0.05</v>
+        <v>0.995</v>
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
-          <t>&lt; 5%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="J5" s="32" t="inlineStr">
@@ -2751,12 +2753,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>جودة الوقود</t>
+          <t>معالجة وتصحيح</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>نسبة مطابقة جودة الوقود</t>
+          <t>نسبة إغلاق الملاحظات في الوقت المحدد</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
@@ -2775,14 +2777,14 @@
         </is>
       </c>
       <c r="G6" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.06897</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>0.995</v>
+        <v>0.9</v>
       </c>
       <c r="I6" s="31" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="J6" s="32" t="inlineStr">
@@ -2816,12 +2818,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>معالجة وتصحيح</t>
+          <t>تحسين ووقاية</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>نسبة إغلاق الملاحظات في الوقت المحدد</t>
+          <t>نسبة فعالية الإجراءات التصحيحية</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
@@ -2840,14 +2842,14 @@
         </is>
       </c>
       <c r="G7" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.06897</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I7" s="31" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>≥ 85%</t>
         </is>
       </c>
       <c r="J7" s="32" t="inlineStr">
@@ -2881,12 +2883,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>تحسين ووقاية</t>
+          <t>منع التكرار</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>نسبة فعالية الإجراءات التصحيحية</t>
+          <t>نسبة تكرار الملاحظات</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
@@ -2896,7 +2898,7 @@
       </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="F8" s="28" t="inlineStr">
@@ -2905,14 +2907,14 @@
         </is>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.06897</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>0.85</v>
+        <v>0.1</v>
       </c>
       <c r="I8" s="31" t="inlineStr">
         <is>
-          <t>≥ 85%</t>
+          <t>&lt; 10%</t>
         </is>
       </c>
       <c r="J8" s="32" t="inlineStr">
@@ -2946,12 +2948,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>منع التكرار</t>
+          <t>تفتيش وتدقيق</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>نسبة تكرار الملاحظات</t>
+          <t>نسبة تنفيذ خطة التفتيش والتدقيق</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
@@ -2961,7 +2963,7 @@
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -2970,14 +2972,14 @@
         </is>
       </c>
       <c r="G9" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.06897</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>0.1</v>
+        <v>0.95</v>
       </c>
       <c r="I9" s="31" t="inlineStr">
         <is>
-          <t>&lt; 10%</t>
+          <t>≥ 95%</t>
         </is>
       </c>
       <c r="J9" s="32" t="inlineStr">
@@ -3011,12 +3013,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>تفتيش وتدقيق</t>
+          <t>حوكمة الجودة</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>نسبة تنفيذ خطة التفتيش والتدقيق</t>
+          <t>نسبة جاهزية نظام إدارة الجودة QMS</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
@@ -3031,18 +3033,18 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>🟠 مهم</t>
+          <t>🔴 رئيسي</t>
         </is>
       </c>
       <c r="G10" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.10345</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I10" s="31" t="inlineStr">
         <is>
-          <t>≥ 95%</t>
+          <t>80% ← 90%</t>
         </is>
       </c>
       <c r="J10" s="32" t="inlineStr">
@@ -3076,38 +3078,38 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>حوكمة الجودة</t>
+          <t>مخاطر الجودة</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>نسبة جاهزية نظام إدارة الجودة QMS</t>
+          <t>عدد مخاطر الجودة الحرجة المفتوحة</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>خطر</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="G11" s="29" t="n">
-        <v>0.09375</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>0.9</v>
+        <v>0.06897</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="I11" s="31" t="inlineStr">
         <is>
-          <t>80% ← 90%</t>
+          <t>صفر</t>
         </is>
       </c>
       <c r="J11" s="32" t="inlineStr">
@@ -3125,7 +3127,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M11" s="36" t="n"/>
+      <c r="M11" s="34" t="n"/>
       <c r="N11" s="16">
         <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
         <v/>
@@ -3146,17 +3148,17 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>عدد مخاطر الجودة الحرجة المفتوحة</t>
+          <t>نسبة إغلاق مخاطر الجودة في الوقت المحدد</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>خطر</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="F12" s="28" t="inlineStr">
@@ -3165,14 +3167,14 @@
         </is>
       </c>
       <c r="G12" s="29" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="H12" s="30" t="n">
-        <v>0</v>
+        <v>0.06897</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>0.9</v>
       </c>
       <c r="I12" s="31" t="inlineStr">
         <is>
-          <t>صفر</t>
+          <t>≥ 90%</t>
         </is>
       </c>
       <c r="J12" s="32" t="inlineStr">
@@ -3190,7 +3192,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="34" t="n"/>
+      <c r="M12" s="36" t="n"/>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -3206,12 +3208,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>مخاطر الجودة</t>
+          <t>تجربة العميل</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>نسبة إغلاق مخاطر الجودة في الوقت المحدد</t>
+          <t>نسبة انخفاض الشكاوى المتكررة ذات العلاقة بالجودة</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
@@ -3230,14 +3232,14 @@
         </is>
       </c>
       <c r="G13" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.06897</v>
       </c>
       <c r="H13" s="29" t="n">
-        <v>0.9</v>
+        <v>0.15</v>
       </c>
       <c r="I13" s="31" t="inlineStr">
         <is>
-          <t>≥ 90%</t>
+          <t>انخفاض 15% ربعياً</t>
         </is>
       </c>
       <c r="J13" s="32" t="inlineStr">
@@ -3247,12 +3249,12 @@
       </c>
       <c r="K13" s="33" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>تعزيز تجربة العملاء</t>
         </is>
       </c>
       <c r="L13" s="28" t="inlineStr">
         <is>
-          <t>العمليات الداخلية</t>
+          <t>العملاء</t>
         </is>
       </c>
       <c r="M13" s="36" t="n"/>
@@ -3271,12 +3273,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>تجربة العميل</t>
+          <t>الجودة الإدارية</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>نسبة انخفاض الشكاوى المتكررة ذات العلاقة بالجودة</t>
+          <t>نسبة اكتمال وتحديث الإجراءات المعتمدة</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
@@ -3291,18 +3293,18 @@
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>🟠 مهم</t>
+          <t>🟡 متابعة</t>
         </is>
       </c>
       <c r="G14" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.03448</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>0.15</v>
+        <v>0.95</v>
       </c>
       <c r="I14" s="31" t="inlineStr">
         <is>
-          <t>انخفاض 15% ربعياً</t>
+          <t>≥ 95%</t>
         </is>
       </c>
       <c r="J14" s="32" t="inlineStr">
@@ -3312,12 +3314,12 @@
       </c>
       <c r="K14" s="33" t="inlineStr">
         <is>
-          <t>تعزيز تجربة العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="L14" s="28" t="inlineStr">
         <is>
-          <t>العملاء</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="M14" s="36" t="n"/>
@@ -3336,12 +3338,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>الجودة الإدارية</t>
+          <t>توثيق وحوكمة</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>نسبة اكتمال وتحديث الإجراءات المعتمدة</t>
+          <t>نسبة اكتمال سجلات الجودة</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
@@ -3356,11 +3358,11 @@
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>🟡 متابعة</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="G15" s="29" t="n">
-        <v>0.03125</v>
+        <v>0.06897</v>
       </c>
       <c r="H15" s="29" t="n">
         <v>0.95</v>
@@ -3401,12 +3403,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>توثيق وحوكمة</t>
+          <t>الابتكار والرقمنة</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>نسبة اكتمال سجلات الجودة</t>
+          <t>نسبة رقمنة عمليات الجودة</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
@@ -3425,24 +3427,24 @@
         </is>
       </c>
       <c r="G16" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.06897</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="I16" s="31" t="inlineStr">
         <is>
-          <t>≥ 95%</t>
+          <t>≥ 80%</t>
         </is>
       </c>
       <c r="J16" s="32" t="inlineStr">
         <is>
-          <t>الاستدامة</t>
+          <t>الابتكار</t>
         </is>
       </c>
       <c r="K16" s="33" t="inlineStr">
         <is>
-          <t>جودة التشغيل</t>
+          <t>التحول التقني</t>
         </is>
       </c>
       <c r="L16" s="28" t="inlineStr">
@@ -3466,17 +3468,17 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>الابتكار والرقمنة</t>
+          <t>التحسين المستمر</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>نسبة رقمنة عمليات الجودة</t>
+          <t>عدد مبادرات التحسين المؤثرة</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مبادرة</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
@@ -3490,24 +3492,24 @@
         </is>
       </c>
       <c r="G17" s="29" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0.8</v>
+        <v>0.06897</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>8</v>
       </c>
       <c r="I17" s="31" t="inlineStr">
         <is>
-          <t>≥ 80%</t>
+          <t>≥ 8 سنوياً (2 ربعياً)</t>
         </is>
       </c>
       <c r="J17" s="32" t="inlineStr">
         <is>
-          <t>الابتكار</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="K17" s="33" t="inlineStr">
         <is>
-          <t>التحول التقني</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="L17" s="28" t="inlineStr">
@@ -3515,7 +3517,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="36" t="n"/>
+      <c r="M17" s="34" t="n"/>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -3525,79 +3527,14 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>التحسين المستمر</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>عدد مبادرات التحسين المؤثرة</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>مبادرة</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F18" s="28" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="H18" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I18" s="31" t="inlineStr">
-        <is>
-          <t>≥ 8 سنوياً (2 ربعياً)</t>
-        </is>
-      </c>
-      <c r="J18" s="32" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K18" s="33" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L18" s="28" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M18" s="34" t="n"/>
-      <c r="N18" s="16">
-        <f>IF($H18="","",IF($M18="","",IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0)))))</f>
-        <v/>
-      </c>
-      <c r="O18" s="15">
-        <f>IF($N18="","—",IF($N18&gt;=1,"✅ محقق",IF($N18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:O18"/>
+  <autoFilter ref="A3:O17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -3606,6 +3543,658 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>إدارة الإدارة القانونية · مؤشرات الأداء 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>المحور</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>المؤشر</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>الوحدة</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>القطبية</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>الأولوية</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>الوزن %</t>
+        </is>
+      </c>
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>المستهدف</t>
+        </is>
+      </c>
+      <c r="I3" s="26" t="inlineStr">
+        <is>
+          <t>نص المستهدف</t>
+        </is>
+      </c>
+      <c r="J3" s="26" t="inlineStr">
+        <is>
+          <t>الركيزة</t>
+        </is>
+      </c>
+      <c r="K3" s="26" t="inlineStr">
+        <is>
+          <t>المشروع</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="inlineStr">
+        <is>
+          <t>منظور BSC</t>
+        </is>
+      </c>
+      <c r="M3" s="26" t="inlineStr">
+        <is>
+          <t>المُحقَّق</t>
+        </is>
+      </c>
+      <c r="N3" s="26" t="inlineStr">
+        <is>
+          <t>نسبة التحقيق</t>
+        </is>
+      </c>
+      <c r="O3" s="26" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>أعمال العقود</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>نسبة العقود المُراجَعة قانونياً قبل التوقيع</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>🔴 رئيسي</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J4" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K4" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M4" s="36" t="n"/>
+      <c r="N4" s="16">
+        <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
+        <v/>
+      </c>
+      <c r="O4" s="15">
+        <f>IF($N4="","—",IF($N4&gt;=1,"✅ محقق",IF($N4&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>أعمال العقود</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>متوسط زمن صياغة ومراجعة العقد</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>يوم</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>🔴 رئيسي</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H5" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>≤ 3 أيام</t>
+        </is>
+      </c>
+      <c r="J5" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K5" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L5" s="28" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M5" s="38" t="n"/>
+      <c r="N5" s="16">
+        <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
+        <v/>
+      </c>
+      <c r="O5" s="15">
+        <f>IF($N5="","—",IF($N5&gt;=1,"✅ محقق",IF($N5&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>أعمال العقود</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>نسبة العقود الخالية من الملاحظات والمخاطر القانونية</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>🔴 رئيسي</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>≥ 95%</t>
+        </is>
+      </c>
+      <c r="J6" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L6" s="28" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M6" s="36" t="n"/>
+      <c r="N6" s="16">
+        <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
+        <v/>
+      </c>
+      <c r="O6" s="15">
+        <f>IF($N6="","—",IF($N6&gt;=1,"✅ محقق",IF($N6&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>أعمال القضايا</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>نسبة القضايا المُغلقة لصالح الشركة</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>≥ 80%</t>
+        </is>
+      </c>
+      <c r="J7" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K7" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L7" s="28" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M7" s="36" t="n"/>
+      <c r="N7" s="16">
+        <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="15">
+        <f>IF($N7="","—",IF($N7&gt;=1,"✅ محقق",IF($N7&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>أعمال القضايا</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>نسبة تقديم المذكرات والردود في المواعيد النظامية</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K8" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L8" s="28" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M8" s="36" t="n"/>
+      <c r="N8" s="16">
+        <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="15">
+        <f>IF($N8="","—",IF($N8&gt;=1,"✅ محقق",IF($N8&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>أعمال القضايا</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>متوسط زمن إعداد المذكرة القانونية</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>يوم</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>≤ 5 أيام</t>
+        </is>
+      </c>
+      <c r="J9" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K9" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L9" s="28" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M9" s="38" t="n"/>
+      <c r="N9" s="16">
+        <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
+        <v/>
+      </c>
+      <c r="O9" s="15">
+        <f>IF($N9="","—",IF($N9&gt;=1,"✅ محقق",IF($N9&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>الاستشارات القانونية</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>نسبة الاستشارات المُنجزة ضمن المدة المستهدفة (SLA)</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>🟠 مهم</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>≥ 90%</t>
+        </is>
+      </c>
+      <c r="J10" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L10" s="28" t="inlineStr">
+        <is>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M10" s="36" t="n"/>
+      <c r="N10" s="16">
+        <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="15">
+        <f>IF($N10="","—",IF($N10&gt;=1,"✅ محقق",IF($N10&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>الاستشارات القانونية</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>مستوى رضا الإدارات عن الدعم القانوني</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>🔴 رئيسي</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I11" s="31" t="inlineStr">
+        <is>
+          <t>≥ 85%</t>
+        </is>
+      </c>
+      <c r="J11" s="32" t="inlineStr">
+        <is>
+          <t>الاستدامة</t>
+        </is>
+      </c>
+      <c r="K11" s="33" t="inlineStr">
+        <is>
+          <t>جودة التشغيل</t>
+        </is>
+      </c>
+      <c r="L11" s="28" t="inlineStr">
+        <is>
+          <t>العملاء</t>
+        </is>
+      </c>
+      <c r="M11" s="36" t="n"/>
+      <c r="N11" s="16">
+        <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="15">
+        <f>IF($N11="","—",IF($N11&gt;=1,"✅ محقق",IF($N11&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O11"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="M4 M5 M6 M7 M8 M9 M10 M11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3916,13 +4505,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4805,8 +5394,66 @@
       </c>
       <c r="H45" s="7" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" s="48" t="inlineStr">
+        <is>
+          <t>▾ مشاريع الإدارة القانونية</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C47" s="49" t="n"/>
+      <c r="D47" s="49" t="n"/>
+      <c r="E47" s="49" t="n"/>
+      <c r="F47" s="49" t="n"/>
+      <c r="G47" s="16">
+        <f>IFERROR(F47/D47,0)</f>
+        <v/>
+      </c>
+      <c r="H47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n"/>
+      <c r="G48" s="16">
+        <f>IFERROR(F48/D48,0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C49" s="49" t="n"/>
+      <c r="D49" s="49" t="n"/>
+      <c r="E49" s="49" t="n"/>
+      <c r="F49" s="49" t="n"/>
+      <c r="G49" s="16">
+        <f>IFERROR(F49/D49,0)</f>
+        <v/>
+      </c>
+      <c r="H49" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
@@ -4815,6 +5462,7 @@
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
@@ -4822,13 +5470,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I159"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10861,35 +11509,301 @@
       </c>
       <c r="B159" s="50" t="inlineStr">
         <is>
-          <t>الجودة</t>
+          <t>الإدارة القانونية</t>
         </is>
       </c>
       <c r="C159" s="50">
-        <f>'الجودة'!C18</f>
+        <f>'الإدارة القانونية'!C4</f>
         <v/>
       </c>
       <c r="D159" s="28">
-        <f>'الجودة'!J18</f>
+        <f>'الإدارة القانونية'!J4</f>
         <v/>
       </c>
       <c r="E159" s="50">
-        <f>'الجودة'!K18</f>
+        <f>'الإدارة القانونية'!K4</f>
         <v/>
       </c>
       <c r="F159" s="28">
-        <f>'الجودة'!L18</f>
+        <f>'الإدارة القانونية'!L4</f>
         <v/>
       </c>
       <c r="G159" s="51">
-        <f>'الجودة'!N18</f>
+        <f>'الإدارة القانونية'!N4</f>
         <v/>
       </c>
       <c r="H159" s="28">
-        <f>'الجودة'!O18</f>
+        <f>'الإدارة القانونية'!O4</f>
         <v/>
       </c>
       <c r="I159" s="52">
-        <f>'الجودة'!G18</f>
+        <f>'الإدارة القانونية'!G4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="28" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="50" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C160" s="50">
+        <f>'الإدارة القانونية'!C5</f>
+        <v/>
+      </c>
+      <c r="D160" s="28">
+        <f>'الإدارة القانونية'!J5</f>
+        <v/>
+      </c>
+      <c r="E160" s="50">
+        <f>'الإدارة القانونية'!K5</f>
+        <v/>
+      </c>
+      <c r="F160" s="28">
+        <f>'الإدارة القانونية'!L5</f>
+        <v/>
+      </c>
+      <c r="G160" s="51">
+        <f>'الإدارة القانونية'!N5</f>
+        <v/>
+      </c>
+      <c r="H160" s="28">
+        <f>'الإدارة القانونية'!O5</f>
+        <v/>
+      </c>
+      <c r="I160" s="52">
+        <f>'الإدارة القانونية'!G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="28" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="50" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C161" s="50">
+        <f>'الإدارة القانونية'!C6</f>
+        <v/>
+      </c>
+      <c r="D161" s="28">
+        <f>'الإدارة القانونية'!J6</f>
+        <v/>
+      </c>
+      <c r="E161" s="50">
+        <f>'الإدارة القانونية'!K6</f>
+        <v/>
+      </c>
+      <c r="F161" s="28">
+        <f>'الإدارة القانونية'!L6</f>
+        <v/>
+      </c>
+      <c r="G161" s="51">
+        <f>'الإدارة القانونية'!N6</f>
+        <v/>
+      </c>
+      <c r="H161" s="28">
+        <f>'الإدارة القانونية'!O6</f>
+        <v/>
+      </c>
+      <c r="I161" s="52">
+        <f>'الإدارة القانونية'!G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="28" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="50" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C162" s="50">
+        <f>'الإدارة القانونية'!C7</f>
+        <v/>
+      </c>
+      <c r="D162" s="28">
+        <f>'الإدارة القانونية'!J7</f>
+        <v/>
+      </c>
+      <c r="E162" s="50">
+        <f>'الإدارة القانونية'!K7</f>
+        <v/>
+      </c>
+      <c r="F162" s="28">
+        <f>'الإدارة القانونية'!L7</f>
+        <v/>
+      </c>
+      <c r="G162" s="51">
+        <f>'الإدارة القانونية'!N7</f>
+        <v/>
+      </c>
+      <c r="H162" s="28">
+        <f>'الإدارة القانونية'!O7</f>
+        <v/>
+      </c>
+      <c r="I162" s="52">
+        <f>'الإدارة القانونية'!G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="28" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="50" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C163" s="50">
+        <f>'الإدارة القانونية'!C8</f>
+        <v/>
+      </c>
+      <c r="D163" s="28">
+        <f>'الإدارة القانونية'!J8</f>
+        <v/>
+      </c>
+      <c r="E163" s="50">
+        <f>'الإدارة القانونية'!K8</f>
+        <v/>
+      </c>
+      <c r="F163" s="28">
+        <f>'الإدارة القانونية'!L8</f>
+        <v/>
+      </c>
+      <c r="G163" s="51">
+        <f>'الإدارة القانونية'!N8</f>
+        <v/>
+      </c>
+      <c r="H163" s="28">
+        <f>'الإدارة القانونية'!O8</f>
+        <v/>
+      </c>
+      <c r="I163" s="52">
+        <f>'الإدارة القانونية'!G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="28" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="50" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C164" s="50">
+        <f>'الإدارة القانونية'!C9</f>
+        <v/>
+      </c>
+      <c r="D164" s="28">
+        <f>'الإدارة القانونية'!J9</f>
+        <v/>
+      </c>
+      <c r="E164" s="50">
+        <f>'الإدارة القانونية'!K9</f>
+        <v/>
+      </c>
+      <c r="F164" s="28">
+        <f>'الإدارة القانونية'!L9</f>
+        <v/>
+      </c>
+      <c r="G164" s="51">
+        <f>'الإدارة القانونية'!N9</f>
+        <v/>
+      </c>
+      <c r="H164" s="28">
+        <f>'الإدارة القانونية'!O9</f>
+        <v/>
+      </c>
+      <c r="I164" s="52">
+        <f>'الإدارة القانونية'!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="28" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="50" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C165" s="50">
+        <f>'الإدارة القانونية'!C10</f>
+        <v/>
+      </c>
+      <c r="D165" s="28">
+        <f>'الإدارة القانونية'!J10</f>
+        <v/>
+      </c>
+      <c r="E165" s="50">
+        <f>'الإدارة القانونية'!K10</f>
+        <v/>
+      </c>
+      <c r="F165" s="28">
+        <f>'الإدارة القانونية'!L10</f>
+        <v/>
+      </c>
+      <c r="G165" s="51">
+        <f>'الإدارة القانونية'!N10</f>
+        <v/>
+      </c>
+      <c r="H165" s="28">
+        <f>'الإدارة القانونية'!O10</f>
+        <v/>
+      </c>
+      <c r="I165" s="52">
+        <f>'الإدارة القانونية'!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="28" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="50" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C166" s="50">
+        <f>'الإدارة القانونية'!C11</f>
+        <v/>
+      </c>
+      <c r="D166" s="28">
+        <f>'الإدارة القانونية'!J11</f>
+        <v/>
+      </c>
+      <c r="E166" s="50">
+        <f>'الإدارة القانونية'!K11</f>
+        <v/>
+      </c>
+      <c r="F166" s="28">
+        <f>'الإدارة القانونية'!L11</f>
+        <v/>
+      </c>
+      <c r="G166" s="51">
+        <f>'الإدارة القانونية'!N11</f>
+        <v/>
+      </c>
+      <c r="H166" s="28">
+        <f>'الإدارة القانونية'!O11</f>
+        <v/>
+      </c>
+      <c r="I166" s="52">
+        <f>'الإدارة القانونية'!G11</f>
         <v/>
       </c>
     </row>
@@ -10904,7 +11818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E18"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10945,19 +11859,19 @@
     </row>
     <row r="5">
       <c r="B5" s="19">
-        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$G$2:$G$159),0)</f>
+        <f>IFERROR(AVERAGE('قاعدة المؤشرات'!$G$2:$G$166),0)</f>
         <v/>
       </c>
       <c r="C5" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$159,"✅ محقق")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$166,"✅ محقق")</f>
         <v/>
       </c>
       <c r="D5" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$159,"🟡 قريب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$166,"🟡 قريب")</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$159,"🔴 تحت الهدف")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$H$2:$H$166,"🔴 تحت الهدف")</f>
         <v/>
       </c>
     </row>
@@ -11004,7 +11918,7 @@
         </is>
       </c>
       <c r="C9" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الإدارة التنفيذية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"الإدارة التنفيذية"),"—")</f>
         <v/>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -11013,7 +11927,7 @@
         </is>
       </c>
       <c r="E9" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$D$2:$D$159,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$D$2:$D$166,"النمو"),"—")</f>
         <v/>
       </c>
     </row>
@@ -11024,7 +11938,7 @@
         </is>
       </c>
       <c r="C10" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -11033,7 +11947,7 @@
         </is>
       </c>
       <c r="E10" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$D$2:$D$159,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$D$2:$D$166,"الابتكار"),"—")</f>
         <v/>
       </c>
     </row>
@@ -11044,7 +11958,7 @@
         </is>
       </c>
       <c r="C11" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"التشغيل والمحطات"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"التشغيل والمحطات"),"—")</f>
         <v/>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -11053,7 +11967,7 @@
         </is>
       </c>
       <c r="E11" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$D$2:$D$159,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$D$2:$D$166,"الاستدامة"),"—")</f>
         <v/>
       </c>
     </row>
@@ -11064,7 +11978,7 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الاستثمار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"الاستثمار"),"—")</f>
         <v/>
       </c>
     </row>
@@ -11075,7 +11989,7 @@
         </is>
       </c>
       <c r="C13" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"العقار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"العقار"),"—")</f>
         <v/>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -11092,7 +12006,7 @@
         </is>
       </c>
       <c r="C14" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"التقنية الرقمية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"التقنية الرقمية"),"—")</f>
         <v/>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -11101,7 +12015,7 @@
         </is>
       </c>
       <c r="E14" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$F$2:$F$166,"مالي"),"—")</f>
         <v/>
       </c>
     </row>
@@ -11112,7 +12026,7 @@
         </is>
       </c>
       <c r="C15" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الموارد البشرية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"الموارد البشرية"),"—")</f>
         <v/>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -11121,7 +12035,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$F$2:$F$166,"العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -11132,7 +12046,7 @@
         </is>
       </c>
       <c r="C16" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"التسويق"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"التسويق"),"—")</f>
         <v/>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -11141,7 +12055,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"العمليات الداخلية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$F$2:$F$166,"العمليات الداخلية"),"—")</f>
         <v/>
       </c>
     </row>
@@ -11152,7 +12066,7 @@
         </is>
       </c>
       <c r="C17" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$B$2:$B$159,"الجودة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"الجودة"),"—")</f>
         <v/>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -11161,17 +12075,28 @@
         </is>
       </c>
       <c r="E17" s="16">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$159,'قاعدة المؤشرات'!$F$2:$F$159,"التعلّم والنمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$F$2:$F$166,"التعلّم والنمو"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>الإدارة القانونية</t>
+        </is>
+      </c>
+      <c r="C18" s="16">
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$166,'قاعدة المؤشرات'!$B$2:$B$166,"الإدارة القانونية"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>الإدارة المالية</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>⛔ فارغة</t>
         </is>

--- a/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
+++ b/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
@@ -1408,7 +1408,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="38" t="n"/>
+      <c r="M5" s="38" t="n">
+        <v>0.723</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -1672,7 +1674,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="38" t="n"/>
+      <c r="M6" s="38" t="n">
+        <v>0.73</v>
+      </c>
       <c r="N6" s="16">
         <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
         <v/>
@@ -1737,7 +1741,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M7" s="38" t="n"/>
+      <c r="M7" s="38" t="n">
+        <v>0.795</v>
+      </c>
       <c r="N7" s="16">
         <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
         <v/>
@@ -1802,7 +1808,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M8" s="38" t="n"/>
+      <c r="M8" s="38" t="n">
+        <v>0.111</v>
+      </c>
       <c r="N8" s="16">
         <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
         <v/>
@@ -1867,7 +1875,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="36" t="n"/>
+      <c r="M9" s="36" t="n">
+        <v>4.53</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -1932,7 +1942,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M10" s="40" t="n"/>
+      <c r="M10" s="40" t="n">
+        <v>33.6</v>
+      </c>
       <c r="N10" s="16">
         <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
         <v/>
@@ -1997,7 +2009,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M11" s="38" t="n"/>
+      <c r="M11" s="38" t="n">
+        <v>0.644</v>
+      </c>
       <c r="N11" s="16">
         <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
         <v/>
@@ -2062,7 +2076,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M12" s="40" t="n"/>
+      <c r="M12" s="40" t="n">
+        <v>27.5</v>
+      </c>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -2190,7 +2206,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="38" t="n"/>
+      <c r="M14" s="38" t="n">
+        <v>0.742</v>
+      </c>
       <c r="N14" s="16">
         <f>IF($H14="","",IF($M14="","",IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0)))))</f>
         <v/>
@@ -2255,7 +2273,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M15" s="38" t="n"/>
+      <c r="M15" s="38" t="n">
+        <v>0.84</v>
+      </c>
       <c r="N15" s="16">
         <f>IF($H15="","",IF($M15="","",IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0)))))</f>
         <v/>
@@ -2320,7 +2340,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="38" t="n"/>
+      <c r="M16" s="38" t="n">
+        <v>0.775</v>
+      </c>
       <c r="N16" s="16">
         <f>IF($H16="","",IF($M16="","",IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0)))))</f>
         <v/>
@@ -2385,7 +2407,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="38" t="n"/>
+      <c r="M17" s="38" t="n">
+        <v>0.671</v>
+      </c>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -2450,7 +2474,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="38" t="n"/>
+      <c r="M18" s="38" t="n">
+        <v>0.984</v>
+      </c>
       <c r="N18" s="16">
         <f>IF($H18="","",IF($M18="","",IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0)))))</f>
         <v/>
@@ -2515,7 +2541,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="38" t="n"/>
+      <c r="M19" s="38" t="n">
+        <v>0.926</v>
+      </c>
       <c r="N19" s="16">
         <f>IF($H19="","",IF($M19="","",IF($H19=0,IF($M19&lt;=0,1,0),IF($E19="↓",IFERROR($H19/$M19,0),IFERROR($M19/$H19,0)))))</f>
         <v/>
@@ -2580,7 +2608,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M20" s="38" t="n"/>
+      <c r="M20" s="38" t="n">
+        <v>0.8080000000000001</v>
+      </c>
       <c r="N20" s="16">
         <f>IF($H20="","",IF($M20="","",IF($H20=0,IF($M20&lt;=0,1,0),IF($E20="↓",IFERROR($H20/$M20,0),IFERROR($M20/$H20,0)))))</f>
         <v/>
@@ -2641,7 +2671,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3678,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M17" s="36" t="n"/>
+      <c r="M17" s="36" t="n">
+        <v>946380</v>
+      </c>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -3713,7 +3745,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="36" t="n"/>
+      <c r="M18" s="36" t="n">
+        <v>180.7</v>
+      </c>
       <c r="N18" s="16">
         <f>IF($H18="","",IF($M18="","",IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0)))))</f>
         <v/>
@@ -3774,7 +3808,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3944,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="38" t="n"/>
+      <c r="M4" s="38" t="n">
+        <v>0.054</v>
+      </c>
       <c r="N4" s="16">
         <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
         <v/>
@@ -3975,7 +4011,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="38" t="n"/>
+      <c r="M5" s="38" t="n">
+        <v>0.804</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -4040,7 +4078,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="38" t="n"/>
+      <c r="M6" s="38" t="n">
+        <v>0.6870000000000001</v>
+      </c>
       <c r="N6" s="16">
         <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
         <v/>
@@ -4105,7 +4145,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="38" t="n"/>
+      <c r="M7" s="38" t="n">
+        <v>0.648</v>
+      </c>
       <c r="N7" s="16">
         <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
         <v/>
@@ -4170,7 +4212,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="38" t="n"/>
+      <c r="M8" s="38" t="n">
+        <v>0.114</v>
+      </c>
       <c r="N8" s="16">
         <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
         <v/>
@@ -4235,7 +4279,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="38" t="n"/>
+      <c r="M9" s="38" t="n">
+        <v>0.728</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -4300,7 +4346,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="38" t="n"/>
+      <c r="M10" s="38" t="n">
+        <v>0.754</v>
+      </c>
       <c r="N10" s="16">
         <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
         <v/>
@@ -4430,7 +4478,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="38" t="n"/>
+      <c r="M12" s="38" t="n">
+        <v>0.908</v>
+      </c>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -4495,7 +4545,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M13" s="38" t="n"/>
+      <c r="M13" s="38" t="n">
+        <v>0.126</v>
+      </c>
       <c r="N13" s="16">
         <f>IF($H13="","",IF($M13="","",IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0)))))</f>
         <v/>
@@ -4560,7 +4612,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="38" t="n"/>
+      <c r="M14" s="38" t="n">
+        <v>0.944</v>
+      </c>
       <c r="N14" s="16">
         <f>IF($H14="","",IF($M14="","",IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0)))))</f>
         <v/>
@@ -4625,7 +4679,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="38" t="n"/>
+      <c r="M15" s="38" t="n">
+        <v>0.982</v>
+      </c>
       <c r="N15" s="16">
         <f>IF($H15="","",IF($M15="","",IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0)))))</f>
         <v/>
@@ -4690,7 +4746,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="38" t="n"/>
+      <c r="M16" s="38" t="n">
+        <v>0.834</v>
+      </c>
       <c r="N16" s="16">
         <f>IF($H16="","",IF($M16="","",IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0)))))</f>
         <v/>
@@ -4755,7 +4813,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="36" t="n"/>
+      <c r="M17" s="36" t="n">
+        <v>6.827</v>
+      </c>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -4816,7 +4876,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -4952,7 +5012,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="38" t="n"/>
+      <c r="M4" s="38" t="n">
+        <v>1.013</v>
+      </c>
       <c r="N4" s="16">
         <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
         <v/>
@@ -5017,7 +5079,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="40" t="n"/>
+      <c r="M5" s="40" t="n">
+        <v>2.994</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -5082,7 +5146,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="38" t="n"/>
+      <c r="M6" s="38" t="n">
+        <v>0.924</v>
+      </c>
       <c r="N6" s="16">
         <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
         <v/>
@@ -5147,7 +5213,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="38" t="n"/>
+      <c r="M7" s="38" t="n">
+        <v>0.664</v>
+      </c>
       <c r="N7" s="16">
         <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
         <v/>
@@ -5212,7 +5280,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="38" t="n"/>
+      <c r="M8" s="38" t="n">
+        <v>0.797</v>
+      </c>
       <c r="N8" s="16">
         <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
         <v/>
@@ -5277,7 +5347,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="40" t="n"/>
+      <c r="M9" s="40" t="n">
+        <v>4.545</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -5342,7 +5414,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="38" t="n"/>
+      <c r="M10" s="38" t="n">
+        <v>0.659</v>
+      </c>
       <c r="N10" s="16">
         <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
         <v/>
@@ -5407,7 +5481,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M11" s="38" t="n"/>
+      <c r="M11" s="38" t="n">
+        <v>0.674</v>
+      </c>
       <c r="N11" s="16">
         <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
         <v/>
@@ -13485,11 +13561,15 @@
       <c r="H2" s="25" t="n">
         <v>235</v>
       </c>
-      <c r="I2" s="25" t="n"/>
-      <c r="J2" s="27" t="n"/>
+      <c r="I2" s="25" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="J2" s="27" t="n">
+        <v>0.8770212765957447</v>
+      </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
@@ -13545,11 +13625,15 @@
       <c r="H3" s="25" t="n">
         <v>357</v>
       </c>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="27" t="n"/>
+      <c r="I3" s="25" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="J3" s="27" t="n">
+        <v>0.9708683473389357</v>
+      </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
@@ -13721,11 +13805,15 @@
       <c r="H6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="25" t="n"/>
-      <c r="J6" s="27" t="n"/>
+      <c r="I6" s="25" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>0.906</v>
+      </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
@@ -13781,11 +13869,15 @@
       <c r="H7" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I7" s="25" t="n"/>
-      <c r="J7" s="27" t="n"/>
+      <c r="I7" s="25" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>1.043333333333333</v>
+      </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
@@ -13841,11 +13933,15 @@
       <c r="H8" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I8" s="25" t="n"/>
-      <c r="J8" s="27" t="n"/>
+      <c r="I8" s="25" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>1.024444444444444</v>
+      </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
@@ -13901,11 +13997,15 @@
       <c r="H9" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="I9" s="25" t="n"/>
-      <c r="J9" s="27" t="n"/>
+      <c r="I9" s="25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>0.75</v>
+      </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
@@ -13961,11 +14061,15 @@
       <c r="H10" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="25" t="n"/>
-      <c r="J10" s="27" t="n"/>
+      <c r="I10" s="25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>0.85</v>
+      </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
@@ -14021,11 +14125,15 @@
       <c r="H11" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="27" t="n"/>
+      <c r="I11" s="25" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>0.749</v>
+      </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
@@ -14081,11 +14189,15 @@
       <c r="H12" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="27" t="n"/>
+      <c r="I12" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="J12" s="27" t="n">
+        <v>0.7333333333333333</v>
+      </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
@@ -14141,11 +14253,15 @@
       <c r="H13" s="25" t="n">
         <v>167</v>
       </c>
-      <c r="I13" s="25" t="n"/>
-      <c r="J13" s="27" t="n"/>
+      <c r="I13" s="25" t="n">
+        <v>159.2</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>0.9532934131736527</v>
+      </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
@@ -14201,11 +14317,15 @@
       <c r="H14" s="25" t="n">
         <v>718838077</v>
       </c>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="27" t="n"/>
+      <c r="I14" s="25" t="n">
+        <v>576630340</v>
+      </c>
+      <c r="J14" s="27" t="n">
+        <v>0.8021699996840874</v>
+      </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
@@ -14261,11 +14381,15 @@
       <c r="H15" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="27" t="n"/>
+      <c r="I15" s="25" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.8755555555555555</v>
+      </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
@@ -14379,11 +14503,15 @@
       <c r="H17" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="27" t="n"/>
+      <c r="I17" s="25" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>1.012857142857143</v>
+      </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
@@ -14497,11 +14625,15 @@
       <c r="H19" s="25" t="n">
         <v>1.8</v>
       </c>
-      <c r="I19" s="25" t="n"/>
-      <c r="J19" s="27" t="n"/>
+      <c r="I19" s="25" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="J19" s="27" t="n">
+        <v>0.8688888888888889</v>
+      </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
@@ -14557,11 +14689,15 @@
       <c r="H20" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I20" s="25" t="n"/>
-      <c r="J20" s="27" t="n"/>
+      <c r="I20" s="25" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="J20" s="27" t="n">
+        <v>0.8547368421052632</v>
+      </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
@@ -14617,11 +14753,15 @@
       <c r="H21" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="I21" s="25" t="n"/>
-      <c r="J21" s="27" t="n"/>
+      <c r="I21" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="J21" s="27" t="n">
+        <v>1.153846153846154</v>
+      </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
@@ -14735,11 +14875,15 @@
       <c r="H23" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="27" t="n"/>
+      <c r="I23" s="25" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J23" s="27" t="n">
+        <v>0.7833333333333332</v>
+      </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
@@ -14795,11 +14939,15 @@
       <c r="H24" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="I24" s="25" t="n"/>
-      <c r="J24" s="27" t="n"/>
+      <c r="I24" s="25" t="n">
+        <v>4.329</v>
+      </c>
+      <c r="J24" s="27" t="n">
+        <v>1.155001155001155</v>
+      </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
@@ -14855,11 +15003,15 @@
       <c r="H25" s="25" t="n">
         <v>0.99</v>
       </c>
-      <c r="I25" s="25" t="n"/>
-      <c r="J25" s="27" t="n"/>
+      <c r="I25" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="27" t="n">
+        <v>1.01010101010101</v>
+      </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
@@ -14975,11 +15127,15 @@
       <c r="H27" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I27" s="25" t="n"/>
-      <c r="J27" s="27" t="n"/>
+      <c r="I27" s="25" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="J27" s="27" t="n">
+        <v>0.9252631578947369</v>
+      </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
@@ -15035,11 +15191,15 @@
       <c r="H28" s="25" t="n">
         <v>85</v>
       </c>
-      <c r="I28" s="25" t="n"/>
-      <c r="J28" s="27" t="n"/>
+      <c r="I28" s="25" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <v>0.9270588235294117</v>
+      </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
@@ -15095,11 +15255,15 @@
       <c r="H29" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="25" t="n"/>
-      <c r="J29" s="27" t="n"/>
+      <c r="I29" s="25" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="J29" s="27" t="n">
+        <v>1.034</v>
+      </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
@@ -15155,11 +15319,15 @@
       <c r="H30" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="27" t="n"/>
+      <c r="I30" s="25" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="J30" s="27" t="n">
+        <v>0.911</v>
+      </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
@@ -15215,11 +15383,15 @@
       <c r="H31" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="I31" s="25" t="n"/>
-      <c r="J31" s="27" t="n"/>
+      <c r="I31" s="25" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J31" s="27" t="n">
+        <v>0.916030534351145</v>
+      </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
@@ -15275,11 +15447,15 @@
       <c r="H32" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I32" s="25" t="n"/>
-      <c r="J32" s="27" t="n"/>
+      <c r="I32" s="25" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J32" s="27" t="n">
+        <v>0.7488888888888889</v>
+      </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
@@ -15335,11 +15511,15 @@
       <c r="H33" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="I33" s="25" t="n"/>
-      <c r="J33" s="27" t="n"/>
+      <c r="I33" s="25" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="J33" s="27" t="n">
+        <v>0.9966666666666667</v>
+      </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
@@ -15395,11 +15575,15 @@
       <c r="H34" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="27" t="n"/>
+      <c r="I34" s="25" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J34" s="27" t="n">
+        <v>0.7999999999999999</v>
+      </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
@@ -15455,11 +15639,15 @@
       <c r="H35" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="25" t="n"/>
-      <c r="J35" s="27" t="n"/>
+      <c r="I35" s="25" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="J35" s="27" t="n">
+        <v>1.028</v>
+      </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
@@ -15515,11 +15703,15 @@
       <c r="H36" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="I36" s="25" t="n"/>
-      <c r="J36" s="27" t="n"/>
+      <c r="I36" s="25" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="J36" s="27" t="n">
+        <v>0.9638554216867471</v>
+      </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
@@ -15575,11 +15767,15 @@
       <c r="H37" s="25" t="n">
         <v>0.6</v>
       </c>
-      <c r="I37" s="25" t="n"/>
-      <c r="J37" s="27" t="n"/>
+      <c r="I37" s="25" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="J37" s="27" t="n">
+        <v>0.8600000000000001</v>
+      </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
@@ -15635,11 +15831,15 @@
       <c r="H38" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="I38" s="25" t="n"/>
-      <c r="J38" s="27" t="n"/>
+      <c r="I38" s="25" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="J38" s="27" t="n">
+        <v>0.944</v>
+      </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
@@ -15695,11 +15895,15 @@
       <c r="H39" s="25" t="n">
         <v>4.7</v>
       </c>
-      <c r="I39" s="25" t="n"/>
-      <c r="J39" s="27" t="n"/>
+      <c r="I39" s="25" t="n">
+        <v>3.474</v>
+      </c>
+      <c r="J39" s="27" t="n">
+        <v>0.7391489361702128</v>
+      </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
@@ -15755,11 +15959,15 @@
       <c r="H40" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I40" s="25" t="n"/>
-      <c r="J40" s="27" t="n"/>
+      <c r="I40" s="25" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="J40" s="27" t="n">
+        <v>0.9299999999999999</v>
+      </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
@@ -15815,11 +16023,15 @@
       <c r="H41" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I41" s="25" t="n"/>
-      <c r="J41" s="27" t="n"/>
+      <c r="I41" s="25" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="J41" s="27" t="n">
+        <v>0.9705263157894738</v>
+      </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
@@ -15933,11 +16145,15 @@
       <c r="H43" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I43" s="25" t="n"/>
-      <c r="J43" s="27" t="n"/>
+      <c r="I43" s="25" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="J43" s="27" t="n">
+        <v>0.9477777777777777</v>
+      </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
@@ -15993,11 +16209,15 @@
       <c r="H44" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="25" t="n"/>
-      <c r="J44" s="27" t="n"/>
+      <c r="I44" s="25" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J44" s="27" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
@@ -16053,11 +16273,15 @@
       <c r="H45" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="25" t="n"/>
-      <c r="J45" s="27" t="n"/>
+      <c r="I45" s="25" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="J45" s="27" t="n">
+        <v>0.751</v>
+      </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
@@ -16113,11 +16337,15 @@
       <c r="H46" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="25" t="n"/>
-      <c r="J46" s="27" t="n"/>
+      <c r="I46" s="25" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="J46" s="27" t="n">
+        <v>1.112347052280311</v>
+      </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
@@ -16173,11 +16401,15 @@
       <c r="H47" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="25" t="n"/>
-      <c r="J47" s="27" t="n"/>
+      <c r="I47" s="25" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="J47" s="27" t="n">
+        <v>0.961</v>
+      </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
@@ -16233,11 +16465,15 @@
       <c r="H48" s="25" t="n">
         <v>85</v>
       </c>
-      <c r="I48" s="25" t="n"/>
-      <c r="J48" s="27" t="n"/>
+      <c r="I48" s="25" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="J48" s="27" t="n">
+        <v>0.9235294117647059</v>
+      </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
@@ -16525,11 +16761,15 @@
       <c r="H53" s="25" t="n">
         <v>0.99</v>
       </c>
-      <c r="I53" s="25" t="n"/>
-      <c r="J53" s="27" t="n"/>
+      <c r="I53" s="25" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="J53" s="27" t="n">
+        <v>0.8393939393939394</v>
+      </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L53" s="14" t="inlineStr">
@@ -16585,11 +16825,15 @@
       <c r="H54" s="25" t="n">
         <v>0.97</v>
       </c>
-      <c r="I54" s="25" t="n"/>
-      <c r="J54" s="27" t="n"/>
+      <c r="I54" s="25" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="J54" s="27" t="n">
+        <v>0.9824742268041237</v>
+      </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L54" s="14" t="inlineStr">
@@ -16703,11 +16947,15 @@
       <c r="H56" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I56" s="25" t="n"/>
-      <c r="J56" s="27" t="n"/>
+      <c r="I56" s="25" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="J56" s="27" t="n">
+        <v>0.7978947368421053</v>
+      </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L56" s="14" t="inlineStr">
@@ -16821,11 +17069,15 @@
       <c r="H58" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="I58" s="25" t="n"/>
-      <c r="J58" s="27" t="n"/>
+      <c r="I58" s="25" t="n">
+        <v>4.048</v>
+      </c>
+      <c r="J58" s="27" t="n">
+        <v>0.8995555555555556</v>
+      </c>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L58" s="14" t="inlineStr">
@@ -16881,11 +17133,15 @@
       <c r="H59" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I59" s="25" t="n"/>
-      <c r="J59" s="27" t="n"/>
+      <c r="I59" s="25" t="n">
+        <v>3.352</v>
+      </c>
+      <c r="J59" s="27" t="n">
+        <v>0.8949880668257757</v>
+      </c>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L59" s="14" t="inlineStr">
@@ -16941,11 +17197,15 @@
       <c r="H60" s="25" t="n">
         <v>0.99</v>
       </c>
-      <c r="I60" s="25" t="n"/>
-      <c r="J60" s="27" t="n"/>
+      <c r="I60" s="25" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="J60" s="27" t="n">
+        <v>0.8393939393939394</v>
+      </c>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L60" s="14" t="inlineStr">
@@ -17001,11 +17261,15 @@
       <c r="H61" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I61" s="25" t="n"/>
-      <c r="J61" s="27" t="n"/>
+      <c r="I61" s="25" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="J61" s="27" t="n">
+        <v>0.98375</v>
+      </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L61" s="14" t="inlineStr">
@@ -17061,11 +17325,15 @@
       <c r="H62" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I62" s="25" t="n"/>
-      <c r="J62" s="27" t="n"/>
+      <c r="I62" s="25" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="J62" s="27" t="n">
+        <v>0.837</v>
+      </c>
       <c r="K62" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L62" s="14" t="inlineStr">
@@ -17121,11 +17389,15 @@
       <c r="H63" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="25" t="n"/>
-      <c r="J63" s="27" t="n"/>
+      <c r="I63" s="25" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="J63" s="27" t="n">
+        <v>0.747</v>
+      </c>
       <c r="K63" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L63" s="14" t="inlineStr">
@@ -17181,11 +17453,15 @@
       <c r="H64" s="25" t="n">
         <v>190</v>
       </c>
-      <c r="I64" s="25" t="n"/>
-      <c r="J64" s="27" t="n"/>
+      <c r="I64" s="25" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="J64" s="27" t="n">
+        <v>0.8721052631578947</v>
+      </c>
       <c r="K64" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L64" s="14" t="inlineStr">
@@ -17241,11 +17517,15 @@
       <c r="H65" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="I65" s="25" t="n"/>
-      <c r="J65" s="27" t="n"/>
+      <c r="I65" s="25" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="J65" s="27" t="n">
+        <v>0.8477777777777777</v>
+      </c>
       <c r="K65" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L65" s="14" t="inlineStr">
@@ -17301,11 +17581,15 @@
       <c r="H66" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="I66" s="25" t="n"/>
-      <c r="J66" s="27" t="n"/>
+      <c r="I66" s="25" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="J66" s="27" t="n">
+        <v>0.8220000000000001</v>
+      </c>
       <c r="K66" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L66" s="14" t="inlineStr">
@@ -17361,11 +17645,15 @@
       <c r="H67" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="I67" s="25" t="n"/>
-      <c r="J67" s="27" t="n"/>
+      <c r="I67" s="25" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="J67" s="27" t="n">
+        <v>1.048333333333333</v>
+      </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L67" s="14" t="inlineStr">
@@ -17421,11 +17709,15 @@
       <c r="H68" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="I68" s="25" t="n"/>
-      <c r="J68" s="27" t="n"/>
+      <c r="I68" s="25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J68" s="27" t="n">
+        <v>0.7363636363636363</v>
+      </c>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L68" s="14" t="inlineStr">
@@ -17481,11 +17773,15 @@
       <c r="H69" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="I69" s="25" t="n"/>
-      <c r="J69" s="27" t="n"/>
+      <c r="I69" s="25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J69" s="27" t="n">
+        <v>1.016666666666667</v>
+      </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L69" s="14" t="inlineStr">
@@ -17541,11 +17837,15 @@
       <c r="H70" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="I70" s="25" t="n"/>
-      <c r="J70" s="27" t="n"/>
+      <c r="I70" s="25" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J70" s="27" t="n">
+        <v>0.7264705882352941</v>
+      </c>
       <c r="K70" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L70" s="14" t="inlineStr">
@@ -17601,11 +17901,15 @@
       <c r="H71" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I71" s="25" t="n"/>
-      <c r="J71" s="27" t="n"/>
+      <c r="I71" s="25" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="J71" s="27" t="n">
+        <v>0.81125</v>
+      </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L71" s="14" t="inlineStr">
@@ -17661,11 +17965,15 @@
       <c r="H72" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="I72" s="25" t="n"/>
-      <c r="J72" s="27" t="n"/>
+      <c r="I72" s="25" t="n">
+        <v>4.983</v>
+      </c>
+      <c r="J72" s="27" t="n">
+        <v>1.00341159943809</v>
+      </c>
       <c r="K72" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L72" s="14" t="inlineStr">
@@ -17779,11 +18087,15 @@
       <c r="H74" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="25" t="n"/>
-      <c r="J74" s="27" t="n"/>
+      <c r="I74" s="25" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="J74" s="27" t="n">
+        <v>1.028</v>
+      </c>
       <c r="K74" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L74" s="14" t="inlineStr">
@@ -17839,11 +18151,15 @@
       <c r="H75" s="25" t="n">
         <v>0.6</v>
       </c>
-      <c r="I75" s="25" t="n"/>
-      <c r="J75" s="27" t="n"/>
+      <c r="I75" s="25" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="J75" s="27" t="n">
+        <v>0.8600000000000001</v>
+      </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L75" s="14" t="inlineStr">
@@ -17899,11 +18215,15 @@
       <c r="H76" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="I76" s="25" t="n"/>
-      <c r="J76" s="27" t="n"/>
+      <c r="I76" s="25" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="J76" s="27" t="n">
+        <v>0.9638554216867471</v>
+      </c>
       <c r="K76" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L76" s="14" t="inlineStr">
@@ -17959,11 +18279,15 @@
       <c r="H77" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="I77" s="25" t="n"/>
-      <c r="J77" s="27" t="n"/>
+      <c r="I77" s="25" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="J77" s="27" t="n">
+        <v>0.944</v>
+      </c>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L77" s="14" t="inlineStr">
@@ -18019,11 +18343,15 @@
       <c r="H78" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I78" s="25" t="n"/>
-      <c r="J78" s="27" t="n"/>
+      <c r="I78" s="25" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="J78" s="27" t="n">
+        <v>1.096491228070175</v>
+      </c>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L78" s="14" t="inlineStr">
@@ -18079,11 +18407,15 @@
       <c r="H79" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="I79" s="25" t="n"/>
-      <c r="J79" s="27" t="n"/>
+      <c r="I79" s="25" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="J79" s="27" t="n">
+        <v>1.026666666666667</v>
+      </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L79" s="14" t="inlineStr">
@@ -18139,11 +18471,15 @@
       <c r="H80" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="I80" s="25" t="n"/>
-      <c r="J80" s="27" t="n"/>
+      <c r="I80" s="25" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="J80" s="27" t="n">
+        <v>0.7366666666666667</v>
+      </c>
       <c r="K80" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L80" s="14" t="inlineStr">
@@ -18199,11 +18535,15 @@
       <c r="H81" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="25" t="n"/>
-      <c r="J81" s="27" t="n"/>
+      <c r="I81" s="25" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="J81" s="27" t="n">
+        <v>0.751</v>
+      </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L81" s="14" t="inlineStr">
@@ -18259,11 +18599,15 @@
       <c r="H82" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I82" s="25" t="n"/>
-      <c r="J82" s="27" t="n"/>
+      <c r="I82" s="25" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="J82" s="27" t="n">
+        <v>0.7747368421052632</v>
+      </c>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L82" s="14" t="inlineStr">
@@ -18319,11 +18663,15 @@
       <c r="H83" s="25" t="n">
         <v>0.98</v>
       </c>
-      <c r="I83" s="25" t="n"/>
-      <c r="J83" s="27" t="n"/>
+      <c r="I83" s="25" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="J83" s="27" t="n">
+        <v>1.029591836734694</v>
+      </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L83" s="14" t="inlineStr">
@@ -18379,11 +18727,15 @@
       <c r="H84" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I84" s="25" t="n"/>
-      <c r="J84" s="27" t="n"/>
+      <c r="I84" s="25" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="J84" s="27" t="n">
+        <v>0.942507068803016</v>
+      </c>
       <c r="K84" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L84" s="14" t="inlineStr">
@@ -18439,11 +18791,15 @@
       <c r="H85" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I85" s="25" t="n"/>
-      <c r="J85" s="27" t="n"/>
+      <c r="I85" s="25" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="J85" s="27" t="n">
+        <v>0.9825</v>
+      </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L85" s="14" t="inlineStr">
@@ -18499,11 +18855,15 @@
       <c r="H86" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I86" s="25" t="n"/>
-      <c r="J86" s="27" t="n"/>
+      <c r="I86" s="25" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="J86" s="27" t="n">
+        <v>0.972</v>
+      </c>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L86" s="14" t="inlineStr">
@@ -18559,11 +18919,15 @@
       <c r="H87" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I87" s="25" t="n"/>
-      <c r="J87" s="27" t="n"/>
+      <c r="I87" s="25" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="J87" s="27" t="n">
+        <v>0.961</v>
+      </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L87" s="14" t="inlineStr">
@@ -18619,11 +18983,15 @@
       <c r="H88" s="25" t="n">
         <v>0.08</v>
       </c>
-      <c r="I88" s="25" t="n"/>
-      <c r="J88" s="27" t="n"/>
+      <c r="I88" s="25" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="J88" s="27" t="n">
+        <v>0.8500000000000001</v>
+      </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L88" s="14" t="inlineStr">
@@ -18679,11 +19047,15 @@
       <c r="H89" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I89" s="25" t="n"/>
-      <c r="J89" s="27" t="n"/>
+      <c r="I89" s="25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J89" s="27" t="n">
+        <v>1.03</v>
+      </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L89" s="14" t="inlineStr">
@@ -18739,11 +19111,15 @@
       <c r="H90" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I90" s="25" t="n"/>
-      <c r="J90" s="27" t="n"/>
+      <c r="I90" s="25" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J90" s="27" t="n">
+        <v>0.7536842105263158</v>
+      </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L90" s="14" t="inlineStr">
@@ -18799,11 +19175,15 @@
       <c r="H91" s="25" t="n">
         <v>0.6</v>
       </c>
-      <c r="I91" s="25" t="n"/>
-      <c r="J91" s="27" t="n"/>
+      <c r="I91" s="25" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="J91" s="27" t="n">
+        <v>1.018333333333333</v>
+      </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L91" s="14" t="inlineStr">
@@ -18859,11 +19239,15 @@
       <c r="H92" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="I92" s="25" t="n"/>
-      <c r="J92" s="27" t="n"/>
+      <c r="I92" s="25" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="J92" s="27" t="n">
+        <v>0.8058823529411764</v>
+      </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L92" s="14" t="inlineStr">
@@ -18919,11 +19303,15 @@
       <c r="H93" s="25" t="n">
         <v>680</v>
       </c>
-      <c r="I93" s="25" t="n"/>
-      <c r="J93" s="27" t="n"/>
+      <c r="I93" s="25" t="n">
+        <v>531.8</v>
+      </c>
+      <c r="J93" s="27" t="n">
+        <v>0.7820588235294117</v>
+      </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L93" s="14" t="inlineStr">
@@ -18979,11 +19367,15 @@
       <c r="H94" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="I94" s="25" t="n"/>
-      <c r="J94" s="27" t="n"/>
+      <c r="I94" s="25" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="J94" s="27" t="n">
+        <v>1.04</v>
+      </c>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L94" s="14" t="inlineStr">
@@ -19039,11 +19431,15 @@
       <c r="H95" s="25" t="n">
         <v>246</v>
       </c>
-      <c r="I95" s="25" t="n"/>
-      <c r="J95" s="27" t="n"/>
+      <c r="I95" s="25" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="J95" s="27" t="n">
+        <v>0.8235772357723578</v>
+      </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L95" s="14" t="inlineStr">
@@ -19099,11 +19495,15 @@
       <c r="H96" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I96" s="25" t="n"/>
-      <c r="J96" s="27" t="n"/>
+      <c r="I96" s="25" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="J96" s="27" t="n">
+        <v>0.83875</v>
+      </c>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L96" s="14" t="inlineStr">
@@ -19159,11 +19559,15 @@
       <c r="H97" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="I97" s="25" t="n"/>
-      <c r="J97" s="27" t="n"/>
+      <c r="I97" s="25" t="n">
+        <v>5.769</v>
+      </c>
+      <c r="J97" s="27" t="n">
+        <v>0.9615</v>
+      </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L97" s="14" t="inlineStr">
@@ -19219,11 +19623,15 @@
       <c r="H98" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="I98" s="25" t="n"/>
-      <c r="J98" s="27" t="n"/>
+      <c r="I98" s="25" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="J98" s="27" t="n">
+        <v>0.9179999999999999</v>
+      </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
@@ -19279,11 +19687,15 @@
       <c r="H99" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I99" s="25" t="n"/>
-      <c r="J99" s="27" t="n"/>
+      <c r="I99" s="25" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J99" s="27" t="n">
+        <v>0.792</v>
+      </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L99" s="14" t="inlineStr">
@@ -19339,11 +19751,15 @@
       <c r="H100" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="I100" s="25" t="n"/>
-      <c r="J100" s="27" t="n"/>
+      <c r="I100" s="25" t="n">
+        <v>7.983</v>
+      </c>
+      <c r="J100" s="27" t="n">
+        <v>0.8768633345859953</v>
+      </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L100" s="14" t="inlineStr">
@@ -19399,11 +19815,15 @@
       <c r="H101" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I101" s="25" t="n"/>
-      <c r="J101" s="27" t="n"/>
+      <c r="I101" s="25" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="J101" s="27" t="n">
+        <v>0.7755555555555554</v>
+      </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L101" s="14" t="inlineStr">
@@ -19459,11 +19879,15 @@
       <c r="H102" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I102" s="25" t="n"/>
-      <c r="J102" s="27" t="n"/>
+      <c r="I102" s="25" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="J102" s="27" t="n">
+        <v>0.8687499999999999</v>
+      </c>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L102" s="14" t="inlineStr">
@@ -19519,11 +19943,15 @@
       <c r="H103" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I103" s="25" t="n"/>
-      <c r="J103" s="27" t="n"/>
+      <c r="I103" s="25" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="J103" s="27" t="n">
+        <v>0.9933333333333333</v>
+      </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L103" s="14" t="inlineStr">
@@ -19643,11 +20071,15 @@
       <c r="H105" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I105" s="25" t="n"/>
-      <c r="J105" s="27" t="n"/>
+      <c r="I105" s="25" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J105" s="27" t="n">
+        <v>0.9222222222222222</v>
+      </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L105" s="14" t="inlineStr">
@@ -19703,11 +20135,15 @@
       <c r="H106" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I106" s="25" t="n"/>
-      <c r="J106" s="27" t="n"/>
+      <c r="I106" s="25" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="J106" s="27" t="n">
+        <v>0.7926315789473685</v>
+      </c>
       <c r="K106" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L106" s="14" t="inlineStr">
@@ -19763,11 +20199,15 @@
       <c r="H107" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I107" s="25" t="n"/>
-      <c r="J107" s="27" t="n"/>
+      <c r="I107" s="25" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="J107" s="27" t="n">
+        <v>0.74</v>
+      </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L107" s="14" t="inlineStr">
@@ -20201,11 +20641,15 @@
       <c r="H114" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I114" s="25" t="n"/>
-      <c r="J114" s="27" t="n"/>
+      <c r="I114" s="25" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J114" s="27" t="n">
+        <v>0.723</v>
+      </c>
       <c r="K114" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L114" s="14" t="inlineStr">
@@ -20261,11 +20705,15 @@
       <c r="H115" s="25" t="n">
         <v>0.85</v>
       </c>
-      <c r="I115" s="25" t="n"/>
-      <c r="J115" s="27" t="n"/>
+      <c r="I115" s="25" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J115" s="27" t="n">
+        <v>0.8588235294117647</v>
+      </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L115" s="14" t="inlineStr">
@@ -20321,11 +20769,15 @@
       <c r="H116" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I116" s="25" t="n"/>
-      <c r="J116" s="27" t="n"/>
+      <c r="I116" s="25" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J116" s="27" t="n">
+        <v>0.8833333333333333</v>
+      </c>
       <c r="K116" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L116" s="14" t="inlineStr">
@@ -20381,11 +20833,15 @@
       <c r="H117" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="I117" s="25" t="n"/>
-      <c r="J117" s="27" t="n"/>
+      <c r="I117" s="25" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J117" s="27" t="n">
+        <v>0.9009009009009009</v>
+      </c>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L117" s="14" t="inlineStr">
@@ -20441,11 +20897,15 @@
       <c r="H118" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="I118" s="25" t="n"/>
-      <c r="J118" s="27" t="n"/>
+      <c r="I118" s="25" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="J118" s="27" t="n">
+        <v>0.755</v>
+      </c>
       <c r="K118" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L118" s="14" t="inlineStr">
@@ -20501,11 +20961,15 @@
       <c r="H119" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="I119" s="25" t="n"/>
-      <c r="J119" s="27" t="n"/>
+      <c r="I119" s="25" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="J119" s="27" t="n">
+        <v>0.8400000000000001</v>
+      </c>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L119" s="14" t="inlineStr">
@@ -20561,11 +21025,15 @@
       <c r="H120" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I120" s="25" t="n"/>
-      <c r="J120" s="27" t="n"/>
+      <c r="I120" s="25" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="J120" s="27" t="n">
+        <v>0.8049999999999999</v>
+      </c>
       <c r="K120" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L120" s="14" t="inlineStr">
@@ -20621,11 +21089,15 @@
       <c r="H121" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="I121" s="25" t="n"/>
-      <c r="J121" s="27" t="n"/>
+      <c r="I121" s="25" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J121" s="27" t="n">
+        <v>0.9166666666666666</v>
+      </c>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L121" s="14" t="inlineStr">
@@ -20739,11 +21211,15 @@
       <c r="H123" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I123" s="25" t="n"/>
-      <c r="J123" s="27" t="n"/>
+      <c r="I123" s="25" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="J123" s="27" t="n">
+        <v>0.742</v>
+      </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L123" s="14" t="inlineStr">
@@ -20799,11 +21275,15 @@
       <c r="H124" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I124" s="25" t="n"/>
-      <c r="J124" s="27" t="n"/>
+      <c r="I124" s="25" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J124" s="27" t="n">
+        <v>0.84</v>
+      </c>
       <c r="K124" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L124" s="14" t="inlineStr">
@@ -20859,11 +21339,15 @@
       <c r="H125" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I125" s="25" t="n"/>
-      <c r="J125" s="27" t="n"/>
+      <c r="I125" s="25" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="J125" s="27" t="n">
+        <v>0.96875</v>
+      </c>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L125" s="14" t="inlineStr">
@@ -20919,11 +21403,15 @@
       <c r="H126" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I126" s="25" t="n"/>
-      <c r="J126" s="27" t="n"/>
+      <c r="I126" s="25" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="J126" s="27" t="n">
+        <v>0.83875</v>
+      </c>
       <c r="K126" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L126" s="14" t="inlineStr">
@@ -20979,11 +21467,15 @@
       <c r="H127" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I127" s="25" t="n"/>
-      <c r="J127" s="27" t="n"/>
+      <c r="I127" s="25" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="J127" s="27" t="n">
+        <v>0.984</v>
+      </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L127" s="14" t="inlineStr">
@@ -21039,11 +21531,15 @@
       <c r="H128" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I128" s="25" t="n"/>
-      <c r="J128" s="27" t="n"/>
+      <c r="I128" s="25" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="J128" s="27" t="n">
+        <v>0.926</v>
+      </c>
       <c r="K128" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L128" s="14" t="inlineStr">
@@ -21099,11 +21595,15 @@
       <c r="H129" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I129" s="25" t="n"/>
-      <c r="J129" s="27" t="n"/>
+      <c r="I129" s="25" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="J129" s="27" t="n">
+        <v>0.8080000000000001</v>
+      </c>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L129" s="14" t="inlineStr">
@@ -21991,11 +22491,15 @@
       <c r="H143" s="25" t="n">
         <v>1000000</v>
       </c>
-      <c r="I143" s="25" t="n"/>
-      <c r="J143" s="27" t="n"/>
+      <c r="I143" s="25" t="n">
+        <v>946380</v>
+      </c>
+      <c r="J143" s="27" t="n">
+        <v>0.94638</v>
+      </c>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L143" s="14" t="inlineStr">
@@ -22051,11 +22555,15 @@
       <c r="H144" s="25" t="n">
         <v>250</v>
       </c>
-      <c r="I144" s="25" t="n"/>
-      <c r="J144" s="27" t="n"/>
+      <c r="I144" s="25" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="J144" s="27" t="n">
+        <v>0.7228</v>
+      </c>
       <c r="K144" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L144" s="14" t="inlineStr">
@@ -22111,11 +22619,15 @@
       <c r="H145" s="25" t="n">
         <v>0.05</v>
       </c>
-      <c r="I145" s="25" t="n"/>
-      <c r="J145" s="27" t="n"/>
+      <c r="I145" s="25" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J145" s="27" t="n">
+        <v>0.925925925925926</v>
+      </c>
       <c r="K145" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L145" s="14" t="inlineStr">
@@ -22171,11 +22683,15 @@
       <c r="H146" s="25" t="n">
         <v>0.995</v>
       </c>
-      <c r="I146" s="25" t="n"/>
-      <c r="J146" s="27" t="n"/>
+      <c r="I146" s="25" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="J146" s="27" t="n">
+        <v>0.8080402010050252</v>
+      </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L146" s="14" t="inlineStr">
@@ -22231,11 +22747,15 @@
       <c r="H147" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I147" s="25" t="n"/>
-      <c r="J147" s="27" t="n"/>
+      <c r="I147" s="25" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J147" s="27" t="n">
+        <v>0.7633333333333334</v>
+      </c>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L147" s="14" t="inlineStr">
@@ -22291,11 +22811,15 @@
       <c r="H148" s="25" t="n">
         <v>0.85</v>
       </c>
-      <c r="I148" s="25" t="n"/>
-      <c r="J148" s="27" t="n"/>
+      <c r="I148" s="25" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="J148" s="27" t="n">
+        <v>0.7623529411764707</v>
+      </c>
       <c r="K148" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L148" s="14" t="inlineStr">
@@ -22351,11 +22875,15 @@
       <c r="H149" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="I149" s="25" t="n"/>
-      <c r="J149" s="27" t="n"/>
+      <c r="I149" s="25" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="J149" s="27" t="n">
+        <v>0.8771929824561404</v>
+      </c>
       <c r="K149" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L149" s="14" t="inlineStr">
@@ -22411,11 +22939,15 @@
       <c r="H150" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I150" s="25" t="n"/>
-      <c r="J150" s="27" t="n"/>
+      <c r="I150" s="25" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="J150" s="27" t="n">
+        <v>0.7663157894736842</v>
+      </c>
       <c r="K150" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L150" s="14" t="inlineStr">
@@ -22471,11 +23003,15 @@
       <c r="H151" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I151" s="25" t="n"/>
-      <c r="J151" s="27" t="n"/>
+      <c r="I151" s="25" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="J151" s="27" t="n">
+        <v>0.8377777777777777</v>
+      </c>
       <c r="K151" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L151" s="14" t="inlineStr">
@@ -22591,11 +23127,15 @@
       <c r="H153" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I153" s="25" t="n"/>
-      <c r="J153" s="27" t="n"/>
+      <c r="I153" s="25" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="J153" s="27" t="n">
+        <v>1.008888888888889</v>
+      </c>
       <c r="K153" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L153" s="14" t="inlineStr">
@@ -22651,11 +23191,15 @@
       <c r="H154" s="25" t="n">
         <v>0.15</v>
       </c>
-      <c r="I154" s="25" t="n"/>
-      <c r="J154" s="27" t="n"/>
+      <c r="I154" s="25" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="J154" s="27" t="n">
+        <v>0.8400000000000001</v>
+      </c>
       <c r="K154" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L154" s="14" t="inlineStr">
@@ -22711,11 +23255,15 @@
       <c r="H155" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I155" s="25" t="n"/>
-      <c r="J155" s="27" t="n"/>
+      <c r="I155" s="25" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="J155" s="27" t="n">
+        <v>0.9936842105263158</v>
+      </c>
       <c r="K155" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L155" s="14" t="inlineStr">
@@ -22771,11 +23319,15 @@
       <c r="H156" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I156" s="25" t="n"/>
-      <c r="J156" s="27" t="n"/>
+      <c r="I156" s="25" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="J156" s="27" t="n">
+        <v>1.033684210526316</v>
+      </c>
       <c r="K156" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L156" s="14" t="inlineStr">
@@ -22831,11 +23383,15 @@
       <c r="H157" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I157" s="25" t="n"/>
-      <c r="J157" s="27" t="n"/>
+      <c r="I157" s="25" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="J157" s="27" t="n">
+        <v>1.0425</v>
+      </c>
       <c r="K157" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L157" s="14" t="inlineStr">
@@ -22891,11 +23447,15 @@
       <c r="H158" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="I158" s="25" t="n"/>
-      <c r="J158" s="27" t="n"/>
+      <c r="I158" s="25" t="n">
+        <v>6.827</v>
+      </c>
+      <c r="J158" s="27" t="n">
+        <v>0.853375</v>
+      </c>
       <c r="K158" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L158" s="14" t="inlineStr">
@@ -22951,11 +23511,15 @@
       <c r="H159" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I159" s="25" t="n"/>
-      <c r="J159" s="27" t="n"/>
+      <c r="I159" s="25" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="J159" s="27" t="n">
+        <v>1.013</v>
+      </c>
       <c r="K159" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L159" s="14" t="inlineStr">
@@ -23011,11 +23575,15 @@
       <c r="H160" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I160" s="25" t="n"/>
-      <c r="J160" s="27" t="n"/>
+      <c r="I160" s="25" t="n">
+        <v>2.994</v>
+      </c>
+      <c r="J160" s="27" t="n">
+        <v>1.002004008016032</v>
+      </c>
       <c r="K160" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L160" s="14" t="inlineStr">
@@ -23071,11 +23639,15 @@
       <c r="H161" s="25" t="n">
         <v>0.95</v>
       </c>
-      <c r="I161" s="25" t="n"/>
-      <c r="J161" s="27" t="n"/>
+      <c r="I161" s="25" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="J161" s="27" t="n">
+        <v>0.9726315789473685</v>
+      </c>
       <c r="K161" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="L161" s="14" t="inlineStr">
@@ -23131,11 +23703,15 @@
       <c r="H162" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="I162" s="25" t="n"/>
-      <c r="J162" s="27" t="n"/>
+      <c r="I162" s="25" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="J162" s="27" t="n">
+        <v>0.83</v>
+      </c>
       <c r="K162" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L162" s="14" t="inlineStr">
@@ -23191,11 +23767,15 @@
       <c r="H163" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I163" s="25" t="n"/>
-      <c r="J163" s="27" t="n"/>
+      <c r="I163" s="25" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J163" s="27" t="n">
+        <v>0.797</v>
+      </c>
       <c r="K163" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L163" s="14" t="inlineStr">
@@ -23251,11 +23831,15 @@
       <c r="H164" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="I164" s="25" t="n"/>
-      <c r="J164" s="27" t="n"/>
+      <c r="I164" s="25" t="n">
+        <v>4.545</v>
+      </c>
+      <c r="J164" s="27" t="n">
+        <v>1.1001100110011</v>
+      </c>
       <c r="K164" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ محقق</t>
         </is>
       </c>
       <c r="L164" s="14" t="inlineStr">
@@ -23311,11 +23895,15 @@
       <c r="H165" s="25" t="n">
         <v>0.9</v>
       </c>
-      <c r="I165" s="25" t="n"/>
-      <c r="J165" s="27" t="n"/>
+      <c r="I165" s="25" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="J165" s="27" t="n">
+        <v>0.7322222222222222</v>
+      </c>
       <c r="K165" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L165" s="14" t="inlineStr">
@@ -23371,11 +23959,15 @@
       <c r="H166" s="25" t="n">
         <v>0.85</v>
       </c>
-      <c r="I166" s="25" t="n"/>
-      <c r="J166" s="27" t="n"/>
+      <c r="I166" s="25" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J166" s="27" t="n">
+        <v>0.7929411764705883</v>
+      </c>
       <c r="K166" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="L166" s="14" t="inlineStr">
@@ -23436,7 +24028,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -23572,7 +24164,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="36" t="n"/>
+      <c r="M4" s="36" t="n">
+        <v>206.1</v>
+      </c>
       <c r="N4" s="16">
         <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
         <v/>
@@ -23637,7 +24231,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="36" t="n"/>
+      <c r="M5" s="36" t="n">
+        <v>346.6</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -23828,7 +24424,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="38" t="n"/>
+      <c r="M8" s="38" t="n">
+        <v>0.906</v>
+      </c>
       <c r="N8" s="16">
         <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
         <v/>
@@ -23893,7 +24491,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M9" s="38" t="n"/>
+      <c r="M9" s="38" t="n">
+        <v>0.9389999999999999</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -23958,7 +24558,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M10" s="38" t="n"/>
+      <c r="M10" s="38" t="n">
+        <v>0.922</v>
+      </c>
       <c r="N10" s="16">
         <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
         <v/>
@@ -24023,7 +24625,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M11" s="40" t="n"/>
+      <c r="M11" s="40" t="n">
+        <v>22.5</v>
+      </c>
       <c r="N11" s="16">
         <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
         <v/>
@@ -24088,7 +24692,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="38" t="n"/>
+      <c r="M12" s="38" t="n">
+        <v>0.85</v>
+      </c>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -24153,7 +24759,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M13" s="38" t="n"/>
+      <c r="M13" s="38" t="n">
+        <v>0.749</v>
+      </c>
       <c r="N13" s="16">
         <f>IF($H13="","",IF($M13="","",IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0)))))</f>
         <v/>
@@ -24214,7 +24822,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -24350,7 +24958,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="36" t="n"/>
+      <c r="M4" s="36" t="n">
+        <v>110</v>
+      </c>
       <c r="N4" s="16">
         <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
         <v/>
@@ -24415,7 +25025,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="36" t="n"/>
+      <c r="M5" s="36" t="n">
+        <v>159.2</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -24480,7 +25092,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M6" s="36" t="n"/>
+      <c r="M6" s="36" t="n">
+        <v>576630340</v>
+      </c>
       <c r="N6" s="16">
         <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
         <v/>
@@ -24545,7 +25159,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M7" s="38" t="n"/>
+      <c r="M7" s="38" t="n">
+        <v>0.788</v>
+      </c>
       <c r="N7" s="16">
         <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
         <v/>
@@ -24673,7 +25289,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="38" t="n"/>
+      <c r="M9" s="38" t="n">
+        <v>0.709</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -24801,7 +25419,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M11" s="40" t="n"/>
+      <c r="M11" s="40" t="n">
+        <v>1.564</v>
+      </c>
       <c r="N11" s="16">
         <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
         <v/>
@@ -24866,7 +25486,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M12" s="38" t="n"/>
+      <c r="M12" s="38" t="n">
+        <v>0.8120000000000001</v>
+      </c>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -24931,7 +25553,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M13" s="40" t="n"/>
+      <c r="M13" s="40" t="n">
+        <v>26</v>
+      </c>
       <c r="N13" s="16">
         <f>IF($H13="","",IF($M13="","",IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0)))))</f>
         <v/>
@@ -25059,7 +25683,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M15" s="38" t="n"/>
+      <c r="M15" s="38" t="n">
+        <v>0.705</v>
+      </c>
       <c r="N15" s="16">
         <f>IF($H15="","",IF($M15="","",IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0)))))</f>
         <v/>
@@ -25124,7 +25750,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M16" s="40" t="n"/>
+      <c r="M16" s="40" t="n">
+        <v>4.329</v>
+      </c>
       <c r="N16" s="16">
         <f>IF($H16="","",IF($M16="","",IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0)))))</f>
         <v/>
@@ -25189,7 +25817,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="38" t="n"/>
+      <c r="M17" s="38" t="n">
+        <v>1</v>
+      </c>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -25319,7 +25949,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="38" t="n"/>
+      <c r="M19" s="38" t="n">
+        <v>0.879</v>
+      </c>
       <c r="N19" s="16">
         <f>IF($H19="","",IF($M19="","",IF($H19=0,IF($M19&lt;=0,1,0),IF($E19="↓",IFERROR($H19/$M19,0),IFERROR($M19/$H19,0)))))</f>
         <v/>
@@ -25384,7 +26016,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M20" s="40" t="n"/>
+      <c r="M20" s="40" t="n">
+        <v>78.8</v>
+      </c>
       <c r="N20" s="16">
         <f>IF($H20="","",IF($M20="","",IF($H20=0,IF($M20&lt;=0,1,0),IF($E20="↓",IFERROR($H20/$M20,0),IFERROR($M20/$H20,0)))))</f>
         <v/>
@@ -25449,7 +26083,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M21" s="38" t="n"/>
+      <c r="M21" s="38" t="n">
+        <v>1.034</v>
+      </c>
       <c r="N21" s="16">
         <f>IF($H21="","",IF($M21="","",IF($H21=0,IF($M21&lt;=0,1,0),IF($E21="↓",IFERROR($H21/$M21,0),IFERROR($M21/$H21,0)))))</f>
         <v/>
@@ -25514,7 +26150,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M22" s="38" t="n"/>
+      <c r="M22" s="38" t="n">
+        <v>0.911</v>
+      </c>
       <c r="N22" s="16">
         <f>IF($H22="","",IF($M22="","",IF($H22=0,IF($M22&lt;=0,1,0),IF($E22="↓",IFERROR($H22/$M22,0),IFERROR($M22/$H22,0)))))</f>
         <v/>
@@ -25579,7 +26217,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M23" s="40" t="n"/>
+      <c r="M23" s="40" t="n">
+        <v>26.2</v>
+      </c>
       <c r="N23" s="16">
         <f>IF($H23="","",IF($M23="","",IF($H23=0,IF($M23&lt;=0,1,0),IF($E23="↓",IFERROR($H23/$M23,0),IFERROR($M23/$H23,0)))))</f>
         <v/>
@@ -25644,7 +26284,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M24" s="38" t="n"/>
+      <c r="M24" s="38" t="n">
+        <v>0.674</v>
+      </c>
       <c r="N24" s="16">
         <f>IF($H24="","",IF($M24="","",IF($H24=0,IF($M24&lt;=0,1,0),IF($E24="↓",IFERROR($H24/$M24,0),IFERROR($M24/$H24,0)))))</f>
         <v/>
@@ -25709,7 +26351,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M25" s="38" t="n"/>
+      <c r="M25" s="38" t="n">
+        <v>0.299</v>
+      </c>
       <c r="N25" s="16">
         <f>IF($H25="","",IF($M25="","",IF($H25=0,IF($M25&lt;=0,1,0),IF($E25="↓",IFERROR($H25/$M25,0),IFERROR($M25/$H25,0)))))</f>
         <v/>
@@ -25774,7 +26418,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M26" s="38" t="n"/>
+      <c r="M26" s="38" t="n">
+        <v>0.44</v>
+      </c>
       <c r="N26" s="16">
         <f>IF($H26="","",IF($M26="","",IF($H26=0,IF($M26&lt;=0,1,0),IF($E26="↓",IFERROR($H26/$M26,0),IFERROR($M26/$H26,0)))))</f>
         <v/>
@@ -25839,7 +26485,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M27" s="38" t="n"/>
+      <c r="M27" s="38" t="n">
+        <v>1.028</v>
+      </c>
       <c r="N27" s="16">
         <f>IF($H27="","",IF($M27="","",IF($H27=0,IF($M27&lt;=0,1,0),IF($E27="↓",IFERROR($H27/$M27,0),IFERROR($M27/$H27,0)))))</f>
         <v/>
@@ -25904,7 +26552,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M28" s="38" t="n"/>
+      <c r="M28" s="38" t="n">
+        <v>0.415</v>
+      </c>
       <c r="N28" s="16">
         <f>IF($H28="","",IF($M28="","",IF($H28=0,IF($M28&lt;=0,1,0),IF($E28="↓",IFERROR($H28/$M28,0),IFERROR($M28/$H28,0)))))</f>
         <v/>
@@ -25969,7 +26619,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M29" s="38" t="n"/>
+      <c r="M29" s="38" t="n">
+        <v>0.516</v>
+      </c>
       <c r="N29" s="16">
         <f>IF($H29="","",IF($M29="","",IF($H29=0,IF($M29&lt;=0,1,0),IF($E29="↓",IFERROR($H29/$M29,0),IFERROR($M29/$H29,0)))))</f>
         <v/>
@@ -26034,7 +26686,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M30" s="38" t="n"/>
+      <c r="M30" s="38" t="n">
+        <v>0.236</v>
+      </c>
       <c r="N30" s="16">
         <f>IF($H30="","",IF($M30="","",IF($H30=0,IF($M30&lt;=0,1,0),IF($E30="↓",IFERROR($H30/$M30,0),IFERROR($M30/$H30,0)))))</f>
         <v/>
@@ -26099,7 +26753,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M31" s="40" t="n"/>
+      <c r="M31" s="40" t="n">
+        <v>3.474</v>
+      </c>
       <c r="N31" s="16">
         <f>IF($H31="","",IF($M31="","",IF($H31=0,IF($M31&lt;=0,1,0),IF($E31="↓",IFERROR($H31/$M31,0),IFERROR($M31/$H31,0)))))</f>
         <v/>
@@ -26164,7 +26820,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M32" s="38" t="n"/>
+      <c r="M32" s="38" t="n">
+        <v>0.837</v>
+      </c>
       <c r="N32" s="16">
         <f>IF($H32="","",IF($M32="","",IF($H32=0,IF($M32&lt;=0,1,0),IF($E32="↓",IFERROR($H32/$M32,0),IFERROR($M32/$H32,0)))))</f>
         <v/>
@@ -26229,7 +26887,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M33" s="38" t="n"/>
+      <c r="M33" s="38" t="n">
+        <v>0.922</v>
+      </c>
       <c r="N33" s="16">
         <f>IF($H33="","",IF($M33="","",IF($H33=0,IF($M33&lt;=0,1,0),IF($E33="↓",IFERROR($H33/$M33,0),IFERROR($M33/$H33,0)))))</f>
         <v/>
@@ -26357,7 +27017,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M35" s="38" t="n"/>
+      <c r="M35" s="38" t="n">
+        <v>0.853</v>
+      </c>
       <c r="N35" s="16">
         <f>IF($H35="","",IF($M35="","",IF($H35=0,IF($M35&lt;=0,1,0),IF($E35="↓",IFERROR($H35/$M35,0),IFERROR($M35/$H35,0)))))</f>
         <v/>
@@ -26422,7 +27084,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M36" s="38" t="n"/>
+      <c r="M36" s="38" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="N36" s="16">
         <f>IF($H36="","",IF($M36="","",IF($H36=0,IF($M36&lt;=0,1,0),IF($E36="↓",IFERROR($H36/$M36,0),IFERROR($M36/$H36,0)))))</f>
         <v/>
@@ -26487,7 +27151,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M37" s="38" t="n"/>
+      <c r="M37" s="38" t="n">
+        <v>0.751</v>
+      </c>
       <c r="N37" s="16">
         <f>IF($H37="","",IF($M37="","",IF($H37=0,IF($M37&lt;=0,1,0),IF($E37="↓",IFERROR($H37/$M37,0),IFERROR($M37/$H37,0)))))</f>
         <v/>
@@ -26552,7 +27218,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M38" s="40" t="n"/>
+      <c r="M38" s="40" t="n">
+        <v>0.899</v>
+      </c>
       <c r="N38" s="16">
         <f>IF($H38="","",IF($M38="","",IF($H38=0,IF($M38&lt;=0,1,0),IF($E38="↓",IFERROR($H38/$M38,0),IFERROR($M38/$H38,0)))))</f>
         <v/>
@@ -26617,7 +27285,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M39" s="38" t="n"/>
+      <c r="M39" s="38" t="n">
+        <v>0.961</v>
+      </c>
       <c r="N39" s="16">
         <f>IF($H39="","",IF($M39="","",IF($H39=0,IF($M39&lt;=0,1,0),IF($E39="↓",IFERROR($H39/$M39,0),IFERROR($M39/$H39,0)))))</f>
         <v/>
@@ -26678,7 +27348,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -26814,7 +27484,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="36" t="n"/>
+      <c r="M4" s="36" t="n">
+        <v>78.5</v>
+      </c>
       <c r="N4" s="16">
         <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
         <v/>
@@ -27131,7 +27803,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="38" t="n"/>
+      <c r="M9" s="38" t="n">
+        <v>0.831</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -27196,7 +27870,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="38" t="n"/>
+      <c r="M10" s="38" t="n">
+        <v>0.953</v>
+      </c>
       <c r="N10" s="16">
         <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
         <v/>
@@ -27324,7 +28000,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="38" t="n"/>
+      <c r="M12" s="38" t="n">
+        <v>0.758</v>
+      </c>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -27452,7 +28130,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="40" t="n"/>
+      <c r="M14" s="40" t="n">
+        <v>4.048</v>
+      </c>
       <c r="N14" s="16">
         <f>IF($H14="","",IF($M14="","",IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0)))))</f>
         <v/>
@@ -27517,7 +28197,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="40" t="n"/>
+      <c r="M15" s="40" t="n">
+        <v>3.352</v>
+      </c>
       <c r="N15" s="16">
         <f>IF($H15="","",IF($M15="","",IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0)))))</f>
         <v/>
@@ -27582,7 +28264,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="38" t="n"/>
+      <c r="M16" s="38" t="n">
+        <v>0.831</v>
+      </c>
       <c r="N16" s="16">
         <f>IF($H16="","",IF($M16="","",IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0)))))</f>
         <v/>
@@ -27647,7 +28331,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="38" t="n"/>
+      <c r="M17" s="38" t="n">
+        <v>0.787</v>
+      </c>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -27712,7 +28398,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="38" t="n"/>
+      <c r="M18" s="38" t="n">
+        <v>0.837</v>
+      </c>
       <c r="N18" s="16">
         <f>IF($H18="","",IF($M18="","",IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0)))))</f>
         <v/>
@@ -27777,7 +28465,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="38" t="n"/>
+      <c r="M19" s="38" t="n">
+        <v>0.747</v>
+      </c>
       <c r="N19" s="16">
         <f>IF($H19="","",IF($M19="","",IF($H19=0,IF($M19&lt;=0,1,0),IF($E19="↓",IFERROR($H19/$M19,0),IFERROR($M19/$H19,0)))))</f>
         <v/>
@@ -27838,7 +28528,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -27974,7 +28664,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="36" t="n"/>
+      <c r="M4" s="36" t="n">
+        <v>165.7</v>
+      </c>
       <c r="N4" s="16">
         <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
         <v/>
@@ -28039,7 +28731,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="36" t="n"/>
+      <c r="M5" s="36" t="n">
+        <v>76.3</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -28104,7 +28798,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="36" t="n"/>
+      <c r="M6" s="36" t="n">
+        <v>82.2</v>
+      </c>
       <c r="N6" s="16">
         <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
         <v/>
@@ -28169,7 +28865,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="36" t="n"/>
+      <c r="M7" s="36" t="n">
+        <v>125.8</v>
+      </c>
       <c r="N7" s="16">
         <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
         <v/>
@@ -28234,7 +28932,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="36" t="n"/>
+      <c r="M8" s="36" t="n">
+        <v>8.1</v>
+      </c>
       <c r="N8" s="16">
         <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
         <v/>
@@ -28299,7 +28999,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="36" t="n"/>
+      <c r="M9" s="36" t="n">
+        <v>12.2</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -28364,7 +29066,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="36" t="n"/>
+      <c r="M10" s="36" t="n">
+        <v>49.4</v>
+      </c>
       <c r="N10" s="16">
         <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
         <v/>
@@ -28429,7 +29133,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M11" s="38" t="n"/>
+      <c r="M11" s="38" t="n">
+        <v>0.649</v>
+      </c>
       <c r="N11" s="16">
         <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
         <v/>
@@ -28494,7 +29200,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M12" s="40" t="n"/>
+      <c r="M12" s="40" t="n">
+        <v>4.983</v>
+      </c>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -28622,7 +29330,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="38" t="n"/>
+      <c r="M14" s="38" t="n">
+        <v>1.028</v>
+      </c>
       <c r="N14" s="16">
         <f>IF($H14="","",IF($M14="","",IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0)))))</f>
         <v/>
@@ -28687,7 +29397,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="38" t="n"/>
+      <c r="M15" s="38" t="n">
+        <v>0.516</v>
+      </c>
       <c r="N15" s="16">
         <f>IF($H15="","",IF($M15="","",IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0)))))</f>
         <v/>
@@ -28752,7 +29464,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="38" t="n"/>
+      <c r="M16" s="38" t="n">
+        <v>0.415</v>
+      </c>
       <c r="N16" s="16">
         <f>IF($H16="","",IF($M16="","",IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0)))))</f>
         <v/>
@@ -28817,7 +29531,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="38" t="n"/>
+      <c r="M17" s="38" t="n">
+        <v>0.236</v>
+      </c>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -28882,7 +29598,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="40" t="n"/>
+      <c r="M18" s="40" t="n">
+        <v>0.912</v>
+      </c>
       <c r="N18" s="16">
         <f>IF($H18="","",IF($M18="","",IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0)))))</f>
         <v/>
@@ -28947,7 +29665,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="38" t="n"/>
+      <c r="M19" s="38" t="n">
+        <v>0.308</v>
+      </c>
       <c r="N19" s="16">
         <f>IF($H19="","",IF($M19="","",IF($H19=0,IF($M19&lt;=0,1,0),IF($E19="↓",IFERROR($H19/$M19,0),IFERROR($M19/$H19,0)))))</f>
         <v/>
@@ -29012,7 +29732,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M20" s="38" t="n"/>
+      <c r="M20" s="38" t="n">
+        <v>0.221</v>
+      </c>
       <c r="N20" s="16">
         <f>IF($H20="","",IF($M20="","",IF($H20=0,IF($M20&lt;=0,1,0),IF($E20="↓",IFERROR($H20/$M20,0),IFERROR($M20/$H20,0)))))</f>
         <v/>
@@ -29077,7 +29799,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M21" s="38" t="n"/>
+      <c r="M21" s="38" t="n">
+        <v>0.751</v>
+      </c>
       <c r="N21" s="16">
         <f>IF($H21="","",IF($M21="","",IF($H21=0,IF($M21&lt;=0,1,0),IF($E21="↓",IFERROR($H21/$M21,0),IFERROR($M21/$H21,0)))))</f>
         <v/>
@@ -29142,7 +29866,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M22" s="38" t="n"/>
+      <c r="M22" s="38" t="n">
+        <v>0.736</v>
+      </c>
       <c r="N22" s="16">
         <f>IF($H22="","",IF($M22="","",IF($H22=0,IF($M22&lt;=0,1,0),IF($E22="↓",IFERROR($H22/$M22,0),IFERROR($M22/$H22,0)))))</f>
         <v/>
@@ -29207,7 +29933,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M23" s="38" t="n"/>
+      <c r="M23" s="38" t="n">
+        <v>1.009</v>
+      </c>
       <c r="N23" s="16">
         <f>IF($H23="","",IF($M23="","",IF($H23=0,IF($M23&lt;=0,1,0),IF($E23="↓",IFERROR($H23/$M23,0),IFERROR($M23/$H23,0)))))</f>
         <v/>
@@ -29272,7 +30000,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M24" s="40" t="n"/>
+      <c r="M24" s="40" t="n">
+        <v>1.061</v>
+      </c>
       <c r="N24" s="16">
         <f>IF($H24="","",IF($M24="","",IF($H24=0,IF($M24&lt;=0,1,0),IF($E24="↓",IFERROR($H24/$M24,0),IFERROR($M24/$H24,0)))))</f>
         <v/>
@@ -29337,7 +30067,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M25" s="38" t="n"/>
+      <c r="M25" s="38" t="n">
+        <v>0.786</v>
+      </c>
       <c r="N25" s="16">
         <f>IF($H25="","",IF($M25="","",IF($H25=0,IF($M25&lt;=0,1,0),IF($E25="↓",IFERROR($H25/$M25,0),IFERROR($M25/$H25,0)))))</f>
         <v/>
@@ -29402,7 +30134,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M26" s="38" t="n"/>
+      <c r="M26" s="38" t="n">
+        <v>0.972</v>
+      </c>
       <c r="N26" s="16">
         <f>IF($H26="","",IF($M26="","",IF($H26=0,IF($M26&lt;=0,1,0),IF($E26="↓",IFERROR($H26/$M26,0),IFERROR($M26/$H26,0)))))</f>
         <v/>
@@ -29467,7 +30201,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M27" s="38" t="n"/>
+      <c r="M27" s="38" t="n">
+        <v>0.961</v>
+      </c>
       <c r="N27" s="16">
         <f>IF($H27="","",IF($M27="","",IF($H27=0,IF($M27&lt;=0,1,0),IF($E27="↓",IFERROR($H27/$M27,0),IFERROR($M27/$H27,0)))))</f>
         <v/>
@@ -29528,7 +30264,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -29664,7 +30400,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M4" s="38" t="n"/>
+      <c r="M4" s="38" t="n">
+        <v>0.068</v>
+      </c>
       <c r="N4" s="16">
         <f>IF($H4="","",IF($M4="","",IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0)))))</f>
         <v/>
@@ -29729,7 +30467,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="38" t="n"/>
+      <c r="M5" s="38" t="n">
+        <v>1.03</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -29794,7 +30534,9 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M6" s="38" t="n"/>
+      <c r="M6" s="38" t="n">
+        <v>0.716</v>
+      </c>
       <c r="N6" s="16">
         <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
         <v/>
@@ -29859,7 +30601,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="38" t="n"/>
+      <c r="M7" s="38" t="n">
+        <v>0.611</v>
+      </c>
       <c r="N7" s="16">
         <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
         <v/>
@@ -29924,7 +30668,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="36" t="n"/>
+      <c r="M8" s="36" t="n">
+        <v>54.8</v>
+      </c>
       <c r="N8" s="16">
         <f>IF($H8="","",IF($M8="","",IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0)))))</f>
         <v/>
@@ -29989,7 +30735,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M9" s="36" t="n"/>
+      <c r="M9" s="36" t="n">
+        <v>531.8</v>
+      </c>
       <c r="N9" s="16">
         <f>IF($H9="","",IF($M9="","",IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0)))))</f>
         <v/>
@@ -30054,7 +30802,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="38" t="n"/>
+      <c r="M10" s="38" t="n">
+        <v>0.208</v>
+      </c>
       <c r="N10" s="16">
         <f>IF($H10="","",IF($M10="","",IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0)))))</f>
         <v/>
@@ -30119,7 +30869,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M11" s="36" t="n"/>
+      <c r="M11" s="36" t="n">
+        <v>202.6</v>
+      </c>
       <c r="N11" s="16">
         <f>IF($H11="","",IF($M11="","",IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0)))))</f>
         <v/>
@@ -30184,7 +30936,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="38" t="n"/>
+      <c r="M12" s="38" t="n">
+        <v>0.671</v>
+      </c>
       <c r="N12" s="16">
         <f>IF($H12="","",IF($M12="","",IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0)))))</f>
         <v/>
@@ -30249,7 +31003,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M13" s="36" t="n"/>
+      <c r="M13" s="36" t="n">
+        <v>5.769</v>
+      </c>
       <c r="N13" s="16">
         <f>IF($H13="","",IF($M13="","",IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0)))))</f>
         <v/>
@@ -30314,7 +31070,9 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M14" s="36" t="n"/>
+      <c r="M14" s="36" t="n">
+        <v>4.59</v>
+      </c>
       <c r="N14" s="16">
         <f>IF($H14="","",IF($M14="","",IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0)))))</f>
         <v/>
@@ -30379,7 +31137,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="38" t="n"/>
+      <c r="M15" s="38" t="n">
+        <v>0.792</v>
+      </c>
       <c r="N15" s="16">
         <f>IF($H15="","",IF($M15="","",IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0)))))</f>
         <v/>
@@ -30444,7 +31204,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="40" t="n"/>
+      <c r="M16" s="40" t="n">
+        <v>7.983</v>
+      </c>
       <c r="N16" s="16">
         <f>IF($H16="","",IF($M16="","",IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0)))))</f>
         <v/>
@@ -30509,7 +31271,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="38" t="n"/>
+      <c r="M17" s="38" t="n">
+        <v>0.698</v>
+      </c>
       <c r="N17" s="16">
         <f>IF($H17="","",IF($M17="","",IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0)))))</f>
         <v/>
@@ -30574,7 +31338,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M18" s="38" t="n"/>
+      <c r="M18" s="38" t="n">
+        <v>0.695</v>
+      </c>
       <c r="N18" s="16">
         <f>IF($H18="","",IF($M18="","",IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0)))))</f>
         <v/>
@@ -30639,7 +31405,9 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M19" s="38" t="n"/>
+      <c r="M19" s="38" t="n">
+        <v>0.894</v>
+      </c>
       <c r="N19" s="16">
         <f>IF($H19="","",IF($M19="","",IF($H19=0,IF($M19&lt;=0,1,0),IF($E19="↓",IFERROR($H19/$M19,0),IFERROR($M19/$H19,0)))))</f>
         <v/>
@@ -30700,7 +31468,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>🟩 أدخل «المُحقَّق» · نسبة التحقيق والحالة دلّات حقيقية تُحسب تلقائياً</t>
+          <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
       </c>
     </row>
@@ -30903,7 +31671,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="38" t="n"/>
+      <c r="M5" s="38" t="n">
+        <v>0.83</v>
+      </c>
       <c r="N5" s="16">
         <f>IF($H5="","",IF($M5="","",IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0)))))</f>
         <v/>
@@ -30968,7 +31738,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="38" t="n"/>
+      <c r="M6" s="38" t="n">
+        <v>0.753</v>
+      </c>
       <c r="N6" s="16">
         <f>IF($H6="","",IF($M6="","",IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0)))))</f>
         <v/>
@@ -31033,7 +31805,9 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="38" t="n"/>
+      <c r="M7" s="38" t="n">
+        <v>0.703</v>
+      </c>
       <c r="N7" s="16">
         <f>IF($H7="","",IF($M7="","",IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0)))))</f>
         <v/>

--- a/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
+++ b/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
@@ -36,7 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'سجل المخاطر'!$A$2:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ESG والاستدامة'!$A$2:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'بطاقة تعريف المؤشرات'!$A$2:$N$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'بيانات الباوربي'!$A$1:$Z$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'بيانات الباوربي'!$A$1:$AC$184</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'الإدارة التنفيذية'!$A$3:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'الامتياز التجاري'!$A$3:$O$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'التشغيل والمحطات'!$A$3:$O$19</definedName>
@@ -59,7 +59,7 @@
     <numFmt numFmtId="164" formatCode="#,##0 &quot;ر.س&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -198,7 +198,27 @@
     </font>
     <font>
       <name val="Tajawal"/>
+      <color rgb="00F2C94C"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tajawal"/>
+      <color rgb="00BDBDBD"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tajawal"/>
+      <color rgb="002EAD6B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tajawal"/>
       <color rgb="00C00000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tajawal"/>
+      <color rgb="00EB5757"/>
       <sz val="8"/>
     </font>
     <font>
@@ -361,9 +381,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -392,19 +412,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -449,28 +469,28 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -507,10 +527,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -529,7 +549,19 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1298,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z184"/>
+  <dimension ref="A1:AC184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1327,6 +1359,9 @@
     <col width="9" customWidth="1" min="24" max="24"/>
     <col width="40" customWidth="1" min="25" max="25"/>
     <col width="42" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1460,6 +1495,21 @@
           <t>الإجراء التصحيحي</t>
         </is>
       </c>
+      <c r="AA1" s="55" t="inlineStr">
+        <is>
+          <t>الحالة (نص)</t>
+        </is>
+      </c>
+      <c r="AB1" s="55" t="inlineStr">
+        <is>
+          <t>ترتيب الحالة</t>
+        </is>
+      </c>
+      <c r="AC1" s="55" t="inlineStr">
+        <is>
+          <t>لون الحالة</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -1572,6 +1622,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA2" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB2" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -1682,6 +1745,19 @@
       <c r="Z3" s="53" t="inlineStr">
         <is>
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
+        </is>
+      </c>
+      <c r="AA3" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
         </is>
       </c>
     </row>
@@ -1774,6 +1850,19 @@
       </c>
       <c r="Y4" s="56" t="inlineStr"/>
       <c r="Z4" s="53" t="inlineStr"/>
+      <c r="AA4" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB4" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1864,6 +1953,19 @@
       </c>
       <c r="Y5" s="56" t="inlineStr"/>
       <c r="Z5" s="53" t="inlineStr"/>
+      <c r="AA5" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB5" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -1976,6 +2078,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA6" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB6" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -2080,6 +2195,19 @@
       </c>
       <c r="Y7" s="56" t="inlineStr"/>
       <c r="Z7" s="53" t="inlineStr"/>
+      <c r="AA7" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -2184,6 +2312,19 @@
       </c>
       <c r="Y8" s="56" t="inlineStr"/>
       <c r="Z8" s="53" t="inlineStr"/>
+      <c r="AA8" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB8" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -2296,6 +2437,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA9" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB9" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -2408,6 +2562,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA10" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -2510,7 +2677,7 @@
       <c r="X11" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y11" s="57" t="inlineStr">
+      <c r="Y11" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 25٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -2518,6 +2685,19 @@
       <c r="Z11" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف الرئيس التنفيذي.</t>
+        </is>
+      </c>
+      <c r="AA11" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB11" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC11" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2802,7 @@
       <c r="X12" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y12" s="57" t="inlineStr">
+      <c r="Y12" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 27٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -2630,6 +2810,19 @@
       <c r="Z12" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA12" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB12" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -2744,6 +2937,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA13" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB13" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -2846,7 +3052,7 @@
       <c r="X14" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y14" s="57" t="inlineStr">
+      <c r="Y14" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 20٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -2854,6 +3060,19 @@
       <c r="Z14" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA14" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB14" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -2966,6 +3185,19 @@
       <c r="Z15" s="53" t="inlineStr">
         <is>
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
+        </is>
+      </c>
+      <c r="AA15" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB15" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
         </is>
       </c>
     </row>
@@ -3058,6 +3290,19 @@
       </c>
       <c r="Y16" s="56" t="inlineStr"/>
       <c r="Z16" s="53" t="inlineStr"/>
+      <c r="AA16" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB16" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC16" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -3162,6 +3407,19 @@
       </c>
       <c r="Y17" s="56" t="inlineStr"/>
       <c r="Z17" s="53" t="inlineStr"/>
+      <c r="AA17" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -3252,6 +3510,19 @@
       </c>
       <c r="Y18" s="56" t="inlineStr"/>
       <c r="Z18" s="53" t="inlineStr"/>
+      <c r="AA18" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB18" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -3364,6 +3635,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA19" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC19" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -3476,6 +3760,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA20" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC20" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -3580,6 +3877,19 @@
       </c>
       <c r="Y21" s="56" t="inlineStr"/>
       <c r="Z21" s="53" t="inlineStr"/>
+      <c r="AA21" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -3670,6 +3980,19 @@
       </c>
       <c r="Y22" s="56" t="inlineStr"/>
       <c r="Z22" s="53" t="inlineStr"/>
+      <c r="AA22" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB22" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC22" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -3772,7 +4095,7 @@
       <c r="X23" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y23" s="57" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 22٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -3780,6 +4103,19 @@
       <c r="Z23" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA23" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB23" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -3886,6 +4222,19 @@
       </c>
       <c r="Y24" s="56" t="inlineStr"/>
       <c r="Z24" s="53" t="inlineStr"/>
+      <c r="AA24" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -3990,6 +4339,19 @@
       </c>
       <c r="Y25" s="56" t="inlineStr"/>
       <c r="Z25" s="53" t="inlineStr"/>
+      <c r="AA25" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -4082,6 +4444,19 @@
       </c>
       <c r="Y26" s="56" t="inlineStr"/>
       <c r="Z26" s="53" t="inlineStr"/>
+      <c r="AA26" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB26" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC26" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -4194,6 +4569,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA27" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB27" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC27" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -4306,6 +4694,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA28" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB28" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -4410,6 +4811,19 @@
       </c>
       <c r="Y29" s="56" t="inlineStr"/>
       <c r="Z29" s="53" t="inlineStr"/>
+      <c r="AA29" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -4512,7 +4926,7 @@
       <c r="X30" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y30" s="57" t="inlineStr">
+      <c r="Y30" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 9٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -4520,6 +4934,19 @@
       <c r="Z30" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA30" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB30" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC30" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -4634,6 +5061,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA31" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB31" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC31" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -4736,7 +5176,7 @@
       <c r="X32" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y32" s="57" t="inlineStr">
+      <c r="Y32" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 25٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -4744,6 +5184,19 @@
       <c r="Z32" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA32" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB32" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -4858,6 +5311,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA33" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB33" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC33" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -4960,7 +5426,7 @@
       <c r="X34" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y34" s="57" t="inlineStr">
+      <c r="Y34" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 20٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -4968,6 +5434,19 @@
       <c r="Z34" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA34" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB34" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC34" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5551,7 @@
       <c r="X35" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y35" s="57" t="inlineStr">
+      <c r="Y35" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 26٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -5080,6 +5559,19 @@
       <c r="Z35" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA35" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB35" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -5186,6 +5678,19 @@
       </c>
       <c r="Y36" s="56" t="inlineStr"/>
       <c r="Z36" s="53" t="inlineStr"/>
+      <c r="AA36" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB36" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -5296,6 +5801,19 @@
       <c r="Z37" s="53" t="inlineStr">
         <is>
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
+        </is>
+      </c>
+      <c r="AA37" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB37" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC37" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
         </is>
       </c>
     </row>
@@ -5388,6 +5906,19 @@
       </c>
       <c r="Y38" s="56" t="inlineStr"/>
       <c r="Z38" s="53" t="inlineStr"/>
+      <c r="AA38" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB38" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC38" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -5500,6 +6031,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA39" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB39" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC39" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
@@ -5602,7 +6146,7 @@
       <c r="X40" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y40" s="57" t="inlineStr">
+      <c r="Y40" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 19٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -5610,6 +6154,19 @@
       <c r="Z40" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الامتياز.</t>
+        </is>
+      </c>
+      <c r="AA40" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB40" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC40" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -5716,6 +6273,19 @@
       </c>
       <c r="Y41" s="56" t="inlineStr"/>
       <c r="Z41" s="53" t="inlineStr"/>
+      <c r="AA41" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB41" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -5826,6 +6396,19 @@
       <c r="Z42" s="53" t="inlineStr">
         <is>
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
+        </is>
+      </c>
+      <c r="AA42" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB42" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC42" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
         </is>
       </c>
     </row>
@@ -5918,6 +6501,19 @@
       </c>
       <c r="Y43" s="56" t="inlineStr"/>
       <c r="Z43" s="53" t="inlineStr"/>
+      <c r="AA43" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB43" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC43" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
@@ -6008,6 +6604,19 @@
       </c>
       <c r="Y44" s="56" t="inlineStr"/>
       <c r="Z44" s="53" t="inlineStr"/>
+      <c r="AA44" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB44" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC44" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -6098,6 +6707,19 @@
       </c>
       <c r="Y45" s="56" t="inlineStr"/>
       <c r="Z45" s="53" t="inlineStr"/>
+      <c r="AA45" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB45" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC45" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
@@ -6188,6 +6810,19 @@
       </c>
       <c r="Y46" s="56" t="inlineStr"/>
       <c r="Z46" s="53" t="inlineStr"/>
+      <c r="AA46" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB46" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC46" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -6290,7 +6925,7 @@
       <c r="X47" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y47" s="57" t="inlineStr">
+      <c r="Y47" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -6298,6 +6933,19 @@
       <c r="Z47" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التشغيل.</t>
+        </is>
+      </c>
+      <c r="AA47" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB47" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC47" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -6410,6 +7058,19 @@
       <c r="Z48" s="53" t="inlineStr">
         <is>
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
+        </is>
+      </c>
+      <c r="AA48" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB48" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC48" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
         </is>
       </c>
     </row>
@@ -6502,6 +7163,19 @@
       </c>
       <c r="Y49" s="56" t="inlineStr"/>
       <c r="Z49" s="53" t="inlineStr"/>
+      <c r="AA49" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB49" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC49" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -6604,7 +7278,7 @@
       <c r="X50" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y50" s="57" t="inlineStr">
+      <c r="Y50" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 20٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -6612,6 +7286,19 @@
       <c r="Z50" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التشغيل.</t>
+        </is>
+      </c>
+      <c r="AA50" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB50" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC50" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -6704,6 +7391,19 @@
       </c>
       <c r="Y51" s="56" t="inlineStr"/>
       <c r="Z51" s="53" t="inlineStr"/>
+      <c r="AA51" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB51" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC51" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
@@ -6816,6 +7516,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA52" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB52" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC52" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -6928,6 +7641,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA53" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB53" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC53" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
@@ -7030,7 +7756,7 @@
       <c r="X54" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y54" s="57" t="inlineStr">
+      <c r="Y54" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -7038,6 +7764,19 @@
       <c r="Z54" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التشغيل.</t>
+        </is>
+      </c>
+      <c r="AA54" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB54" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -7152,6 +7891,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA55" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB55" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC55" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
@@ -7254,7 +8006,7 @@
       <c r="X56" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y56" s="57" t="inlineStr">
+      <c r="Y56" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -7262,6 +8014,19 @@
       <c r="Z56" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التشغيل.</t>
+        </is>
+      </c>
+      <c r="AA56" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB56" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC56" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -7366,7 +8131,7 @@
       <c r="X57" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y57" s="57" t="inlineStr">
+      <c r="Y57" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 25٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -7374,6 +8139,19 @@
       <c r="Z57" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التشغيل.</t>
+        </is>
+      </c>
+      <c r="AA57" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB57" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -7488,6 +8266,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA58" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB58" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC58" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -7590,7 +8381,7 @@
       <c r="X59" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y59" s="57" t="inlineStr">
+      <c r="Y59" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 15٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -7598,6 +8389,19 @@
       <c r="Z59" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA59" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB59" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -7702,7 +8506,7 @@
       <c r="X60" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y60" s="57" t="inlineStr">
+      <c r="Y60" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 18٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -7710,6 +8514,19 @@
       <c r="Z60" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA60" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB60" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -7816,6 +8633,19 @@
       </c>
       <c r="Y61" s="56" t="inlineStr"/>
       <c r="Z61" s="53" t="inlineStr"/>
+      <c r="AA61" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB61" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -7918,7 +8748,7 @@
       <c r="X62" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y62" s="57" t="inlineStr">
+      <c r="Y62" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 26٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -7926,6 +8756,19 @@
       <c r="Z62" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA62" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB62" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -8032,6 +8875,19 @@
       </c>
       <c r="Y63" s="56" t="inlineStr"/>
       <c r="Z63" s="53" t="inlineStr"/>
+      <c r="AA63" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB63" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
@@ -8134,7 +8990,7 @@
       <c r="X64" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y64" s="57" t="inlineStr">
+      <c r="Y64" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 27٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -8142,6 +8998,19 @@
       <c r="Z64" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA64" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB64" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC64" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -8246,7 +9115,7 @@
       <c r="X65" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y65" s="57" t="inlineStr">
+      <c r="Y65" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 19٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -8254,6 +9123,19 @@
       <c r="Z65" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA65" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB65" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC65" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -8360,6 +9242,19 @@
       </c>
       <c r="Y66" s="56" t="inlineStr"/>
       <c r="Z66" s="53" t="inlineStr"/>
+      <c r="AA66" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB66" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
@@ -8450,6 +9345,19 @@
       </c>
       <c r="Y67" s="56" t="inlineStr"/>
       <c r="Z67" s="53" t="inlineStr"/>
+      <c r="AA67" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB67" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC67" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
@@ -8554,6 +9462,19 @@
       </c>
       <c r="Y68" s="56" t="inlineStr"/>
       <c r="Z68" s="53" t="inlineStr"/>
+      <c r="AA68" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB68" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC68" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
@@ -8666,6 +9587,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA69" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB69" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC69" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
@@ -8778,6 +9712,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA70" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB70" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC70" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
@@ -8890,6 +9837,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA71" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB71" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC71" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
@@ -8994,6 +9954,19 @@
       </c>
       <c r="Y72" s="56" t="inlineStr"/>
       <c r="Z72" s="53" t="inlineStr"/>
+      <c r="AA72" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB72" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC72" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
@@ -9098,6 +10071,19 @@
       </c>
       <c r="Y73" s="56" t="inlineStr"/>
       <c r="Z73" s="53" t="inlineStr"/>
+      <c r="AA73" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB73" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC73" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -9200,7 +10186,7 @@
       <c r="X74" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y74" s="57" t="inlineStr">
+      <c r="Y74" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 26٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -9208,6 +10194,19 @@
       <c r="Z74" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA74" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB74" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC74" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -9312,7 +10311,7 @@
       <c r="X75" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y75" s="57" t="inlineStr">
+      <c r="Y75" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 25٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -9320,6 +10319,19 @@
       <c r="Z75" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA75" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB75" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC75" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -9424,7 +10436,7 @@
       <c r="X76" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y76" s="57" t="inlineStr">
+      <c r="Y76" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 23٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -9432,6 +10444,19 @@
       <c r="Z76" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الاستثمار.</t>
+        </is>
+      </c>
+      <c r="AA76" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB76" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -9538,6 +10563,19 @@
       </c>
       <c r="Y77" s="56" t="inlineStr"/>
       <c r="Z77" s="53" t="inlineStr"/>
+      <c r="AA77" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB77" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC77" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
@@ -9650,6 +10688,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA78" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB78" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC78" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
@@ -9754,6 +10805,19 @@
       </c>
       <c r="Y79" s="56" t="inlineStr"/>
       <c r="Z79" s="53" t="inlineStr"/>
+      <c r="AA79" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB79" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC79" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
@@ -9866,6 +10930,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA80" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB80" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC80" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
@@ -9978,6 +11055,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA81" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB81" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC81" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
@@ -10090,6 +11180,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA82" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB82" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC82" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
@@ -10194,6 +11297,19 @@
       </c>
       <c r="Y83" s="56" t="inlineStr"/>
       <c r="Z83" s="53" t="inlineStr"/>
+      <c r="AA83" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB83" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC83" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
@@ -10296,7 +11412,7 @@
       <c r="X84" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y84" s="57" t="inlineStr">
+      <c r="Y84" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 15٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -10304,6 +11420,19 @@
       <c r="Z84" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير العقار.</t>
+        </is>
+      </c>
+      <c r="AA84" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB84" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC84" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -10410,6 +11539,19 @@
       </c>
       <c r="Y85" s="56" t="inlineStr"/>
       <c r="Z85" s="53" t="inlineStr"/>
+      <c r="AA85" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB85" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
@@ -10512,7 +11654,7 @@
       <c r="X86" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y86" s="57" t="inlineStr">
+      <c r="Y86" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 19٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -10520,6 +11662,19 @@
       <c r="Z86" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير العقار.</t>
+        </is>
+      </c>
+      <c r="AA86" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB86" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC86" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -10624,7 +11779,7 @@
       <c r="X87" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y87" s="57" t="inlineStr">
+      <c r="Y87" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 22٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -10632,6 +11787,19 @@
       <c r="Z87" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير العقار.</t>
+        </is>
+      </c>
+      <c r="AA87" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB87" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC87" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -10738,6 +11906,19 @@
       </c>
       <c r="Y88" s="56" t="inlineStr"/>
       <c r="Z88" s="53" t="inlineStr"/>
+      <c r="AA88" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB88" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
@@ -10840,7 +12021,7 @@
       <c r="X89" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y89" s="57" t="inlineStr">
+      <c r="Y89" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 18٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -10848,6 +12029,19 @@
       <c r="Z89" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير العقار.</t>
+        </is>
+      </c>
+      <c r="AA89" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB89" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC89" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -10952,7 +12146,7 @@
       <c r="X90" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y90" s="57" t="inlineStr">
+      <c r="Y90" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -10960,6 +12154,19 @@
       <c r="Z90" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير العقار.</t>
+        </is>
+      </c>
+      <c r="AA90" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB90" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC90" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -11074,6 +12281,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA91" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB91" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC91" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
@@ -11186,6 +12406,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA92" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB92" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC92" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
@@ -11288,7 +12521,7 @@
       <c r="X93" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y93" s="57" t="inlineStr">
+      <c r="Y93" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 21٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -11296,6 +12529,19 @@
       <c r="Z93" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير العقار.</t>
+        </is>
+      </c>
+      <c r="AA93" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB93" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC93" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -11410,6 +12656,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA94" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB94" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC94" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
@@ -11512,7 +12771,7 @@
       <c r="X95" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y95" s="57" t="inlineStr">
+      <c r="Y95" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 22٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -11520,6 +12779,19 @@
       <c r="Z95" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير العقار.</t>
+        </is>
+      </c>
+      <c r="AA95" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB95" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC95" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -11634,6 +12906,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA96" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB96" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC96" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
@@ -11738,6 +13023,19 @@
       </c>
       <c r="Y97" s="56" t="inlineStr"/>
       <c r="Z97" s="53" t="inlineStr"/>
+      <c r="AA97" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB97" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
@@ -11840,7 +13138,7 @@
       <c r="X98" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y98" s="57" t="inlineStr">
+      <c r="Y98" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 94٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -11848,6 +13146,19 @@
       <c r="Z98" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التقنية.</t>
+        </is>
+      </c>
+      <c r="AA98" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB98" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC98" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -11962,6 +13273,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA99" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB99" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC99" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -12064,7 +13388,7 @@
       <c r="X100" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y100" s="57" t="inlineStr">
+      <c r="Y100" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 21٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -12072,6 +13396,19 @@
       <c r="Z100" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التقنية.</t>
+        </is>
+      </c>
+      <c r="AA100" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB100" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -12176,7 +13513,7 @@
       <c r="X101" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y101" s="57" t="inlineStr">
+      <c r="Y101" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 26٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -12184,6 +13521,19 @@
       <c r="Z101" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التقنية.</t>
+        </is>
+      </c>
+      <c r="AA101" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB101" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC101" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -12288,7 +13638,7 @@
       <c r="X102" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y102" s="57" t="inlineStr">
+      <c r="Y102" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 67٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -12296,6 +13646,19 @@
       <c r="Z102" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التقنية.</t>
+        </is>
+      </c>
+      <c r="AA102" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB102" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -12400,7 +13763,7 @@
       <c r="X103" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y103" s="57" t="inlineStr">
+      <c r="Y103" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 9٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -12408,6 +13771,19 @@
       <c r="Z103" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التقنية.</t>
+        </is>
+      </c>
+      <c r="AA103" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB103" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC103" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -12512,7 +13888,7 @@
       <c r="X104" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y104" s="57" t="inlineStr">
+      <c r="Y104" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 70٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -12520,6 +13896,19 @@
       <c r="Z104" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التقنية.</t>
+        </is>
+      </c>
+      <c r="AA104" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB104" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC104" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -12626,6 +14015,19 @@
       </c>
       <c r="Y105" s="56" t="inlineStr"/>
       <c r="Z105" s="53" t="inlineStr"/>
+      <c r="AA105" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB105" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC105" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
@@ -12728,7 +14130,7 @@
       <c r="X106" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y106" s="57" t="inlineStr">
+      <c r="Y106" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 80٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -12736,6 +14138,19 @@
       <c r="Z106" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التقنية.</t>
+        </is>
+      </c>
+      <c r="AA106" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB106" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC106" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -12828,6 +14243,19 @@
       </c>
       <c r="Y107" s="56" t="inlineStr"/>
       <c r="Z107" s="53" t="inlineStr"/>
+      <c r="AA107" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB107" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC107" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
@@ -12930,7 +14358,7 @@
       <c r="X108" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y108" s="57" t="inlineStr">
+      <c r="Y108" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 28٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -12938,6 +14366,19 @@
       <c r="Z108" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA108" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB108" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC108" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -13052,6 +14493,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA109" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB109" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC109" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -13164,6 +14618,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA110" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB110" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC110" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
@@ -13276,6 +14743,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA111" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB111" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC111" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
@@ -13378,7 +14858,7 @@
       <c r="X112" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y112" s="57" t="inlineStr">
+      <c r="Y112" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 24٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -13386,6 +14866,19 @@
       <c r="Z112" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA112" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB112" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC112" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -13490,7 +14983,7 @@
       <c r="X113" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y113" s="57" t="inlineStr">
+      <c r="Y113" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -13498,6 +14991,19 @@
       <c r="Z113" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA113" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB113" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC113" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -13602,7 +15108,7 @@
       <c r="X114" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y114" s="57" t="inlineStr">
+      <c r="Y114" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 20٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -13610,6 +15116,19 @@
       <c r="Z114" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA114" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB114" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC114" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -13716,6 +15235,19 @@
       </c>
       <c r="Y115" s="56" t="inlineStr"/>
       <c r="Z115" s="53" t="inlineStr"/>
+      <c r="AA115" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB115" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC115" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
@@ -13806,6 +15338,19 @@
       </c>
       <c r="Y116" s="56" t="inlineStr"/>
       <c r="Z116" s="53" t="inlineStr"/>
+      <c r="AA116" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB116" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC116" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
@@ -13908,7 +15453,7 @@
       <c r="X117" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y117" s="57" t="inlineStr">
+      <c r="Y117" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 26٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -13916,6 +15461,19 @@
       <c r="Z117" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA117" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB117" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC117" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -14020,7 +15578,7 @@
       <c r="X118" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y118" s="57" t="inlineStr">
+      <c r="Y118" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -14028,6 +15586,19 @@
       <c r="Z118" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA118" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB118" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC118" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -14142,6 +15713,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA119" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB119" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC119" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
@@ -14244,7 +15828,7 @@
       <c r="X120" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y120" s="57" t="inlineStr">
+      <c r="Y120" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -14252,6 +15836,19 @@
       <c r="Z120" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA120" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB120" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC120" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -14366,6 +15963,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA121" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB121" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC121" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
@@ -14478,6 +16088,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA122" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB122" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC122" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
@@ -14580,7 +16203,7 @@
       <c r="X123" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y123" s="57" t="inlineStr">
+      <c r="Y123" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 19٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -14588,6 +16211,19 @@
       <c r="Z123" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الموارد البشرية.</t>
+        </is>
+      </c>
+      <c r="AA123" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB123" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC123" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -14692,7 +16328,7 @@
       <c r="X124" s="54" t="n">
         <v>0.75</v>
       </c>
-      <c r="Y124" s="57" t="inlineStr">
+      <c r="Y124" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 90٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -14700,6 +16336,19 @@
       <c r="Z124" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA124" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB124" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC124" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -14804,7 +16453,7 @@
       <c r="X125" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y125" s="57" t="inlineStr">
+      <c r="Y125" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 100٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -14812,6 +16461,19 @@
       <c r="Z125" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA125" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB125" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC125" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -14916,7 +16578,7 @@
       <c r="X126" s="54" t="n">
         <v>0.75</v>
       </c>
-      <c r="Y126" s="57" t="inlineStr">
+      <c r="Y126" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 33٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -14924,6 +16586,19 @@
       <c r="Z126" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA126" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB126" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC126" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15026,7 +16701,7 @@
       <c r="X127" s="54" t="n">
         <v>0.75</v>
       </c>
-      <c r="Y127" s="57" t="inlineStr">
+      <c r="Y127" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 100٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15034,6 +16709,19 @@
       <c r="Z127" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA127" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB127" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC127" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15138,7 +16826,7 @@
       <c r="X128" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y128" s="57" t="inlineStr">
+      <c r="Y128" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 77٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15146,6 +16834,19 @@
       <c r="Z128" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA128" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB128" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC128" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15250,7 +16951,7 @@
       <c r="X129" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y129" s="57" t="inlineStr">
+      <c r="Y129" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 32٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15258,6 +16959,19 @@
       <c r="Z129" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA129" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB129" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC129" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15362,7 +17076,7 @@
       <c r="X130" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y130" s="57" t="inlineStr">
+      <c r="Y130" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 84٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15370,6 +17084,19 @@
       <c r="Z130" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA130" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB130" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC130" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15474,7 +17201,7 @@
       <c r="X131" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y131" s="57" t="inlineStr">
+      <c r="Y131" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 90٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15482,6 +17209,19 @@
       <c r="Z131" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA131" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB131" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC131" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15586,7 +17326,7 @@
       <c r="X132" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y132" s="57" t="inlineStr">
+      <c r="Y132" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 79٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15594,6 +17334,19 @@
       <c r="Z132" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA132" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB132" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC132" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15696,7 +17449,7 @@
       <c r="X133" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y133" s="57" t="inlineStr">
+      <c r="Y133" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 100٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15704,6 +17457,19 @@
       <c r="Z133" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA133" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB133" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC133" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15806,7 +17572,7 @@
       <c r="X134" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y134" s="57" t="inlineStr">
+      <c r="Y134" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 100٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -15814,6 +17580,19 @@
       <c r="Z134" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA134" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB134" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC134" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -15928,6 +17707,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA135" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB135" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC135" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
@@ -16030,7 +17822,7 @@
       <c r="X136" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y136" s="57" t="inlineStr">
+      <c r="Y136" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 30٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -16038,6 +17830,19 @@
       <c r="Z136" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA136" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB136" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC136" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -16152,6 +17957,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA137" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB137" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC137" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
@@ -16254,7 +18072,7 @@
       <c r="X138" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y138" s="57" t="inlineStr">
+      <c r="Y138" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 28٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -16262,6 +18080,19 @@
       <c r="Z138" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير التسويق.</t>
+        </is>
+      </c>
+      <c r="AA138" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB138" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC138" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -16376,6 +18207,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA139" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB139" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC139" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
@@ -16478,7 +18322,7 @@
       <c r="X140" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y140" s="57" t="inlineStr">
+      <c r="Y140" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 19٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -16486,6 +18330,19 @@
       <c r="Z140" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الجودة.</t>
+        </is>
+      </c>
+      <c r="AA140" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB140" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC140" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -16590,7 +18447,7 @@
       <c r="X141" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y141" s="57" t="inlineStr">
+      <c r="Y141" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 24٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -16598,6 +18455,19 @@
       <c r="Z141" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الجودة.</t>
+        </is>
+      </c>
+      <c r="AA141" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB141" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC141" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -16702,7 +18572,7 @@
       <c r="X142" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y142" s="57" t="inlineStr">
+      <c r="Y142" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 24٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -16710,6 +18580,19 @@
       <c r="Z142" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الجودة.</t>
+        </is>
+      </c>
+      <c r="AA142" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB142" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC142" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -16824,6 +18707,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA143" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB143" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC143" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
@@ -16926,7 +18822,7 @@
       <c r="X144" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y144" s="57" t="inlineStr">
+      <c r="Y144" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 23٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -16934,6 +18830,19 @@
       <c r="Z144" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الجودة.</t>
+        </is>
+      </c>
+      <c r="AA144" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB144" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC144" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -17038,7 +18947,7 @@
       <c r="X145" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y145" s="57" t="inlineStr">
+      <c r="Y145" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -17046,6 +18955,19 @@
       <c r="Z145" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الجودة.</t>
+        </is>
+      </c>
+      <c r="AA145" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB145" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC145" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -17140,6 +19062,19 @@
       </c>
       <c r="Y146" s="56" t="inlineStr"/>
       <c r="Z146" s="53" t="inlineStr"/>
+      <c r="AA146" s="27" t="inlineStr">
+        <is>
+          <t>بانتظار هدف</t>
+        </is>
+      </c>
+      <c r="AB146" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC146" s="58" t="inlineStr">
+        <is>
+          <t>#BDBDBD</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -17244,6 +19179,19 @@
       </c>
       <c r="Y147" s="56" t="inlineStr"/>
       <c r="Z147" s="53" t="inlineStr"/>
+      <c r="AA147" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB147" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC147" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
@@ -17346,7 +19294,7 @@
       <c r="X148" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y148" s="57" t="inlineStr">
+      <c r="Y148" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -17354,6 +19302,19 @@
       <c r="Z148" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف مدير الجودة.</t>
+        </is>
+      </c>
+      <c r="AA148" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB148" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC148" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -17468,6 +19429,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA149" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB149" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC149" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
@@ -17572,6 +19546,19 @@
       </c>
       <c r="Y150" s="56" t="inlineStr"/>
       <c r="Z150" s="53" t="inlineStr"/>
+      <c r="AA150" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB150" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC150" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
@@ -17676,6 +19663,19 @@
       </c>
       <c r="Y151" s="56" t="inlineStr"/>
       <c r="Z151" s="53" t="inlineStr"/>
+      <c r="AA151" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB151" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC151" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
@@ -17788,6 +19788,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA152" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB152" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC152" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
@@ -17892,6 +19905,19 @@
       </c>
       <c r="Y153" s="56" t="inlineStr"/>
       <c r="Z153" s="53" t="inlineStr"/>
+      <c r="AA153" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB153" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC153" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
@@ -17996,6 +20022,19 @@
       </c>
       <c r="Y154" s="56" t="inlineStr"/>
       <c r="Z154" s="53" t="inlineStr"/>
+      <c r="AA154" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB154" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC154" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
@@ -18108,6 +20147,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA155" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB155" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC155" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
@@ -18210,7 +20262,7 @@
       <c r="X156" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y156" s="57" t="inlineStr">
+      <c r="Y156" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 17٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -18218,6 +20270,19 @@
       <c r="Z156" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير القانوني.</t>
+        </is>
+      </c>
+      <c r="AA156" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB156" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC156" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -18322,7 +20387,7 @@
       <c r="X157" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y157" s="57" t="inlineStr">
+      <c r="Y157" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 20٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -18330,6 +20395,19 @@
       <c r="Z157" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير القانوني.</t>
+        </is>
+      </c>
+      <c r="AA157" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB157" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC157" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -18436,6 +20514,19 @@
       </c>
       <c r="Y158" s="56" t="inlineStr"/>
       <c r="Z158" s="53" t="inlineStr"/>
+      <c r="AA158" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB158" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC158" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
@@ -18538,7 +20629,7 @@
       <c r="X159" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y159" s="57" t="inlineStr">
+      <c r="Y159" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 27٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -18546,6 +20637,19 @@
       <c r="Z159" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير القانوني.</t>
+        </is>
+      </c>
+      <c r="AA159" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB159" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC159" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -18660,6 +20764,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA160" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB160" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC160" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
@@ -18762,7 +20879,7 @@
       <c r="X161" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y161" s="57" t="inlineStr">
+      <c r="Y161" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 16٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -18770,6 +20887,19 @@
       <c r="Z161" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA161" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB161" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC161" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -18874,7 +21004,7 @@
       <c r="X162" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y162" s="57" t="inlineStr">
+      <c r="Y162" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 22٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -18882,6 +21012,19 @@
       <c r="Z162" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA162" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB162" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC162" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -18986,7 +21129,7 @@
       <c r="X163" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y163" s="57" t="inlineStr">
+      <c r="Y163" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 20٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -18994,6 +21137,19 @@
       <c r="Z163" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA163" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB163" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC163" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -19098,7 +21254,7 @@
       <c r="X164" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y164" s="57" t="inlineStr">
+      <c r="Y164" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 26٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -19106,6 +21262,19 @@
       <c r="Z164" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA164" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB164" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC164" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -19220,6 +21389,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA165" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB165" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC165" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
@@ -19332,6 +21514,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA166" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB166" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC166" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
@@ -19436,6 +21631,19 @@
       </c>
       <c r="Y167" s="56" t="inlineStr"/>
       <c r="Z167" s="53" t="inlineStr"/>
+      <c r="AA167" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB167" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC167" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
@@ -19540,6 +21748,19 @@
       </c>
       <c r="Y168" s="56" t="inlineStr"/>
       <c r="Z168" s="53" t="inlineStr"/>
+      <c r="AA168" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB168" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC168" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
@@ -19642,7 +21863,7 @@
       <c r="X169" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y169" s="57" t="inlineStr">
+      <c r="Y169" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 26٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -19650,6 +21871,19 @@
       <c r="Z169" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA169" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB169" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC169" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -19756,6 +21990,19 @@
       </c>
       <c r="Y170" s="56" t="inlineStr"/>
       <c r="Z170" s="53" t="inlineStr"/>
+      <c r="AA170" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB170" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC170" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
@@ -19860,6 +22107,19 @@
       </c>
       <c r="Y171" s="56" t="inlineStr"/>
       <c r="Z171" s="53" t="inlineStr"/>
+      <c r="AA171" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB171" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC171" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
@@ -19962,7 +22222,7 @@
       <c r="X172" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y172" s="57" t="inlineStr">
+      <c r="Y172" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 23٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -19970,6 +22230,19 @@
       <c r="Z172" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA172" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB172" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC172" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -20084,6 +22357,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA173" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB173" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC173" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
@@ -20188,6 +22474,19 @@
       </c>
       <c r="Y174" s="56" t="inlineStr"/>
       <c r="Z174" s="53" t="inlineStr"/>
+      <c r="AA174" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB174" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC174" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
@@ -20292,6 +22591,19 @@
       </c>
       <c r="Y175" s="56" t="inlineStr"/>
       <c r="Z175" s="53" t="inlineStr"/>
+      <c r="AA175" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB175" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC175" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
@@ -20394,7 +22706,7 @@
       <c r="X176" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y176" s="57" t="inlineStr">
+      <c r="Y176" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 22٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -20402,6 +22714,19 @@
       <c r="Z176" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA176" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB176" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC176" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -20506,7 +22831,7 @@
       <c r="X177" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y177" s="57" t="inlineStr">
+      <c r="Y177" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 24٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -20514,6 +22839,19 @@
       <c r="Z177" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA177" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB177" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC177" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -20628,6 +22966,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA178" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB178" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC178" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
@@ -20740,6 +23091,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA179" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB179" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC179" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
@@ -20844,6 +23208,19 @@
       </c>
       <c r="Y180" s="56" t="inlineStr"/>
       <c r="Z180" s="53" t="inlineStr"/>
+      <c r="AA180" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB180" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC180" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
@@ -20946,7 +23323,7 @@
       <c r="X181" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y181" s="57" t="inlineStr">
+      <c r="Y181" s="60" t="inlineStr">
         <is>
           <t>دون المستهدف — فجوة 22٪، يتطلب إجراءً تصحيحياً عاجلاً.</t>
         </is>
@@ -20954,6 +23331,19 @@
       <c r="Z181" s="53" t="inlineStr">
         <is>
           <t>إطلاق إجراء تصحيحي خلال 30 يوماً بإشراف المدير المالي.</t>
+        </is>
+      </c>
+      <c r="AA181" s="27" t="inlineStr">
+        <is>
+          <t>تحت الهدف</t>
+        </is>
+      </c>
+      <c r="AB181" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC181" s="61" t="inlineStr">
+        <is>
+          <t>#EB5757</t>
         </is>
       </c>
     </row>
@@ -21068,6 +23458,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA182" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB182" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC182" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
@@ -21180,6 +23583,19 @@
           <t>متابعة أسبوعية حتى بلوغ المستهدف.</t>
         </is>
       </c>
+      <c r="AA183" s="27" t="inlineStr">
+        <is>
+          <t>قريب</t>
+        </is>
+      </c>
+      <c r="AB183" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC183" s="57" t="inlineStr">
+        <is>
+          <t>#F2C94C</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
@@ -21284,9 +23700,22 @@
       </c>
       <c r="Y184" s="56" t="inlineStr"/>
       <c r="Z184" s="53" t="inlineStr"/>
+      <c r="AA184" s="27" t="inlineStr">
+        <is>
+          <t>محقق</t>
+        </is>
+      </c>
+      <c r="AB184" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC184" s="59" t="inlineStr">
+        <is>
+          <t>#2EAD6B</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z184"/>
+  <autoFilter ref="A1:AC184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21325,7 +23754,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -21440,15 +23869,15 @@
       <c r="G4" s="54" t="n">
         <v>0.12</v>
       </c>
-      <c r="H4" s="59" t="n">
+      <c r="H4" s="63" t="n">
         <v>235</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>≥ 235 محطة</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -21463,7 +23892,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="62" t="n">
+      <c r="M4" s="66" t="n">
         <v>206.1</v>
       </c>
       <c r="N4" s="10">
@@ -21507,15 +23936,15 @@
       <c r="G5" s="54" t="n">
         <v>0.12</v>
       </c>
-      <c r="H5" s="59" t="n">
+      <c r="H5" s="63" t="n">
         <v>357</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>357 عقد</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -21530,7 +23959,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="62" t="n">
+      <c r="M5" s="66" t="n">
         <v>346.6</v>
       </c>
       <c r="N5" s="10">
@@ -21575,12 +24004,12 @@
         <v>0.11</v>
       </c>
       <c r="H6" s="46" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>تصاعدي مستمر</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -21595,7 +24024,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M6" s="63" t="n"/>
+      <c r="M6" s="67" t="n"/>
       <c r="N6" s="10">
         <f>IF($H6="","",IF($M6="","",MIN(1,IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0))))))</f>
         <v/>
@@ -21638,12 +24067,12 @@
         <v>0.11</v>
       </c>
       <c r="H7" s="46" t="inlineStr"/>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>مستهدف تنفيذي</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -21658,7 +24087,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n"/>
+      <c r="M7" s="68" t="n"/>
       <c r="N7" s="10">
         <f>IF($H7="","",IF($M7="","",MIN(1,IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0))))))</f>
         <v/>
@@ -21703,12 +24132,12 @@
       <c r="H8" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -21723,7 +24152,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="64" t="n">
+      <c r="M8" s="68" t="n">
         <v>0.906</v>
       </c>
       <c r="N8" s="10">
@@ -21770,12 +24199,12 @@
       <c r="H9" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -21790,7 +24219,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M9" s="64" t="n">
+      <c r="M9" s="68" t="n">
         <v>0.9389999999999999</v>
       </c>
       <c r="N9" s="10">
@@ -21837,12 +24266,12 @@
       <c r="H10" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -21857,7 +24286,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M10" s="64" t="n">
+      <c r="M10" s="68" t="n">
         <v>0.922</v>
       </c>
       <c r="N10" s="10">
@@ -21901,15 +24330,15 @@
       <c r="G11" s="54" t="n">
         <v>0.11</v>
       </c>
-      <c r="H11" s="65" t="n">
+      <c r="H11" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>≥ 30</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -21924,7 +24353,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M11" s="66" t="n">
+      <c r="M11" s="70" t="n">
         <v>22.5</v>
       </c>
       <c r="N11" s="10">
@@ -21971,12 +24400,12 @@
       <c r="H12" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -21991,7 +24420,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="64" t="n">
+      <c r="M12" s="68" t="n">
         <v>0.85</v>
       </c>
       <c r="N12" s="10">
@@ -22038,12 +24467,12 @@
       <c r="H13" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22058,7 +24487,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M13" s="64" t="n">
+      <c r="M13" s="68" t="n">
         <v>0.749</v>
       </c>
       <c r="N13" s="10">
@@ -22119,7 +24548,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -22234,15 +24663,15 @@
       <c r="G4" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H4" s="59" t="n">
+      <c r="H4" s="63" t="n">
         <v>150</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>150 محطة</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22257,7 +24686,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="62" t="n">
+      <c r="M4" s="66" t="n">
         <v>110</v>
       </c>
       <c r="N4" s="10">
@@ -22301,15 +24730,15 @@
       <c r="G5" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H5" s="59" t="n">
+      <c r="H5" s="63" t="n">
         <v>167</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>167 عقد</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22324,7 +24753,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="62" t="n">
+      <c r="M5" s="66" t="n">
         <v>159.2</v>
       </c>
       <c r="N5" s="10">
@@ -22368,15 +24797,15 @@
       <c r="G6" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H6" s="59" t="n">
+      <c r="H6" s="63" t="n">
         <v>718838077</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>718.8M لتر</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22391,7 +24820,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M6" s="62" t="n">
+      <c r="M6" s="66" t="n">
         <v>576630340</v>
       </c>
       <c r="N6" s="10">
@@ -22438,12 +24867,12 @@
       <c r="H7" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>90%+</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22458,7 +24887,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0.788</v>
       </c>
       <c r="N7" s="10">
@@ -22503,12 +24932,12 @@
         <v>0.04</v>
       </c>
       <c r="H8" s="46" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>+10% نمو شهري</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22523,7 +24952,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M8" s="62" t="n"/>
+      <c r="M8" s="66" t="n"/>
       <c r="N8" s="10">
         <f>IF($H8="","",IF($M8="","",MIN(1,IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0))))))</f>
         <v/>
@@ -22568,12 +24997,12 @@
       <c r="H9" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -22588,7 +25017,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="64" t="n">
+      <c r="M9" s="68" t="n">
         <v>0.709</v>
       </c>
       <c r="N9" s="10">
@@ -22633,12 +25062,12 @@
         <v>0.04</v>
       </c>
       <c r="H10" s="46" t="inlineStr"/>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>تصاعدي مستمر</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22653,7 +25082,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M10" s="63" t="n"/>
+      <c r="M10" s="67" t="n"/>
       <c r="N10" s="10">
         <f>IF($H10="","",IF($M10="","",MIN(1,IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0))))))</f>
         <v/>
@@ -22695,15 +25124,15 @@
       <c r="G11" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H11" s="65" t="n">
+      <c r="H11" s="69" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>+1.8 هللة/لتر</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -22718,7 +25147,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M11" s="66" t="n">
+      <c r="M11" s="70" t="n">
         <v>1.564</v>
       </c>
       <c r="N11" s="10">
@@ -22765,12 +25194,12 @@
       <c r="H12" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>95%+</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -22785,7 +25214,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M12" s="64" t="n">
+      <c r="M12" s="68" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="N12" s="10">
@@ -22829,15 +25258,15 @@
       <c r="G13" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H13" s="65" t="n">
+      <c r="H13" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>≤ 30 يوم</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -22852,7 +25281,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M13" s="66" t="n">
+      <c r="M13" s="70" t="n">
         <v>26.2</v>
       </c>
       <c r="N13" s="10">
@@ -22897,12 +25326,12 @@
         <v>0.03</v>
       </c>
       <c r="H14" s="46" t="inlineStr"/>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>تراجع مستمر</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -22917,7 +25346,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M14" s="63" t="n"/>
+      <c r="M14" s="67" t="n"/>
       <c r="N14" s="10">
         <f>IF($H14="","",IF($M14="","",MIN(1,IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0))))))</f>
         <v/>
@@ -22962,12 +25391,12 @@
       <c r="H15" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>90%+</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -22982,7 +25411,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M15" s="64" t="n">
+      <c r="M15" s="68" t="n">
         <v>0.705</v>
       </c>
       <c r="N15" s="10">
@@ -23026,15 +25455,15 @@
       <c r="G16" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H16" s="65" t="n">
+      <c r="H16" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>≤ 5 أيام</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23049,7 +25478,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M16" s="66" t="n">
+      <c r="M16" s="70" t="n">
         <v>4.329</v>
       </c>
       <c r="N16" s="10">
@@ -23096,12 +25525,12 @@
       <c r="H17" s="54" t="n">
         <v>0.99</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>99%+</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23116,7 +25545,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="64" t="n">
+      <c r="M17" s="68" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="10">
@@ -23160,15 +25589,15 @@
       <c r="G18" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H18" s="59" t="n">
+      <c r="H18" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="64" t="inlineStr">
         <is>
           <t>0 حالة</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23183,7 +25612,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="62" t="n"/>
+      <c r="M18" s="66" t="n"/>
       <c r="N18" s="10">
         <f>IF($H18="","",IF($M18="","",MIN(1,IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0))))))</f>
         <v/>
@@ -23228,12 +25657,12 @@
       <c r="H19" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="64" t="inlineStr">
         <is>
           <t>95%+</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="J19" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23248,7 +25677,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="64" t="n">
+      <c r="M19" s="68" t="n">
         <v>0.879</v>
       </c>
       <c r="N19" s="10">
@@ -23292,15 +25721,15 @@
       <c r="G20" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H20" s="65" t="n">
+      <c r="H20" s="69" t="n">
         <v>85</v>
       </c>
-      <c r="I20" s="60" t="inlineStr">
+      <c r="I20" s="64" t="inlineStr">
         <is>
           <t>85+</t>
         </is>
       </c>
-      <c r="J20" s="61" t="inlineStr">
+      <c r="J20" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23315,7 +25744,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M20" s="66" t="n">
+      <c r="M20" s="70" t="n">
         <v>78.8</v>
       </c>
       <c r="N20" s="10">
@@ -23362,12 +25791,12 @@
       <c r="H21" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="60" t="inlineStr">
+      <c r="I21" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="61" t="inlineStr">
+      <c r="J21" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23382,7 +25811,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M21" s="64" t="n">
+      <c r="M21" s="68" t="n">
         <v>1.034</v>
       </c>
       <c r="N21" s="10">
@@ -23429,12 +25858,12 @@
       <c r="H22" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="60" t="inlineStr">
+      <c r="I22" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J22" s="61" t="inlineStr">
+      <c r="J22" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23449,7 +25878,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M22" s="64" t="n">
+      <c r="M22" s="68" t="n">
         <v>0.911</v>
       </c>
       <c r="N22" s="10">
@@ -23493,15 +25922,15 @@
       <c r="G23" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H23" s="65" t="n">
+      <c r="H23" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="I23" s="60" t="inlineStr">
+      <c r="I23" s="64" t="inlineStr">
         <is>
           <t>≤ 24 ساعة</t>
         </is>
       </c>
-      <c r="J23" s="61" t="inlineStr">
+      <c r="J23" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23516,7 +25945,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M23" s="66" t="n">
+      <c r="M23" s="70" t="n">
         <v>26.2</v>
       </c>
       <c r="N23" s="10">
@@ -23563,12 +25992,12 @@
       <c r="H24" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I24" s="60" t="inlineStr">
+      <c r="I24" s="64" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="J24" s="61" t="inlineStr">
+      <c r="J24" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -23583,7 +26012,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M24" s="64" t="n">
+      <c r="M24" s="68" t="n">
         <v>0.674</v>
       </c>
       <c r="N24" s="10">
@@ -23630,12 +26059,12 @@
       <c r="H25" s="54" t="n">
         <v>0.3</v>
       </c>
-      <c r="I25" s="60" t="inlineStr">
+      <c r="I25" s="64" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J25" s="61" t="inlineStr">
+      <c r="J25" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -23650,7 +26079,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M25" s="64" t="n">
+      <c r="M25" s="68" t="n">
         <v>0.299</v>
       </c>
       <c r="N25" s="10">
@@ -23697,12 +26126,12 @@
       <c r="H26" s="54" t="n">
         <v>0.55</v>
       </c>
-      <c r="I26" s="60" t="inlineStr">
+      <c r="I26" s="64" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="J26" s="61" t="inlineStr">
+      <c r="J26" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -23717,7 +26146,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M26" s="64" t="n">
+      <c r="M26" s="68" t="n">
         <v>0.44</v>
       </c>
       <c r="N26" s="10">
@@ -23761,15 +26190,15 @@
       <c r="G27" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H27" s="65" t="n">
+      <c r="H27" s="69" t="n">
         <v>4.7</v>
       </c>
-      <c r="I27" s="60" t="inlineStr">
+      <c r="I27" s="64" t="inlineStr">
         <is>
           <t>≥ 4.7 نجمة</t>
         </is>
       </c>
-      <c r="J27" s="61" t="inlineStr">
+      <c r="J27" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23784,7 +26213,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M27" s="66" t="n">
+      <c r="M27" s="70" t="n">
         <v>3.474</v>
       </c>
       <c r="N27" s="10">
@@ -23831,12 +26260,12 @@
       <c r="H28" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I28" s="60" t="inlineStr">
+      <c r="I28" s="64" t="inlineStr">
         <is>
           <t>90%+</t>
         </is>
       </c>
-      <c r="J28" s="61" t="inlineStr">
+      <c r="J28" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23851,7 +26280,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M28" s="64" t="n">
+      <c r="M28" s="68" t="n">
         <v>0.837</v>
       </c>
       <c r="N28" s="10">
@@ -23898,12 +26327,12 @@
       <c r="H29" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I29" s="60" t="inlineStr">
+      <c r="I29" s="64" t="inlineStr">
         <is>
           <t>95%+</t>
         </is>
       </c>
-      <c r="J29" s="61" t="inlineStr">
+      <c r="J29" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23918,7 +26347,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M29" s="64" t="n">
+      <c r="M29" s="68" t="n">
         <v>0.922</v>
       </c>
       <c r="N29" s="10">
@@ -23963,12 +26392,12 @@
         <v>0.02</v>
       </c>
       <c r="H30" s="46" t="inlineStr"/>
-      <c r="I30" s="60" t="inlineStr">
+      <c r="I30" s="64" t="inlineStr">
         <is>
           <t>-30%</t>
         </is>
       </c>
-      <c r="J30" s="61" t="inlineStr">
+      <c r="J30" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -23983,7 +26412,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M30" s="64" t="n"/>
+      <c r="M30" s="68" t="n"/>
       <c r="N30" s="10">
         <f>IF($H30="","",IF($M30="","",MIN(1,IF($H30=0,IF($M30&lt;=0,1,0),IF($E30="↓",IFERROR($H30/$M30,0),IFERROR($M30/$H30,0))))))</f>
         <v/>
@@ -24028,12 +26457,12 @@
       <c r="H31" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I31" s="60" t="inlineStr">
+      <c r="I31" s="64" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="J31" s="61" t="inlineStr">
+      <c r="J31" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -24048,7 +26477,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M31" s="64" t="n">
+      <c r="M31" s="68" t="n">
         <v>0.853</v>
       </c>
       <c r="N31" s="10">
@@ -24095,12 +26524,12 @@
       <c r="H32" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="60" t="inlineStr">
+      <c r="I32" s="64" t="inlineStr">
         <is>
           <t>100% نمو</t>
         </is>
       </c>
-      <c r="J32" s="61" t="inlineStr">
+      <c r="J32" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -24115,7 +26544,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M32" s="64" t="n">
+      <c r="M32" s="68" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N32" s="10">
@@ -24159,15 +26588,15 @@
       <c r="G33" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H33" s="65" t="n">
+      <c r="H33" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="60" t="inlineStr">
+      <c r="I33" s="64" t="inlineStr">
         <is>
           <t>≤ أسبوع</t>
         </is>
       </c>
-      <c r="J33" s="61" t="inlineStr">
+      <c r="J33" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -24182,7 +26611,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M33" s="66" t="n">
+      <c r="M33" s="70" t="n">
         <v>0.899</v>
       </c>
       <c r="N33" s="10">
@@ -24243,7 +26672,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -24358,15 +26787,15 @@
       <c r="G4" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="H4" s="59" t="n">
+      <c r="H4" s="63" t="n">
         <v>85</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>85 محطة</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -24381,7 +26810,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="62" t="n">
+      <c r="M4" s="66" t="n">
         <v>78.5</v>
       </c>
       <c r="N4" s="10">
@@ -24426,12 +26855,12 @@
         <v>0.08</v>
       </c>
       <c r="H5" s="46" t="inlineStr"/>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>يُحدد لاحقاً</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -24446,7 +26875,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M5" s="64" t="n"/>
+      <c r="M5" s="68" t="n"/>
       <c r="N5" s="10">
         <f>IF($H5="","",IF($M5="","",MIN(1,IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0))))))</f>
         <v/>
@@ -24489,12 +26918,12 @@
         <v>0.08</v>
       </c>
       <c r="H6" s="46" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>يُحدد لاحقاً</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -24509,7 +26938,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n"/>
+      <c r="M6" s="68" t="n"/>
       <c r="N6" s="10">
         <f>IF($H6="","",IF($M6="","",MIN(1,IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0))))))</f>
         <v/>
@@ -24552,12 +26981,12 @@
         <v>0.08</v>
       </c>
       <c r="H7" s="46" t="inlineStr"/>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>يُحدد لاحقاً</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -24572,7 +27001,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n"/>
+      <c r="M7" s="68" t="n"/>
       <c r="N7" s="10">
         <f>IF($H7="","",IF($M7="","",MIN(1,IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0))))))</f>
         <v/>
@@ -24615,12 +27044,12 @@
         <v>0.08</v>
       </c>
       <c r="H8" s="46" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>يُحدد لاحقاً</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -24635,7 +27064,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M8" s="64" t="n"/>
+      <c r="M8" s="68" t="n"/>
       <c r="N8" s="10">
         <f>IF($H8="","",IF($M8="","",MIN(1,IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0))))))</f>
         <v/>
@@ -24680,12 +27109,12 @@
       <c r="H9" s="54" t="n">
         <v>0.99</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>99%+</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -24700,7 +27129,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="64" t="n">
+      <c r="M9" s="68" t="n">
         <v>0.831</v>
       </c>
       <c r="N9" s="10">
@@ -24747,12 +27176,12 @@
       <c r="H10" s="54" t="n">
         <v>0.97</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>≥ 97%</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -24767,7 +27196,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="64" t="n">
+      <c r="M10" s="68" t="n">
         <v>0.953</v>
       </c>
       <c r="N10" s="10">
@@ -24812,12 +27241,12 @@
         <v>0.05</v>
       </c>
       <c r="H11" s="46" t="inlineStr"/>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>خفض ≥5% سنوياً</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -24832,7 +27261,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M11" s="66" t="n"/>
+      <c r="M11" s="70" t="n"/>
       <c r="N11" s="10">
         <f>IF($H11="","",IF($M11="","",MIN(1,IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0))))))</f>
         <v/>
@@ -24877,12 +27306,12 @@
       <c r="H12" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -24897,7 +27326,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="64" t="n">
+      <c r="M12" s="68" t="n">
         <v>0.758</v>
       </c>
       <c r="N12" s="10">
@@ -24942,12 +27371,12 @@
         <v>0.05</v>
       </c>
       <c r="H13" s="46" t="inlineStr"/>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>−30%</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -24962,7 +27391,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M13" s="64" t="n"/>
+      <c r="M13" s="68" t="n"/>
       <c r="N13" s="10">
         <f>IF($H13="","",IF($M13="","",MIN(1,IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0))))))</f>
         <v/>
@@ -25004,15 +27433,15 @@
       <c r="G14" s="54" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H14" s="65" t="n">
+      <c r="H14" s="69" t="n">
         <v>4.5</v>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>≥ 4.5</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -25027,7 +27456,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M14" s="66" t="n">
+      <c r="M14" s="70" t="n">
         <v>4.048</v>
       </c>
       <c r="N14" s="10">
@@ -25071,15 +27500,15 @@
       <c r="G15" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H15" s="65" t="n">
+      <c r="H15" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>≤ 3 دقائق</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -25094,7 +27523,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="66" t="n">
+      <c r="M15" s="70" t="n">
         <v>3.352</v>
       </c>
       <c r="N15" s="10">
@@ -25141,12 +27570,12 @@
       <c r="H16" s="54" t="n">
         <v>0.99</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>≥ 99%</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -25161,7 +27590,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="64" t="n">
+      <c r="M16" s="68" t="n">
         <v>0.831</v>
       </c>
       <c r="N16" s="10">
@@ -25208,12 +27637,12 @@
       <c r="H17" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -25228,7 +27657,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M17" s="64" t="n">
+      <c r="M17" s="68" t="n">
         <v>0.787</v>
       </c>
       <c r="N17" s="10">
@@ -25275,12 +27704,12 @@
       <c r="H18" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -25295,7 +27724,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="64" t="n">
+      <c r="M18" s="68" t="n">
         <v>0.837</v>
       </c>
       <c r="N18" s="10">
@@ -25342,12 +27771,12 @@
       <c r="H19" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="J19" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -25362,7 +27791,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="64" t="n">
+      <c r="M19" s="68" t="n">
         <v>0.747</v>
       </c>
       <c r="N19" s="10">
@@ -25423,7 +27852,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -25538,15 +27967,15 @@
       <c r="G4" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H4" s="59" t="n">
+      <c r="H4" s="63" t="n">
         <v>190</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>190 عقد</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -25561,7 +27990,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="62" t="n">
+      <c r="M4" s="66" t="n">
         <v>165.7</v>
       </c>
       <c r="N4" s="10">
@@ -25605,15 +28034,15 @@
       <c r="G5" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H5" s="59" t="n">
+      <c r="H5" s="63" t="n">
         <v>90</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>90 عقد</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -25628,7 +28057,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="62" t="n">
+      <c r="M5" s="66" t="n">
         <v>76.3</v>
       </c>
       <c r="N5" s="10">
@@ -25672,15 +28101,15 @@
       <c r="G6" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H6" s="59" t="n">
+      <c r="H6" s="63" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>100 عقد</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -25695,7 +28124,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="62" t="n">
+      <c r="M6" s="66" t="n">
         <v>82.2</v>
       </c>
       <c r="N6" s="10">
@@ -25739,15 +28168,15 @@
       <c r="G7" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="59" t="n">
+      <c r="H7" s="63" t="n">
         <v>120</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>120 محطة</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -25762,7 +28191,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="62" t="n">
+      <c r="M7" s="66" t="n">
         <v>125.8</v>
       </c>
       <c r="N7" s="10">
@@ -25806,15 +28235,15 @@
       <c r="G8" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="59" t="n">
+      <c r="H8" s="63" t="n">
         <v>11</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>11 عقد</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -25829,7 +28258,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="62" t="n">
+      <c r="M8" s="66" t="n">
         <v>8.1</v>
       </c>
       <c r="N8" s="10">
@@ -25873,15 +28302,15 @@
       <c r="G9" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H9" s="59" t="n">
+      <c r="H9" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>12 عقد</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -25896,7 +28325,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="62" t="n">
+      <c r="M9" s="66" t="n">
         <v>12.2</v>
       </c>
       <c r="N9" s="10">
@@ -25940,15 +28369,15 @@
       <c r="G10" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H10" s="59" t="n">
+      <c r="H10" s="63" t="n">
         <v>68</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>68 عقد</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -25963,7 +28392,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="62" t="n">
+      <c r="M10" s="66" t="n">
         <v>49.4</v>
       </c>
       <c r="N10" s="10">
@@ -26010,12 +28439,12 @@
       <c r="H11" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>80%+</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -26030,7 +28459,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M11" s="64" t="n">
+      <c r="M11" s="68" t="n">
         <v>0.649</v>
       </c>
       <c r="N11" s="10">
@@ -26074,15 +28503,15 @@
       <c r="G12" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H12" s="65" t="n">
+      <c r="H12" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>≤ 5 سنوات</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -26097,7 +28526,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M12" s="66" t="n">
+      <c r="M12" s="70" t="n">
         <v>4.983</v>
       </c>
       <c r="N12" s="10">
@@ -26142,12 +28571,12 @@
         <v>0.05</v>
       </c>
       <c r="H13" s="46" t="inlineStr"/>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>يُحدد لاحقاً</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26162,7 +28591,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M13" s="63" t="n"/>
+      <c r="M13" s="67" t="n"/>
       <c r="N13" s="10">
         <f>IF($H13="","",IF($M13="","",MIN(1,IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0))))))</f>
         <v/>
@@ -26207,12 +28636,12 @@
       <c r="H14" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26227,7 +28656,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="64" t="n">
+      <c r="M14" s="68" t="n">
         <v>1.028</v>
       </c>
       <c r="N14" s="10">
@@ -26274,12 +28703,12 @@
       <c r="H15" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>&gt; 60%</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26294,7 +28723,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="64" t="n">
+      <c r="M15" s="68" t="n">
         <v>0.516</v>
       </c>
       <c r="N15" s="10">
@@ -26341,12 +28770,12 @@
       <c r="H16" s="54" t="n">
         <v>0.4</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>&lt; 40%</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26361,7 +28790,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="64" t="n">
+      <c r="M16" s="68" t="n">
         <v>0.415</v>
       </c>
       <c r="N16" s="10">
@@ -26408,12 +28837,12 @@
       <c r="H17" s="54" t="n">
         <v>0.25</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>&gt; 25%</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26428,7 +28857,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="64" t="n">
+      <c r="M17" s="68" t="n">
         <v>0.236</v>
       </c>
       <c r="N17" s="10">
@@ -26472,15 +28901,15 @@
       <c r="G18" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H18" s="65" t="n">
+      <c r="H18" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="64" t="inlineStr">
         <is>
           <t>≤ أسبوع</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26495,7 +28924,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="66" t="n">
+      <c r="M18" s="70" t="n">
         <v>0.912</v>
       </c>
       <c r="N18" s="10">
@@ -26542,12 +28971,12 @@
       <c r="H19" s="54" t="n">
         <v>0.3</v>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="64" t="inlineStr">
         <is>
           <t>≥ 30%</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="J19" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26562,7 +28991,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="64" t="n">
+      <c r="M19" s="68" t="n">
         <v>0.308</v>
       </c>
       <c r="N19" s="10">
@@ -26609,12 +29038,12 @@
       <c r="H20" s="54" t="n">
         <v>0.3</v>
       </c>
-      <c r="I20" s="60" t="inlineStr">
+      <c r="I20" s="64" t="inlineStr">
         <is>
           <t>≥ 30%</t>
         </is>
       </c>
-      <c r="J20" s="61" t="inlineStr">
+      <c r="J20" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -26629,7 +29058,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M20" s="64" t="n">
+      <c r="M20" s="68" t="n">
         <v>0.221</v>
       </c>
       <c r="N20" s="10">
@@ -26676,12 +29105,12 @@
       <c r="H21" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="60" t="inlineStr">
+      <c r="I21" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="61" t="inlineStr">
+      <c r="J21" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -26696,7 +29125,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M21" s="64" t="n">
+      <c r="M21" s="68" t="n">
         <v>0.751</v>
       </c>
       <c r="N21" s="10">
@@ -26743,12 +29172,12 @@
       <c r="H22" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I22" s="60" t="inlineStr">
+      <c r="I22" s="64" t="inlineStr">
         <is>
           <t>95%+</t>
         </is>
       </c>
-      <c r="J22" s="61" t="inlineStr">
+      <c r="J22" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -26763,7 +29192,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M22" s="64" t="n">
+      <c r="M22" s="68" t="n">
         <v>0.736</v>
       </c>
       <c r="N22" s="10">
@@ -26810,12 +29239,12 @@
       <c r="H23" s="54" t="n">
         <v>0.98</v>
       </c>
-      <c r="I23" s="60" t="inlineStr">
+      <c r="I23" s="64" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
       </c>
-      <c r="J23" s="61" t="inlineStr">
+      <c r="J23" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26830,7 +29259,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M23" s="64" t="n">
+      <c r="M23" s="68" t="n">
         <v>1.009</v>
       </c>
       <c r="N23" s="10">
@@ -26874,15 +29303,15 @@
       <c r="G24" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H24" s="65" t="n">
+      <c r="H24" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="60" t="inlineStr">
+      <c r="I24" s="64" t="inlineStr">
         <is>
           <t>≤ أسبوع</t>
         </is>
       </c>
-      <c r="J24" s="61" t="inlineStr">
+      <c r="J24" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -26897,7 +29326,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M24" s="66" t="n">
+      <c r="M24" s="70" t="n">
         <v>1.061</v>
       </c>
       <c r="N24" s="10">
@@ -26944,12 +29373,12 @@
       <c r="H25" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I25" s="60" t="inlineStr">
+      <c r="I25" s="64" t="inlineStr">
         <is>
           <t>80%+</t>
         </is>
       </c>
-      <c r="J25" s="61" t="inlineStr">
+      <c r="J25" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -26964,7 +29393,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M25" s="64" t="n">
+      <c r="M25" s="68" t="n">
         <v>0.786</v>
       </c>
       <c r="N25" s="10">
@@ -27011,12 +29440,12 @@
       <c r="H26" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="60" t="inlineStr">
+      <c r="I26" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J26" s="61" t="inlineStr">
+      <c r="J26" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27031,7 +29460,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M26" s="64" t="n">
+      <c r="M26" s="68" t="n">
         <v>0.972</v>
       </c>
       <c r="N26" s="10">
@@ -27078,12 +29507,12 @@
       <c r="H27" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="60" t="inlineStr">
+      <c r="I27" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="61" t="inlineStr">
+      <c r="J27" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27098,7 +29527,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M27" s="64" t="n">
+      <c r="M27" s="68" t="n">
         <v>0.961</v>
       </c>
       <c r="N27" s="10">
@@ -27159,7 +29588,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -27277,12 +29706,12 @@
       <c r="H4" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>&gt; 8% سنوياً</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27297,7 +29726,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M4" s="64" t="n">
+      <c r="M4" s="68" t="n">
         <v>0.068</v>
       </c>
       <c r="N4" s="10">
@@ -27344,12 +29773,12 @@
       <c r="H5" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27364,7 +29793,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="64" t="n">
+      <c r="M5" s="68" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" s="10">
@@ -27411,12 +29840,12 @@
       <c r="H6" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>&gt; 95%</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27431,7 +29860,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n">
+      <c r="M6" s="68" t="n">
         <v>0.805</v>
       </c>
       <c r="N6" s="10">
@@ -27478,12 +29907,12 @@
       <c r="H7" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>≥ 60%</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27498,7 +29927,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0.611</v>
       </c>
       <c r="N7" s="10">
@@ -27542,15 +29971,15 @@
       <c r="G8" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="59" t="n">
+      <c r="H8" s="63" t="n">
         <v>68</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>68 شهرياً</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27565,7 +29994,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="62" t="n">
+      <c r="M8" s="66" t="n">
         <v>54.8</v>
       </c>
       <c r="N8" s="10">
@@ -27609,15 +30038,15 @@
       <c r="G9" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H9" s="59" t="n">
+      <c r="H9" s="63" t="n">
         <v>680</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>544–680</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -27632,7 +30061,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M9" s="62" t="n">
+      <c r="M9" s="66" t="n">
         <v>531.8</v>
       </c>
       <c r="N9" s="10">
@@ -27679,12 +30108,12 @@
       <c r="H10" s="54" t="n">
         <v>0.2</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>15–25%</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -27699,7 +30128,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="64" t="n">
+      <c r="M10" s="68" t="n">
         <v>0.208</v>
       </c>
       <c r="N10" s="10">
@@ -27743,15 +30172,15 @@
       <c r="G11" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H11" s="59" t="n">
+      <c r="H11" s="63" t="n">
         <v>246</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>246 علامة</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -27766,7 +30195,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M11" s="62" t="n">
+      <c r="M11" s="66" t="n">
         <v>202.6</v>
       </c>
       <c r="N11" s="10">
@@ -27813,12 +30242,12 @@
       <c r="H12" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -27833,7 +30262,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="64" t="n">
+      <c r="M12" s="68" t="n">
         <v>0.671</v>
       </c>
       <c r="N12" s="10">
@@ -27877,15 +30306,15 @@
       <c r="G13" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H13" s="59" t="n">
+      <c r="H13" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>6 علامات</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -27900,7 +30329,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M13" s="62" t="n">
+      <c r="M13" s="66" t="n">
         <v>5.769</v>
       </c>
       <c r="N13" s="10">
@@ -27944,15 +30373,15 @@
       <c r="G14" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H14" s="59" t="n">
+      <c r="H14" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>5 شراكات</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -27967,7 +30396,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M14" s="62" t="n">
+      <c r="M14" s="66" t="n">
         <v>4.59</v>
       </c>
       <c r="N14" s="10">
@@ -28014,12 +30443,12 @@
       <c r="H15" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28034,7 +30463,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="64" t="n">
+      <c r="M15" s="68" t="n">
         <v>0.792</v>
       </c>
       <c r="N15" s="10">
@@ -28078,15 +30507,15 @@
       <c r="G16" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H16" s="65" t="n">
+      <c r="H16" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>≤ 7 أيام</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28101,7 +30530,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="66" t="n">
+      <c r="M16" s="70" t="n">
         <v>7.983</v>
       </c>
       <c r="N16" s="10">
@@ -28148,12 +30577,12 @@
       <c r="H17" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>&gt; 90%</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28168,7 +30597,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="64" t="n">
+      <c r="M17" s="68" t="n">
         <v>0.698</v>
       </c>
       <c r="N17" s="10">
@@ -28215,12 +30644,12 @@
       <c r="H18" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28235,7 +30664,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M18" s="64" t="n">
+      <c r="M18" s="68" t="n">
         <v>0.695</v>
       </c>
       <c r="N18" s="10">
@@ -28282,12 +30711,12 @@
       <c r="H19" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="J19" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28302,7 +30731,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M19" s="64" t="n">
+      <c r="M19" s="68" t="n">
         <v>0.894</v>
       </c>
       <c r="N19" s="10">
@@ -28363,7 +30792,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -28481,12 +30910,12 @@
       <c r="H4" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -28501,7 +30930,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M4" s="64" t="n">
+      <c r="M4" s="68" t="n">
         <v>0.06</v>
       </c>
       <c r="N4" s="10">
@@ -28548,12 +30977,12 @@
       <c r="H5" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -28568,7 +30997,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="64" t="n">
+      <c r="M5" s="68" t="n">
         <v>0.83</v>
       </c>
       <c r="N5" s="10">
@@ -28615,12 +31044,12 @@
       <c r="H6" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -28635,7 +31064,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n">
+      <c r="M6" s="68" t="n">
         <v>0.753</v>
       </c>
       <c r="N6" s="10">
@@ -28682,12 +31111,12 @@
       <c r="H7" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -28702,7 +31131,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0.703</v>
       </c>
       <c r="N7" s="10">
@@ -28749,12 +31178,12 @@
       <c r="H8" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28769,7 +31198,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M8" s="64" t="n">
+      <c r="M8" s="68" t="n">
         <v>0.33</v>
       </c>
       <c r="N8" s="10">
@@ -28816,12 +31245,12 @@
       <c r="H9" s="54" t="n">
         <v>0.99</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>≥ 99%</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28836,7 +31265,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M9" s="64" t="n">
+      <c r="M9" s="68" t="n">
         <v>0.9</v>
       </c>
       <c r="N9" s="10">
@@ -28883,12 +31312,12 @@
       <c r="H10" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28903,7 +31332,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M10" s="64" t="n">
+      <c r="M10" s="68" t="n">
         <v>0.3</v>
       </c>
       <c r="N10" s="10">
@@ -28947,15 +31376,15 @@
       <c r="G11" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="H11" s="65" t="n">
+      <c r="H11" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>≤ ساعة</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -28970,7 +31399,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M11" s="66" t="n">
+      <c r="M11" s="70" t="n">
         <v>0.8</v>
       </c>
       <c r="N11" s="10">
@@ -29017,12 +31446,12 @@
       <c r="H12" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29037,7 +31466,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M12" s="64" t="n">
+      <c r="M12" s="68" t="n">
         <v>0.2</v>
       </c>
       <c r="N12" s="10">
@@ -29098,7 +31527,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -29214,12 +31643,12 @@
         <v>0.06</v>
       </c>
       <c r="H4" s="46" t="inlineStr"/>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>أخضر مرتفع (حسب الوزارة)</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29234,7 +31663,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M4" s="64" t="n"/>
+      <c r="M4" s="68" t="n"/>
       <c r="N4" s="10">
         <f>IF($H4="","",IF($M4="","",MIN(1,IF($H4=0,IF($M4&lt;=0,1,0),IF($E4="↓",IFERROR($H4/$M4,0),IFERROR($M4/$H4,0))))))</f>
         <v/>
@@ -29279,12 +31708,12 @@
       <c r="H5" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29299,7 +31728,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="64" t="n">
+      <c r="M5" s="68" t="n">
         <v>0.723</v>
       </c>
       <c r="N5" s="10">
@@ -29346,12 +31775,12 @@
       <c r="H6" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>≥ 85%</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29366,7 +31795,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n">
+      <c r="M6" s="68" t="n">
         <v>0.73</v>
       </c>
       <c r="N6" s="10">
@@ -29413,12 +31842,12 @@
       <c r="H7" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29433,7 +31862,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0.795</v>
       </c>
       <c r="N7" s="10">
@@ -29480,12 +31909,12 @@
       <c r="H8" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>≤ 10%</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29500,7 +31929,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M8" s="64" t="n">
+      <c r="M8" s="68" t="n">
         <v>0.111</v>
       </c>
       <c r="N8" s="10">
@@ -29544,15 +31973,15 @@
       <c r="G9" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="H9" s="59" t="n">
+      <c r="H9" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>6 دورات</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29567,7 +31996,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="62" t="n">
+      <c r="M9" s="66" t="n">
         <v>4.53</v>
       </c>
       <c r="N9" s="10">
@@ -29611,15 +32040,15 @@
       <c r="G10" s="54" t="n">
         <v>0.06</v>
       </c>
-      <c r="H10" s="65" t="n">
+      <c r="H10" s="69" t="n">
         <v>40</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>≥ 40 ساعة</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29634,7 +32063,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M10" s="66" t="n">
+      <c r="M10" s="70" t="n">
         <v>33.6</v>
       </c>
       <c r="N10" s="10">
@@ -29681,12 +32110,12 @@
       <c r="H11" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29701,7 +32130,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M11" s="64" t="n">
+      <c r="M11" s="68" t="n">
         <v>0.644</v>
       </c>
       <c r="N11" s="10">
@@ -29745,15 +32174,15 @@
       <c r="G12" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="H12" s="65" t="n">
+      <c r="H12" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>≥ 30</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29768,7 +32197,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M12" s="66" t="n">
+      <c r="M12" s="70" t="n">
         <v>27.5</v>
       </c>
       <c r="N12" s="10">
@@ -29813,12 +32242,12 @@
         <v>0.08</v>
       </c>
       <c r="H13" s="46" t="inlineStr"/>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>مستهدف سنوي</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29833,7 +32262,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M13" s="64" t="n"/>
+      <c r="M13" s="68" t="n"/>
       <c r="N13" s="10">
         <f>IF($H13="","",IF($M13="","",MIN(1,IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0))))))</f>
         <v/>
@@ -29878,12 +32307,12 @@
       <c r="H14" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -29898,7 +32327,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="64" t="n">
+      <c r="M14" s="68" t="n">
         <v>0.742</v>
       </c>
       <c r="N14" s="10">
@@ -29945,12 +32374,12 @@
       <c r="H15" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -29965,7 +32394,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M15" s="64" t="n">
+      <c r="M15" s="68" t="n">
         <v>0.84</v>
       </c>
       <c r="N15" s="10">
@@ -30012,12 +32441,12 @@
       <c r="H16" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -30032,7 +32461,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M16" s="64" t="n">
+      <c r="M16" s="68" t="n">
         <v>0.775</v>
       </c>
       <c r="N16" s="10">
@@ -30079,12 +32508,12 @@
       <c r="H17" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -30099,7 +32528,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M17" s="64" t="n">
+      <c r="M17" s="68" t="n">
         <v>0.671</v>
       </c>
       <c r="N17" s="10">
@@ -30146,12 +32575,12 @@
       <c r="H18" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -30166,7 +32595,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="64" t="n">
+      <c r="M18" s="68" t="n">
         <v>0.984</v>
       </c>
       <c r="N18" s="10">
@@ -30213,12 +32642,12 @@
       <c r="H19" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="J19" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -30233,7 +32662,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="64" t="n">
+      <c r="M19" s="68" t="n">
         <v>0.926</v>
       </c>
       <c r="N19" s="10">
@@ -30280,12 +32709,12 @@
       <c r="H20" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="60" t="inlineStr">
+      <c r="I20" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J20" s="61" t="inlineStr">
+      <c r="J20" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -30300,7 +32729,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M20" s="64" t="n">
+      <c r="M20" s="68" t="n">
         <v>0.8080000000000001</v>
       </c>
       <c r="N20" s="10">
@@ -30361,7 +32790,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -30476,15 +32905,15 @@
       <c r="G4" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="H4" s="59" t="n">
+      <c r="H4" s="63" t="n">
         <v>50000000</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>50م وصول</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -30499,7 +32928,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M4" s="62" t="n">
+      <c r="M4" s="66" t="n">
         <v>5000000</v>
       </c>
       <c r="N4" s="10">
@@ -30543,15 +32972,15 @@
       <c r="G5" s="54" t="n">
         <v>0.06</v>
       </c>
-      <c r="H5" s="59" t="n">
+      <c r="H5" s="63" t="n">
         <v>200</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>200 عميل</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -30566,7 +32995,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M5" s="62" t="n">
+      <c r="M5" s="66" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="10">
@@ -30610,15 +33039,15 @@
       <c r="G6" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="H6" s="59" t="n">
+      <c r="H6" s="63" t="n">
         <v>380000</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>380ك متابع</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -30633,7 +33062,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M6" s="62" t="n">
+      <c r="M6" s="66" t="n">
         <v>253000</v>
       </c>
       <c r="N6" s="10">
@@ -30680,12 +33109,12 @@
       <c r="H7" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -30700,7 +33129,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="10">
@@ -30744,15 +33173,15 @@
       <c r="G8" s="54" t="n">
         <v>0.06</v>
       </c>
-      <c r="H8" s="59" t="n">
+      <c r="H8" s="63" t="n">
         <v>48</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>48 حملة</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -30767,7 +33196,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="62" t="n">
+      <c r="M8" s="66" t="n">
         <v>11</v>
       </c>
       <c r="N8" s="10">
@@ -30814,12 +33243,12 @@
       <c r="H9" s="54" t="n">
         <v>0.25</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -30834,7 +33263,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="64" t="n">
+      <c r="M9" s="68" t="n">
         <v>0.17</v>
       </c>
       <c r="N9" s="10">
@@ -30881,12 +33310,12 @@
       <c r="H10" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -30901,7 +33330,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M10" s="64" t="n">
+      <c r="M10" s="68" t="n">
         <v>0.16</v>
       </c>
       <c r="N10" s="10">
@@ -30948,12 +33377,12 @@
       <c r="H11" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -30968,7 +33397,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M11" s="64" t="n">
+      <c r="M11" s="68" t="n">
         <v>0.1</v>
       </c>
       <c r="N11" s="10">
@@ -31012,15 +33441,15 @@
       <c r="G12" s="54" t="n">
         <v>0.06</v>
       </c>
-      <c r="H12" s="59" t="n">
+      <c r="H12" s="63" t="n">
         <v>7000000</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>7م وصول</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -31035,7 +33464,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M12" s="62" t="n">
+      <c r="M12" s="66" t="n">
         <v>1500000</v>
       </c>
       <c r="N12" s="10">
@@ -31079,15 +33508,15 @@
       <c r="G13" s="54" t="n">
         <v>0.06</v>
       </c>
-      <c r="H13" s="59" t="n">
+      <c r="H13" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>3 معارض</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -31102,7 +33531,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M13" s="62" t="n">
+      <c r="M13" s="66" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="10">
@@ -31146,15 +33575,15 @@
       <c r="G14" s="54" t="n">
         <v>0.06</v>
       </c>
-      <c r="H14" s="59" t="n">
+      <c r="H14" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>3 اتفاقيات</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -31169,7 +33598,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="62" t="n">
+      <c r="M14" s="66" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="10">
@@ -31213,15 +33642,15 @@
       <c r="G15" s="54" t="n">
         <v>0.06</v>
       </c>
-      <c r="H15" s="65" t="n">
+      <c r="H15" s="69" t="n">
         <v>4.7</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>4.7 ⭐</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31236,7 +33665,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M15" s="66" t="n">
+      <c r="M15" s="70" t="n">
         <v>4</v>
       </c>
       <c r="N15" s="10">
@@ -31283,12 +33712,12 @@
       <c r="H16" s="54" t="n">
         <v>0.3</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31303,7 +33732,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M16" s="64" t="n">
+      <c r="M16" s="68" t="n">
         <v>0.21</v>
       </c>
       <c r="N16" s="10">
@@ -31347,15 +33776,15 @@
       <c r="G17" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H17" s="59" t="n">
+      <c r="H17" s="63" t="n">
         <v>1000000</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>1م وصول</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -31370,7 +33799,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M17" s="62" t="n">
+      <c r="M17" s="66" t="n">
         <v>946380</v>
       </c>
       <c r="N17" s="10">
@@ -31414,15 +33843,15 @@
       <c r="G18" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H18" s="59" t="n">
+      <c r="H18" s="63" t="n">
         <v>250</v>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="64" t="inlineStr">
         <is>
           <t>250 مشاركة</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -31437,7 +33866,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="62" t="n">
+      <c r="M18" s="66" t="n">
         <v>180.7</v>
       </c>
       <c r="N18" s="10">
@@ -31498,7 +33927,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -31616,12 +34045,12 @@
       <c r="H4" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>&lt; 5%</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31636,7 +34065,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="64" t="n">
+      <c r="M4" s="68" t="n">
         <v>0.054</v>
       </c>
       <c r="N4" s="10">
@@ -31683,12 +34112,12 @@
       <c r="H5" s="54" t="n">
         <v>0.995</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>99.5%</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31703,7 +34132,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="64" t="n">
+      <c r="M5" s="68" t="n">
         <v>0.804</v>
       </c>
       <c r="N5" s="10">
@@ -31750,12 +34179,12 @@
       <c r="H6" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31770,7 +34199,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n">
+      <c r="M6" s="68" t="n">
         <v>0.6870000000000001</v>
       </c>
       <c r="N6" s="10">
@@ -31817,12 +34246,12 @@
       <c r="H7" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>≥ 85%</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31837,7 +34266,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0.648</v>
       </c>
       <c r="N7" s="10">
@@ -31884,12 +34313,12 @@
       <c r="H8" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>&lt; 10%</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31904,7 +34333,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="64" t="n">
+      <c r="M8" s="68" t="n">
         <v>0.114</v>
       </c>
       <c r="N8" s="10">
@@ -31951,12 +34380,12 @@
       <c r="H9" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -31971,7 +34400,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="64" t="n">
+      <c r="M9" s="68" t="n">
         <v>0.728</v>
       </c>
       <c r="N9" s="10">
@@ -32018,12 +34447,12 @@
       <c r="H10" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>80% ← 90%</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -32038,7 +34467,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="64" t="n">
+      <c r="M10" s="68" t="n">
         <v>0.754</v>
       </c>
       <c r="N10" s="10">
@@ -32082,15 +34511,15 @@
       <c r="G11" s="54" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H11" s="59" t="n">
+      <c r="H11" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>صفر</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -32105,7 +34534,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M11" s="62" t="n"/>
+      <c r="M11" s="66" t="n"/>
       <c r="N11" s="10">
         <f>IF($H11="","",IF($M11="","",MIN(1,IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0))))))</f>
         <v/>
@@ -32150,12 +34579,12 @@
       <c r="H12" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -32170,7 +34599,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M12" s="64" t="n">
+      <c r="M12" s="68" t="n">
         <v>0.908</v>
       </c>
       <c r="N12" s="10">
@@ -32217,12 +34646,12 @@
       <c r="H13" s="54" t="n">
         <v>0.15</v>
       </c>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>انخفاض 15% ربعياً</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -32237,7 +34666,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M13" s="64" t="n">
+      <c r="M13" s="68" t="n">
         <v>0.126</v>
       </c>
       <c r="N13" s="10">
@@ -32284,12 +34713,12 @@
       <c r="H14" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -32304,7 +34733,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="64" t="n">
+      <c r="M14" s="68" t="n">
         <v>0.944</v>
       </c>
       <c r="N14" s="10">
@@ -32351,12 +34780,12 @@
       <c r="H15" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -32371,7 +34800,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M15" s="64" t="n">
+      <c r="M15" s="68" t="n">
         <v>0.982</v>
       </c>
       <c r="N15" s="10">
@@ -32418,12 +34847,12 @@
       <c r="H16" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>الابتكار</t>
         </is>
@@ -32438,7 +34867,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M16" s="64" t="n">
+      <c r="M16" s="68" t="n">
         <v>0.834</v>
       </c>
       <c r="N16" s="10">
@@ -32482,15 +34911,15 @@
       <c r="G17" s="54" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H17" s="59" t="n">
+      <c r="H17" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>≥ 8 سنوياً (2 ربعياً)</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -32505,7 +34934,7 @@
           <t>التعلّم والنمو</t>
         </is>
       </c>
-      <c r="M17" s="62" t="n">
+      <c r="M17" s="66" t="n">
         <v>6.827</v>
       </c>
       <c r="N17" s="10">
@@ -33076,7 +35505,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -33194,12 +35623,12 @@
       <c r="H4" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33214,7 +35643,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M4" s="64" t="n">
+      <c r="M4" s="68" t="n">
         <v>1.013</v>
       </c>
       <c r="N4" s="10">
@@ -33258,15 +35687,15 @@
       <c r="G5" s="54" t="n">
         <v>0.15</v>
       </c>
-      <c r="H5" s="65" t="n">
+      <c r="H5" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>≤ 3 أيام</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33281,7 +35710,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M5" s="66" t="n">
+      <c r="M5" s="70" t="n">
         <v>2.994</v>
       </c>
       <c r="N5" s="10">
@@ -33328,12 +35757,12 @@
       <c r="H6" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33348,7 +35777,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n">
+      <c r="M6" s="68" t="n">
         <v>0.924</v>
       </c>
       <c r="N6" s="10">
@@ -33395,12 +35824,12 @@
       <c r="H7" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33415,7 +35844,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0.664</v>
       </c>
       <c r="N7" s="10">
@@ -33462,12 +35891,12 @@
       <c r="H8" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33482,7 +35911,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="64" t="n">
+      <c r="M8" s="68" t="n">
         <v>0.797</v>
       </c>
       <c r="N8" s="10">
@@ -33526,15 +35955,15 @@
       <c r="G9" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="H9" s="65" t="n">
+      <c r="H9" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>≤ 5 أيام</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33549,7 +35978,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="66" t="n">
+      <c r="M9" s="70" t="n">
         <v>4.545</v>
       </c>
       <c r="N9" s="10">
@@ -33596,12 +36025,12 @@
       <c r="H10" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>≥ 90%</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33616,7 +36045,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="64" t="n">
+      <c r="M10" s="68" t="n">
         <v>0.659</v>
       </c>
       <c r="N10" s="10">
@@ -33663,12 +36092,12 @@
       <c r="H11" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>≥ 85%</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -33683,7 +36112,7 @@
           <t>العملاء</t>
         </is>
       </c>
-      <c r="M11" s="64" t="n">
+      <c r="M11" s="68" t="n">
         <v>0.674</v>
       </c>
       <c r="N11" s="10">
@@ -33744,7 +36173,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>🟩 عمود «المُحقَّق» أرقام تجريبية — استبدلها بالفعلية · نسبة التحقيق والحالة دلّات تُحسب تلقائياً</t>
         </is>
@@ -33862,12 +36291,12 @@
       <c r="H4" s="54" t="n">
         <v>0.2</v>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>&gt; 20%</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -33882,7 +36311,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M4" s="64" t="n">
+      <c r="M4" s="68" t="n">
         <v>0.169</v>
       </c>
       <c r="N4" s="10">
@@ -33929,12 +36358,12 @@
       <c r="H5" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="I5" s="60" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>&gt; 8%</t>
         </is>
       </c>
-      <c r="J5" s="61" t="inlineStr">
+      <c r="J5" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -33949,7 +36378,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M5" s="64" t="n">
+      <c r="M5" s="68" t="n">
         <v>0.062</v>
       </c>
       <c r="N5" s="10">
@@ -33996,12 +36425,12 @@
       <c r="H6" s="54" t="n">
         <v>0.01</v>
       </c>
-      <c r="I6" s="60" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>&gt; 1%</t>
         </is>
       </c>
-      <c r="J6" s="61" t="inlineStr">
+      <c r="J6" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -34016,7 +36445,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M6" s="64" t="n">
+      <c r="M6" s="68" t="n">
         <v>0.008</v>
       </c>
       <c r="N6" s="10">
@@ -34063,12 +36492,12 @@
       <c r="H7" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="I7" s="60" t="inlineStr">
+      <c r="I7" s="64" t="inlineStr">
         <is>
           <t>&gt; 10%</t>
         </is>
       </c>
-      <c r="J7" s="61" t="inlineStr">
+      <c r="J7" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -34083,7 +36512,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M7" s="64" t="n">
+      <c r="M7" s="68" t="n">
         <v>0.074</v>
       </c>
       <c r="N7" s="10">
@@ -34127,15 +36556,15 @@
       <c r="G8" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H8" s="65" t="n">
+      <c r="H8" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="I8" s="64" t="inlineStr">
         <is>
           <t>&gt; 1</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34150,7 +36579,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="66" t="n">
+      <c r="M8" s="70" t="n">
         <v>0.902</v>
       </c>
       <c r="N8" s="10">
@@ -34194,15 +36623,15 @@
       <c r="G9" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="H9" s="65" t="n">
+      <c r="H9" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="60" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
         <is>
           <t>0.8 – 1</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34217,7 +36646,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="66" t="n">
+      <c r="M9" s="70" t="n">
         <v>0.852</v>
       </c>
       <c r="N9" s="10">
@@ -34261,15 +36690,15 @@
       <c r="G10" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H10" s="65" t="n">
+      <c r="H10" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="I10" s="64" t="inlineStr">
         <is>
           <t>&lt; 20 يوم</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34284,7 +36713,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M10" s="66" t="n">
+      <c r="M10" s="70" t="n">
         <v>19.3</v>
       </c>
       <c r="N10" s="10">
@@ -34328,15 +36757,15 @@
       <c r="G11" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H11" s="65" t="n">
+      <c r="H11" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
         <is>
           <t>&lt; 30 يوم</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34351,7 +36780,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M11" s="66" t="n">
+      <c r="M11" s="70" t="n">
         <v>28.1</v>
       </c>
       <c r="N11" s="10">
@@ -34398,12 +36827,12 @@
       <c r="H12" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
         <is>
           <t>&gt; 95%</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34418,7 +36847,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M12" s="64" t="n">
+      <c r="M12" s="68" t="n">
         <v>0.699</v>
       </c>
       <c r="N12" s="10">
@@ -34465,12 +36894,12 @@
       <c r="H13" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="I13" s="64" t="inlineStr">
         <is>
           <t>&lt; 10%</t>
         </is>
       </c>
-      <c r="J13" s="61" t="inlineStr">
+      <c r="J13" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34485,7 +36914,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M13" s="64" t="n">
+      <c r="M13" s="68" t="n">
         <v>0.099</v>
       </c>
       <c r="N13" s="10">
@@ -34532,12 +36961,12 @@
       <c r="H14" s="54" t="n">
         <v>0.01</v>
       </c>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="I14" s="64" t="inlineStr">
         <is>
           <t>&lt; 1%</t>
         </is>
       </c>
-      <c r="J14" s="61" t="inlineStr">
+      <c r="J14" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34552,7 +36981,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M14" s="64" t="n">
+      <c r="M14" s="68" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="N14" s="10">
@@ -34599,12 +37028,12 @@
       <c r="H15" s="54" t="n">
         <v>0.98</v>
       </c>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="I15" s="64" t="inlineStr">
         <is>
           <t>&gt; 98%</t>
         </is>
       </c>
-      <c r="J15" s="61" t="inlineStr">
+      <c r="J15" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34619,7 +37048,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M15" s="64" t="n">
+      <c r="M15" s="68" t="n">
         <v>0.754</v>
       </c>
       <c r="N15" s="10">
@@ -34666,12 +37095,12 @@
       <c r="H16" s="54" t="n">
         <v>0.95</v>
       </c>
-      <c r="I16" s="60" t="inlineStr">
+      <c r="I16" s="64" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="J16" s="61" t="inlineStr">
+      <c r="J16" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34686,7 +37115,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M16" s="64" t="n">
+      <c r="M16" s="68" t="n">
         <v>0.926</v>
       </c>
       <c r="N16" s="10">
@@ -34733,12 +37162,12 @@
       <c r="H17" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
         <is>
           <t>±10%</t>
         </is>
       </c>
-      <c r="J17" s="61" t="inlineStr">
+      <c r="J17" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34753,7 +37182,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M17" s="64" t="n">
+      <c r="M17" s="68" t="n">
         <v>0.9</v>
       </c>
       <c r="N17" s="10">
@@ -34800,12 +37229,12 @@
       <c r="H18" s="54" t="n">
         <v>0.001</v>
       </c>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="I18" s="64" t="inlineStr">
         <is>
           <t>&lt; 0.1%</t>
         </is>
       </c>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="J18" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34820,7 +37249,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M18" s="64" t="n">
+      <c r="M18" s="68" t="n">
         <v>0.001</v>
       </c>
       <c r="N18" s="10">
@@ -34867,12 +37296,12 @@
       <c r="H19" s="54" t="n">
         <v>0.995</v>
       </c>
-      <c r="I19" s="60" t="inlineStr">
+      <c r="I19" s="64" t="inlineStr">
         <is>
           <t>&gt; 99.5%</t>
         </is>
       </c>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="J19" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34887,7 +37316,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M19" s="64" t="n">
+      <c r="M19" s="68" t="n">
         <v>0.776</v>
       </c>
       <c r="N19" s="10">
@@ -34934,12 +37363,12 @@
       <c r="H20" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="60" t="inlineStr">
+      <c r="I20" s="64" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J20" s="61" t="inlineStr">
+      <c r="J20" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -34954,7 +37383,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M20" s="64" t="n">
+      <c r="M20" s="68" t="n">
         <v>0.76</v>
       </c>
       <c r="N20" s="10">
@@ -35001,12 +37430,12 @@
       <c r="H21" s="54" t="n">
         <v>0.98</v>
       </c>
-      <c r="I21" s="60" t="inlineStr">
+      <c r="I21" s="64" t="inlineStr">
         <is>
           <t>&gt; 98%</t>
         </is>
       </c>
-      <c r="J21" s="61" t="inlineStr">
+      <c r="J21" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -35021,7 +37450,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M21" s="64" t="n">
+      <c r="M21" s="68" t="n">
         <v>0.91</v>
       </c>
       <c r="N21" s="10">
@@ -35065,15 +37494,15 @@
       <c r="G22" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H22" s="65" t="n">
+      <c r="H22" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="I22" s="60" t="inlineStr">
+      <c r="I22" s="64" t="inlineStr">
         <is>
           <t>&lt; 15 يوم</t>
         </is>
       </c>
-      <c r="J22" s="61" t="inlineStr">
+      <c r="J22" s="65" t="inlineStr">
         <is>
           <t>النمو</t>
         </is>
@@ -35088,7 +37517,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M22" s="66" t="n">
+      <c r="M22" s="70" t="n">
         <v>15.8</v>
       </c>
       <c r="N22" s="10">
@@ -35135,12 +37564,12 @@
       <c r="H23" s="54" t="n">
         <v>0.98</v>
       </c>
-      <c r="I23" s="60" t="inlineStr">
+      <c r="I23" s="64" t="inlineStr">
         <is>
           <t>&gt; 98%</t>
         </is>
       </c>
-      <c r="J23" s="61" t="inlineStr">
+      <c r="J23" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -35155,7 +37584,7 @@
           <t>مالي</t>
         </is>
       </c>
-      <c r="M23" s="64" t="n">
+      <c r="M23" s="68" t="n">
         <v>1.027</v>
       </c>
       <c r="N23" s="10">
@@ -35202,12 +37631,12 @@
       <c r="H24" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="I24" s="60" t="inlineStr">
+      <c r="I24" s="64" t="inlineStr">
         <is>
           <t>&gt; 90%</t>
         </is>
       </c>
-      <c r="J24" s="61" t="inlineStr">
+      <c r="J24" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -35222,7 +37651,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M24" s="64" t="n">
+      <c r="M24" s="68" t="n">
         <v>0.702</v>
       </c>
       <c r="N24" s="10">
@@ -35269,12 +37698,12 @@
       <c r="H25" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="I25" s="60" t="inlineStr">
+      <c r="I25" s="64" t="inlineStr">
         <is>
           <t>≤ ±10%</t>
         </is>
       </c>
-      <c r="J25" s="61" t="inlineStr">
+      <c r="J25" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -35289,7 +37718,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M25" s="64" t="n">
+      <c r="M25" s="68" t="n">
         <v>0.101</v>
       </c>
       <c r="N25" s="10">
@@ -35333,15 +37762,15 @@
       <c r="G26" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H26" s="65" t="n">
+      <c r="H26" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="60" t="inlineStr">
+      <c r="I26" s="64" t="inlineStr">
         <is>
           <t>≤ 6 أيام</t>
         </is>
       </c>
-      <c r="J26" s="61" t="inlineStr">
+      <c r="J26" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -35356,7 +37785,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M26" s="66" t="n">
+      <c r="M26" s="70" t="n">
         <v>7.044</v>
       </c>
       <c r="N26" s="10">
@@ -35403,12 +37832,12 @@
       <c r="H27" s="54" t="n">
         <v>0.02</v>
       </c>
-      <c r="I27" s="60" t="inlineStr">
+      <c r="I27" s="64" t="inlineStr">
         <is>
           <t>&lt; 2%</t>
         </is>
       </c>
-      <c r="J27" s="61" t="inlineStr">
+      <c r="J27" s="65" t="inlineStr">
         <is>
           <t>الاستدامة</t>
         </is>
@@ -35423,7 +37852,7 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M27" s="64" t="n">
+      <c r="M27" s="68" t="n">
         <v>0.02</v>
       </c>
       <c r="N27" s="10">
@@ -35519,7 +37948,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>▾ مشاريع إدارة التقنية</t>
         </is>
@@ -35554,7 +37983,7 @@
         <f>IFERROR(F4/D4,0)</f>
         <v/>
       </c>
-      <c r="H4" s="68" t="inlineStr">
+      <c r="H4" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35589,7 +38018,7 @@
         <f>IFERROR(F5/D5,0)</f>
         <v/>
       </c>
-      <c r="H5" s="68" t="inlineStr">
+      <c r="H5" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35624,7 +38053,7 @@
         <f>IFERROR(F6/D6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="68" t="inlineStr">
+      <c r="H6" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35659,7 +38088,7 @@
         <f>IFERROR(F7/D7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="68" t="inlineStr">
+      <c r="H7" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35694,7 +38123,7 @@
         <f>IFERROR(F8/D8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="68" t="inlineStr">
+      <c r="H8" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35729,7 +38158,7 @@
         <f>IFERROR(F9/D9,0)</f>
         <v/>
       </c>
-      <c r="H9" s="68" t="inlineStr">
+      <c r="H9" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35764,7 +38193,7 @@
         <f>IFERROR(F10/D10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="68" t="inlineStr">
+      <c r="H10" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35799,7 +38228,7 @@
         <f>IFERROR(F11/D11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="68" t="inlineStr">
+      <c r="H11" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35834,7 +38263,7 @@
         <f>IFERROR(F12/D12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="68" t="inlineStr">
+      <c r="H12" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
@@ -35869,14 +38298,14 @@
         <f>IFERROR(F13/D13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="68" t="inlineStr">
+      <c r="H13" s="72" t="inlineStr">
         <is>
           <t>نسبة إنجاز محفظة مشاريع التحول الرقمي</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="69" t="inlineStr">
+      <c r="A14" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع الإدارة التنفيذية</t>
         </is>
@@ -35889,10 +38318,10 @@
           <t>الإدارة التنفيذية</t>
         </is>
       </c>
-      <c r="C15" s="70" t="n"/>
-      <c r="D15" s="70" t="n"/>
-      <c r="E15" s="70" t="n"/>
-      <c r="F15" s="70" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="74" t="n"/>
       <c r="G15" s="10">
         <f>IFERROR(F15/D15,0)</f>
         <v/>
@@ -35906,10 +38335,10 @@
           <t>الإدارة التنفيذية</t>
         </is>
       </c>
-      <c r="C16" s="70" t="n"/>
-      <c r="D16" s="70" t="n"/>
-      <c r="E16" s="70" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="C16" s="74" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="74" t="n"/>
       <c r="G16" s="10">
         <f>IFERROR(F16/D16,0)</f>
         <v/>
@@ -35923,10 +38352,10 @@
           <t>الإدارة التنفيذية</t>
         </is>
       </c>
-      <c r="C17" s="70" t="n"/>
-      <c r="D17" s="70" t="n"/>
-      <c r="E17" s="70" t="n"/>
-      <c r="F17" s="70" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="74" t="n"/>
       <c r="G17" s="10">
         <f>IFERROR(F17/D17,0)</f>
         <v/>
@@ -35934,7 +38363,7 @@
       <c r="H17" s="22" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="69" t="inlineStr">
+      <c r="A18" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع الامتياز التجاري</t>
         </is>
@@ -35947,10 +38376,10 @@
           <t>الامتياز التجاري</t>
         </is>
       </c>
-      <c r="C19" s="70" t="n"/>
-      <c r="D19" s="70" t="n"/>
-      <c r="E19" s="70" t="n"/>
-      <c r="F19" s="70" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
       <c r="G19" s="10">
         <f>IFERROR(F19/D19,0)</f>
         <v/>
@@ -35964,10 +38393,10 @@
           <t>الامتياز التجاري</t>
         </is>
       </c>
-      <c r="C20" s="70" t="n"/>
-      <c r="D20" s="70" t="n"/>
-      <c r="E20" s="70" t="n"/>
-      <c r="F20" s="70" t="n"/>
+      <c r="C20" s="74" t="n"/>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="74" t="n"/>
+      <c r="F20" s="74" t="n"/>
       <c r="G20" s="10">
         <f>IFERROR(F20/D20,0)</f>
         <v/>
@@ -35981,10 +38410,10 @@
           <t>الامتياز التجاري</t>
         </is>
       </c>
-      <c r="C21" s="70" t="n"/>
-      <c r="D21" s="70" t="n"/>
-      <c r="E21" s="70" t="n"/>
-      <c r="F21" s="70" t="n"/>
+      <c r="C21" s="74" t="n"/>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="74" t="n"/>
       <c r="G21" s="10">
         <f>IFERROR(F21/D21,0)</f>
         <v/>
@@ -35992,7 +38421,7 @@
       <c r="H21" s="22" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="69" t="inlineStr">
+      <c r="A22" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع التشغيل والمحطات</t>
         </is>
@@ -36005,10 +38434,10 @@
           <t>التشغيل والمحطات</t>
         </is>
       </c>
-      <c r="C23" s="70" t="n"/>
-      <c r="D23" s="70" t="n"/>
-      <c r="E23" s="70" t="n"/>
-      <c r="F23" s="70" t="n"/>
+      <c r="C23" s="74" t="n"/>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="74" t="n"/>
       <c r="G23" s="10">
         <f>IFERROR(F23/D23,0)</f>
         <v/>
@@ -36022,10 +38451,10 @@
           <t>التشغيل والمحطات</t>
         </is>
       </c>
-      <c r="C24" s="70" t="n"/>
-      <c r="D24" s="70" t="n"/>
-      <c r="E24" s="70" t="n"/>
-      <c r="F24" s="70" t="n"/>
+      <c r="C24" s="74" t="n"/>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="74" t="n"/>
+      <c r="F24" s="74" t="n"/>
       <c r="G24" s="10">
         <f>IFERROR(F24/D24,0)</f>
         <v/>
@@ -36039,10 +38468,10 @@
           <t>التشغيل والمحطات</t>
         </is>
       </c>
-      <c r="C25" s="70" t="n"/>
-      <c r="D25" s="70" t="n"/>
-      <c r="E25" s="70" t="n"/>
-      <c r="F25" s="70" t="n"/>
+      <c r="C25" s="74" t="n"/>
+      <c r="D25" s="74" t="n"/>
+      <c r="E25" s="74" t="n"/>
+      <c r="F25" s="74" t="n"/>
       <c r="G25" s="10">
         <f>IFERROR(F25/D25,0)</f>
         <v/>
@@ -36050,7 +38479,7 @@
       <c r="H25" s="22" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="69" t="inlineStr">
+      <c r="A26" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع الاستثمار</t>
         </is>
@@ -36063,10 +38492,10 @@
           <t>الاستثمار</t>
         </is>
       </c>
-      <c r="C27" s="70" t="n"/>
-      <c r="D27" s="70" t="n"/>
-      <c r="E27" s="70" t="n"/>
-      <c r="F27" s="70" t="n"/>
+      <c r="C27" s="74" t="n"/>
+      <c r="D27" s="74" t="n"/>
+      <c r="E27" s="74" t="n"/>
+      <c r="F27" s="74" t="n"/>
       <c r="G27" s="10">
         <f>IFERROR(F27/D27,0)</f>
         <v/>
@@ -36080,10 +38509,10 @@
           <t>الاستثمار</t>
         </is>
       </c>
-      <c r="C28" s="70" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="C28" s="74" t="n"/>
+      <c r="D28" s="74" t="n"/>
+      <c r="E28" s="74" t="n"/>
+      <c r="F28" s="74" t="n"/>
       <c r="G28" s="10">
         <f>IFERROR(F28/D28,0)</f>
         <v/>
@@ -36097,10 +38526,10 @@
           <t>الاستثمار</t>
         </is>
       </c>
-      <c r="C29" s="70" t="n"/>
-      <c r="D29" s="70" t="n"/>
-      <c r="E29" s="70" t="n"/>
-      <c r="F29" s="70" t="n"/>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="74" t="n"/>
       <c r="G29" s="10">
         <f>IFERROR(F29/D29,0)</f>
         <v/>
@@ -36108,7 +38537,7 @@
       <c r="H29" s="22" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="69" t="inlineStr">
+      <c r="A30" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع العقار</t>
         </is>
@@ -36121,10 +38550,10 @@
           <t>العقار</t>
         </is>
       </c>
-      <c r="C31" s="70" t="n"/>
-      <c r="D31" s="70" t="n"/>
-      <c r="E31" s="70" t="n"/>
-      <c r="F31" s="70" t="n"/>
+      <c r="C31" s="74" t="n"/>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="74" t="n"/>
+      <c r="F31" s="74" t="n"/>
       <c r="G31" s="10">
         <f>IFERROR(F31/D31,0)</f>
         <v/>
@@ -36138,10 +38567,10 @@
           <t>العقار</t>
         </is>
       </c>
-      <c r="C32" s="70" t="n"/>
-      <c r="D32" s="70" t="n"/>
-      <c r="E32" s="70" t="n"/>
-      <c r="F32" s="70" t="n"/>
+      <c r="C32" s="74" t="n"/>
+      <c r="D32" s="74" t="n"/>
+      <c r="E32" s="74" t="n"/>
+      <c r="F32" s="74" t="n"/>
       <c r="G32" s="10">
         <f>IFERROR(F32/D32,0)</f>
         <v/>
@@ -36155,10 +38584,10 @@
           <t>العقار</t>
         </is>
       </c>
-      <c r="C33" s="70" t="n"/>
-      <c r="D33" s="70" t="n"/>
-      <c r="E33" s="70" t="n"/>
-      <c r="F33" s="70" t="n"/>
+      <c r="C33" s="74" t="n"/>
+      <c r="D33" s="74" t="n"/>
+      <c r="E33" s="74" t="n"/>
+      <c r="F33" s="74" t="n"/>
       <c r="G33" s="10">
         <f>IFERROR(F33/D33,0)</f>
         <v/>
@@ -36166,7 +38595,7 @@
       <c r="H33" s="22" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="69" t="inlineStr">
+      <c r="A34" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع الموارد البشرية</t>
         </is>
@@ -36179,10 +38608,10 @@
           <t>الموارد البشرية</t>
         </is>
       </c>
-      <c r="C35" s="70" t="n"/>
-      <c r="D35" s="70" t="n"/>
-      <c r="E35" s="70" t="n"/>
-      <c r="F35" s="70" t="n"/>
+      <c r="C35" s="74" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="74" t="n"/>
+      <c r="F35" s="74" t="n"/>
       <c r="G35" s="10">
         <f>IFERROR(F35/D35,0)</f>
         <v/>
@@ -36196,10 +38625,10 @@
           <t>الموارد البشرية</t>
         </is>
       </c>
-      <c r="C36" s="70" t="n"/>
-      <c r="D36" s="70" t="n"/>
-      <c r="E36" s="70" t="n"/>
-      <c r="F36" s="70" t="n"/>
+      <c r="C36" s="74" t="n"/>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="74" t="n"/>
+      <c r="F36" s="74" t="n"/>
       <c r="G36" s="10">
         <f>IFERROR(F36/D36,0)</f>
         <v/>
@@ -36213,10 +38642,10 @@
           <t>الموارد البشرية</t>
         </is>
       </c>
-      <c r="C37" s="70" t="n"/>
-      <c r="D37" s="70" t="n"/>
-      <c r="E37" s="70" t="n"/>
-      <c r="F37" s="70" t="n"/>
+      <c r="C37" s="74" t="n"/>
+      <c r="D37" s="74" t="n"/>
+      <c r="E37" s="74" t="n"/>
+      <c r="F37" s="74" t="n"/>
       <c r="G37" s="10">
         <f>IFERROR(F37/D37,0)</f>
         <v/>
@@ -36224,7 +38653,7 @@
       <c r="H37" s="22" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="69" t="inlineStr">
+      <c r="A38" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع التسويق</t>
         </is>
@@ -36237,10 +38666,10 @@
           <t>التسويق</t>
         </is>
       </c>
-      <c r="C39" s="70" t="n"/>
-      <c r="D39" s="70" t="n"/>
-      <c r="E39" s="70" t="n"/>
-      <c r="F39" s="70" t="n"/>
+      <c r="C39" s="74" t="n"/>
+      <c r="D39" s="74" t="n"/>
+      <c r="E39" s="74" t="n"/>
+      <c r="F39" s="74" t="n"/>
       <c r="G39" s="10">
         <f>IFERROR(F39/D39,0)</f>
         <v/>
@@ -36254,10 +38683,10 @@
           <t>التسويق</t>
         </is>
       </c>
-      <c r="C40" s="70" t="n"/>
-      <c r="D40" s="70" t="n"/>
-      <c r="E40" s="70" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="C40" s="74" t="n"/>
+      <c r="D40" s="74" t="n"/>
+      <c r="E40" s="74" t="n"/>
+      <c r="F40" s="74" t="n"/>
       <c r="G40" s="10">
         <f>IFERROR(F40/D40,0)</f>
         <v/>
@@ -36271,10 +38700,10 @@
           <t>التسويق</t>
         </is>
       </c>
-      <c r="C41" s="70" t="n"/>
-      <c r="D41" s="70" t="n"/>
-      <c r="E41" s="70" t="n"/>
-      <c r="F41" s="70" t="n"/>
+      <c r="C41" s="74" t="n"/>
+      <c r="D41" s="74" t="n"/>
+      <c r="E41" s="74" t="n"/>
+      <c r="F41" s="74" t="n"/>
       <c r="G41" s="10">
         <f>IFERROR(F41/D41,0)</f>
         <v/>
@@ -36282,7 +38711,7 @@
       <c r="H41" s="22" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="69" t="inlineStr">
+      <c r="A42" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع الجودة</t>
         </is>
@@ -36295,10 +38724,10 @@
           <t>الجودة</t>
         </is>
       </c>
-      <c r="C43" s="70" t="n"/>
-      <c r="D43" s="70" t="n"/>
-      <c r="E43" s="70" t="n"/>
-      <c r="F43" s="70" t="n"/>
+      <c r="C43" s="74" t="n"/>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="74" t="n"/>
+      <c r="F43" s="74" t="n"/>
       <c r="G43" s="10">
         <f>IFERROR(F43/D43,0)</f>
         <v/>
@@ -36312,10 +38741,10 @@
           <t>الجودة</t>
         </is>
       </c>
-      <c r="C44" s="70" t="n"/>
-      <c r="D44" s="70" t="n"/>
-      <c r="E44" s="70" t="n"/>
-      <c r="F44" s="70" t="n"/>
+      <c r="C44" s="74" t="n"/>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="74" t="n"/>
+      <c r="F44" s="74" t="n"/>
       <c r="G44" s="10">
         <f>IFERROR(F44/D44,0)</f>
         <v/>
@@ -36329,10 +38758,10 @@
           <t>الجودة</t>
         </is>
       </c>
-      <c r="C45" s="70" t="n"/>
-      <c r="D45" s="70" t="n"/>
-      <c r="E45" s="70" t="n"/>
-      <c r="F45" s="70" t="n"/>
+      <c r="C45" s="74" t="n"/>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="74" t="n"/>
+      <c r="F45" s="74" t="n"/>
       <c r="G45" s="10">
         <f>IFERROR(F45/D45,0)</f>
         <v/>
@@ -36340,7 +38769,7 @@
       <c r="H45" s="22" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="69" t="inlineStr">
+      <c r="A46" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع الإدارة القانونية</t>
         </is>
@@ -36353,10 +38782,10 @@
           <t>الإدارة القانونية</t>
         </is>
       </c>
-      <c r="C47" s="70" t="n"/>
-      <c r="D47" s="70" t="n"/>
-      <c r="E47" s="70" t="n"/>
-      <c r="F47" s="70" t="n"/>
+      <c r="C47" s="74" t="n"/>
+      <c r="D47" s="74" t="n"/>
+      <c r="E47" s="74" t="n"/>
+      <c r="F47" s="74" t="n"/>
       <c r="G47" s="10">
         <f>IFERROR(F47/D47,0)</f>
         <v/>
@@ -36370,10 +38799,10 @@
           <t>الإدارة القانونية</t>
         </is>
       </c>
-      <c r="C48" s="70" t="n"/>
-      <c r="D48" s="70" t="n"/>
-      <c r="E48" s="70" t="n"/>
-      <c r="F48" s="70" t="n"/>
+      <c r="C48" s="74" t="n"/>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="74" t="n"/>
+      <c r="F48" s="74" t="n"/>
       <c r="G48" s="10">
         <f>IFERROR(F48/D48,0)</f>
         <v/>
@@ -36387,10 +38816,10 @@
           <t>الإدارة القانونية</t>
         </is>
       </c>
-      <c r="C49" s="70" t="n"/>
-      <c r="D49" s="70" t="n"/>
-      <c r="E49" s="70" t="n"/>
-      <c r="F49" s="70" t="n"/>
+      <c r="C49" s="74" t="n"/>
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="74" t="n"/>
+      <c r="F49" s="74" t="n"/>
       <c r="G49" s="10">
         <f>IFERROR(F49/D49,0)</f>
         <v/>
@@ -36398,7 +38827,7 @@
       <c r="H49" s="22" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="69" t="inlineStr">
+      <c r="A50" s="73" t="inlineStr">
         <is>
           <t>▾ مشاريع الإدارة المالية</t>
         </is>
@@ -36411,10 +38840,10 @@
           <t>الإدارة المالية</t>
         </is>
       </c>
-      <c r="C51" s="70" t="n"/>
-      <c r="D51" s="70" t="n"/>
-      <c r="E51" s="70" t="n"/>
-      <c r="F51" s="70" t="n"/>
+      <c r="C51" s="74" t="n"/>
+      <c r="D51" s="74" t="n"/>
+      <c r="E51" s="74" t="n"/>
+      <c r="F51" s="74" t="n"/>
       <c r="G51" s="10">
         <f>IFERROR(F51/D51,0)</f>
         <v/>
@@ -36428,10 +38857,10 @@
           <t>الإدارة المالية</t>
         </is>
       </c>
-      <c r="C52" s="70" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="C52" s="74" t="n"/>
+      <c r="D52" s="74" t="n"/>
+      <c r="E52" s="74" t="n"/>
+      <c r="F52" s="74" t="n"/>
       <c r="G52" s="10">
         <f>IFERROR(F52/D52,0)</f>
         <v/>
@@ -36445,10 +38874,10 @@
           <t>الإدارة المالية</t>
         </is>
       </c>
-      <c r="C53" s="70" t="n"/>
-      <c r="D53" s="70" t="n"/>
-      <c r="E53" s="70" t="n"/>
-      <c r="F53" s="70" t="n"/>
+      <c r="C53" s="74" t="n"/>
+      <c r="D53" s="74" t="n"/>
+      <c r="E53" s="74" t="n"/>
+      <c r="F53" s="74" t="n"/>
       <c r="G53" s="10">
         <f>IFERROR(F53/D53,0)</f>
         <v/>

--- a/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
+++ b/درب-المؤشرات-والمشاريع-الموحّد-2026.xlsx
@@ -36,11 +36,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قاعدة المؤشرات" sheetId="27" state="hidden" r:id="rId27"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'تحليل الانحراف'!$A$2:$M$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'التتبّع الشهري'!$A$3:$X$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'تحليل الانحراف'!$A$2:$M$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'التتبّع الشهري'!$A$3:$X$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'سجل المخاطر'!$A$2:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ESG والاستدامة'!$A$2:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'بطاقة تعريف المؤشرات'!$A$2:$N$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'بطاقة تعريف المؤشرات'!$A$2:$N$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'الإدارة التنفيذية'!$A$3:$R$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'الامتياز التجاري'!$A$3:$R$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'التشغيل والمحطات'!$A$3:$R$7</definedName>
@@ -54,7 +54,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'التسويق'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'الجودة'!$A$3:$R$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'الإدارة القانونية'!$A$3:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'الإدارة المالية'!$A$3:$R$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'الإدارة المالية'!$A$3:$R$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$D$2:$D$116,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$D$2:$D$98,"النمو"),"—")</f>
         <v/>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$D$2:$D$116,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$D$2:$D$98,"الابتكار"),"—")</f>
         <v/>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$D$2:$D$116,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$D$2:$D$98,"الاستدامة"),"—")</f>
         <v/>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1702,19 +1702,19 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D18" s="70" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="C22" s="15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D22" s="24" t="n">
-        <v>0.209</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="23">
@@ -1781,7 +1781,7 @@
         <v>12</v>
       </c>
       <c r="D23" s="24" t="n">
-        <v>0.104</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="24">
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="C24" s="15" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D24" s="24" t="n">
-        <v>0.591</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="25">
@@ -1813,7 +1813,7 @@
         <v>11</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>0.096</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="27">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="I94" s="59" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="J94" s="15" t="inlineStr">
         <is>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>هامش EBITDA</t>
+          <t>نسبة التدفق النقدي التشغيلي</t>
         </is>
       </c>
       <c r="D95" s="71" t="inlineStr">
         <is>
-          <t>يقيس هامش EBITDA ضمن محور «المالية الاستراتيجية»، ويعكس مساهمة الإدارة في ركيزة النمو.</t>
+          <t>يقيس نسبة التدفق النقدي التشغيلي ضمن محور «المالية الاستراتيجية»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -8101,21 +8101,21 @@
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>🎯 نتيجة</t>
+          <t>🔧 تشغيلي</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>النمو · زيادة وصول العملاء</t>
+          <t>الاستدامة · جودة التشغيل</t>
         </is>
       </c>
       <c r="H95" s="15" t="inlineStr">
         <is>
-          <t>مالي</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="I95" s="59" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="J95" s="15" t="inlineStr">
         <is>
@@ -8150,12 +8150,12 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>هامش صافي الربح</t>
+          <t>نسبة التحصيل العام (الشركة)</t>
         </is>
       </c>
       <c r="D96" s="71" t="inlineStr">
         <is>
-          <t>يقيس هامش صافي الربح ضمن محور «المالية الاستراتيجية»، ويعكس مساهمة الإدارة في ركيزة النمو.</t>
+          <t>يقيس نسبة التحصيل العام (الشركة) ضمن محور «الذمم المدينة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>النمو · زيادة وصول العملاء</t>
+          <t>الاستدامة · جودة التشغيل</t>
         </is>
       </c>
       <c r="H96" s="15" t="inlineStr">
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="I96" s="59" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="J96" s="15" t="inlineStr">
         <is>
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>العائد على حقوق الملكية (ROE)</t>
+          <t>دقة التنبؤ النقدي</t>
         </is>
       </c>
       <c r="D97" s="71" t="inlineStr">
         <is>
-          <t>يقيس العائد على حقوق الملكية (ROE) ضمن محور «المالية الاستراتيجية»، ويعكس مساهمة الإدارة في ركيزة النمو.</t>
+          <t>يقيس دقة التنبؤ النقدي ضمن محور «الخزينة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -8234,16 +8234,16 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>النمو · زيادة وصول العملاء</t>
+          <t>الاستدامة · جودة التشغيل</t>
         </is>
       </c>
       <c r="H97" s="15" t="inlineStr">
         <is>
-          <t>مالي</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="I97" s="59" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="J97" s="15" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="L97" s="15" t="inlineStr">
         <is>
-          <t>ربعي</t>
+          <t>شهري</t>
         </is>
       </c>
       <c r="M97" s="15" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>نسبة التدفق النقدي التشغيلي</t>
+          <t>دقة تسوية أرامكو</t>
         </is>
       </c>
       <c r="D98" s="71" t="inlineStr">
         <is>
-          <t>يقيس نسبة التدفق النقدي التشغيلي ضمن محور «المالية الاستراتيجية»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
+          <t>يقيس دقة تسوية أرامكو ضمن محور «صناعة الوقود»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>🔧 تشغيلي</t>
+          <t>🎯 نتيجة</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I98" s="59" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="J98" s="15" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
+          <t>نظام تشغيل المحطات</t>
         </is>
       </c>
       <c r="L98" s="15" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>المدير المالي</t>
         </is>
       </c>
       <c r="N98" s="51" t="n"/>
@@ -8342,12 +8342,12 @@
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>النسبة الجارية (Current Ratio)</t>
+          <t>انحراف الموازنة</t>
         </is>
       </c>
       <c r="D99" s="71" t="inlineStr">
         <is>
-          <t>يقيس النسبة الجارية (Current Ratio) ضمن محور «السيولة ورأس المال»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
+          <t>يقيس انحراف الموازنة ضمن محور «الموازنة والتقارير»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="I99" s="59" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="J99" s="15" t="inlineStr">
         <is>
@@ -8380,1175 +8380,23 @@
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>سجلات الإدارة</t>
+          <t>نظام المحاسبة / ERP (D365)</t>
         </is>
       </c>
       <c r="L99" s="15" t="inlineStr">
         <is>
-          <t>شهري</t>
+          <t>ربعي</t>
         </is>
       </c>
       <c r="M99" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>الإدارة المالية</t>
         </is>
       </c>
       <c r="N99" s="51" t="n"/>
     </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="15" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C100" s="21" t="inlineStr">
-        <is>
-          <t>دورة التحويل النقدي</t>
-        </is>
-      </c>
-      <c r="D100" s="71" t="inlineStr">
-        <is>
-          <t>يقيس دورة التحويل النقدي ضمن محور «السيولة ورأس المال»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr">
-        <is>
-          <t>متوسط يوم خلال الفترة</t>
-        </is>
-      </c>
-      <c r="F100" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G100" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H100" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I100" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J100" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K100" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L100" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M100" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N100" s="51" t="n"/>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C101" s="21" t="inlineStr">
-        <is>
-          <t>متوسط أيام التحصيل العام (DSO)</t>
-        </is>
-      </c>
-      <c r="D101" s="71" t="inlineStr">
-        <is>
-          <t>يقيس متوسط أيام التحصيل العام (DSO) ضمن محور «الذمم المدينة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>متوسط يوم خلال الفترة</t>
-        </is>
-      </c>
-      <c r="F101" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G101" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H101" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="I101" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J101" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K101" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L101" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M101" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N101" s="51" t="n"/>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C102" s="21" t="inlineStr">
-        <is>
-          <t>نسبة التحصيل العام (الشركة)</t>
-        </is>
-      </c>
-      <c r="D102" s="71" t="inlineStr">
-        <is>
-          <t>يقيس نسبة التحصيل العام (الشركة) ضمن محور «الذمم المدينة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F102" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G102" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H102" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="I102" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J102" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K102" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L102" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M102" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N102" s="51" t="n"/>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C103" s="21" t="inlineStr">
-        <is>
-          <t>نسبة الذمم المتأخرة</t>
-        </is>
-      </c>
-      <c r="D103" s="71" t="inlineStr">
-        <is>
-          <t>يقيس نسبة الذمم المتأخرة ضمن محور «الذمم المدينة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F103" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G103" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H103" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I103" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J103" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K103" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L103" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M103" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N103" s="51" t="n"/>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="15" t="n">
-        <v>102</v>
-      </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C104" s="21" t="inlineStr">
-        <is>
-          <t>نسبة الديون المعدومة</t>
-        </is>
-      </c>
-      <c r="D104" s="71" t="inlineStr">
-        <is>
-          <t>يقيس نسبة الديون المعدومة ضمن محور «الذمم المدينة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F104" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G104" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H104" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I104" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J104" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K104" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L104" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M104" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N104" s="51" t="n"/>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="15" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C105" s="21" t="inlineStr">
-        <is>
-          <t>سداد الموردين في الموعد</t>
-        </is>
-      </c>
-      <c r="D105" s="71" t="inlineStr">
-        <is>
-          <t>يقيس سداد الموردين في الموعد ضمن محور «الذمم الدائنة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F105" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G105" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H105" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="I105" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J105" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K105" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L105" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M105" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N105" s="51" t="n"/>
-    </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C106" s="21" t="inlineStr">
-        <is>
-          <t>اكتمال مطابقة حسابات الموردين</t>
-        </is>
-      </c>
-      <c r="D106" s="71" t="inlineStr">
-        <is>
-          <t>يقيس اكتمال مطابقة حسابات الموردين ضمن محور «الذمم الدائنة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E106" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F106" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G106" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H106" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I106" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J106" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K106" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L106" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M106" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N106" s="51" t="n"/>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="15" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="inlineStr">
-        <is>
-          <t>دقة التنبؤ النقدي</t>
-        </is>
-      </c>
-      <c r="D107" s="71" t="inlineStr">
-        <is>
-          <t>يقيس دقة التنبؤ النقدي ضمن محور «الخزينة»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F107" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G107" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H107" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I107" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J107" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K107" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L107" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M107" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N107" s="51" t="n"/>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C108" s="21" t="inlineStr">
-        <is>
-          <t>تباين مخزون الوقود</t>
-        </is>
-      </c>
-      <c r="D108" s="71" t="inlineStr">
-        <is>
-          <t>يقيس تباين مخزون الوقود ضمن محور «صناعة الوقود»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F108" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G108" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H108" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I108" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J108" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K108" s="11" t="inlineStr">
-        <is>
-          <t>نظام تشغيل المحطات</t>
-        </is>
-      </c>
-      <c r="L108" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M108" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="N108" s="51" t="n"/>
-    </row>
-    <row r="109" ht="30" customHeight="1">
-      <c r="A109" s="15" t="n">
-        <v>107</v>
-      </c>
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C109" s="21" t="inlineStr">
-        <is>
-          <t>دقة مطابقة المخزون</t>
-        </is>
-      </c>
-      <c r="D109" s="71" t="inlineStr">
-        <is>
-          <t>يقيس دقة مطابقة المخزون ضمن محور «صناعة الوقود»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F109" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G109" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H109" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I109" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J109" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K109" s="11" t="inlineStr">
-        <is>
-          <t>نظام إدارة الجودة (QMS)</t>
-        </is>
-      </c>
-      <c r="L109" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M109" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="N109" s="51" t="n"/>
-    </row>
-    <row r="110" ht="30" customHeight="1">
-      <c r="A110" s="15" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C110" s="21" t="inlineStr">
-        <is>
-          <t>دقة تسوية أرامكو</t>
-        </is>
-      </c>
-      <c r="D110" s="71" t="inlineStr">
-        <is>
-          <t>يقيس دقة تسوية أرامكو ضمن محور «صناعة الوقود»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F110" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G110" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H110" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I110" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J110" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K110" s="11" t="inlineStr">
-        <is>
-          <t>نظام تشغيل المحطات</t>
-        </is>
-      </c>
-      <c r="L110" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M110" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="N110" s="51" t="n"/>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="15" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C111" s="21" t="inlineStr">
-        <is>
-          <t>نسبة تحصيل الامتياز</t>
-        </is>
-      </c>
-      <c r="D111" s="71" t="inlineStr">
-        <is>
-          <t>يقيس نسبة تحصيل الامتياز ضمن محور «تمويل الامتياز»، ويعكس مساهمة الإدارة في ركيزة النمو.</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F111" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G111" s="11" t="inlineStr">
-        <is>
-          <t>النمو · الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="H111" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="I111" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J111" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K111" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L111" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M111" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N111" s="51" t="n"/>
-    </row>
-    <row r="112" ht="30" customHeight="1">
-      <c r="A112" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C112" s="21" t="inlineStr">
-        <is>
-          <t>أيام تحصيل رسوم الامتياز</t>
-        </is>
-      </c>
-      <c r="D112" s="71" t="inlineStr">
-        <is>
-          <t>يقيس أيام تحصيل رسوم الامتياز ضمن محور «تمويل الامتياز»، ويعكس مساهمة الإدارة في ركيزة النمو.</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr">
-        <is>
-          <t>متوسط يوم خلال الفترة</t>
-        </is>
-      </c>
-      <c r="F112" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G112" s="11" t="inlineStr">
-        <is>
-          <t>النمو · الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="H112" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="I112" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J112" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K112" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M112" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N112" s="51" t="n"/>
-    </row>
-    <row r="113" ht="30" customHeight="1">
-      <c r="A113" s="15" t="n">
-        <v>111</v>
-      </c>
-      <c r="B113" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C113" s="21" t="inlineStr">
-        <is>
-          <t>نسبة تحصيل الإيجار</t>
-        </is>
-      </c>
-      <c r="D113" s="71" t="inlineStr">
-        <is>
-          <t>يقيس نسبة تحصيل الإيجار ضمن محور «العقار والإيجار»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F113" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G113" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · منظومة التأجير</t>
-        </is>
-      </c>
-      <c r="H113" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="I113" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J113" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K113" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L113" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M113" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N113" s="51" t="n"/>
-    </row>
-    <row r="114" ht="30" customHeight="1">
-      <c r="A114" s="15" t="n">
-        <v>112</v>
-      </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C114" s="21" t="inlineStr">
-        <is>
-          <t>معدل تجديد عقود الإيجار</t>
-        </is>
-      </c>
-      <c r="D114" s="71" t="inlineStr">
-        <is>
-          <t>يقيس معدل تجديد عقود الإيجار ضمن محور «العقار والإيجار»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F114" s="15" t="inlineStr">
-        <is>
-          <t>🎯 نتيجة</t>
-        </is>
-      </c>
-      <c r="G114" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · منظومة التأجير</t>
-        </is>
-      </c>
-      <c r="H114" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I114" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J114" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K114" s="11" t="inlineStr">
-        <is>
-          <t>نظام إدارة العقود (CRM)</t>
-        </is>
-      </c>
-      <c r="L114" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M114" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="N114" s="51" t="n"/>
-    </row>
-    <row r="115" ht="30" customHeight="1">
-      <c r="A115" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C115" s="21" t="inlineStr">
-        <is>
-          <t>انحراف الموازنة</t>
-        </is>
-      </c>
-      <c r="D115" s="71" t="inlineStr">
-        <is>
-          <t>يقيس انحراف الموازنة ضمن محور «الموازنة والتقارير»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F115" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G115" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H115" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I115" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J115" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K115" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L115" s="15" t="inlineStr">
-        <is>
-          <t>ربعي</t>
-        </is>
-      </c>
-      <c r="M115" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N115" s="51" t="n"/>
-    </row>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C116" s="21" t="inlineStr">
-        <is>
-          <t>أيام الإقفال الشهري</t>
-        </is>
-      </c>
-      <c r="D116" s="71" t="inlineStr">
-        <is>
-          <t>يقيس أيام الإقفال الشهري ضمن محور «الموازنة والتقارير»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E116" s="11" t="inlineStr">
-        <is>
-          <t>متوسط يوم خلال الفترة</t>
-        </is>
-      </c>
-      <c r="F116" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G116" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H116" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I116" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J116" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K116" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L116" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="M116" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N116" s="51" t="n"/>
-    </row>
-    <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="15" t="n">
-        <v>115</v>
-      </c>
-      <c r="B117" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C117" s="21" t="inlineStr">
-        <is>
-          <t>نسبة تسويات التدقيق</t>
-        </is>
-      </c>
-      <c r="D117" s="71" t="inlineStr">
-        <is>
-          <t>يقيس نسبة تسويات التدقيق ضمن محور «الموازنة والتقارير»، ويعكس مساهمة الإدارة في ركيزة الاستدامة.</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>(المتحقّق ÷ الإجمالي) × 100٪</t>
-        </is>
-      </c>
-      <c r="F117" s="15" t="inlineStr">
-        <is>
-          <t>🔧 تشغيلي</t>
-        </is>
-      </c>
-      <c r="G117" s="11" t="inlineStr">
-        <is>
-          <t>الاستدامة · جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="H117" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="I117" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J117" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="K117" s="11" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="L117" s="15" t="inlineStr">
-        <is>
-          <t>ربعي</t>
-        </is>
-      </c>
-      <c r="M117" s="15" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="N117" s="51" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:N117"/>
+  <autoFilter ref="A2:N99"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -17448,27 +16296,27 @@
         <v>2</v>
       </c>
       <c r="B70" s="21">
-        <f>'الإدارة المالية'!C7</f>
+        <f>'الإدارة المالية'!C6</f>
         <v/>
       </c>
       <c r="C70" s="22">
-        <f>'الإدارة المالية'!I7</f>
+        <f>'الإدارة المالية'!I6</f>
         <v/>
       </c>
       <c r="D70" s="23">
-        <f>'الإدارة المالية'!M7</f>
+        <f>'الإدارة المالية'!M6</f>
         <v/>
       </c>
       <c r="E70" s="10">
-        <f>'الإدارة المالية'!N7</f>
+        <f>'الإدارة المالية'!N6</f>
         <v/>
       </c>
       <c r="F70" s="20">
-        <f>'الإدارة المالية'!O7</f>
+        <f>'الإدارة المالية'!O6</f>
         <v/>
       </c>
       <c r="G70" s="24">
-        <f>'الإدارة المالية'!G7</f>
+        <f>'الإدارة المالية'!G6</f>
         <v/>
       </c>
     </row>
@@ -17477,27 +16325,27 @@
         <v>3</v>
       </c>
       <c r="B71" s="21">
-        <f>'الإدارة المالية'!C10</f>
+        <f>'الإدارة المالية'!C5</f>
         <v/>
       </c>
       <c r="C71" s="22">
-        <f>'الإدارة المالية'!I10</f>
+        <f>'الإدارة المالية'!I5</f>
         <v/>
       </c>
       <c r="D71" s="23">
-        <f>'الإدارة المالية'!M10</f>
+        <f>'الإدارة المالية'!M5</f>
         <v/>
       </c>
       <c r="E71" s="10">
-        <f>'الإدارة المالية'!N10</f>
+        <f>'الإدارة المالية'!N5</f>
         <v/>
       </c>
       <c r="F71" s="20">
-        <f>'الإدارة المالية'!O10</f>
+        <f>'الإدارة المالية'!O5</f>
         <v/>
       </c>
       <c r="G71" s="24">
-        <f>'الإدارة المالية'!G10</f>
+        <f>'الإدارة المالية'!G5</f>
         <v/>
       </c>
     </row>
@@ -17506,27 +16354,27 @@
         <v>4</v>
       </c>
       <c r="B72" s="21">
-        <f>'الإدارة المالية'!C11</f>
+        <f>'الإدارة المالية'!C7</f>
         <v/>
       </c>
       <c r="C72" s="22">
-        <f>'الإدارة المالية'!I11</f>
+        <f>'الإدارة المالية'!I7</f>
         <v/>
       </c>
       <c r="D72" s="23">
-        <f>'الإدارة المالية'!M11</f>
+        <f>'الإدارة المالية'!M7</f>
         <v/>
       </c>
       <c r="E72" s="10">
-        <f>'الإدارة المالية'!N11</f>
+        <f>'الإدارة المالية'!N7</f>
         <v/>
       </c>
       <c r="F72" s="20">
-        <f>'الإدارة المالية'!O11</f>
+        <f>'الإدارة المالية'!O7</f>
         <v/>
       </c>
       <c r="G72" s="24">
-        <f>'الإدارة المالية'!G11</f>
+        <f>'الإدارة المالية'!G7</f>
         <v/>
       </c>
     </row>
@@ -17535,27 +16383,27 @@
         <v>5</v>
       </c>
       <c r="B73" s="21">
-        <f>'الإدارة المالية'!C12</f>
+        <f>'الإدارة المالية'!C8</f>
         <v/>
       </c>
       <c r="C73" s="22">
-        <f>'الإدارة المالية'!I12</f>
+        <f>'الإدارة المالية'!I8</f>
         <v/>
       </c>
       <c r="D73" s="23">
-        <f>'الإدارة المالية'!M12</f>
+        <f>'الإدارة المالية'!M8</f>
         <v/>
       </c>
       <c r="E73" s="10">
-        <f>'الإدارة المالية'!N12</f>
+        <f>'الإدارة المالية'!N8</f>
         <v/>
       </c>
       <c r="F73" s="20">
-        <f>'الإدارة المالية'!O12</f>
+        <f>'الإدارة المالية'!O8</f>
         <v/>
       </c>
       <c r="G73" s="24">
-        <f>'الإدارة المالية'!G12</f>
+        <f>'الإدارة المالية'!G8</f>
         <v/>
       </c>
     </row>
@@ -19987,7 +18835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -20146,14 +18994,14 @@
         </is>
       </c>
       <c r="G4" s="59" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="H4" s="59" t="n">
         <v>0.2</v>
       </c>
       <c r="I4" s="22" t="inlineStr">
         <is>
-          <t>&gt; 20%</t>
+          <t>≥ 20%</t>
         </is>
       </c>
       <c r="J4" s="73" t="inlineStr">
@@ -20209,12 +19057,12 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>هامش EBITDA</t>
+          <t>نسبة التدفق النقدي التشغيلي</t>
         </is>
       </c>
       <c r="D5" s="49" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>نسبة</t>
         </is>
       </c>
       <c r="E5" s="49" t="inlineStr">
@@ -20228,33 +19076,33 @@
         </is>
       </c>
       <c r="G5" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H5" s="59" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
+      </c>
+      <c r="H5" s="62" t="n">
+        <v>1</v>
       </c>
       <c r="I5" s="22" t="inlineStr">
         <is>
-          <t>&gt; 8%</t>
+          <t>&gt; 1</t>
         </is>
       </c>
       <c r="J5" s="73" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="L5" s="15" t="inlineStr">
         <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="M5" s="60" t="n">
-        <v>0.062</v>
+          <t>العمليات الداخلية</t>
+        </is>
+      </c>
+      <c r="M5" s="63" t="n">
+        <v>0.902</v>
       </c>
       <c r="N5" s="10">
         <f>IF($H5="","",IF($M5="","",MIN(1,IF($H5=0,IF($M5&lt;=0,1,0),IF($E5="↓",IFERROR($H5/$M5,0),IFERROR($M5/$H5,0))))))</f>
@@ -20266,7 +19114,7 @@
       </c>
       <c r="P5" s="74" t="inlineStr">
         <is>
-          <t>القيمة المتحقّقة من «هامش EBITDA» ÷ المستهدف × 100٪</t>
+          <t>قيمة/عدد المتحقّق من «التدفق النقدي التشغيلي» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
         </is>
       </c>
       <c r="Q5" s="74" t="inlineStr">
@@ -20286,12 +19134,12 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>المالية الاستراتيجية</t>
+          <t>الذمم المدينة</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>هامش صافي الربح</t>
+          <t>نسبة التحصيل العام (الشركة)</t>
         </is>
       </c>
       <c r="D6" s="49" t="inlineStr">
@@ -20306,28 +19154,28 @@
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>🟠 مهم</t>
+          <t>🔴 رئيسي</t>
         </is>
       </c>
       <c r="G6" s="59" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="H6" s="59" t="n">
-        <v>0.01</v>
+        <v>0.95</v>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>&gt; 1%</t>
+          <t>≥ 95%</t>
         </is>
       </c>
       <c r="J6" s="73" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -20336,7 +19184,7 @@
         </is>
       </c>
       <c r="M6" s="60" t="n">
-        <v>0.008</v>
+        <v>0.699</v>
       </c>
       <c r="N6" s="10">
         <f>IF($H6="","",IF($M6="","",MIN(1,IF($H6=0,IF($M6&lt;=0,1,0),IF($E6="↓",IFERROR($H6/$M6,0),IFERROR($M6/$H6,0))))))</f>
@@ -20348,7 +19196,7 @@
       </c>
       <c r="P6" s="74" t="inlineStr">
         <is>
-          <t>القيمة المتحقّقة من «هامش صافي الربح» ÷ المستهدف × 100٪</t>
+          <t>قيمة/عدد المتحقّق من «التحصيل العام» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
         </is>
       </c>
       <c r="Q6" s="74" t="inlineStr">
@@ -20368,12 +19216,12 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>المالية الاستراتيجية</t>
+          <t>الخزينة</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>العائد على حقوق الملكية (ROE)</t>
+          <t>دقة التنبؤ النقدي</t>
         </is>
       </c>
       <c r="D7" s="49" t="inlineStr">
@@ -20388,37 +19236,37 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>🔴 رئيسي</t>
+          <t>🟠 مهم</t>
         </is>
       </c>
       <c r="G7" s="59" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="H7" s="59" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>&gt; 10%</t>
+          <t>±10%</t>
         </is>
       </c>
       <c r="J7" s="73" t="inlineStr">
         <is>
-          <t>النمو</t>
+          <t>الاستدامة</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>زيادة وصول العملاء</t>
+          <t>جودة التشغيل</t>
         </is>
       </c>
       <c r="L7" s="15" t="inlineStr">
         <is>
-          <t>مالي</t>
+          <t>العمليات الداخلية</t>
         </is>
       </c>
       <c r="M7" s="60" t="n">
-        <v>0.074</v>
+        <v>0.9</v>
       </c>
       <c r="N7" s="10">
         <f>IF($H7="","",IF($M7="","",MIN(1,IF($H7=0,IF($M7&lt;=0,1,0),IF($E7="↓",IFERROR($H7/$M7,0),IFERROR($M7/$H7,0))))))</f>
@@ -20430,7 +19278,7 @@
       </c>
       <c r="P7" s="74" t="inlineStr">
         <is>
-          <t>القيمة المتحقّقة من «العائد على حقوق الملكية» ÷ المستهدف × 100٪</t>
+          <t>القيمة المتحقّقة من «دقة التنبؤ النقدي» ÷ المستهدف × 100٪</t>
         </is>
       </c>
       <c r="Q7" s="74" t="inlineStr">
@@ -20440,7 +19288,7 @@
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
-          <t>ربعي</t>
+          <t>شهري</t>
         </is>
       </c>
     </row>
@@ -20450,17 +19298,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>المالية الاستراتيجية</t>
+          <t>صناعة الوقود</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>نسبة التدفق النقدي التشغيلي</t>
+          <t>دقة تسوية أرامكو</t>
         </is>
       </c>
       <c r="D8" s="49" t="inlineStr">
         <is>
-          <t>نسبة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E8" s="49" t="inlineStr">
@@ -20474,14 +19322,14 @@
         </is>
       </c>
       <c r="G8" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H8" s="62" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H8" s="59" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>&gt; 1</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="73" t="inlineStr">
@@ -20499,25 +19347,25 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M8" s="63" t="n">
-        <v>0.902</v>
+      <c r="M8" s="60" t="n">
+        <v>0.76</v>
       </c>
       <c r="N8" s="10">
         <f>IF($H8="","",IF($M8="","",MIN(1,IF($H8=0,IF($M8&lt;=0,1,0),IF($E8="↓",IFERROR($H8/$M8,0),IFERROR($M8/$H8,0))))))</f>
         <v/>
       </c>
       <c r="O8" s="20">
-        <f>IF($N8="","⏳ بانتظار هدف",IF($N8&gt;=1.0,"✅ محقق",IF($N8&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <f>IF($N8="","⏳ بانتظار هدف",IF($N8&gt;=1.0,"✅ محقق",IF($N8&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
       <c r="P8" s="74" t="inlineStr">
         <is>
-          <t>قيمة/عدد المتحقّق من «التدفق النقدي التشغيلي» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
+          <t>القيمة المتحقّقة من «دقة تسوية أرامكو» ÷ المستهدف × 100٪</t>
         </is>
       </c>
       <c r="Q8" s="74" t="inlineStr">
         <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
+          <t>نظام تشغيل المحطات</t>
         </is>
       </c>
       <c r="R8" s="15" t="inlineStr">
@@ -20532,22 +19380,22 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>السيولة ورأس المال</t>
+          <t>الموازنة والتقارير</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>النسبة الجارية (Current Ratio)</t>
+          <t>انحراف الموازنة</t>
         </is>
       </c>
       <c r="D9" s="49" t="inlineStr">
         <is>
-          <t>نسبة</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E9" s="49" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -20556,14 +19404,14 @@
         </is>
       </c>
       <c r="G9" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H9" s="62" t="n">
-        <v>1</v>
+        <v>0.14</v>
+      </c>
+      <c r="H9" s="59" t="n">
+        <v>0.1</v>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t>0.8 – 1</t>
+          <t>≤ ±10%</t>
         </is>
       </c>
       <c r="J9" s="73" t="inlineStr">
@@ -20581,8 +19429,8 @@
           <t>العمليات الداخلية</t>
         </is>
       </c>
-      <c r="M9" s="63" t="n">
-        <v>0.852</v>
+      <c r="M9" s="60" t="n">
+        <v>0.101</v>
       </c>
       <c r="N9" s="10">
         <f>IF($H9="","",IF($M9="","",MIN(1,IF($H9=0,IF($M9&lt;=0,1,0),IF($E9="↓",IFERROR($H9/$M9,0),IFERROR($M9/$H9,0))))))</f>
@@ -20594,1504 +19442,28 @@
       </c>
       <c r="P9" s="74" t="inlineStr">
         <is>
-          <t>قياس «النسبة الجارية» مقابل مستهدفه المعتمد خلال الفترة</t>
+          <t>القيمة المتحقّقة من «انحراف الموازنة» ÷ المستهدف × 100٪</t>
         </is>
       </c>
       <c r="Q9" s="74" t="inlineStr">
         <is>
-          <t>سجلات الإدارة</t>
+          <t>نظام المحاسبة / ERP (D365)</t>
         </is>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>السيولة ورأس المال</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>دورة التحويل النقدي</t>
-        </is>
-      </c>
-      <c r="D10" s="49" t="inlineStr">
-        <is>
-          <t>يوم</t>
-        </is>
-      </c>
-      <c r="E10" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="G10" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H10" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 20 يوم</t>
-        </is>
-      </c>
-      <c r="J10" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M10" s="63" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N10" s="10">
-        <f>IF($H10="","",IF($M10="","",MIN(1,IF($H10=0,IF($M10&lt;=0,1,0),IF($E10="↓",IFERROR($H10/$M10,0),IFERROR($M10/$H10,0))))))</f>
-        <v/>
-      </c>
-      <c r="O10" s="20">
-        <f>IF($N10="","⏳ بانتظار هدف",IF($N10&gt;=1.0,"✅ محقق",IF($N10&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P10" s="74" t="inlineStr">
-        <is>
-          <t>متوسط عدد أيام «دورة التحويل النقدي» خلال الفترة</t>
-        </is>
-      </c>
-      <c r="Q10" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R10" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>الذمم المدينة</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>متوسط أيام التحصيل العام (DSO)</t>
-        </is>
-      </c>
-      <c r="D11" s="49" t="inlineStr">
-        <is>
-          <t>يوم</t>
-        </is>
-      </c>
-      <c r="E11" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="G11" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H11" s="62" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 30 يوم</t>
-        </is>
-      </c>
-      <c r="J11" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="M11" s="63" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="N11" s="10">
-        <f>IF($H11="","",IF($M11="","",MIN(1,IF($H11=0,IF($M11&lt;=0,1,0),IF($E11="↓",IFERROR($H11/$M11,0),IFERROR($M11/$H11,0))))))</f>
-        <v/>
-      </c>
-      <c r="O11" s="20">
-        <f>IF($N11="","⏳ بانتظار هدف",IF($N11&gt;=1.0,"✅ محقق",IF($N11&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P11" s="74" t="inlineStr">
-        <is>
-          <t>مجموع أيام «أيام التحصيل العام» ÷ عدد الحالات</t>
-        </is>
-      </c>
-      <c r="Q11" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R11" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>الذمم المدينة</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>نسبة التحصيل العام (الشركة)</t>
-        </is>
-      </c>
-      <c r="D12" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E12" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="G12" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H12" s="59" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 95%</t>
-        </is>
-      </c>
-      <c r="J12" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="M12" s="60" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="N12" s="10">
-        <f>IF($H12="","",IF($M12="","",MIN(1,IF($H12=0,IF($M12&lt;=0,1,0),IF($E12="↓",IFERROR($H12/$M12,0),IFERROR($M12/$H12,0))))))</f>
-        <v/>
-      </c>
-      <c r="O12" s="20">
-        <f>IF($N12="","⏳ بانتظار هدف",IF($N12&gt;=1.0,"✅ محقق",IF($N12&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P12" s="74" t="inlineStr">
-        <is>
-          <t>قيمة/عدد المتحقّق من «التحصيل العام» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
-        </is>
-      </c>
-      <c r="Q12" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R12" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>الذمم المدينة</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>نسبة الذمم المتأخرة</t>
-        </is>
-      </c>
-      <c r="D13" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E13" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G13" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H13" s="59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 10%</t>
-        </is>
-      </c>
-      <c r="J13" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M13" s="60" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="N13" s="10">
-        <f>IF($H13="","",IF($M13="","",MIN(1,IF($H13=0,IF($M13&lt;=0,1,0),IF($E13="↓",IFERROR($H13/$M13,0),IFERROR($M13/$H13,0))))))</f>
-        <v/>
-      </c>
-      <c r="O13" s="20">
-        <f>IF($N13="","⏳ بانتظار هدف",IF($N13&gt;=1.0,"✅ محقق",IF($N13&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P13" s="74" t="inlineStr">
-        <is>
-          <t>قيمة/عدد المتحقّق من «الذمم المتأخرة» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
-        </is>
-      </c>
-      <c r="Q13" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R13" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>الذمم المدينة</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>نسبة الديون المعدومة</t>
-        </is>
-      </c>
-      <c r="D14" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E14" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G14" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H14" s="59" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 1%</t>
-        </is>
-      </c>
-      <c r="J14" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M14" s="60" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="N14" s="10">
-        <f>IF($H14="","",IF($M14="","",MIN(1,IF($H14=0,IF($M14&lt;=0,1,0),IF($E14="↓",IFERROR($H14/$M14,0),IFERROR($M14/$H14,0))))))</f>
-        <v/>
-      </c>
-      <c r="O14" s="20">
-        <f>IF($N14="","⏳ بانتظار هدف",IF($N14&gt;=1.0,"✅ محقق",IF($N14&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P14" s="74" t="inlineStr">
-        <is>
-          <t>قيمة/عدد المتحقّق من «الديون المعدومة» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
-        </is>
-      </c>
-      <c r="Q14" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R14" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>الذمم الدائنة</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>سداد الموردين في الموعد</t>
-        </is>
-      </c>
-      <c r="D15" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E15" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G15" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H15" s="59" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 98%</t>
-        </is>
-      </c>
-      <c r="J15" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="M15" s="60" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="N15" s="10">
-        <f>IF($H15="","",IF($M15="","",MIN(1,IF($H15=0,IF($M15&lt;=0,1,0),IF($E15="↓",IFERROR($H15/$M15,0),IFERROR($M15/$H15,0))))))</f>
-        <v/>
-      </c>
-      <c r="O15" s="20">
-        <f>IF($N15="","⏳ بانتظار هدف",IF($N15&gt;=1.0,"✅ محقق",IF($N15&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P15" s="74" t="inlineStr">
-        <is>
-          <t>القيمة المتحقّقة من «سداد الموردين في الموعد» ÷ المستهدف × 100٪</t>
-        </is>
-      </c>
-      <c r="Q15" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R15" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>الذمم الدائنة</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>اكتمال مطابقة حسابات الموردين</t>
-        </is>
-      </c>
-      <c r="D16" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E16" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G16" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H16" s="59" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>≥ 95%</t>
-        </is>
-      </c>
-      <c r="J16" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M16" s="60" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="N16" s="10">
-        <f>IF($H16="","",IF($M16="","",MIN(1,IF($H16=0,IF($M16&lt;=0,1,0),IF($E16="↓",IFERROR($H16/$M16,0),IFERROR($M16/$H16,0))))))</f>
-        <v/>
-      </c>
-      <c r="O16" s="20">
-        <f>IF($N16="","⏳ بانتظار هدف",IF($N16&gt;=1.0,"✅ محقق",IF($N16&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P16" s="74" t="inlineStr">
-        <is>
-          <t>القيمة المتحقّقة من «اكتمال مطابقة حسابات الموردين» ÷ المستهدف × 100٪</t>
-        </is>
-      </c>
-      <c r="Q16" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R16" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>الخزينة</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>دقة التنبؤ النقدي</t>
-        </is>
-      </c>
-      <c r="D17" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E17" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G17" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H17" s="59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>±10%</t>
-        </is>
-      </c>
-      <c r="J17" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L17" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M17" s="60" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N17" s="10">
-        <f>IF($H17="","",IF($M17="","",MIN(1,IF($H17=0,IF($M17&lt;=0,1,0),IF($E17="↓",IFERROR($H17/$M17,0),IFERROR($M17/$H17,0))))))</f>
-        <v/>
-      </c>
-      <c r="O17" s="20">
-        <f>IF($N17="","⏳ بانتظار هدف",IF($N17&gt;=1.0,"✅ محقق",IF($N17&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P17" s="74" t="inlineStr">
-        <is>
-          <t>القيمة المتحقّقة من «دقة التنبؤ النقدي» ÷ المستهدف × 100٪</t>
-        </is>
-      </c>
-      <c r="Q17" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R17" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>صناعة الوقود</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>تباين مخزون الوقود</t>
-        </is>
-      </c>
-      <c r="D18" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E18" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G18" s="59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H18" s="59" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 0.1%</t>
-        </is>
-      </c>
-      <c r="J18" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M18" s="60" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N18" s="10">
-        <f>IF($H18="","",IF($M18="","",MIN(1,IF($H18=0,IF($M18&lt;=0,1,0),IF($E18="↓",IFERROR($H18/$M18,0),IFERROR($M18/$H18,0))))))</f>
-        <v/>
-      </c>
-      <c r="O18" s="20">
-        <f>IF($N18="","⏳ بانتظار هدف",IF($N18&gt;=1.0,"✅ محقق",IF($N18&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P18" s="74" t="inlineStr">
-        <is>
-          <t>القيمة المتحقّقة من «تباين مخزون الوقود» ÷ المستهدف × 100٪</t>
-        </is>
-      </c>
-      <c r="Q18" s="74" t="inlineStr">
-        <is>
-          <t>نظام تشغيل المحطات</t>
-        </is>
-      </c>
-      <c r="R18" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>صناعة الوقود</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>دقة مطابقة المخزون</t>
-        </is>
-      </c>
-      <c r="D19" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E19" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G19" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H19" s="59" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 99.5%</t>
-        </is>
-      </c>
-      <c r="J19" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L19" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M19" s="60" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="N19" s="10">
-        <f>IF($H19="","",IF($M19="","",MIN(1,IF($H19=0,IF($M19&lt;=0,1,0),IF($E19="↓",IFERROR($H19/$M19,0),IFERROR($M19/$H19,0))))))</f>
-        <v/>
-      </c>
-      <c r="O19" s="20">
-        <f>IF($N19="","⏳ بانتظار هدف",IF($N19&gt;=1.0,"✅ محقق",IF($N19&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P19" s="74" t="inlineStr">
-        <is>
-          <t>القيمة المتحقّقة من «دقة مطابقة المخزون» ÷ المستهدف × 100٪</t>
-        </is>
-      </c>
-      <c r="Q19" s="74" t="inlineStr">
-        <is>
-          <t>نظام إدارة الجودة (QMS)</t>
-        </is>
-      </c>
-      <c r="R19" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>صناعة الوقود</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>دقة تسوية أرامكو</t>
-        </is>
-      </c>
-      <c r="D20" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E20" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G20" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H20" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M20" s="60" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="N20" s="10">
-        <f>IF($H20="","",IF($M20="","",MIN(1,IF($H20=0,IF($M20&lt;=0,1,0),IF($E20="↓",IFERROR($H20/$M20,0),IFERROR($M20/$H20,0))))))</f>
-        <v/>
-      </c>
-      <c r="O20" s="20">
-        <f>IF($N20="","⏳ بانتظار هدف",IF($N20&gt;=1.0,"✅ محقق",IF($N20&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P20" s="74" t="inlineStr">
-        <is>
-          <t>القيمة المتحقّقة من «دقة تسوية أرامكو» ÷ المستهدف × 100٪</t>
-        </is>
-      </c>
-      <c r="Q20" s="74" t="inlineStr">
-        <is>
-          <t>نظام تشغيل المحطات</t>
-        </is>
-      </c>
-      <c r="R20" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>تمويل الامتياز</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>نسبة تحصيل الامتياز</t>
-        </is>
-      </c>
-      <c r="D21" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E21" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="G21" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H21" s="59" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 98%</t>
-        </is>
-      </c>
-      <c r="J21" s="73" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="L21" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="M21" s="60" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="N21" s="10">
-        <f>IF($H21="","",IF($M21="","",MIN(1,IF($H21=0,IF($M21&lt;=0,1,0),IF($E21="↓",IFERROR($H21/$M21,0),IFERROR($M21/$H21,0))))))</f>
-        <v/>
-      </c>
-      <c r="O21" s="20">
-        <f>IF($N21="","⏳ بانتظار هدف",IF($N21&gt;=1.0,"✅ محقق",IF($N21&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P21" s="74" t="inlineStr">
-        <is>
-          <t>قيمة/عدد المتحقّق من «تحصيل الامتياز» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
-        </is>
-      </c>
-      <c r="Q21" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R21" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>تمويل الامتياز</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>أيام تحصيل رسوم الامتياز</t>
-        </is>
-      </c>
-      <c r="D22" s="49" t="inlineStr">
-        <is>
-          <t>يوم</t>
-        </is>
-      </c>
-      <c r="E22" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="G22" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H22" s="62" t="n">
-        <v>15</v>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 15 يوم</t>
-        </is>
-      </c>
-      <c r="J22" s="73" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="M22" s="63" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N22" s="10">
-        <f>IF($H22="","",IF($M22="","",MIN(1,IF($H22=0,IF($M22&lt;=0,1,0),IF($E22="↓",IFERROR($H22/$M22,0),IFERROR($M22/$H22,0))))))</f>
-        <v/>
-      </c>
-      <c r="O22" s="20">
-        <f>IF($N22="","⏳ بانتظار هدف",IF($N22&gt;=1.0,"✅ محقق",IF($N22&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P22" s="74" t="inlineStr">
-        <is>
-          <t>متوسط عدد أيام «أيام تحصيل رسوم الامتياز» خلال الفترة</t>
-        </is>
-      </c>
-      <c r="Q22" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R22" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>العقار والإيجار</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>نسبة تحصيل الإيجار</t>
-        </is>
-      </c>
-      <c r="D23" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E23" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="G23" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H23" s="59" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 98%</t>
-        </is>
-      </c>
-      <c r="J23" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>منظومة التأجير</t>
-        </is>
-      </c>
-      <c r="L23" s="15" t="inlineStr">
-        <is>
-          <t>مالي</t>
-        </is>
-      </c>
-      <c r="M23" s="60" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="N23" s="10">
-        <f>IF($H23="","",IF($M23="","",MIN(1,IF($H23=0,IF($M23&lt;=0,1,0),IF($E23="↓",IFERROR($H23/$M23,0),IFERROR($M23/$H23,0))))))</f>
-        <v/>
-      </c>
-      <c r="O23" s="20">
-        <f>IF($N23="","⏳ بانتظار هدف",IF($N23&gt;=1.0,"✅ محقق",IF($N23&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P23" s="74" t="inlineStr">
-        <is>
-          <t>قيمة/عدد المتحقّق من «تحصيل الإيجار» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
-        </is>
-      </c>
-      <c r="Q23" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R23" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>العقار والإيجار</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>معدل تجديد عقود الإيجار</t>
-        </is>
-      </c>
-      <c r="D24" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>🔴 رئيسي</t>
-        </is>
-      </c>
-      <c r="G24" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H24" s="59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 90%</t>
-        </is>
-      </c>
-      <c r="J24" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>منظومة التأجير</t>
-        </is>
-      </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M24" s="60" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="N24" s="10">
-        <f>IF($H24="","",IF($M24="","",MIN(1,IF($H24=0,IF($M24&lt;=0,1,0),IF($E24="↓",IFERROR($H24/$M24,0),IFERROR($M24/$H24,0))))))</f>
-        <v/>
-      </c>
-      <c r="O24" s="20">
-        <f>IF($N24="","⏳ بانتظار هدف",IF($N24&gt;=1.0,"✅ محقق",IF($N24&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P24" s="74" t="inlineStr">
-        <is>
-          <t>عدد حالات «تجديد عقود الإيجار» خلال الفترة ÷ إجمالي الحالات القابلة للقياس × 100٪</t>
-        </is>
-      </c>
-      <c r="Q24" s="74" t="inlineStr">
-        <is>
-          <t>نظام إدارة العقود (CRM)</t>
-        </is>
-      </c>
-      <c r="R24" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>الموازنة والتقارير</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>انحراف الموازنة</t>
-        </is>
-      </c>
-      <c r="D25" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E25" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G25" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H25" s="59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>≤ ±10%</t>
-        </is>
-      </c>
-      <c r="J25" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M25" s="60" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="N25" s="10">
-        <f>IF($H25="","",IF($M25="","",MIN(1,IF($H25=0,IF($M25&lt;=0,1,0),IF($E25="↓",IFERROR($H25/$M25,0),IFERROR($M25/$H25,0))))))</f>
-        <v/>
-      </c>
-      <c r="O25" s="20">
-        <f>IF($N25="","⏳ بانتظار هدف",IF($N25&gt;=1.0,"✅ محقق",IF($N25&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P25" s="74" t="inlineStr">
-        <is>
-          <t>القيمة المتحقّقة من «انحراف الموازنة» ÷ المستهدف × 100٪</t>
-        </is>
-      </c>
-      <c r="Q25" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R25" s="15" t="inlineStr">
-        <is>
           <t>ربعي</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>الموازنة والتقارير</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>أيام الإقفال الشهري</t>
-        </is>
-      </c>
-      <c r="D26" s="49" t="inlineStr">
-        <is>
-          <t>يوم</t>
-        </is>
-      </c>
-      <c r="E26" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G26" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H26" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" s="22" t="inlineStr">
-        <is>
-          <t>≤ 6 أيام</t>
-        </is>
-      </c>
-      <c r="J26" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M26" s="63" t="n">
-        <v>7.044</v>
-      </c>
-      <c r="N26" s="10">
-        <f>IF($H26="","",IF($M26="","",MIN(1,IF($H26=0,IF($M26&lt;=0,1,0),IF($E26="↓",IFERROR($H26/$M26,0),IFERROR($M26/$H26,0))))))</f>
-        <v/>
-      </c>
-      <c r="O26" s="20">
-        <f>IF($N26="","⏳ بانتظار هدف",IF($N26&gt;=1.0,"✅ محقق",IF($N26&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P26" s="74" t="inlineStr">
-        <is>
-          <t>متوسط عدد أيام «أيام الإقفال الشهري» خلال الفترة</t>
-        </is>
-      </c>
-      <c r="Q26" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R26" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>الموازنة والتقارير</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>نسبة تسويات التدقيق</t>
-        </is>
-      </c>
-      <c r="D27" s="49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E27" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>🟠 مهم</t>
-        </is>
-      </c>
-      <c r="G27" s="59" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H27" s="59" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 2%</t>
-        </is>
-      </c>
-      <c r="J27" s="73" t="inlineStr">
-        <is>
-          <t>الاستدامة</t>
-        </is>
-      </c>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>جودة التشغيل</t>
-        </is>
-      </c>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>العمليات الداخلية</t>
-        </is>
-      </c>
-      <c r="M27" s="60" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N27" s="10">
-        <f>IF($H27="","",IF($M27="","",MIN(1,IF($H27=0,IF($M27&lt;=0,1,0),IF($E27="↓",IFERROR($H27/$M27,0),IFERROR($M27/$H27,0))))))</f>
-        <v/>
-      </c>
-      <c r="O27" s="20">
-        <f>IF($N27="","⏳ بانتظار هدف",IF($N27&gt;=1.0,"✅ محقق",IF($N27&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="P27" s="74" t="inlineStr">
-        <is>
-          <t>قيمة/عدد المتحقّق من «تسويات التدقيق» ÷ الإجمالي المستهدف لنفس البند × 100٪</t>
-        </is>
-      </c>
-      <c r="Q27" s="74" t="inlineStr">
-        <is>
-          <t>نظام المحاسبة / ERP (D365)</t>
-        </is>
-      </c>
-      <c r="R27" s="15" t="inlineStr">
-        <is>
-          <t>ربعي</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:R27"/>
+  <autoFilter ref="A3:R9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="M4 M5 M6 M7 M8 M9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -23306,7 +20678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -27836,834 +25208,6 @@
       </c>
       <c r="K98" s="15">
         <f>IF($G98="",0,$I98)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="15" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C99" s="13">
-        <f>'الإدارة المالية'!C10</f>
-        <v/>
-      </c>
-      <c r="D99" s="15">
-        <f>'الإدارة المالية'!J10</f>
-        <v/>
-      </c>
-      <c r="E99" s="13">
-        <f>'الإدارة المالية'!K10</f>
-        <v/>
-      </c>
-      <c r="F99" s="15">
-        <f>'الإدارة المالية'!L10</f>
-        <v/>
-      </c>
-      <c r="G99" s="50">
-        <f>'الإدارة المالية'!N10</f>
-        <v/>
-      </c>
-      <c r="H99" s="15">
-        <f>'الإدارة المالية'!O10</f>
-        <v/>
-      </c>
-      <c r="I99" s="24">
-        <f>'الإدارة المالية'!G10</f>
-        <v/>
-      </c>
-      <c r="J99" s="15">
-        <f>IF($G99="",0,$G99*$I99)</f>
-        <v/>
-      </c>
-      <c r="K99" s="15">
-        <f>IF($G99="",0,$I99)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C100" s="13">
-        <f>'الإدارة المالية'!C11</f>
-        <v/>
-      </c>
-      <c r="D100" s="15">
-        <f>'الإدارة المالية'!J11</f>
-        <v/>
-      </c>
-      <c r="E100" s="13">
-        <f>'الإدارة المالية'!K11</f>
-        <v/>
-      </c>
-      <c r="F100" s="15">
-        <f>'الإدارة المالية'!L11</f>
-        <v/>
-      </c>
-      <c r="G100" s="50">
-        <f>'الإدارة المالية'!N11</f>
-        <v/>
-      </c>
-      <c r="H100" s="15">
-        <f>'الإدارة المالية'!O11</f>
-        <v/>
-      </c>
-      <c r="I100" s="24">
-        <f>'الإدارة المالية'!G11</f>
-        <v/>
-      </c>
-      <c r="J100" s="15">
-        <f>IF($G100="",0,$G100*$I100)</f>
-        <v/>
-      </c>
-      <c r="K100" s="15">
-        <f>IF($G100="",0,$I100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C101" s="13">
-        <f>'الإدارة المالية'!C12</f>
-        <v/>
-      </c>
-      <c r="D101" s="15">
-        <f>'الإدارة المالية'!J12</f>
-        <v/>
-      </c>
-      <c r="E101" s="13">
-        <f>'الإدارة المالية'!K12</f>
-        <v/>
-      </c>
-      <c r="F101" s="15">
-        <f>'الإدارة المالية'!L12</f>
-        <v/>
-      </c>
-      <c r="G101" s="50">
-        <f>'الإدارة المالية'!N12</f>
-        <v/>
-      </c>
-      <c r="H101" s="15">
-        <f>'الإدارة المالية'!O12</f>
-        <v/>
-      </c>
-      <c r="I101" s="24">
-        <f>'الإدارة المالية'!G12</f>
-        <v/>
-      </c>
-      <c r="J101" s="15">
-        <f>IF($G101="",0,$G101*$I101)</f>
-        <v/>
-      </c>
-      <c r="K101" s="15">
-        <f>IF($G101="",0,$I101)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C102" s="13">
-        <f>'الإدارة المالية'!C13</f>
-        <v/>
-      </c>
-      <c r="D102" s="15">
-        <f>'الإدارة المالية'!J13</f>
-        <v/>
-      </c>
-      <c r="E102" s="13">
-        <f>'الإدارة المالية'!K13</f>
-        <v/>
-      </c>
-      <c r="F102" s="15">
-        <f>'الإدارة المالية'!L13</f>
-        <v/>
-      </c>
-      <c r="G102" s="50">
-        <f>'الإدارة المالية'!N13</f>
-        <v/>
-      </c>
-      <c r="H102" s="15">
-        <f>'الإدارة المالية'!O13</f>
-        <v/>
-      </c>
-      <c r="I102" s="24">
-        <f>'الإدارة المالية'!G13</f>
-        <v/>
-      </c>
-      <c r="J102" s="15">
-        <f>IF($G102="",0,$G102*$I102)</f>
-        <v/>
-      </c>
-      <c r="K102" s="15">
-        <f>IF($G102="",0,$I102)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="15" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C103" s="13">
-        <f>'الإدارة المالية'!C14</f>
-        <v/>
-      </c>
-      <c r="D103" s="15">
-        <f>'الإدارة المالية'!J14</f>
-        <v/>
-      </c>
-      <c r="E103" s="13">
-        <f>'الإدارة المالية'!K14</f>
-        <v/>
-      </c>
-      <c r="F103" s="15">
-        <f>'الإدارة المالية'!L14</f>
-        <v/>
-      </c>
-      <c r="G103" s="50">
-        <f>'الإدارة المالية'!N14</f>
-        <v/>
-      </c>
-      <c r="H103" s="15">
-        <f>'الإدارة المالية'!O14</f>
-        <v/>
-      </c>
-      <c r="I103" s="24">
-        <f>'الإدارة المالية'!G14</f>
-        <v/>
-      </c>
-      <c r="J103" s="15">
-        <f>IF($G103="",0,$G103*$I103)</f>
-        <v/>
-      </c>
-      <c r="K103" s="15">
-        <f>IF($G103="",0,$I103)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="15" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C104" s="13">
-        <f>'الإدارة المالية'!C15</f>
-        <v/>
-      </c>
-      <c r="D104" s="15">
-        <f>'الإدارة المالية'!J15</f>
-        <v/>
-      </c>
-      <c r="E104" s="13">
-        <f>'الإدارة المالية'!K15</f>
-        <v/>
-      </c>
-      <c r="F104" s="15">
-        <f>'الإدارة المالية'!L15</f>
-        <v/>
-      </c>
-      <c r="G104" s="50">
-        <f>'الإدارة المالية'!N15</f>
-        <v/>
-      </c>
-      <c r="H104" s="15">
-        <f>'الإدارة المالية'!O15</f>
-        <v/>
-      </c>
-      <c r="I104" s="24">
-        <f>'الإدارة المالية'!G15</f>
-        <v/>
-      </c>
-      <c r="J104" s="15">
-        <f>IF($G104="",0,$G104*$I104)</f>
-        <v/>
-      </c>
-      <c r="K104" s="15">
-        <f>IF($G104="",0,$I104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C105" s="13">
-        <f>'الإدارة المالية'!C16</f>
-        <v/>
-      </c>
-      <c r="D105" s="15">
-        <f>'الإدارة المالية'!J16</f>
-        <v/>
-      </c>
-      <c r="E105" s="13">
-        <f>'الإدارة المالية'!K16</f>
-        <v/>
-      </c>
-      <c r="F105" s="15">
-        <f>'الإدارة المالية'!L16</f>
-        <v/>
-      </c>
-      <c r="G105" s="50">
-        <f>'الإدارة المالية'!N16</f>
-        <v/>
-      </c>
-      <c r="H105" s="15">
-        <f>'الإدارة المالية'!O16</f>
-        <v/>
-      </c>
-      <c r="I105" s="24">
-        <f>'الإدارة المالية'!G16</f>
-        <v/>
-      </c>
-      <c r="J105" s="15">
-        <f>IF($G105="",0,$G105*$I105)</f>
-        <v/>
-      </c>
-      <c r="K105" s="15">
-        <f>IF($G105="",0,$I105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="15" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C106" s="13">
-        <f>'الإدارة المالية'!C17</f>
-        <v/>
-      </c>
-      <c r="D106" s="15">
-        <f>'الإدارة المالية'!J17</f>
-        <v/>
-      </c>
-      <c r="E106" s="13">
-        <f>'الإدارة المالية'!K17</f>
-        <v/>
-      </c>
-      <c r="F106" s="15">
-        <f>'الإدارة المالية'!L17</f>
-        <v/>
-      </c>
-      <c r="G106" s="50">
-        <f>'الإدارة المالية'!N17</f>
-        <v/>
-      </c>
-      <c r="H106" s="15">
-        <f>'الإدارة المالية'!O17</f>
-        <v/>
-      </c>
-      <c r="I106" s="24">
-        <f>'الإدارة المالية'!G17</f>
-        <v/>
-      </c>
-      <c r="J106" s="15">
-        <f>IF($G106="",0,$G106*$I106)</f>
-        <v/>
-      </c>
-      <c r="K106" s="15">
-        <f>IF($G106="",0,$I106)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C107" s="13">
-        <f>'الإدارة المالية'!C18</f>
-        <v/>
-      </c>
-      <c r="D107" s="15">
-        <f>'الإدارة المالية'!J18</f>
-        <v/>
-      </c>
-      <c r="E107" s="13">
-        <f>'الإدارة المالية'!K18</f>
-        <v/>
-      </c>
-      <c r="F107" s="15">
-        <f>'الإدارة المالية'!L18</f>
-        <v/>
-      </c>
-      <c r="G107" s="50">
-        <f>'الإدارة المالية'!N18</f>
-        <v/>
-      </c>
-      <c r="H107" s="15">
-        <f>'الإدارة المالية'!O18</f>
-        <v/>
-      </c>
-      <c r="I107" s="24">
-        <f>'الإدارة المالية'!G18</f>
-        <v/>
-      </c>
-      <c r="J107" s="15">
-        <f>IF($G107="",0,$G107*$I107)</f>
-        <v/>
-      </c>
-      <c r="K107" s="15">
-        <f>IF($G107="",0,$I107)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C108" s="13">
-        <f>'الإدارة المالية'!C19</f>
-        <v/>
-      </c>
-      <c r="D108" s="15">
-        <f>'الإدارة المالية'!J19</f>
-        <v/>
-      </c>
-      <c r="E108" s="13">
-        <f>'الإدارة المالية'!K19</f>
-        <v/>
-      </c>
-      <c r="F108" s="15">
-        <f>'الإدارة المالية'!L19</f>
-        <v/>
-      </c>
-      <c r="G108" s="50">
-        <f>'الإدارة المالية'!N19</f>
-        <v/>
-      </c>
-      <c r="H108" s="15">
-        <f>'الإدارة المالية'!O19</f>
-        <v/>
-      </c>
-      <c r="I108" s="24">
-        <f>'الإدارة المالية'!G19</f>
-        <v/>
-      </c>
-      <c r="J108" s="15">
-        <f>IF($G108="",0,$G108*$I108)</f>
-        <v/>
-      </c>
-      <c r="K108" s="15">
-        <f>IF($G108="",0,$I108)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C109" s="13">
-        <f>'الإدارة المالية'!C20</f>
-        <v/>
-      </c>
-      <c r="D109" s="15">
-        <f>'الإدارة المالية'!J20</f>
-        <v/>
-      </c>
-      <c r="E109" s="13">
-        <f>'الإدارة المالية'!K20</f>
-        <v/>
-      </c>
-      <c r="F109" s="15">
-        <f>'الإدارة المالية'!L20</f>
-        <v/>
-      </c>
-      <c r="G109" s="50">
-        <f>'الإدارة المالية'!N20</f>
-        <v/>
-      </c>
-      <c r="H109" s="15">
-        <f>'الإدارة المالية'!O20</f>
-        <v/>
-      </c>
-      <c r="I109" s="24">
-        <f>'الإدارة المالية'!G20</f>
-        <v/>
-      </c>
-      <c r="J109" s="15">
-        <f>IF($G109="",0,$G109*$I109)</f>
-        <v/>
-      </c>
-      <c r="K109" s="15">
-        <f>IF($G109="",0,$I109)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="15" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C110" s="13">
-        <f>'الإدارة المالية'!C21</f>
-        <v/>
-      </c>
-      <c r="D110" s="15">
-        <f>'الإدارة المالية'!J21</f>
-        <v/>
-      </c>
-      <c r="E110" s="13">
-        <f>'الإدارة المالية'!K21</f>
-        <v/>
-      </c>
-      <c r="F110" s="15">
-        <f>'الإدارة المالية'!L21</f>
-        <v/>
-      </c>
-      <c r="G110" s="50">
-        <f>'الإدارة المالية'!N21</f>
-        <v/>
-      </c>
-      <c r="H110" s="15">
-        <f>'الإدارة المالية'!O21</f>
-        <v/>
-      </c>
-      <c r="I110" s="24">
-        <f>'الإدارة المالية'!G21</f>
-        <v/>
-      </c>
-      <c r="J110" s="15">
-        <f>IF($G110="",0,$G110*$I110)</f>
-        <v/>
-      </c>
-      <c r="K110" s="15">
-        <f>IF($G110="",0,$I110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C111" s="13">
-        <f>'الإدارة المالية'!C22</f>
-        <v/>
-      </c>
-      <c r="D111" s="15">
-        <f>'الإدارة المالية'!J22</f>
-        <v/>
-      </c>
-      <c r="E111" s="13">
-        <f>'الإدارة المالية'!K22</f>
-        <v/>
-      </c>
-      <c r="F111" s="15">
-        <f>'الإدارة المالية'!L22</f>
-        <v/>
-      </c>
-      <c r="G111" s="50">
-        <f>'الإدارة المالية'!N22</f>
-        <v/>
-      </c>
-      <c r="H111" s="15">
-        <f>'الإدارة المالية'!O22</f>
-        <v/>
-      </c>
-      <c r="I111" s="24">
-        <f>'الإدارة المالية'!G22</f>
-        <v/>
-      </c>
-      <c r="J111" s="15">
-        <f>IF($G111="",0,$G111*$I111)</f>
-        <v/>
-      </c>
-      <c r="K111" s="15">
-        <f>IF($G111="",0,$I111)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="15" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C112" s="13">
-        <f>'الإدارة المالية'!C23</f>
-        <v/>
-      </c>
-      <c r="D112" s="15">
-        <f>'الإدارة المالية'!J23</f>
-        <v/>
-      </c>
-      <c r="E112" s="13">
-        <f>'الإدارة المالية'!K23</f>
-        <v/>
-      </c>
-      <c r="F112" s="15">
-        <f>'الإدارة المالية'!L23</f>
-        <v/>
-      </c>
-      <c r="G112" s="50">
-        <f>'الإدارة المالية'!N23</f>
-        <v/>
-      </c>
-      <c r="H112" s="15">
-        <f>'الإدارة المالية'!O23</f>
-        <v/>
-      </c>
-      <c r="I112" s="24">
-        <f>'الإدارة المالية'!G23</f>
-        <v/>
-      </c>
-      <c r="J112" s="15">
-        <f>IF($G112="",0,$G112*$I112)</f>
-        <v/>
-      </c>
-      <c r="K112" s="15">
-        <f>IF($G112="",0,$I112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="15" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C113" s="13">
-        <f>'الإدارة المالية'!C24</f>
-        <v/>
-      </c>
-      <c r="D113" s="15">
-        <f>'الإدارة المالية'!J24</f>
-        <v/>
-      </c>
-      <c r="E113" s="13">
-        <f>'الإدارة المالية'!K24</f>
-        <v/>
-      </c>
-      <c r="F113" s="15">
-        <f>'الإدارة المالية'!L24</f>
-        <v/>
-      </c>
-      <c r="G113" s="50">
-        <f>'الإدارة المالية'!N24</f>
-        <v/>
-      </c>
-      <c r="H113" s="15">
-        <f>'الإدارة المالية'!O24</f>
-        <v/>
-      </c>
-      <c r="I113" s="24">
-        <f>'الإدارة المالية'!G24</f>
-        <v/>
-      </c>
-      <c r="J113" s="15">
-        <f>IF($G113="",0,$G113*$I113)</f>
-        <v/>
-      </c>
-      <c r="K113" s="15">
-        <f>IF($G113="",0,$I113)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C114" s="13">
-        <f>'الإدارة المالية'!C25</f>
-        <v/>
-      </c>
-      <c r="D114" s="15">
-        <f>'الإدارة المالية'!J25</f>
-        <v/>
-      </c>
-      <c r="E114" s="13">
-        <f>'الإدارة المالية'!K25</f>
-        <v/>
-      </c>
-      <c r="F114" s="15">
-        <f>'الإدارة المالية'!L25</f>
-        <v/>
-      </c>
-      <c r="G114" s="50">
-        <f>'الإدارة المالية'!N25</f>
-        <v/>
-      </c>
-      <c r="H114" s="15">
-        <f>'الإدارة المالية'!O25</f>
-        <v/>
-      </c>
-      <c r="I114" s="24">
-        <f>'الإدارة المالية'!G25</f>
-        <v/>
-      </c>
-      <c r="J114" s="15">
-        <f>IF($G114="",0,$G114*$I114)</f>
-        <v/>
-      </c>
-      <c r="K114" s="15">
-        <f>IF($G114="",0,$I114)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C115" s="13">
-        <f>'الإدارة المالية'!C26</f>
-        <v/>
-      </c>
-      <c r="D115" s="15">
-        <f>'الإدارة المالية'!J26</f>
-        <v/>
-      </c>
-      <c r="E115" s="13">
-        <f>'الإدارة المالية'!K26</f>
-        <v/>
-      </c>
-      <c r="F115" s="15">
-        <f>'الإدارة المالية'!L26</f>
-        <v/>
-      </c>
-      <c r="G115" s="50">
-        <f>'الإدارة المالية'!N26</f>
-        <v/>
-      </c>
-      <c r="H115" s="15">
-        <f>'الإدارة المالية'!O26</f>
-        <v/>
-      </c>
-      <c r="I115" s="24">
-        <f>'الإدارة المالية'!G26</f>
-        <v/>
-      </c>
-      <c r="J115" s="15">
-        <f>IF($G115="",0,$G115*$I115)</f>
-        <v/>
-      </c>
-      <c r="K115" s="15">
-        <f>IF($G115="",0,$I115)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="15" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C116" s="13">
-        <f>'الإدارة المالية'!C27</f>
-        <v/>
-      </c>
-      <c r="D116" s="15">
-        <f>'الإدارة المالية'!J27</f>
-        <v/>
-      </c>
-      <c r="E116" s="13">
-        <f>'الإدارة المالية'!K27</f>
-        <v/>
-      </c>
-      <c r="F116" s="15">
-        <f>'الإدارة المالية'!L27</f>
-        <v/>
-      </c>
-      <c r="G116" s="50">
-        <f>'الإدارة المالية'!N27</f>
-        <v/>
-      </c>
-      <c r="H116" s="15">
-        <f>'الإدارة المالية'!O27</f>
-        <v/>
-      </c>
-      <c r="I116" s="24">
-        <f>'الإدارة المالية'!G27</f>
-        <v/>
-      </c>
-      <c r="J116" s="15">
-        <f>IF($G116="",0,$G116*$I116)</f>
-        <v/>
-      </c>
-      <c r="K116" s="15">
-        <f>IF($G116="",0,$I116)</f>
         <v/>
       </c>
     </row>
@@ -28943,11 +25487,11 @@
         </is>
       </c>
       <c r="D19" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"التوسع في المواقع")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"التوسع في المواقع")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"التوسع في المواقع"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"التوسع في المواقع"),"—")</f>
         <v/>
       </c>
     </row>
@@ -28963,11 +25507,11 @@
         </is>
       </c>
       <c r="D20" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"الامتياز التجاري")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"الامتياز التجاري")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
     </row>
@@ -28983,11 +25527,11 @@
         </is>
       </c>
       <c r="D21" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"زيادة وصول العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"زيادة وصول العملاء")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"زيادة وصول العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"زيادة وصول العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29003,11 +25547,11 @@
         </is>
       </c>
       <c r="D22" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"إطلاق مشاريع جديدة")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"إطلاق مشاريع جديدة")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"إطلاق مشاريع جديدة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"إطلاق مشاريع جديدة"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29023,11 +25567,11 @@
         </is>
       </c>
       <c r="D23" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"تطوير التصاميم والهوية")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"تطوير التصاميم والهوية")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"تطوير التصاميم والهوية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"تطوير التصاميم والهوية"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29043,11 +25587,11 @@
         </is>
       </c>
       <c r="D24" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"التحول التقني")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"التحول التقني")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"التحول التقني"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"التحول التقني"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29063,11 +25607,11 @@
         </is>
       </c>
       <c r="D25" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"ساحات درب")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"ساحات درب")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"ساحات درب"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"ساحات درب"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29083,11 +25627,11 @@
         </is>
       </c>
       <c r="D26" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"تطبيق «تانكي»")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"تطبيق «تانكي»")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"تطبيق «تانكي»"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"تطبيق «تانكي»"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29103,11 +25647,11 @@
         </is>
       </c>
       <c r="D27" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"تعزيز تجربة العملاء")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"تعزيز تجربة العملاء")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"تعزيز تجربة العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"تعزيز تجربة العملاء"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29123,11 +25667,11 @@
         </is>
       </c>
       <c r="D28" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"جودة التشغيل")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"جودة التشغيل")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"جودة التشغيل"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"جودة التشغيل"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29143,11 +25687,11 @@
         </is>
       </c>
       <c r="D29" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"منظومة التأجير")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"منظومة التأجير")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"منظومة التأجير"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"منظومة التأجير"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29163,11 +25707,11 @@
         </is>
       </c>
       <c r="D30" s="20">
-        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$116,"الاستثمار في الموظفين")</f>
+        <f>COUNTIF('قاعدة المؤشرات'!$E$2:$E$98,"الاستثمار في الموظفين")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"الاستثمار في الموظفين"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"الاستثمار في الموظفين"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29224,7 +25768,7 @@
     </row>
     <row r="6">
       <c r="B6" s="37">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$F$2:$F$116,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$F$2:$F$98,"مالي"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29281,15 +25825,15 @@
     </row>
     <row r="10">
       <c r="B10" s="40">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"زيادة وصول العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"زيادة وصول العملاء"),"—")</f>
         <v/>
       </c>
       <c r="E10" s="40">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"تعزيز تجربة العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"تعزيز تجربة العملاء"),"—")</f>
         <v/>
       </c>
       <c r="H10" s="40">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"تطبيق «تانكي»"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"تطبيق «تانكي»"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29356,23 +25900,23 @@
     </row>
     <row r="14">
       <c r="B14" s="42">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"التوسع في المواقع"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"التوسع في المواقع"),"—")</f>
         <v/>
       </c>
       <c r="D14" s="42">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"الامتياز التجاري"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"الامتياز التجاري"),"—")</f>
         <v/>
       </c>
       <c r="F14" s="42">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"منظومة التأجير"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"منظومة التأجير"),"—")</f>
         <v/>
       </c>
       <c r="H14" s="42">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"ساحات درب"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"ساحات درب"),"—")</f>
         <v/>
       </c>
       <c r="J14" s="42">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"جودة التشغيل"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"جودة التشغيل"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29434,19 +25978,19 @@
     </row>
     <row r="18">
       <c r="B18" s="44">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"الاستثمار في الموظفين"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"الاستثمار في الموظفين"),"—")</f>
         <v/>
       </c>
       <c r="D18" s="44">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"التحول التقني"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"التحول التقني"),"—")</f>
         <v/>
       </c>
       <c r="F18" s="44">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"إطلاق مشاريع جديدة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"إطلاق مشاريع جديدة"),"—")</f>
         <v/>
       </c>
       <c r="H18" s="44">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$E$2:$E$116,"تطوير التصاميم والهوية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$E$2:$E$98,"تطوير التصاميم والهوية"),"—")</f>
         <v/>
       </c>
     </row>
@@ -29550,15 +26094,15 @@
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('قاعدة المؤشرات'!$H$2:$H$116,"✅ محقق",'قاعدة المؤشرات'!$B$2:$B$116,"&lt;&gt;الإدارة التنفيذية")</f>
+        <f>COUNTIFS('قاعدة المؤشرات'!$H$2:$H$98,"✅ محقق",'قاعدة المؤشرات'!$B$2:$B$98,"&lt;&gt;الإدارة التنفيذية")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('قاعدة المؤشرات'!$H$2:$H$116,"🟡 قريب",'قاعدة المؤشرات'!$B$2:$B$116,"&lt;&gt;الإدارة التنفيذية")</f>
+        <f>COUNTIFS('قاعدة المؤشرات'!$H$2:$H$98,"🟡 قريب",'قاعدة المؤشرات'!$B$2:$B$98,"&lt;&gt;الإدارة التنفيذية")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('قاعدة المؤشرات'!$H$2:$H$116,"🔴 تحت الهدف",'قاعدة المؤشرات'!$B$2:$B$116,"&lt;&gt;الإدارة التنفيذية")</f>
+        <f>COUNTIFS('قاعدة المؤشرات'!$H$2:$H$98,"🔴 تحت الهدف",'قاعدة المؤشرات'!$B$2:$B$98,"&lt;&gt;الإدارة التنفيذية")</f>
         <v/>
       </c>
     </row>
@@ -29605,7 +26149,7 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة التنفيذية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة التنفيذية",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة التنفيذية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة التنفيذية",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -29614,18 +26158,18 @@
         </is>
       </c>
       <c r="E9" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$D$2:$D$116,"النمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$D$2:$D$98,"النمو"),"—")</f>
         <v/>
       </c>
       <c r="H9" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة التنفيذية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة التنفيذية",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة التنفيذية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة التنفيذية",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة التنفيذية",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة التنفيذية",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29636,7 +26180,7 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الامتياز التجاري",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الامتياز التجاري",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الامتياز التجاري",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الامتياز التجاري",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -29645,18 +26189,18 @@
         </is>
       </c>
       <c r="E10" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$D$2:$D$116,"الابتكار"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$D$2:$D$98,"الابتكار"),"—")</f>
         <v/>
       </c>
       <c r="H10" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الامتياز التجاري",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الامتياز التجاري",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الامتياز التجاري",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الامتياز التجاري",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I10" s="15" t="n">
         <v>0.14</v>
       </c>
       <c r="J10" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الامتياز التجاري",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الامتياز التجاري",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29667,7 +26211,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التشغيل والمحطات",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التشغيل والمحطات",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التشغيل والمحطات",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التشغيل والمحطات",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -29676,18 +26220,18 @@
         </is>
       </c>
       <c r="E11" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$D$2:$D$116,"الاستدامة"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$D$2:$D$98,"الاستدامة"),"—")</f>
         <v/>
       </c>
       <c r="H11" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التشغيل والمحطات",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التشغيل والمحطات",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التشغيل والمحطات",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التشغيل والمحطات",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I11" s="15" t="n">
         <v>0.12</v>
       </c>
       <c r="J11" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التشغيل والمحطات",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التشغيل والمحطات",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29698,18 +26242,18 @@
         </is>
       </c>
       <c r="C12" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الاستثمار",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الاستثمار",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الاستثمار",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الاستثمار",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="H12" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الاستثمار",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الاستثمار",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الاستثمار",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الاستثمار",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I12" s="15" t="n">
         <v>0.11</v>
       </c>
       <c r="J12" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الاستثمار",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الاستثمار",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29720,7 +26264,7 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"العقار",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"العقار",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"العقار",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"العقار",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D13" s="46" t="inlineStr">
@@ -29730,14 +26274,14 @@
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="H13" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"العقار",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"العقار",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"العقار",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"العقار",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I13" s="15" t="n">
         <v>0.09</v>
       </c>
       <c r="J13" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"العقار",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"العقار",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29748,7 +26292,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"إدارة المشاريع",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"إدارة المشاريع",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"إدارة المشاريع",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"إدارة المشاريع",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -29757,18 +26301,18 @@
         </is>
       </c>
       <c r="E14" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$F$2:$F$116,"مالي"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$F$2:$F$98,"مالي"),"—")</f>
         <v/>
       </c>
       <c r="H14" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"إدارة المشاريع",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"إدارة المشاريع",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"إدارة المشاريع",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"إدارة المشاريع",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I14" s="15" t="n">
         <v>0.08</v>
       </c>
       <c r="J14" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"إدارة المشاريع",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"إدارة المشاريع",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29779,7 +26323,7 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"سلاسل الإمداد",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"سلاسل الإمداد",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"سلاسل الإمداد",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"سلاسل الإمداد",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -29788,18 +26332,18 @@
         </is>
       </c>
       <c r="E15" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$F$2:$F$116,"العملاء"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$F$2:$F$98,"العملاء"),"—")</f>
         <v/>
       </c>
       <c r="H15" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"سلاسل الإمداد",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"سلاسل الإمداد",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"سلاسل الإمداد",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"سلاسل الإمداد",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I15" s="15" t="n">
         <v>0.1</v>
       </c>
       <c r="J15" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"سلاسل الإمداد",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"سلاسل الإمداد",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29810,7 +26354,7 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الصيانة والأتمتة",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الصيانة والأتمتة",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الصيانة والأتمتة",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الصيانة والأتمتة",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -29819,18 +26363,18 @@
         </is>
       </c>
       <c r="E16" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$F$2:$F$116,"العمليات الداخلية"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$F$2:$F$98,"العمليات الداخلية"),"—")</f>
         <v/>
       </c>
       <c r="H16" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الصيانة والأتمتة",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الصيانة والأتمتة",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الصيانة والأتمتة",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الصيانة والأتمتة",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I16" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="J16" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الصيانة والأتمتة",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الصيانة والأتمتة",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29841,7 +26385,7 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التقنية الرقمية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التقنية الرقمية",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التقنية الرقمية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التقنية الرقمية",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -29850,18 +26394,18 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$116,'قاعدة المؤشرات'!$F$2:$F$116,"التعلّم والنمو"),"—")</f>
+        <f>IFERROR(AVERAGEIFS('قاعدة المؤشرات'!$G$2:$G$98,'قاعدة المؤشرات'!$F$2:$F$98,"التعلّم والنمو"),"—")</f>
         <v/>
       </c>
       <c r="H17" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التقنية الرقمية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التقنية الرقمية",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التقنية الرقمية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التقنية الرقمية",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I17" s="15" t="n">
         <v>0.04</v>
       </c>
       <c r="J17" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التقنية الرقمية",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التقنية الرقمية",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29872,18 +26416,18 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الموارد البشرية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الموارد البشرية",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الموارد البشرية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الموارد البشرية",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="H18" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الموارد البشرية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الموارد البشرية",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الموارد البشرية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الموارد البشرية",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I18" s="15" t="n">
         <v>0.04</v>
       </c>
       <c r="J18" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الموارد البشرية",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الموارد البشرية",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29894,18 +26438,18 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التسويق",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التسويق",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التسويق",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التسويق",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="H19" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التسويق",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التسويق",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التسويق",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التسويق",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I19" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="J19" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"التسويق",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"التسويق",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29916,18 +26460,18 @@
         </is>
       </c>
       <c r="C20" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الجودة",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الجودة",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الجودة",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الجودة",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="H20" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الجودة",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الجودة",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الجودة",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الجودة",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I20" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="J20" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الجودة",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الجودة",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29938,18 +26482,18 @@
         </is>
       </c>
       <c r="C21" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة القانونية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة القانونية",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة القانونية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة القانونية",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="H21" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة القانونية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة القانونية",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة القانونية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة القانونية",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I21" s="15" t="n">
         <v>0.03</v>
       </c>
       <c r="J21" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة القانونية",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة القانونية",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29960,18 +26504,18 @@
         </is>
       </c>
       <c r="C22" s="10">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة المالية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة المالية",'قاعدة المؤشرات'!$K$2:$K$116),"—")</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة المالية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة المالية",'قاعدة المؤشرات'!$K$2:$K$98),"—")</f>
         <v/>
       </c>
       <c r="H22" s="15">
-        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة المالية",'قاعدة المؤشرات'!$J$2:$J$116)/SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة المالية",'قاعدة المؤشرات'!$K$2:$K$116),0)</f>
+        <f>IFERROR(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة المالية",'قاعدة المؤشرات'!$J$2:$J$98)/SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة المالية",'قاعدة المؤشرات'!$K$2:$K$98),0)</f>
         <v/>
       </c>
       <c r="I22" s="15" t="n">
         <v>0.08</v>
       </c>
       <c r="J22" s="15">
-        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$116,"الإدارة المالية",'قاعدة المؤشرات'!$K$2:$K$116)=0,0,1)</f>
+        <f>IF(SUMIF('قاعدة المؤشرات'!$B$2:$B$98,"الإدارة المالية",'قاعدة المؤشرات'!$K$2:$K$98)=0,0,1)</f>
         <v/>
       </c>
     </row>
@@ -29992,7 +26536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -30447,28 +26991,28 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>العائد على حقوق الملكية (ROE)</t>
+          <t>نسبة أتمتة محطات الامتياز</t>
         </is>
       </c>
       <c r="D10" s="49" t="n">
-        <v>0.074</v>
+        <v>0.674</v>
       </c>
       <c r="E10" s="49" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F10" s="50" t="n">
-        <v>0.7399999999999999</v>
+        <v>0.7488888888888889</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.2600000000000001</v>
+        <v>0.2511111111111111</v>
       </c>
       <c r="H10" s="49" t="n">
-        <v>0.074</v>
+        <v>0.674</v>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
@@ -30487,7 +27031,7 @@
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M10" s="51" t="n"/>
@@ -30498,28 +27042,28 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>الإدارة التنفيذية</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>نسبة أتمتة محطات الامتياز</t>
+          <t>الالتزام بمعايير وزارة الطاقة (تغطية 13 منطقة)</t>
         </is>
       </c>
       <c r="D11" s="49" t="n">
-        <v>0.674</v>
+        <v>0.749</v>
       </c>
       <c r="E11" s="49" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F11" s="50" t="n">
-        <v>0.7488888888888889</v>
+        <v>0.749</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.2511111111111111</v>
+        <v>0.251</v>
       </c>
       <c r="H11" s="49" t="n">
-        <v>0.674</v>
+        <v>0.749</v>
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
@@ -30538,7 +27082,7 @@
       </c>
       <c r="L11" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="M11" s="51" t="n"/>
@@ -30554,37 +27098,37 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>الالتزام بمعايير وزارة الطاقة (تغطية 13 منطقة)</t>
+          <t>مؤشر رضا الموظفين العام (eNPS)</t>
         </is>
       </c>
       <c r="D12" s="49" t="n">
-        <v>0.749</v>
+        <v>22.5</v>
       </c>
       <c r="E12" s="49" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F12" s="50" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="H12" s="49" t="n">
-        <v>0.749</v>
+        <v>22.5</v>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L12" s="15" t="inlineStr">
@@ -30600,47 +27144,47 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>الإدارة التنفيذية</t>
+          <t>الإدارة المالية</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>مؤشر رضا الموظفين العام (eNPS)</t>
+          <t>دقة تسوية أرامكو</t>
         </is>
       </c>
       <c r="D13" s="49" t="n">
-        <v>22.5</v>
+        <v>0.76</v>
       </c>
       <c r="E13" s="49" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F13" s="50" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>22.5</v>
+        <v>0.76</v>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>🟡 قريب</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>فجوة محدودة — متابعة.</t>
+          <t>انحراف جوهري — أولوية عاجلة.</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
+          <t>إجراء تصحيحي خلال 30 يوماً.</t>
         </is>
       </c>
       <c r="L13" s="15" t="inlineStr">
         <is>
-          <t>الرئيس التنفيذي</t>
+          <t>المدير المالي</t>
         </is>
       </c>
       <c r="M13" s="51" t="n"/>
@@ -30651,28 +27195,28 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>دقة تسوية أرامكو</t>
+          <t>نسبة تنفيذ برامج التدريب والتأهيل المعتمدة</t>
         </is>
       </c>
       <c r="D14" s="49" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E14" s="49" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F14" s="50" t="n">
-        <v>0.76</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.24</v>
+        <v>0.2333333333333334</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -30691,7 +27235,7 @@
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير الموارد البشرية</t>
         </is>
       </c>
       <c r="M14" s="51" t="n"/>
@@ -30702,28 +27246,28 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>الإدارة التنفيذية</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>نسبة تنفيذ برامج التدريب والتأهيل المعتمدة</t>
+          <t>نسبة الالتزام بإطار الحوكمة المؤسسية والامتثال التنظيمي</t>
         </is>
       </c>
       <c r="D15" s="49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="E15" s="49" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F15" s="50" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7673684210526316</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.2333333333333334</v>
+        <v>0.2326315789473684</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -30742,7 +27286,7 @@
       </c>
       <c r="L15" s="15" t="inlineStr">
         <is>
-          <t>مدير الموارد البشرية</t>
+          <t>الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="M15" s="51" t="n"/>
@@ -30753,47 +27297,47 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>الإدارة التنفيذية</t>
+          <t>سلاسل الإمداد</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>نسبة الالتزام بإطار الحوكمة المؤسسية والامتثال التنظيمي</t>
+          <t>مستوى رضا الموردين</t>
         </is>
       </c>
       <c r="D16" s="49" t="n">
-        <v>0.729</v>
+        <v>0.663</v>
       </c>
       <c r="E16" s="49" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="F16" s="50" t="n">
-        <v>0.7673684210526316</v>
+        <v>0.78</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.2326315789473684</v>
+        <v>0.22</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>0.729</v>
+        <v>0.663</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>الرئيس التنفيذي</t>
+          <t>مدير سلاسل الإمداد</t>
         </is>
       </c>
       <c r="M16" s="51" t="n"/>
@@ -30804,28 +27348,28 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>سداد الموردين في الموعد</t>
+          <t>عدد شراكات التطبيق</t>
         </is>
       </c>
       <c r="D17" s="49" t="n">
-        <v>0.754</v>
+        <v>7.8</v>
       </c>
       <c r="E17" s="49" t="n">
-        <v>0.98</v>
+        <v>10</v>
       </c>
       <c r="F17" s="50" t="n">
-        <v>0.7693877551020408</v>
+        <v>0.78</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.2306122448979592</v>
+        <v>0.22</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>0.754</v>
+        <v>15.6</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -30844,7 +27388,7 @@
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير التسويق</t>
         </is>
       </c>
       <c r="M17" s="51" t="n"/>
@@ -30855,28 +27399,28 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>التسويق</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>هامش EBITDA</t>
+          <t>عدد تنزيلات التطبيق</t>
         </is>
       </c>
       <c r="D18" s="49" t="n">
-        <v>0.062</v>
+        <v>78204</v>
       </c>
       <c r="E18" s="49" t="n">
-        <v>0.08</v>
+        <v>100000</v>
       </c>
       <c r="F18" s="50" t="n">
-        <v>0.775</v>
+        <v>0.78204</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.225</v>
+        <v>0.21796</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>0.062</v>
+        <v>156408</v>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
@@ -30895,7 +27439,7 @@
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير التسويق</t>
         </is>
       </c>
       <c r="M18" s="51" t="n"/>
@@ -30906,28 +27450,28 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>دقة مطابقة المخزون</t>
+          <t>نسبة الشركاء الملتزمين بمواعيد السداد</t>
         </is>
       </c>
       <c r="D19" s="49" t="n">
-        <v>0.776</v>
+        <v>0.705</v>
       </c>
       <c r="E19" s="49" t="n">
-        <v>0.995</v>
+        <v>0.9</v>
       </c>
       <c r="F19" s="50" t="n">
-        <v>0.7798994974874373</v>
+        <v>0.7833333333333332</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.2201005025125627</v>
+        <v>0.2166666666666668</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>0.776</v>
+        <v>0.705</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -30946,7 +27490,7 @@
       </c>
       <c r="L19" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M19" s="51" t="n"/>
@@ -30957,47 +27501,47 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>الإدارة القانونية</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>معدل تجديد عقود الإيجار</t>
+          <t>مستوى رضا الإدارات عن الدعم القانوني</t>
         </is>
       </c>
       <c r="D20" s="49" t="n">
-        <v>0.702</v>
+        <v>0.674</v>
       </c>
       <c r="E20" s="49" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F20" s="50" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.7929411764705883</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.2200000000000001</v>
+        <v>0.2070588235294117</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>0.702</v>
+        <v>0.674</v>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>المدير القانوني</t>
         </is>
       </c>
       <c r="M20" s="51" t="n"/>
@@ -31008,47 +27552,47 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>سلاسل الإمداد</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>مستوى رضا الموردين</t>
+          <t>نسبة التزام المحطات بالهوية المؤسسية</t>
         </is>
       </c>
       <c r="D21" s="49" t="n">
-        <v>0.663</v>
+        <v>0.44</v>
       </c>
       <c r="E21" s="49" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="F21" s="50" t="n">
-        <v>0.78</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.22</v>
+        <v>0.2000000000000001</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>0.663</v>
+        <v>0.44</v>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>🟡 قريب</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>فجوة محدودة — متابعة.</t>
+          <t>انحراف جوهري — أولوية عاجلة.</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
+          <t>إجراء تصحيحي خلال 30 يوماً.</t>
         </is>
       </c>
       <c r="L21" s="15" t="inlineStr">
         <is>
-          <t>مدير سلاسل الإمداد</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M21" s="51" t="n"/>
@@ -31059,28 +27603,28 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>عدد شراكات التطبيق</t>
+          <t>إجمالي مبيعات وقود محطات الامتياز</t>
         </is>
       </c>
       <c r="D22" s="49" t="n">
-        <v>7.8</v>
+        <v>576630340</v>
       </c>
       <c r="E22" s="49" t="n">
-        <v>10</v>
+        <v>718838077</v>
       </c>
       <c r="F22" s="50" t="n">
-        <v>0.78</v>
+        <v>0.8021699996840874</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.22</v>
+        <v>0.1978300003159126</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>15.6</v>
+        <v>1153260680</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -31099,7 +27643,7 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>مدير التسويق</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M22" s="51" t="n"/>
@@ -31110,28 +27654,28 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>التسويق</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>عدد تنزيلات التطبيق</t>
+          <t>نسبة استقرار التشغيل التقني للمحطات</t>
         </is>
       </c>
       <c r="D23" s="49" t="n">
-        <v>78204</v>
+        <v>0.8</v>
       </c>
       <c r="E23" s="49" t="n">
-        <v>100000</v>
+        <v>0.99</v>
       </c>
       <c r="F23" s="50" t="n">
-        <v>0.78204</v>
+        <v>0.8080808080808082</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.21796</v>
+        <v>0.1919191919191918</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>156408</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -31150,7 +27694,7 @@
       </c>
       <c r="L23" s="15" t="inlineStr">
         <is>
-          <t>مدير التسويق</t>
+          <t>مدير التقنية</t>
         </is>
       </c>
       <c r="M23" s="51" t="n"/>
@@ -31166,23 +27710,23 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>نسبة الشركاء الملتزمين بمواعيد السداد</t>
+          <t>نسبة زيادة عدد أصحاب الامتياز</t>
         </is>
       </c>
       <c r="D24" s="49" t="n">
-        <v>0.705</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E24" s="49" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F24" s="50" t="n">
-        <v>0.7833333333333332</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.2166666666666668</v>
+        <v>0.1899999999999999</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>0.705</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
@@ -31212,47 +27756,47 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>الإدارة القانونية</t>
+          <t>الإدارة التنفيذية</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>مستوى رضا الإدارات عن الدعم القانوني</t>
+          <t>نسبة نمو إيرادات الشركة (سنوي)</t>
         </is>
       </c>
       <c r="D25" s="49" t="n">
-        <v>0.674</v>
+        <v>0.122</v>
       </c>
       <c r="E25" s="49" t="n">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="F25" s="50" t="n">
-        <v>0.7929411764705883</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.2070588235294117</v>
+        <v>0.1866666666666666</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>0.674</v>
+        <v>0.122</v>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>🟡 قريب</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>فجوة محدودة — متابعة.</t>
+          <t>انحراف جوهري — أولوية عاجلة.</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
+          <t>إجراء تصحيحي خلال 30 يوماً.</t>
         </is>
       </c>
       <c r="L25" s="15" t="inlineStr">
         <is>
-          <t>المدير القانوني</t>
+          <t>الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="M25" s="51" t="n"/>
@@ -31263,28 +27807,28 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>التشغيل والمحطات</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>نسبة التزام المحطات بالهوية المؤسسية</t>
+          <t>نسبة انخفاض الشكاوى مقارنة بالعام السابق</t>
         </is>
       </c>
       <c r="D26" s="49" t="n">
-        <v>0.44</v>
+        <v>0.163</v>
       </c>
       <c r="E26" s="49" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="F26" s="50" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.2000000000000001</v>
+        <v>0.1850000000000001</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>0.44</v>
+        <v>0.163</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -31303,7 +27847,7 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>مدير التشغيل</t>
         </is>
       </c>
       <c r="M26" s="51" t="n"/>
@@ -31314,28 +27858,28 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>العقار</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>هامش صافي الربح</t>
+          <t>زيادة عدد العلامات التجارية</t>
         </is>
       </c>
       <c r="D27" s="49" t="n">
-        <v>0.008</v>
+        <v>202.6</v>
       </c>
       <c r="E27" s="49" t="n">
-        <v>0.01</v>
+        <v>246</v>
       </c>
       <c r="F27" s="50" t="n">
-        <v>0.8</v>
+        <v>0.8235772357723578</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.2</v>
+        <v>0.1764227642276422</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>0.008</v>
+        <v>202.6</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -31354,7 +27898,7 @@
       </c>
       <c r="L27" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير العقار</t>
         </is>
       </c>
       <c r="M27" s="51" t="n"/>
@@ -31365,28 +27909,28 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>الإدارة القانونية</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>إجمالي مبيعات وقود محطات الامتياز</t>
+          <t>نسبة القضايا المُغلقة لصالح الشركة</t>
         </is>
       </c>
       <c r="D28" s="49" t="n">
-        <v>576630340</v>
+        <v>0.664</v>
       </c>
       <c r="E28" s="49" t="n">
-        <v>718838077</v>
+        <v>0.8</v>
       </c>
       <c r="F28" s="50" t="n">
-        <v>0.8021699996840874</v>
+        <v>0.83</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.1978300003159126</v>
+        <v>0.17</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>1153260680</v>
+        <v>0.664</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -31405,7 +27949,7 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>المدير القانوني</t>
         </is>
       </c>
       <c r="M28" s="51" t="n"/>
@@ -31416,28 +27960,28 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>التقنية الرقمية</t>
+          <t>الإدارة المالية</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>نسبة استقرار التشغيل التقني للمحطات</t>
+          <t>نمو الإيرادات السنوي</t>
         </is>
       </c>
       <c r="D29" s="49" t="n">
-        <v>0.8</v>
+        <v>0.169</v>
       </c>
       <c r="E29" s="49" t="n">
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
       <c r="F29" s="50" t="n">
-        <v>0.8080808080808082</v>
+        <v>0.845</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.1919191919191918</v>
+        <v>0.155</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>0.8</v>
+        <v>0.169</v>
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
@@ -31456,7 +28000,7 @@
       </c>
       <c r="L29" s="15" t="inlineStr">
         <is>
-          <t>مدير التقنية</t>
+          <t>المدير المالي</t>
         </is>
       </c>
       <c r="M29" s="51" t="n"/>
@@ -31467,28 +28011,28 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>العقار</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>نسبة زيادة عدد أصحاب الامتياز</t>
+          <t>نسبة تحصيل الإيجارات</t>
         </is>
       </c>
       <c r="D30" s="49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="E30" s="49" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F30" s="50" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8473684210526317</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.1899999999999999</v>
+        <v>0.1526315789473683</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
@@ -31507,7 +28051,7 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>مدير العقار</t>
         </is>
       </c>
       <c r="M30" s="51" t="n"/>
@@ -31523,37 +28067,37 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>نسبة نمو إيرادات الشركة (سنوي)</t>
+          <t>نسبة تحقيق المستهدفات الاستراتيجية العامة</t>
         </is>
       </c>
       <c r="D31" s="49" t="n">
-        <v>0.122</v>
+        <v>0.85</v>
       </c>
       <c r="E31" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="50" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G31" s="12" t="n">
         <v>0.15</v>
       </c>
-      <c r="F31" s="50" t="n">
-        <v>0.8133333333333334</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>0.1866666666666666</v>
-      </c>
       <c r="H31" s="49" t="n">
-        <v>0.122</v>
+        <v>0.85</v>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L31" s="15" t="inlineStr">
@@ -31569,47 +28113,47 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>التشغيل والمحطات</t>
+          <t>سلاسل الإمداد</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>نسبة انخفاض الشكاوى مقارنة بالعام السابق</t>
+          <t>نسبة إنجاز أوامر الشراء</t>
         </is>
       </c>
       <c r="D32" s="49" t="n">
-        <v>0.163</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E32" s="49" t="n">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="F32" s="50" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8526315789473685</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.1850000000000001</v>
+        <v>0.1473684210526315</v>
       </c>
       <c r="H32" s="49" t="n">
-        <v>0.163</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>مدير التشغيل</t>
+          <t>مدير سلاسل الإمداد</t>
         </is>
       </c>
       <c r="M32" s="51" t="n"/>
@@ -31620,47 +28164,47 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>العقار</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>زيادة عدد العلامات التجارية</t>
+          <t>نسبة التحصيل المالي من شركاء الامتياز</t>
         </is>
       </c>
       <c r="D33" s="49" t="n">
-        <v>202.6</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E33" s="49" t="n">
-        <v>246</v>
+        <v>0.95</v>
       </c>
       <c r="F33" s="50" t="n">
-        <v>0.8235772357723578</v>
+        <v>0.8547368421052632</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.1764227642276422</v>
+        <v>0.1452631578947368</v>
       </c>
       <c r="H33" s="49" t="n">
-        <v>202.6</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L33" s="15" t="inlineStr">
         <is>
-          <t>مدير العقار</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M33" s="51" t="n"/>
@@ -31671,47 +28215,47 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>الإدارة القانونية</t>
+          <t>إدارة المشاريع</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>نسبة القضايا المُغلقة لصالح الشركة</t>
+          <t>نسبة إنجاز محفظة المشاريع</t>
         </is>
       </c>
       <c r="D34" s="49" t="n">
-        <v>0.664</v>
+        <v>0.607</v>
       </c>
       <c r="E34" s="49" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F34" s="50" t="n">
-        <v>0.83</v>
+        <v>0.8671428571428572</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.17</v>
+        <v>0.1328571428571428</v>
       </c>
       <c r="H34" s="49" t="n">
-        <v>0.664</v>
+        <v>0.607</v>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>المدير القانوني</t>
+          <t>مدير إدارة المشاريع</t>
         </is>
       </c>
       <c r="M34" s="51" t="n"/>
@@ -31722,47 +28266,47 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>نمو الإيرادات السنوي</t>
+          <t>رفع هامش الربحية للامتياز</t>
         </is>
       </c>
       <c r="D35" s="49" t="n">
-        <v>0.169</v>
+        <v>1.564</v>
       </c>
       <c r="E35" s="49" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="F35" s="50" t="n">
-        <v>0.845</v>
+        <v>0.8688888888888889</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.155</v>
+        <v>0.1311111111111111</v>
       </c>
       <c r="H35" s="49" t="n">
-        <v>0.169</v>
+        <v>1.564</v>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L35" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M35" s="51" t="n"/>
@@ -31773,47 +28317,47 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>العقار</t>
+          <t>الإدارة التنفيذية</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>نسبة تحصيل الإيجارات</t>
+          <t>إجمالي المحطات المشغّلة — الشركة (تراكمي)</t>
         </is>
       </c>
       <c r="D36" s="49" t="n">
-        <v>0.805</v>
+        <v>206.1</v>
       </c>
       <c r="E36" s="49" t="n">
-        <v>0.95</v>
+        <v>235</v>
       </c>
       <c r="F36" s="50" t="n">
-        <v>0.8473684210526317</v>
+        <v>0.8770212765957447</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.1526315789473683</v>
+        <v>0.1229787234042553</v>
       </c>
       <c r="H36" s="49" t="n">
-        <v>0.805</v>
+        <v>206.1</v>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>مدير العقار</t>
+          <t>الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="M36" s="51" t="n"/>
@@ -31824,28 +28368,28 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>الإدارة التنفيذية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>نسبة تحقيق المستهدفات الاستراتيجية العامة</t>
+          <t>نسبة دقة الرواتب والمستحقات الشهرية</t>
         </is>
       </c>
       <c r="D37" s="49" t="n">
-        <v>0.85</v>
+        <v>0.888</v>
       </c>
       <c r="E37" s="49" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="F37" s="50" t="n">
-        <v>0.85</v>
+        <v>0.892462311557789</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.15</v>
+        <v>0.107537688442211</v>
       </c>
       <c r="H37" s="49" t="n">
-        <v>0.85</v>
+        <v>0.888</v>
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
@@ -31864,7 +28408,7 @@
       </c>
       <c r="L37" s="15" t="inlineStr">
         <is>
-          <t>الرئيس التنفيذي</t>
+          <t>مدير الموارد البشرية</t>
         </is>
       </c>
       <c r="M37" s="51" t="n"/>
@@ -31875,28 +28419,28 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>الموارد البشرية</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>أيام الإقفال الشهري</t>
+          <t>متوسط مدة إغلاق الشواغر المعتمدة</t>
         </is>
       </c>
       <c r="D38" s="49" t="n">
-        <v>7.044</v>
+        <v>33.5</v>
       </c>
       <c r="E38" s="49" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F38" s="50" t="n">
-        <v>0.8517887563884157</v>
+        <v>0.8955223880597015</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.1482112436115843</v>
+        <v>0.1044776119402985</v>
       </c>
       <c r="H38" s="49" t="n">
-        <v>7.044</v>
+        <v>33.5</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -31915,7 +28459,7 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير الموارد البشرية</t>
         </is>
       </c>
       <c r="M38" s="51" t="n"/>
@@ -31926,28 +28470,28 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>التشغيل والمحطات</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>النسبة الجارية (Current Ratio)</t>
+          <t>نمو مبيعات الوقود مقارنة بالعام السابق</t>
         </is>
       </c>
       <c r="D39" s="49" t="n">
-        <v>0.852</v>
+        <v>0.09</v>
       </c>
       <c r="E39" s="49" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F39" s="50" t="n">
-        <v>0.852</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.148</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="H39" s="49" t="n">
-        <v>0.852</v>
+        <v>0.09</v>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
@@ -31966,7 +28510,7 @@
       </c>
       <c r="L39" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير التشغيل</t>
         </is>
       </c>
       <c r="M39" s="51" t="n"/>
@@ -31977,28 +28521,28 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>سلاسل الإمداد</t>
+          <t>الإدارة المالية</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>نسبة إنجاز أوامر الشراء</t>
+          <t>نسبة التدفق النقدي التشغيلي</t>
         </is>
       </c>
       <c r="D40" s="49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.902</v>
       </c>
       <c r="E40" s="49" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F40" s="50" t="n">
-        <v>0.8526315789473685</v>
+        <v>0.902</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.1473684210526315</v>
+        <v>0.09799999999999998</v>
       </c>
       <c r="H40" s="49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.902</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -32017,7 +28561,7 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>مدير سلاسل الإمداد</t>
+          <t>المدير المالي</t>
         </is>
       </c>
       <c r="M40" s="51" t="n"/>
@@ -32028,28 +28572,28 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>الإدارة التنفيذية</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>نسبة التحصيل المالي من شركاء الامتياز</t>
+          <t>نسبة إنجاز مشاريع الخارطة التنفيذية</t>
         </is>
       </c>
       <c r="D41" s="49" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.906</v>
       </c>
       <c r="E41" s="49" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F41" s="50" t="n">
-        <v>0.8547368421052632</v>
+        <v>0.906</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.1452631578947368</v>
+        <v>0.09399999999999997</v>
       </c>
       <c r="H41" s="49" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.906</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
@@ -32068,7 +28612,7 @@
       </c>
       <c r="L41" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="M41" s="51" t="n"/>
@@ -32079,28 +28623,28 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>إدارة المشاريع</t>
+          <t>العقار</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>نسبة إنجاز محفظة المشاريع</t>
+          <t>نسبة إشغال الوحدات</t>
         </is>
       </c>
       <c r="D42" s="49" t="n">
-        <v>0.607</v>
+        <v>0.545</v>
       </c>
       <c r="E42" s="49" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F42" s="50" t="n">
-        <v>0.8671428571428572</v>
+        <v>0.9083333333333334</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.1328571428571428</v>
+        <v>0.09166666666666656</v>
       </c>
       <c r="H42" s="49" t="n">
-        <v>0.607</v>
+        <v>0.545</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -32119,7 +28663,7 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>مدير إدارة المشاريع</t>
+          <t>مدير العقار</t>
         </is>
       </c>
       <c r="M42" s="51" t="n"/>
@@ -32135,37 +28679,37 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>رفع هامش الربحية للامتياز</t>
+          <t>نسبة المحطات المستوفية لمعايير السلامة</t>
         </is>
       </c>
       <c r="D43" s="49" t="n">
-        <v>1.564</v>
+        <v>0.911</v>
       </c>
       <c r="E43" s="49" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="F43" s="50" t="n">
-        <v>0.8688888888888889</v>
+        <v>0.911</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.1311111111111111</v>
+        <v>0.08899999999999997</v>
       </c>
       <c r="H43" s="49" t="n">
-        <v>1.564</v>
+        <v>0.911</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>🟡 قريب</t>
+          <t>🔴 تحت الهدف</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>فجوة محدودة — متابعة.</t>
+          <t>انحراف جوهري — أولوية عاجلة.</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
+          <t>إجراء تصحيحي خلال 30 يوماً.</t>
         </is>
       </c>
       <c r="L43" s="15" t="inlineStr">
@@ -32181,28 +28725,28 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>الإدارة التنفيذية</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>إجمالي المحطات المشغّلة — الشركة (تراكمي)</t>
+          <t>نسبة انخفاض الشكاوى التشغيلية والإدارية</t>
         </is>
       </c>
       <c r="D44" s="49" t="n">
-        <v>206.1</v>
+        <v>0.274</v>
       </c>
       <c r="E44" s="49" t="n">
-        <v>235</v>
+        <v>0.3</v>
       </c>
       <c r="F44" s="50" t="n">
-        <v>0.8770212765957447</v>
+        <v>0.9133333333333334</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.1229787234042553</v>
+        <v>0.08666666666666656</v>
       </c>
       <c r="H44" s="49" t="n">
-        <v>206.1</v>
+        <v>0.274</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -32221,7 +28765,7 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>الرئيس التنفيذي</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M44" s="51" t="n"/>
@@ -32232,28 +28776,28 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>نسبة دقة الرواتب والمستحقات الشهرية</t>
+          <t>متوسط وقت معالجة البلاغات التشغيلية</t>
         </is>
       </c>
       <c r="D45" s="49" t="n">
-        <v>0.888</v>
+        <v>26.2</v>
       </c>
       <c r="E45" s="49" t="n">
-        <v>0.995</v>
+        <v>24</v>
       </c>
       <c r="F45" s="50" t="n">
-        <v>0.892462311557789</v>
+        <v>0.916030534351145</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.107537688442211</v>
+        <v>0.08396946564885499</v>
       </c>
       <c r="H45" s="49" t="n">
-        <v>0.888</v>
+        <v>26.2</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -32272,7 +28816,7 @@
       </c>
       <c r="L45" s="15" t="inlineStr">
         <is>
-          <t>مدير الموارد البشرية</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M45" s="51" t="n"/>
@@ -32283,28 +28827,28 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>الموارد البشرية</t>
+          <t>التشغيل والمحطات</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>متوسط مدة إغلاق الشواغر المعتمدة</t>
+          <t>عدد المحطات المشغّلة (تراكمي)</t>
         </is>
       </c>
       <c r="D46" s="49" t="n">
-        <v>33.5</v>
+        <v>78.5</v>
       </c>
       <c r="E46" s="49" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="F46" s="50" t="n">
-        <v>0.8955223880597015</v>
+        <v>0.9235294117647059</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.1044776119402985</v>
+        <v>0.07647058823529407</v>
       </c>
       <c r="H46" s="49" t="n">
-        <v>33.5</v>
+        <v>78.5</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -32323,7 +28867,7 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>مدير الموارد البشرية</t>
+          <t>مدير التشغيل</t>
         </is>
       </c>
       <c r="M46" s="51" t="n"/>
@@ -32334,28 +28878,28 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>التشغيل والمحطات</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>نمو مبيعات الوقود مقارنة بالعام السابق</t>
+          <t>نسبة إغلاق ملاحظات الجودة الميدانية</t>
         </is>
       </c>
       <c r="D47" s="49" t="n">
-        <v>0.09</v>
+        <v>0.879</v>
       </c>
       <c r="E47" s="49" t="n">
-        <v>0.1</v>
+        <v>0.95</v>
       </c>
       <c r="F47" s="50" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.9252631578947369</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.0747368421052631</v>
       </c>
       <c r="H47" s="49" t="n">
-        <v>0.09</v>
+        <v>0.879</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -32374,7 +28918,7 @@
       </c>
       <c r="L47" s="15" t="inlineStr">
         <is>
-          <t>مدير التشغيل</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M47" s="51" t="n"/>
@@ -32385,28 +28929,28 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>إدارة المشاريع</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>نسبة التدفق النقدي التشغيلي</t>
+          <t>متوسط مدة إغلاق قائمة الملاحظات النهائية</t>
         </is>
       </c>
       <c r="D48" s="49" t="n">
-        <v>0.902</v>
+        <v>32.4</v>
       </c>
       <c r="E48" s="49" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F48" s="50" t="n">
-        <v>0.902</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.09799999999999998</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="H48" s="49" t="n">
-        <v>0.902</v>
+        <v>32.4</v>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
@@ -32425,7 +28969,7 @@
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير إدارة المشاريع</t>
         </is>
       </c>
       <c r="M48" s="51" t="n"/>
@@ -32436,28 +28980,28 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>الإدارة التنفيذية</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>نسبة إنجاز مشاريع الخارطة التنفيذية</t>
+          <t>متوسط درجة تقييم جودة المحطة (قائمة التحقق)</t>
         </is>
       </c>
       <c r="D49" s="49" t="n">
-        <v>0.906</v>
+        <v>78.8</v>
       </c>
       <c r="E49" s="49" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F49" s="50" t="n">
-        <v>0.906</v>
+        <v>0.9270588235294117</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.09399999999999997</v>
+        <v>0.07294117647058829</v>
       </c>
       <c r="H49" s="49" t="n">
-        <v>0.906</v>
+        <v>78.8</v>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
@@ -32476,7 +29020,7 @@
       </c>
       <c r="L49" s="15" t="inlineStr">
         <is>
-          <t>الرئيس التنفيذي</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M49" s="51" t="n"/>
@@ -32487,28 +29031,28 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>العقار</t>
+          <t>الاستثمار</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>نسبة إشغال الوحدات</t>
+          <t>عدد العقود التي تغطي المناطق الـ13</t>
         </is>
       </c>
       <c r="D50" s="49" t="n">
-        <v>0.545</v>
+        <v>12.1</v>
       </c>
       <c r="E50" s="49" t="n">
-        <v>0.6</v>
+        <v>13</v>
       </c>
       <c r="F50" s="50" t="n">
-        <v>0.9083333333333334</v>
+        <v>0.9307692307692308</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.09166666666666656</v>
+        <v>0.06923076923076921</v>
       </c>
       <c r="H50" s="49" t="n">
-        <v>0.545</v>
+        <v>12.1</v>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
@@ -32527,7 +29071,7 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>مدير العقار</t>
+          <t>مدير الاستثمار</t>
         </is>
       </c>
       <c r="M50" s="51" t="n"/>
@@ -32538,47 +29082,47 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>الاستثمار</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>نسبة المحطات المستوفية لمعايير السلامة</t>
+          <t>نسبة المواقع المشغّلة ذات العائد المجدي</t>
         </is>
       </c>
       <c r="D51" s="49" t="n">
-        <v>0.911</v>
+        <v>0.748</v>
       </c>
       <c r="E51" s="49" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F51" s="50" t="n">
-        <v>0.911</v>
+        <v>0.9349999999999999</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.08899999999999997</v>
+        <v>0.06500000000000006</v>
       </c>
       <c r="H51" s="49" t="n">
-        <v>0.911</v>
+        <v>0.748</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t>🔴 تحت الهدف</t>
+          <t>🟡 قريب</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>انحراف جوهري — أولوية عاجلة.</t>
+          <t>فجوة محدودة — متابعة.</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>إجراء تصحيحي خلال 30 يوماً.</t>
+          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
         </is>
       </c>
       <c r="L51" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>مدير الاستثمار</t>
         </is>
       </c>
       <c r="M51" s="51" t="n"/>
@@ -32594,23 +29138,23 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>نسبة انخفاض الشكاوى التشغيلية والإدارية</t>
+          <t>نسبة استدامة أصحاب الامتياز (Retention)</t>
         </is>
       </c>
       <c r="D52" s="49" t="n">
-        <v>0.274</v>
+        <v>0.853</v>
       </c>
       <c r="E52" s="49" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F52" s="50" t="n">
-        <v>0.9133333333333334</v>
+        <v>0.9477777777777777</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.08666666666666656</v>
+        <v>0.05222222222222228</v>
       </c>
       <c r="H52" s="49" t="n">
-        <v>0.274</v>
+        <v>0.853</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
@@ -32645,23 +29189,23 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>متوسط وقت معالجة البلاغات التشغيلية</t>
+          <t>عدد عقود الامتياز الجديدة الموقّعة</t>
         </is>
       </c>
       <c r="D53" s="49" t="n">
-        <v>26.2</v>
+        <v>159.2</v>
       </c>
       <c r="E53" s="49" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="F53" s="50" t="n">
-        <v>0.916030534351145</v>
+        <v>0.9532934131736527</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.08396946564885499</v>
+        <v>0.04670658682634732</v>
       </c>
       <c r="H53" s="49" t="n">
-        <v>26.2</v>
+        <v>318.4</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -32691,28 +29235,28 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>التشغيل والمحطات</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>عدد المحطات المشغّلة (تراكمي)</t>
+          <t>نسبة حل الشكاوى خلال المدة المحددة</t>
         </is>
       </c>
       <c r="D54" s="49" t="n">
-        <v>78.5</v>
+        <v>0.922</v>
       </c>
       <c r="E54" s="49" t="n">
-        <v>85</v>
+        <v>0.95</v>
       </c>
       <c r="F54" s="50" t="n">
-        <v>0.9235294117647059</v>
+        <v>0.9705263157894738</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.07647058823529407</v>
+        <v>0.02947368421052621</v>
       </c>
       <c r="H54" s="49" t="n">
-        <v>78.5</v>
+        <v>0.922</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -32731,7 +29275,7 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>مدير التشغيل</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M54" s="51" t="n"/>
@@ -32742,28 +29286,28 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>الإدارة التنفيذية</t>
         </is>
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
-          <t>نسبة إغلاق ملاحظات الجودة الميدانية</t>
+          <t>إجمالي العقود الجديدة — الشركة</t>
         </is>
       </c>
       <c r="D55" s="49" t="n">
-        <v>0.879</v>
+        <v>346.6</v>
       </c>
       <c r="E55" s="49" t="n">
-        <v>0.95</v>
+        <v>357</v>
       </c>
       <c r="F55" s="50" t="n">
-        <v>0.9252631578947369</v>
+        <v>0.9708683473389357</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.0747368421052631</v>
+        <v>0.02913165266106432</v>
       </c>
       <c r="H55" s="49" t="n">
-        <v>0.879</v>
+        <v>693.2</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
@@ -32782,7 +29326,7 @@
       </c>
       <c r="L55" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="M55" s="51" t="n"/>
@@ -32793,28 +29337,28 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>إدارة المشاريع</t>
+          <t>سلاسل الإمداد</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>متوسط مدة إغلاق قائمة الملاحظات النهائية</t>
+          <t>نسبة نقليات أسطول درب</t>
         </is>
       </c>
       <c r="D56" s="49" t="n">
-        <v>32.4</v>
+        <v>0.293</v>
       </c>
       <c r="E56" s="49" t="n">
-        <v>30</v>
+        <v>0.3</v>
       </c>
       <c r="F56" s="50" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9766666666666667</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.07407407407407407</v>
+        <v>0.02333333333333332</v>
       </c>
       <c r="H56" s="49" t="n">
-        <v>32.4</v>
+        <v>0.293</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -32833,7 +29377,7 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>مدير إدارة المشاريع</t>
+          <t>مدير سلاسل الإمداد</t>
         </is>
       </c>
       <c r="M56" s="51" t="n"/>
@@ -32844,28 +29388,28 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>الامتياز التجاري</t>
+          <t>التشغيل والمحطات</t>
         </is>
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
-          <t>متوسط درجة تقييم جودة المحطة (قائمة التحقق)</t>
+          <t>تطبيق المعيار الشامل في المحطات</t>
         </is>
       </c>
       <c r="D57" s="49" t="n">
-        <v>78.8</v>
+        <v>0.787</v>
       </c>
       <c r="E57" s="49" t="n">
-        <v>85</v>
+        <v>0.8</v>
       </c>
       <c r="F57" s="50" t="n">
-        <v>0.9270588235294117</v>
+        <v>0.98375</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.07294117647058829</v>
+        <v>0.01624999999999999</v>
       </c>
       <c r="H57" s="49" t="n">
-        <v>78.8</v>
+        <v>0.787</v>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
@@ -32884,7 +29428,7 @@
       </c>
       <c r="L57" s="15" t="inlineStr">
         <is>
-          <t>مدير الامتياز</t>
+          <t>مدير التشغيل</t>
         </is>
       </c>
       <c r="M57" s="51" t="n"/>
@@ -32895,28 +29439,28 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>الإدارة المالية</t>
+          <t>التقنية الرقمية</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>نسبة تحصيل الامتياز</t>
+          <t>نسبة إنجاز مشاريع التحول الرقمي والمشاريع التقنية حسب الخطة</t>
         </is>
       </c>
       <c r="D58" s="49" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="E58" s="49" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="F58" s="50" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.01111111111111107</v>
       </c>
       <c r="H58" s="49" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -32935,7 +29479,7 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>المدير المالي</t>
+          <t>مدير التقنية</t>
         </is>
       </c>
       <c r="M58" s="51" t="n"/>
@@ -32946,28 +29490,28 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>الاستثمار</t>
+          <t>الإدارة المالية</t>
         </is>
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>عدد العقود التي تغطي المناطق الـ13</t>
+          <t>انحراف الموازنة</t>
         </is>
       </c>
       <c r="D59" s="49" t="n">
-        <v>12.1</v>
+        <v>0.101</v>
       </c>
       <c r="E59" s="49" t="n">
-        <v>13</v>
+        <v>0.1</v>
       </c>
       <c r="F59" s="50" t="n">
-        <v>0.9307692307692308</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.06923076923076921</v>
+        <v>0.00990099009900991</v>
       </c>
       <c r="H59" s="49" t="n">
-        <v>12.1</v>
+        <v>0.101</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -32986,7 +29530,7 @@
       </c>
       <c r="L59" s="15" t="inlineStr">
         <is>
-          <t>مدير الاستثمار</t>
+          <t>المدير المالي</t>
         </is>
       </c>
       <c r="M59" s="51" t="n"/>
@@ -32997,28 +29541,28 @@
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>الاستثمار</t>
+          <t>الامتياز التجاري</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>نسبة المواقع المشغّلة ذات العائد المجدي</t>
+          <t>نسبة تطبيق المعيار الشامل داخل المحطات</t>
         </is>
       </c>
       <c r="D60" s="49" t="n">
-        <v>0.748</v>
+        <v>0.299</v>
       </c>
       <c r="E60" s="49" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F60" s="50" t="n">
-        <v>0.9349999999999999</v>
+        <v>0.9966666666666667</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.06500000000000006</v>
+        <v>0.003333333333333299</v>
       </c>
       <c r="H60" s="49" t="n">
-        <v>0.748</v>
+        <v>0.299</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
@@ -33037,574 +29581,13 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>مدير الاستثمار</t>
+          <t>مدير الامتياز</t>
         </is>
       </c>
       <c r="M60" s="51" t="n"/>
     </row>
-    <row r="61">
-      <c r="A61" s="15" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="C61" s="21" t="inlineStr">
-        <is>
-          <t>نسبة استدامة أصحاب الامتياز (Retention)</t>
-        </is>
-      </c>
-      <c r="D61" s="49" t="n">
-        <v>0.853</v>
-      </c>
-      <c r="E61" s="49" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F61" s="50" t="n">
-        <v>0.9477777777777777</v>
-      </c>
-      <c r="G61" s="12" t="n">
-        <v>0.05222222222222228</v>
-      </c>
-      <c r="H61" s="49" t="n">
-        <v>0.853</v>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K61" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L61" s="15" t="inlineStr">
-        <is>
-          <t>مدير الامتياز</t>
-        </is>
-      </c>
-      <c r="M61" s="51" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C62" s="21" t="inlineStr">
-        <is>
-          <t>أيام تحصيل رسوم الامتياز</t>
-        </is>
-      </c>
-      <c r="D62" s="49" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="E62" s="49" t="n">
-        <v>15</v>
-      </c>
-      <c r="F62" s="50" t="n">
-        <v>0.9493670886075949</v>
-      </c>
-      <c r="G62" s="12" t="n">
-        <v>0.05063291139240511</v>
-      </c>
-      <c r="H62" s="49" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L62" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="M62" s="51" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="inlineStr">
-        <is>
-          <t>عدد عقود الامتياز الجديدة الموقّعة</t>
-        </is>
-      </c>
-      <c r="D63" s="49" t="n">
-        <v>159.2</v>
-      </c>
-      <c r="E63" s="49" t="n">
-        <v>167</v>
-      </c>
-      <c r="F63" s="50" t="n">
-        <v>0.9532934131736527</v>
-      </c>
-      <c r="G63" s="12" t="n">
-        <v>0.04670658682634732</v>
-      </c>
-      <c r="H63" s="49" t="n">
-        <v>318.4</v>
-      </c>
-      <c r="I63" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K63" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L63" s="15" t="inlineStr">
-        <is>
-          <t>مدير الامتياز</t>
-        </is>
-      </c>
-      <c r="M63" s="51" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="C64" s="21" t="inlineStr">
-        <is>
-          <t>نسبة حل الشكاوى خلال المدة المحددة</t>
-        </is>
-      </c>
-      <c r="D64" s="49" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="E64" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F64" s="50" t="n">
-        <v>0.9705263157894738</v>
-      </c>
-      <c r="G64" s="12" t="n">
-        <v>0.02947368421052621</v>
-      </c>
-      <c r="H64" s="49" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="I64" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L64" s="15" t="inlineStr">
-        <is>
-          <t>مدير الامتياز</t>
-        </is>
-      </c>
-      <c r="M64" s="51" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة التنفيذية</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="inlineStr">
-        <is>
-          <t>إجمالي العقود الجديدة — الشركة</t>
-        </is>
-      </c>
-      <c r="D65" s="49" t="n">
-        <v>346.6</v>
-      </c>
-      <c r="E65" s="49" t="n">
-        <v>357</v>
-      </c>
-      <c r="F65" s="50" t="n">
-        <v>0.9708683473389357</v>
-      </c>
-      <c r="G65" s="12" t="n">
-        <v>0.02913165266106432</v>
-      </c>
-      <c r="H65" s="49" t="n">
-        <v>693.2</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K65" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L65" s="15" t="inlineStr">
-        <is>
-          <t>الرئيس التنفيذي</t>
-        </is>
-      </c>
-      <c r="M65" s="51" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="inlineStr">
-        <is>
-          <t>اكتمال مطابقة حسابات الموردين</t>
-        </is>
-      </c>
-      <c r="D66" s="49" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="E66" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F66" s="50" t="n">
-        <v>0.9747368421052632</v>
-      </c>
-      <c r="G66" s="12" t="n">
-        <v>0.02526315789473677</v>
-      </c>
-      <c r="H66" s="49" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="M66" s="51" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>سلاسل الإمداد</t>
-        </is>
-      </c>
-      <c r="C67" s="21" t="inlineStr">
-        <is>
-          <t>نسبة نقليات أسطول درب</t>
-        </is>
-      </c>
-      <c r="D67" s="49" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="E67" s="49" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F67" s="50" t="n">
-        <v>0.9766666666666667</v>
-      </c>
-      <c r="G67" s="12" t="n">
-        <v>0.02333333333333332</v>
-      </c>
-      <c r="H67" s="49" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K67" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L67" s="15" t="inlineStr">
-        <is>
-          <t>مدير سلاسل الإمداد</t>
-        </is>
-      </c>
-      <c r="M67" s="51" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>التشغيل والمحطات</t>
-        </is>
-      </c>
-      <c r="C68" s="21" t="inlineStr">
-        <is>
-          <t>تطبيق المعيار الشامل في المحطات</t>
-        </is>
-      </c>
-      <c r="D68" s="49" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="E68" s="49" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F68" s="50" t="n">
-        <v>0.98375</v>
-      </c>
-      <c r="G68" s="12" t="n">
-        <v>0.01624999999999999</v>
-      </c>
-      <c r="H68" s="49" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K68" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L68" s="15" t="inlineStr">
-        <is>
-          <t>مدير التشغيل</t>
-        </is>
-      </c>
-      <c r="M68" s="51" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="15" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>التقنية الرقمية</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="inlineStr">
-        <is>
-          <t>نسبة إنجاز مشاريع التحول الرقمي والمشاريع التقنية حسب الخطة</t>
-        </is>
-      </c>
-      <c r="D69" s="49" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E69" s="49" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F69" s="50" t="n">
-        <v>0.9888888888888889</v>
-      </c>
-      <c r="G69" s="12" t="n">
-        <v>0.01111111111111107</v>
-      </c>
-      <c r="H69" s="49" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K69" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L69" s="15" t="inlineStr">
-        <is>
-          <t>مدير التقنية</t>
-        </is>
-      </c>
-      <c r="M69" s="51" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="15" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C70" s="21" t="inlineStr">
-        <is>
-          <t>انحراف الموازنة</t>
-        </is>
-      </c>
-      <c r="D70" s="49" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="E70" s="49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F70" s="50" t="n">
-        <v>0.9900990099009901</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>0.00990099009900991</v>
-      </c>
-      <c r="H70" s="49" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L70" s="15" t="inlineStr">
-        <is>
-          <t>المدير المالي</t>
-        </is>
-      </c>
-      <c r="M70" s="51" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>الامتياز التجاري</t>
-        </is>
-      </c>
-      <c r="C71" s="21" t="inlineStr">
-        <is>
-          <t>نسبة تطبيق المعيار الشامل داخل المحطات</t>
-        </is>
-      </c>
-      <c r="D71" s="49" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="E71" s="49" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F71" s="50" t="n">
-        <v>0.9966666666666667</v>
-      </c>
-      <c r="G71" s="12" t="n">
-        <v>0.003333333333333299</v>
-      </c>
-      <c r="H71" s="49" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>🟡 قريب</t>
-        </is>
-      </c>
-      <c r="J71" s="11" t="inlineStr">
-        <is>
-          <t>فجوة محدودة — متابعة.</t>
-        </is>
-      </c>
-      <c r="K71" s="11" t="inlineStr">
-        <is>
-          <t>متابعة أسبوعية لإغلاق الفجوة.</t>
-        </is>
-      </c>
-      <c r="L71" s="15" t="inlineStr">
-        <is>
-          <t>مدير الامتياز</t>
-        </is>
-      </c>
-      <c r="M71" s="51" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:M71"/>
+  <autoFilter ref="A2:M60"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
@@ -33618,7 +29601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X118"/>
+  <dimension ref="A1:X100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -39680,7 +35663,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>هامش EBITDA</t>
+          <t>نسبة التدفق النقدي التشغيلي</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
@@ -39698,22 +35681,22 @@
           <t>↑</t>
         </is>
       </c>
-      <c r="G96" s="59" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H96" s="60" t="n"/>
-      <c r="I96" s="60" t="n"/>
-      <c r="J96" s="60" t="n"/>
-      <c r="K96" s="60" t="n"/>
-      <c r="L96" s="60" t="n"/>
-      <c r="M96" s="60" t="n"/>
-      <c r="N96" s="60" t="n"/>
-      <c r="O96" s="60" t="n"/>
-      <c r="P96" s="60" t="n"/>
-      <c r="Q96" s="60" t="n"/>
-      <c r="R96" s="60" t="n"/>
-      <c r="S96" s="60" t="n"/>
-      <c r="T96" s="50">
+      <c r="G96" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="63" t="n"/>
+      <c r="I96" s="63" t="n"/>
+      <c r="J96" s="63" t="n"/>
+      <c r="K96" s="63" t="n"/>
+      <c r="L96" s="63" t="n"/>
+      <c r="M96" s="63" t="n"/>
+      <c r="N96" s="63" t="n"/>
+      <c r="O96" s="63" t="n"/>
+      <c r="P96" s="63" t="n"/>
+      <c r="Q96" s="63" t="n"/>
+      <c r="R96" s="63" t="n"/>
+      <c r="S96" s="63" t="n"/>
+      <c r="T96" s="64">
         <f>IF(COUNT($H96:$S96)=0,"",SUM($H96:$S96)/COUNT($H96:$S96))</f>
         <v/>
       </c>
@@ -39725,7 +35708,7 @@
         <f>IF($U96="","⏳ بانتظار هدف",IF($U96&gt;=1.0,"✅ محقق",IF($U96&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
-      <c r="W96" s="61">
+      <c r="W96" s="65">
         <f>IF($G96="","",$G96)</f>
         <v/>
       </c>
@@ -39745,7 +35728,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>هامش صافي الربح</t>
+          <t>نسبة التحصيل العام (الشركة)</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
@@ -39764,7 +35747,7 @@
         </is>
       </c>
       <c r="G97" s="59" t="n">
-        <v>0.01</v>
+        <v>0.95</v>
       </c>
       <c r="H97" s="60" t="n"/>
       <c r="I97" s="60" t="n"/>
@@ -39810,12 +35793,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>العائد على حقوق الملكية (ROE)</t>
+          <t>دقة التنبؤ النقدي</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>ربعي</t>
+          <t>شهري</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
@@ -39829,7 +35812,7 @@
         </is>
       </c>
       <c r="G98" s="59" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="H98" s="60" t="n"/>
       <c r="I98" s="60" t="n"/>
@@ -39875,7 +35858,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>نسبة التدفق النقدي التشغيلي</t>
+          <t>دقة تسوية أرامكو</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
@@ -39893,22 +35876,22 @@
           <t>↑</t>
         </is>
       </c>
-      <c r="G99" s="62" t="n">
+      <c r="G99" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="63" t="n"/>
-      <c r="I99" s="63" t="n"/>
-      <c r="J99" s="63" t="n"/>
-      <c r="K99" s="63" t="n"/>
-      <c r="L99" s="63" t="n"/>
-      <c r="M99" s="63" t="n"/>
-      <c r="N99" s="63" t="n"/>
-      <c r="O99" s="63" t="n"/>
-      <c r="P99" s="63" t="n"/>
-      <c r="Q99" s="63" t="n"/>
-      <c r="R99" s="63" t="n"/>
-      <c r="S99" s="63" t="n"/>
-      <c r="T99" s="64">
+      <c r="H99" s="60" t="n"/>
+      <c r="I99" s="60" t="n"/>
+      <c r="J99" s="60" t="n"/>
+      <c r="K99" s="60" t="n"/>
+      <c r="L99" s="60" t="n"/>
+      <c r="M99" s="60" t="n"/>
+      <c r="N99" s="60" t="n"/>
+      <c r="O99" s="60" t="n"/>
+      <c r="P99" s="60" t="n"/>
+      <c r="Q99" s="60" t="n"/>
+      <c r="R99" s="60" t="n"/>
+      <c r="S99" s="60" t="n"/>
+      <c r="T99" s="50">
         <f>IF(COUNT($H99:$S99)=0,"",SUM($H99:$S99)/COUNT($H99:$S99))</f>
         <v/>
       </c>
@@ -39917,15 +35900,15 @@
         <v/>
       </c>
       <c r="V99" s="54">
-        <f>IF($U99="","⏳ بانتظار هدف",IF($U99&gt;=1.0,"✅ محقق",IF($U99&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W99" s="65">
+        <f>IF($U99="","⏳ بانتظار هدف",IF($U99&gt;=1.0,"✅ محقق",IF($U99&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
+        <v/>
+      </c>
+      <c r="W99" s="61">
         <f>IF($G99="","",$G99)</f>
         <v/>
       </c>
       <c r="X99" s="54">
-        <f>IF($U99="","—",IF($U99&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
+        <f>IF($U99="","—",IF($U99&gt;=0.97,"🟢 على المسار","🟠 متأخّر"))</f>
         <v/>
       </c>
     </row>
@@ -39940,41 +35923,41 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>النسبة الجارية (Current Ratio)</t>
+          <t>انحراف الموازنة</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>شهري</t>
+          <t>ربعي</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>لقطة</t>
+          <t>معدل</t>
         </is>
       </c>
       <c r="F100" s="49" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G100" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" s="63" t="n"/>
-      <c r="I100" s="63" t="n"/>
-      <c r="J100" s="63" t="n"/>
-      <c r="K100" s="63" t="n"/>
-      <c r="L100" s="63" t="n"/>
-      <c r="M100" s="63" t="n"/>
-      <c r="N100" s="63" t="n"/>
-      <c r="O100" s="63" t="n"/>
-      <c r="P100" s="63" t="n"/>
-      <c r="Q100" s="63" t="n"/>
-      <c r="R100" s="63" t="n"/>
-      <c r="S100" s="63" t="n"/>
-      <c r="T100" s="64">
-        <f>IFERROR(LOOKUP(2,1/($H100:$S100&lt;&gt;""),$H100:$S100),"")</f>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="G100" s="59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H100" s="60" t="n"/>
+      <c r="I100" s="60" t="n"/>
+      <c r="J100" s="60" t="n"/>
+      <c r="K100" s="60" t="n"/>
+      <c r="L100" s="60" t="n"/>
+      <c r="M100" s="60" t="n"/>
+      <c r="N100" s="60" t="n"/>
+      <c r="O100" s="60" t="n"/>
+      <c r="P100" s="60" t="n"/>
+      <c r="Q100" s="60" t="n"/>
+      <c r="R100" s="60" t="n"/>
+      <c r="S100" s="60" t="n"/>
+      <c r="T100" s="50">
+        <f>IF(COUNT($H100:$S100)=0,"",SUM($H100:$S100)/COUNT($H100:$S100))</f>
         <v/>
       </c>
       <c r="U100" s="50">
@@ -39985,7 +35968,7 @@
         <f>IF($U100="","⏳ بانتظار هدف",IF($U100&gt;=1.0,"✅ محقق",IF($U100&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
         <v/>
       </c>
-      <c r="W100" s="65">
+      <c r="W100" s="61">
         <f>IF($G100="","",$G100)</f>
         <v/>
       </c>
@@ -39994,1178 +35977,8 @@
         <v/>
       </c>
     </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="54" t="n">
-        <v>98</v>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C101" s="11" t="inlineStr">
-        <is>
-          <t>دورة التحويل النقدي</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F101" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G101" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="H101" s="63" t="n"/>
-      <c r="I101" s="63" t="n"/>
-      <c r="J101" s="63" t="n"/>
-      <c r="K101" s="63" t="n"/>
-      <c r="L101" s="63" t="n"/>
-      <c r="M101" s="63" t="n"/>
-      <c r="N101" s="63" t="n"/>
-      <c r="O101" s="63" t="n"/>
-      <c r="P101" s="63" t="n"/>
-      <c r="Q101" s="63" t="n"/>
-      <c r="R101" s="63" t="n"/>
-      <c r="S101" s="63" t="n"/>
-      <c r="T101" s="64">
-        <f>IF(COUNT($H101:$S101)=0,"",SUM($H101:$S101)/COUNT($H101:$S101))</f>
-        <v/>
-      </c>
-      <c r="U101" s="50">
-        <f>IF($G101="","",IF($T101="","",MIN(1,IF($G101=0,IF($T101&lt;=0,1,0),IF($F101="↓",IFERROR($G101/$T101,0),IFERROR($T101/$G101,0))))))</f>
-        <v/>
-      </c>
-      <c r="V101" s="54">
-        <f>IF($U101="","⏳ بانتظار هدف",IF($U101&gt;=1.0,"✅ محقق",IF($U101&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W101" s="65">
-        <f>IF($G101="","",$G101)</f>
-        <v/>
-      </c>
-      <c r="X101" s="54">
-        <f>IF($U101="","—",IF($U101&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="54" t="n">
-        <v>99</v>
-      </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="inlineStr">
-        <is>
-          <t>متوسط أيام التحصيل العام (DSO)</t>
-        </is>
-      </c>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F102" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G102" s="62" t="n">
-        <v>30</v>
-      </c>
-      <c r="H102" s="63" t="n"/>
-      <c r="I102" s="63" t="n"/>
-      <c r="J102" s="63" t="n"/>
-      <c r="K102" s="63" t="n"/>
-      <c r="L102" s="63" t="n"/>
-      <c r="M102" s="63" t="n"/>
-      <c r="N102" s="63" t="n"/>
-      <c r="O102" s="63" t="n"/>
-      <c r="P102" s="63" t="n"/>
-      <c r="Q102" s="63" t="n"/>
-      <c r="R102" s="63" t="n"/>
-      <c r="S102" s="63" t="n"/>
-      <c r="T102" s="64">
-        <f>IF(COUNT($H102:$S102)=0,"",SUM($H102:$S102)/COUNT($H102:$S102))</f>
-        <v/>
-      </c>
-      <c r="U102" s="50">
-        <f>IF($G102="","",IF($T102="","",MIN(1,IF($G102=0,IF($T102&lt;=0,1,0),IF($F102="↓",IFERROR($G102/$T102,0),IFERROR($T102/$G102,0))))))</f>
-        <v/>
-      </c>
-      <c r="V102" s="54">
-        <f>IF($U102="","⏳ بانتظار هدف",IF($U102&gt;=1.0,"✅ محقق",IF($U102&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W102" s="65">
-        <f>IF($G102="","",$G102)</f>
-        <v/>
-      </c>
-      <c r="X102" s="54">
-        <f>IF($U102="","—",IF($U102&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="54" t="n">
-        <v>100</v>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C103" s="11" t="inlineStr">
-        <is>
-          <t>نسبة التحصيل العام (الشركة)</t>
-        </is>
-      </c>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E103" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F103" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G103" s="59" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H103" s="60" t="n"/>
-      <c r="I103" s="60" t="n"/>
-      <c r="J103" s="60" t="n"/>
-      <c r="K103" s="60" t="n"/>
-      <c r="L103" s="60" t="n"/>
-      <c r="M103" s="60" t="n"/>
-      <c r="N103" s="60" t="n"/>
-      <c r="O103" s="60" t="n"/>
-      <c r="P103" s="60" t="n"/>
-      <c r="Q103" s="60" t="n"/>
-      <c r="R103" s="60" t="n"/>
-      <c r="S103" s="60" t="n"/>
-      <c r="T103" s="50">
-        <f>IF(COUNT($H103:$S103)=0,"",SUM($H103:$S103)/COUNT($H103:$S103))</f>
-        <v/>
-      </c>
-      <c r="U103" s="50">
-        <f>IF($G103="","",IF($T103="","",MIN(1,IF($G103=0,IF($T103&lt;=0,1,0),IF($F103="↓",IFERROR($G103/$T103,0),IFERROR($T103/$G103,0))))))</f>
-        <v/>
-      </c>
-      <c r="V103" s="54">
-        <f>IF($U103="","⏳ بانتظار هدف",IF($U103&gt;=1.0,"✅ محقق",IF($U103&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W103" s="61">
-        <f>IF($G103="","",$G103)</f>
-        <v/>
-      </c>
-      <c r="X103" s="54">
-        <f>IF($U103="","—",IF($U103&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="54" t="n">
-        <v>101</v>
-      </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C104" s="11" t="inlineStr">
-        <is>
-          <t>نسبة الذمم المتأخرة</t>
-        </is>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F104" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G104" s="59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H104" s="60" t="n"/>
-      <c r="I104" s="60" t="n"/>
-      <c r="J104" s="60" t="n"/>
-      <c r="K104" s="60" t="n"/>
-      <c r="L104" s="60" t="n"/>
-      <c r="M104" s="60" t="n"/>
-      <c r="N104" s="60" t="n"/>
-      <c r="O104" s="60" t="n"/>
-      <c r="P104" s="60" t="n"/>
-      <c r="Q104" s="60" t="n"/>
-      <c r="R104" s="60" t="n"/>
-      <c r="S104" s="60" t="n"/>
-      <c r="T104" s="50">
-        <f>IF(COUNT($H104:$S104)=0,"",SUM($H104:$S104)/COUNT($H104:$S104))</f>
-        <v/>
-      </c>
-      <c r="U104" s="50">
-        <f>IF($G104="","",IF($T104="","",MIN(1,IF($G104=0,IF($T104&lt;=0,1,0),IF($F104="↓",IFERROR($G104/$T104,0),IFERROR($T104/$G104,0))))))</f>
-        <v/>
-      </c>
-      <c r="V104" s="54">
-        <f>IF($U104="","⏳ بانتظار هدف",IF($U104&gt;=1.0,"✅ محقق",IF($U104&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W104" s="61">
-        <f>IF($G104="","",$G104)</f>
-        <v/>
-      </c>
-      <c r="X104" s="54">
-        <f>IF($U104="","—",IF($U104&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="54" t="n">
-        <v>102</v>
-      </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>نسبة الديون المعدومة</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E105" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F105" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G105" s="59" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H105" s="60" t="n"/>
-      <c r="I105" s="60" t="n"/>
-      <c r="J105" s="60" t="n"/>
-      <c r="K105" s="60" t="n"/>
-      <c r="L105" s="60" t="n"/>
-      <c r="M105" s="60" t="n"/>
-      <c r="N105" s="60" t="n"/>
-      <c r="O105" s="60" t="n"/>
-      <c r="P105" s="60" t="n"/>
-      <c r="Q105" s="60" t="n"/>
-      <c r="R105" s="60" t="n"/>
-      <c r="S105" s="60" t="n"/>
-      <c r="T105" s="50">
-        <f>IF(COUNT($H105:$S105)=0,"",SUM($H105:$S105)/COUNT($H105:$S105))</f>
-        <v/>
-      </c>
-      <c r="U105" s="50">
-        <f>IF($G105="","",IF($T105="","",MIN(1,IF($G105=0,IF($T105&lt;=0,1,0),IF($F105="↓",IFERROR($G105/$T105,0),IFERROR($T105/$G105,0))))))</f>
-        <v/>
-      </c>
-      <c r="V105" s="54">
-        <f>IF($U105="","⏳ بانتظار هدف",IF($U105&gt;=1.0,"✅ محقق",IF($U105&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W105" s="61">
-        <f>IF($G105="","",$G105)</f>
-        <v/>
-      </c>
-      <c r="X105" s="54">
-        <f>IF($U105="","—",IF($U105&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="54" t="n">
-        <v>103</v>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>سداد الموردين في الموعد</t>
-        </is>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F106" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G106" s="59" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="H106" s="60" t="n"/>
-      <c r="I106" s="60" t="n"/>
-      <c r="J106" s="60" t="n"/>
-      <c r="K106" s="60" t="n"/>
-      <c r="L106" s="60" t="n"/>
-      <c r="M106" s="60" t="n"/>
-      <c r="N106" s="60" t="n"/>
-      <c r="O106" s="60" t="n"/>
-      <c r="P106" s="60" t="n"/>
-      <c r="Q106" s="60" t="n"/>
-      <c r="R106" s="60" t="n"/>
-      <c r="S106" s="60" t="n"/>
-      <c r="T106" s="50">
-        <f>IF(COUNT($H106:$S106)=0,"",SUM($H106:$S106)/COUNT($H106:$S106))</f>
-        <v/>
-      </c>
-      <c r="U106" s="50">
-        <f>IF($G106="","",IF($T106="","",MIN(1,IF($G106=0,IF($T106&lt;=0,1,0),IF($F106="↓",IFERROR($G106/$T106,0),IFERROR($T106/$G106,0))))))</f>
-        <v/>
-      </c>
-      <c r="V106" s="54">
-        <f>IF($U106="","⏳ بانتظار هدف",IF($U106&gt;=1.0,"✅ محقق",IF($U106&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W106" s="61">
-        <f>IF($G106="","",$G106)</f>
-        <v/>
-      </c>
-      <c r="X106" s="54">
-        <f>IF($U106="","—",IF($U106&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="54" t="n">
-        <v>104</v>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr">
-        <is>
-          <t>اكتمال مطابقة حسابات الموردين</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E107" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F107" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G107" s="59" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H107" s="60" t="n"/>
-      <c r="I107" s="60" t="n"/>
-      <c r="J107" s="60" t="n"/>
-      <c r="K107" s="60" t="n"/>
-      <c r="L107" s="60" t="n"/>
-      <c r="M107" s="60" t="n"/>
-      <c r="N107" s="60" t="n"/>
-      <c r="O107" s="60" t="n"/>
-      <c r="P107" s="60" t="n"/>
-      <c r="Q107" s="60" t="n"/>
-      <c r="R107" s="60" t="n"/>
-      <c r="S107" s="60" t="n"/>
-      <c r="T107" s="50">
-        <f>IF(COUNT($H107:$S107)=0,"",SUM($H107:$S107)/COUNT($H107:$S107))</f>
-        <v/>
-      </c>
-      <c r="U107" s="50">
-        <f>IF($G107="","",IF($T107="","",MIN(1,IF($G107=0,IF($T107&lt;=0,1,0),IF($F107="↓",IFERROR($G107/$T107,0),IFERROR($T107/$G107,0))))))</f>
-        <v/>
-      </c>
-      <c r="V107" s="54">
-        <f>IF($U107="","⏳ بانتظار هدف",IF($U107&gt;=1.0,"✅ محقق",IF($U107&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W107" s="61">
-        <f>IF($G107="","",$G107)</f>
-        <v/>
-      </c>
-      <c r="X107" s="54">
-        <f>IF($U107="","—",IF($U107&gt;=0.97,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="54" t="n">
-        <v>105</v>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C108" s="11" t="inlineStr">
-        <is>
-          <t>دقة التنبؤ النقدي</t>
-        </is>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F108" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G108" s="59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H108" s="60" t="n"/>
-      <c r="I108" s="60" t="n"/>
-      <c r="J108" s="60" t="n"/>
-      <c r="K108" s="60" t="n"/>
-      <c r="L108" s="60" t="n"/>
-      <c r="M108" s="60" t="n"/>
-      <c r="N108" s="60" t="n"/>
-      <c r="O108" s="60" t="n"/>
-      <c r="P108" s="60" t="n"/>
-      <c r="Q108" s="60" t="n"/>
-      <c r="R108" s="60" t="n"/>
-      <c r="S108" s="60" t="n"/>
-      <c r="T108" s="50">
-        <f>IF(COUNT($H108:$S108)=0,"",SUM($H108:$S108)/COUNT($H108:$S108))</f>
-        <v/>
-      </c>
-      <c r="U108" s="50">
-        <f>IF($G108="","",IF($T108="","",MIN(1,IF($G108=0,IF($T108&lt;=0,1,0),IF($F108="↓",IFERROR($G108/$T108,0),IFERROR($T108/$G108,0))))))</f>
-        <v/>
-      </c>
-      <c r="V108" s="54">
-        <f>IF($U108="","⏳ بانتظار هدف",IF($U108&gt;=1.0,"✅ محقق",IF($U108&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W108" s="61">
-        <f>IF($G108="","",$G108)</f>
-        <v/>
-      </c>
-      <c r="X108" s="54">
-        <f>IF($U108="","—",IF($U108&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="54" t="n">
-        <v>106</v>
-      </c>
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C109" s="11" t="inlineStr">
-        <is>
-          <t>تباين مخزون الوقود</t>
-        </is>
-      </c>
-      <c r="D109" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E109" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F109" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G109" s="59" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H109" s="60" t="n"/>
-      <c r="I109" s="60" t="n"/>
-      <c r="J109" s="60" t="n"/>
-      <c r="K109" s="60" t="n"/>
-      <c r="L109" s="60" t="n"/>
-      <c r="M109" s="60" t="n"/>
-      <c r="N109" s="60" t="n"/>
-      <c r="O109" s="60" t="n"/>
-      <c r="P109" s="60" t="n"/>
-      <c r="Q109" s="60" t="n"/>
-      <c r="R109" s="60" t="n"/>
-      <c r="S109" s="60" t="n"/>
-      <c r="T109" s="50">
-        <f>IF(COUNT($H109:$S109)=0,"",SUM($H109:$S109)/COUNT($H109:$S109))</f>
-        <v/>
-      </c>
-      <c r="U109" s="50">
-        <f>IF($G109="","",IF($T109="","",MIN(1,IF($G109=0,IF($T109&lt;=0,1,0),IF($F109="↓",IFERROR($G109/$T109,0),IFERROR($T109/$G109,0))))))</f>
-        <v/>
-      </c>
-      <c r="V109" s="54">
-        <f>IF($U109="","⏳ بانتظار هدف",IF($U109&gt;=1.0,"✅ محقق",IF($U109&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W109" s="61">
-        <f>IF($G109="","",$G109)</f>
-        <v/>
-      </c>
-      <c r="X109" s="54">
-        <f>IF($U109="","—",IF($U109&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="54" t="n">
-        <v>107</v>
-      </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>دقة مطابقة المخزون</t>
-        </is>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F110" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G110" s="59" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="H110" s="60" t="n"/>
-      <c r="I110" s="60" t="n"/>
-      <c r="J110" s="60" t="n"/>
-      <c r="K110" s="60" t="n"/>
-      <c r="L110" s="60" t="n"/>
-      <c r="M110" s="60" t="n"/>
-      <c r="N110" s="60" t="n"/>
-      <c r="O110" s="60" t="n"/>
-      <c r="P110" s="60" t="n"/>
-      <c r="Q110" s="60" t="n"/>
-      <c r="R110" s="60" t="n"/>
-      <c r="S110" s="60" t="n"/>
-      <c r="T110" s="50">
-        <f>IF(COUNT($H110:$S110)=0,"",SUM($H110:$S110)/COUNT($H110:$S110))</f>
-        <v/>
-      </c>
-      <c r="U110" s="50">
-        <f>IF($G110="","",IF($T110="","",MIN(1,IF($G110=0,IF($T110&lt;=0,1,0),IF($F110="↓",IFERROR($G110/$T110,0),IFERROR($T110/$G110,0))))))</f>
-        <v/>
-      </c>
-      <c r="V110" s="54">
-        <f>IF($U110="","⏳ بانتظار هدف",IF($U110&gt;=1.0,"✅ محقق",IF($U110&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W110" s="61">
-        <f>IF($G110="","",$G110)</f>
-        <v/>
-      </c>
-      <c r="X110" s="54">
-        <f>IF($U110="","—",IF($U110&gt;=0.97,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="54" t="n">
-        <v>108</v>
-      </c>
-      <c r="B111" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>دقة تسوية أرامكو</t>
-        </is>
-      </c>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F111" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G111" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="60" t="n"/>
-      <c r="I111" s="60" t="n"/>
-      <c r="J111" s="60" t="n"/>
-      <c r="K111" s="60" t="n"/>
-      <c r="L111" s="60" t="n"/>
-      <c r="M111" s="60" t="n"/>
-      <c r="N111" s="60" t="n"/>
-      <c r="O111" s="60" t="n"/>
-      <c r="P111" s="60" t="n"/>
-      <c r="Q111" s="60" t="n"/>
-      <c r="R111" s="60" t="n"/>
-      <c r="S111" s="60" t="n"/>
-      <c r="T111" s="50">
-        <f>IF(COUNT($H111:$S111)=0,"",SUM($H111:$S111)/COUNT($H111:$S111))</f>
-        <v/>
-      </c>
-      <c r="U111" s="50">
-        <f>IF($G111="","",IF($T111="","",MIN(1,IF($G111=0,IF($T111&lt;=0,1,0),IF($F111="↓",IFERROR($G111/$T111,0),IFERROR($T111/$G111,0))))))</f>
-        <v/>
-      </c>
-      <c r="V111" s="54">
-        <f>IF($U111="","⏳ بانتظار هدف",IF($U111&gt;=1.0,"✅ محقق",IF($U111&gt;=0.97,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W111" s="61">
-        <f>IF($G111="","",$G111)</f>
-        <v/>
-      </c>
-      <c r="X111" s="54">
-        <f>IF($U111="","—",IF($U111&gt;=0.97,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="54" t="n">
-        <v>109</v>
-      </c>
-      <c r="B112" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C112" s="11" t="inlineStr">
-        <is>
-          <t>نسبة تحصيل الامتياز</t>
-        </is>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F112" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G112" s="59" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="H112" s="60" t="n"/>
-      <c r="I112" s="60" t="n"/>
-      <c r="J112" s="60" t="n"/>
-      <c r="K112" s="60" t="n"/>
-      <c r="L112" s="60" t="n"/>
-      <c r="M112" s="60" t="n"/>
-      <c r="N112" s="60" t="n"/>
-      <c r="O112" s="60" t="n"/>
-      <c r="P112" s="60" t="n"/>
-      <c r="Q112" s="60" t="n"/>
-      <c r="R112" s="60" t="n"/>
-      <c r="S112" s="60" t="n"/>
-      <c r="T112" s="50">
-        <f>IF(COUNT($H112:$S112)=0,"",SUM($H112:$S112)/COUNT($H112:$S112))</f>
-        <v/>
-      </c>
-      <c r="U112" s="50">
-        <f>IF($G112="","",IF($T112="","",MIN(1,IF($G112=0,IF($T112&lt;=0,1,0),IF($F112="↓",IFERROR($G112/$T112,0),IFERROR($T112/$G112,0))))))</f>
-        <v/>
-      </c>
-      <c r="V112" s="54">
-        <f>IF($U112="","⏳ بانتظار هدف",IF($U112&gt;=1.0,"✅ محقق",IF($U112&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W112" s="61">
-        <f>IF($G112="","",$G112)</f>
-        <v/>
-      </c>
-      <c r="X112" s="54">
-        <f>IF($U112="","—",IF($U112&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="1">
-      <c r="A113" s="54" t="n">
-        <v>110</v>
-      </c>
-      <c r="B113" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C113" s="11" t="inlineStr">
-        <is>
-          <t>أيام تحصيل رسوم الامتياز</t>
-        </is>
-      </c>
-      <c r="D113" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E113" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F113" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G113" s="62" t="n">
-        <v>15</v>
-      </c>
-      <c r="H113" s="63" t="n"/>
-      <c r="I113" s="63" t="n"/>
-      <c r="J113" s="63" t="n"/>
-      <c r="K113" s="63" t="n"/>
-      <c r="L113" s="63" t="n"/>
-      <c r="M113" s="63" t="n"/>
-      <c r="N113" s="63" t="n"/>
-      <c r="O113" s="63" t="n"/>
-      <c r="P113" s="63" t="n"/>
-      <c r="Q113" s="63" t="n"/>
-      <c r="R113" s="63" t="n"/>
-      <c r="S113" s="63" t="n"/>
-      <c r="T113" s="64">
-        <f>IF(COUNT($H113:$S113)=0,"",SUM($H113:$S113)/COUNT($H113:$S113))</f>
-        <v/>
-      </c>
-      <c r="U113" s="50">
-        <f>IF($G113="","",IF($T113="","",MIN(1,IF($G113=0,IF($T113&lt;=0,1,0),IF($F113="↓",IFERROR($G113/$T113,0),IFERROR($T113/$G113,0))))))</f>
-        <v/>
-      </c>
-      <c r="V113" s="54">
-        <f>IF($U113="","⏳ بانتظار هدف",IF($U113&gt;=1.0,"✅ محقق",IF($U113&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W113" s="65">
-        <f>IF($G113="","",$G113)</f>
-        <v/>
-      </c>
-      <c r="X113" s="54">
-        <f>IF($U113="","—",IF($U113&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="54" t="n">
-        <v>111</v>
-      </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C114" s="11" t="inlineStr">
-        <is>
-          <t>نسبة تحصيل الإيجار</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F114" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G114" s="59" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="H114" s="60" t="n"/>
-      <c r="I114" s="60" t="n"/>
-      <c r="J114" s="60" t="n"/>
-      <c r="K114" s="60" t="n"/>
-      <c r="L114" s="60" t="n"/>
-      <c r="M114" s="60" t="n"/>
-      <c r="N114" s="60" t="n"/>
-      <c r="O114" s="60" t="n"/>
-      <c r="P114" s="60" t="n"/>
-      <c r="Q114" s="60" t="n"/>
-      <c r="R114" s="60" t="n"/>
-      <c r="S114" s="60" t="n"/>
-      <c r="T114" s="50">
-        <f>IF(COUNT($H114:$S114)=0,"",SUM($H114:$S114)/COUNT($H114:$S114))</f>
-        <v/>
-      </c>
-      <c r="U114" s="50">
-        <f>IF($G114="","",IF($T114="","",MIN(1,IF($G114=0,IF($T114&lt;=0,1,0),IF($F114="↓",IFERROR($G114/$T114,0),IFERROR($T114/$G114,0))))))</f>
-        <v/>
-      </c>
-      <c r="V114" s="54">
-        <f>IF($U114="","⏳ بانتظار هدف",IF($U114&gt;=1.0,"✅ محقق",IF($U114&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W114" s="61">
-        <f>IF($G114="","",$G114)</f>
-        <v/>
-      </c>
-      <c r="X114" s="54">
-        <f>IF($U114="","—",IF($U114&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="54" t="n">
-        <v>112</v>
-      </c>
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="inlineStr">
-        <is>
-          <t>معدل تجديد عقود الإيجار</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E115" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F115" s="49" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="G115" s="59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H115" s="60" t="n"/>
-      <c r="I115" s="60" t="n"/>
-      <c r="J115" s="60" t="n"/>
-      <c r="K115" s="60" t="n"/>
-      <c r="L115" s="60" t="n"/>
-      <c r="M115" s="60" t="n"/>
-      <c r="N115" s="60" t="n"/>
-      <c r="O115" s="60" t="n"/>
-      <c r="P115" s="60" t="n"/>
-      <c r="Q115" s="60" t="n"/>
-      <c r="R115" s="60" t="n"/>
-      <c r="S115" s="60" t="n"/>
-      <c r="T115" s="50">
-        <f>IF(COUNT($H115:$S115)=0,"",SUM($H115:$S115)/COUNT($H115:$S115))</f>
-        <v/>
-      </c>
-      <c r="U115" s="50">
-        <f>IF($G115="","",IF($T115="","",MIN(1,IF($G115=0,IF($T115&lt;=0,1,0),IF($F115="↓",IFERROR($G115/$T115,0),IFERROR($T115/$G115,0))))))</f>
-        <v/>
-      </c>
-      <c r="V115" s="54">
-        <f>IF($U115="","⏳ بانتظار هدف",IF($U115&gt;=1.0,"✅ محقق",IF($U115&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W115" s="61">
-        <f>IF($G115="","",$G115)</f>
-        <v/>
-      </c>
-      <c r="X115" s="54">
-        <f>IF($U115="","—",IF($U115&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="54" t="n">
-        <v>113</v>
-      </c>
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C116" s="11" t="inlineStr">
-        <is>
-          <t>انحراف الموازنة</t>
-        </is>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>ربعي</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F116" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G116" s="59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H116" s="60" t="n"/>
-      <c r="I116" s="60" t="n"/>
-      <c r="J116" s="60" t="n"/>
-      <c r="K116" s="60" t="n"/>
-      <c r="L116" s="60" t="n"/>
-      <c r="M116" s="60" t="n"/>
-      <c r="N116" s="60" t="n"/>
-      <c r="O116" s="60" t="n"/>
-      <c r="P116" s="60" t="n"/>
-      <c r="Q116" s="60" t="n"/>
-      <c r="R116" s="60" t="n"/>
-      <c r="S116" s="60" t="n"/>
-      <c r="T116" s="50">
-        <f>IF(COUNT($H116:$S116)=0,"",SUM($H116:$S116)/COUNT($H116:$S116))</f>
-        <v/>
-      </c>
-      <c r="U116" s="50">
-        <f>IF($G116="","",IF($T116="","",MIN(1,IF($G116=0,IF($T116&lt;=0,1,0),IF($F116="↓",IFERROR($G116/$T116,0),IFERROR($T116/$G116,0))))))</f>
-        <v/>
-      </c>
-      <c r="V116" s="54">
-        <f>IF($U116="","⏳ بانتظار هدف",IF($U116&gt;=1.0,"✅ محقق",IF($U116&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W116" s="61">
-        <f>IF($G116="","",$G116)</f>
-        <v/>
-      </c>
-      <c r="X116" s="54">
-        <f>IF($U116="","—",IF($U116&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="54" t="n">
-        <v>114</v>
-      </c>
-      <c r="B117" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr">
-        <is>
-          <t>أيام الإقفال الشهري</t>
-        </is>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>شهري</t>
-        </is>
-      </c>
-      <c r="E117" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F117" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G117" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="H117" s="63" t="n"/>
-      <c r="I117" s="63" t="n"/>
-      <c r="J117" s="63" t="n"/>
-      <c r="K117" s="63" t="n"/>
-      <c r="L117" s="63" t="n"/>
-      <c r="M117" s="63" t="n"/>
-      <c r="N117" s="63" t="n"/>
-      <c r="O117" s="63" t="n"/>
-      <c r="P117" s="63" t="n"/>
-      <c r="Q117" s="63" t="n"/>
-      <c r="R117" s="63" t="n"/>
-      <c r="S117" s="63" t="n"/>
-      <c r="T117" s="64">
-        <f>IF(COUNT($H117:$S117)=0,"",SUM($H117:$S117)/COUNT($H117:$S117))</f>
-        <v/>
-      </c>
-      <c r="U117" s="50">
-        <f>IF($G117="","",IF($T117="","",MIN(1,IF($G117=0,IF($T117&lt;=0,1,0),IF($F117="↓",IFERROR($G117/$T117,0),IFERROR($T117/$G117,0))))))</f>
-        <v/>
-      </c>
-      <c r="V117" s="54">
-        <f>IF($U117="","⏳ بانتظار هدف",IF($U117&gt;=1.0,"✅ محقق",IF($U117&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W117" s="65">
-        <f>IF($G117="","",$G117)</f>
-        <v/>
-      </c>
-      <c r="X117" s="54">
-        <f>IF($U117="","—",IF($U117&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" ht="22" customHeight="1">
-      <c r="A118" s="54" t="n">
-        <v>115</v>
-      </c>
-      <c r="B118" s="13" t="inlineStr">
-        <is>
-          <t>الإدارة المالية</t>
-        </is>
-      </c>
-      <c r="C118" s="11" t="inlineStr">
-        <is>
-          <t>نسبة تسويات التدقيق</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>ربعي</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>معدل</t>
-        </is>
-      </c>
-      <c r="F118" s="49" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="G118" s="59" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H118" s="60" t="n"/>
-      <c r="I118" s="60" t="n"/>
-      <c r="J118" s="60" t="n"/>
-      <c r="K118" s="60" t="n"/>
-      <c r="L118" s="60" t="n"/>
-      <c r="M118" s="60" t="n"/>
-      <c r="N118" s="60" t="n"/>
-      <c r="O118" s="60" t="n"/>
-      <c r="P118" s="60" t="n"/>
-      <c r="Q118" s="60" t="n"/>
-      <c r="R118" s="60" t="n"/>
-      <c r="S118" s="60" t="n"/>
-      <c r="T118" s="50">
-        <f>IF(COUNT($H118:$S118)=0,"",SUM($H118:$S118)/COUNT($H118:$S118))</f>
-        <v/>
-      </c>
-      <c r="U118" s="50">
-        <f>IF($G118="","",IF($T118="","",MIN(1,IF($G118=0,IF($T118&lt;=0,1,0),IF($F118="↓",IFERROR($G118/$T118,0),IFERROR($T118/$G118,0))))))</f>
-        <v/>
-      </c>
-      <c r="V118" s="54">
-        <f>IF($U118="","⏳ بانتظار هدف",IF($U118&gt;=1.0,"✅ محقق",IF($U118&gt;=0.85,"🟡 قريب","🔴 تحت الهدف")))</f>
-        <v/>
-      </c>
-      <c r="W118" s="61">
-        <f>IF($G118="","",$G118)</f>
-        <v/>
-      </c>
-      <c r="X118" s="54">
-        <f>IF($U118="","—",IF($U118&gt;=0.85,"🟢 على المسار","🟠 متأخّر"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:X118"/>
+  <autoFilter ref="A3:X100"/>
   <mergeCells count="2">
     <mergeCell ref="A2:X2"/>
     <mergeCell ref="A1:X1"/>
